--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -27811,6 +27811,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1194" t="n">
+        <v>874595</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>14.0900001525879</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>14.0699996948242</v>
+      </c>
+      <c r="G1194" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -27834,6 +27834,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1195" t="n">
+        <v>756822</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>14.0950002670288</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>14.0649995803833</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -27857,6 +27857,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>1250289</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>14.1199998855591</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>14.1049995422363</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -27880,6 +27880,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>627567</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -27721,22 +27721,22 @@
     </row>
     <row r="1190">
       <c r="A1190" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1190" t="n">
-        <v>1153300</v>
+        <v>1016800</v>
       </c>
       <c r="C1190" t="n">
-        <v>14.0500001907349</v>
+        <v>14.0450000762939</v>
       </c>
       <c r="D1190" t="n">
-        <v>14.0299997329712</v>
+        <v>14.0249996185303</v>
       </c>
       <c r="E1190" t="n">
-        <v>14.0299997329712</v>
+        <v>14.0249996185303</v>
       </c>
       <c r="F1190" t="n">
-        <v>14.0349998474121</v>
+        <v>14.0450000762939</v>
       </c>
       <c r="G1190" t="s">
         <v>7</v>
@@ -27744,22 +27744,22 @@
     </row>
     <row r="1191">
       <c r="A1191" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1191" t="n">
-        <v>857397</v>
+        <v>1153300</v>
       </c>
       <c r="C1191" t="n">
         <v>14.0500001907349</v>
       </c>
       <c r="D1191" t="n">
+        <v>14.0299997329712</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>14.0299997329712</v>
+      </c>
+      <c r="F1191" t="n">
         <v>14.0349998474121</v>
-      </c>
-      <c r="E1191" t="n">
-        <v>14.039999961853</v>
-      </c>
-      <c r="F1191" t="n">
-        <v>14.0500001907349</v>
       </c>
       <c r="G1191" t="s">
         <v>7</v>
@@ -27767,22 +27767,22 @@
     </row>
     <row r="1192">
       <c r="A1192" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1192" t="n">
-        <v>1046978</v>
+        <v>857397</v>
       </c>
       <c r="C1192" t="n">
-        <v>14.0550003051758</v>
+        <v>14.0500001907349</v>
       </c>
       <c r="D1192" t="n">
-        <v>14.039999961853</v>
+        <v>14.0349998474121</v>
       </c>
       <c r="E1192" t="n">
         <v>14.039999961853</v>
       </c>
       <c r="F1192" t="n">
-        <v>14.0550003051758</v>
+        <v>14.0500001907349</v>
       </c>
       <c r="G1192" t="s">
         <v>7</v>
@@ -27790,22 +27790,22 @@
     </row>
     <row r="1193">
       <c r="A1193" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1193" t="n">
-        <v>1150636</v>
+        <v>1046978</v>
       </c>
       <c r="C1193" t="n">
-        <v>14.0699996948242</v>
+        <v>14.0550003051758</v>
       </c>
       <c r="D1193" t="n">
-        <v>14.0450000762939</v>
+        <v>14.039999961853</v>
       </c>
       <c r="E1193" t="n">
-        <v>14.0450000762939</v>
+        <v>14.039999961853</v>
       </c>
       <c r="F1193" t="n">
-        <v>14.0500001907349</v>
+        <v>14.0550003051758</v>
       </c>
       <c r="G1193" t="s">
         <v>7</v>
@@ -27813,22 +27813,22 @@
     </row>
     <row r="1194">
       <c r="A1194" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1194" t="n">
-        <v>874595</v>
+        <v>1150636</v>
       </c>
       <c r="C1194" t="n">
-        <v>14.0900001525879</v>
+        <v>14.0699996948242</v>
       </c>
       <c r="D1194" t="n">
+        <v>14.0450000762939</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>14.0450000762939</v>
+      </c>
+      <c r="F1194" t="n">
         <v>14.0500001907349</v>
-      </c>
-      <c r="E1194" t="n">
-        <v>14.0600004196167</v>
-      </c>
-      <c r="F1194" t="n">
-        <v>14.0699996948242</v>
       </c>
       <c r="G1194" t="s">
         <v>7</v>
@@ -27836,22 +27836,22 @@
     </row>
     <row r="1195">
       <c r="A1195" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1195" t="n">
-        <v>756822</v>
+        <v>874595</v>
       </c>
       <c r="C1195" t="n">
-        <v>14.0950002670288</v>
+        <v>14.0900001525879</v>
       </c>
       <c r="D1195" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E1195" t="n">
         <v>14.0600004196167</v>
       </c>
-      <c r="E1195" t="n">
-        <v>14.0649995803833</v>
-      </c>
       <c r="F1195" t="n">
-        <v>14.0799999237061</v>
+        <v>14.0699996948242</v>
       </c>
       <c r="G1195" t="s">
         <v>7</v>
@@ -27859,22 +27859,22 @@
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1196" t="n">
-        <v>1250289</v>
+        <v>756822</v>
       </c>
       <c r="C1196" t="n">
-        <v>14.1199998855591</v>
+        <v>14.0950002670288</v>
       </c>
       <c r="D1196" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>14.0649995803833</v>
+      </c>
+      <c r="F1196" t="n">
         <v>14.0799999237061</v>
-      </c>
-      <c r="E1196" t="n">
-        <v>14.0799999237061</v>
-      </c>
-      <c r="F1196" t="n">
-        <v>14.1049995422363</v>
       </c>
       <c r="G1196" t="s">
         <v>7</v>
@@ -27882,13 +27882,13 @@
     </row>
     <row r="1197">
       <c r="A1197" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1197" t="n">
-        <v>627567</v>
+        <v>1250289</v>
       </c>
       <c r="C1197" t="n">
-        <v>14.125</v>
+        <v>14.1199998855591</v>
       </c>
       <c r="D1197" t="n">
         <v>14.0799999237061</v>
@@ -27897,9 +27897,32 @@
         <v>14.0799999237061</v>
       </c>
       <c r="F1197" t="n">
+        <v>14.1049995422363</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>870703</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>14.1149997711182</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>14.1099996566772</v>
+      </c>
+      <c r="F1198" t="n">
         <v>14.1000003814697</v>
       </c>
-      <c r="G1197" t="s">
+      <c r="G1198" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418298721313</v>
+        <v>6.82418346405029</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024492263794</v>
+        <v>7.68024444580078</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634632110596</v>
+        <v>7.15634679794312</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.85929012298584</v>
+        <v>6.859290599823</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253858566284</v>
+        <v>6.85253810882568</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411249160767</v>
+        <v>7.24411201477051</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040723800659</v>
+        <v>7.48040676116943</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385835647583</v>
+        <v>7.22385883331299</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132034301758</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132034301758</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731042861938</v>
+        <v>6.96731090545654</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956884384155</v>
+        <v>6.34956932067871</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.39345264434814</v>
+        <v>6.3934531211853</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08626985549927</v>
+        <v>6.08627033233643</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238605499268</v>
+        <v>6.04238653182983</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284284591675</v>
+        <v>5.81284332275391</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637145996094</v>
+        <v>5.29637098312378</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548246383667</v>
+        <v>5.22548294067383</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850280761719</v>
+        <v>4.66850328445435</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692985534668</v>
+        <v>4.27692937850952</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187833786011</v>
+        <v>4.67187881469727</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347730636597</v>
+        <v>4.53347778320312</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.40520334243774</v>
+        <v>4.4052038192749</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.4119553565979</v>
+        <v>4.41195487976074</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967004776001</v>
+        <v>4.22967052459717</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667572021484</v>
+        <v>4.25667524337769</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.6875433921814</v>
+        <v>3.68754315376282</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0851936340332</v>
+        <v>4.08519315719604</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822368621826</v>
+        <v>3.84822344779968</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286336898804</v>
+        <v>3.79286313056946</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311702728271</v>
+        <v>3.81311678886414</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045751571655</v>
+        <v>3.76045727729797</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437608718872</v>
+        <v>3.5943763256073</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496503829956</v>
+        <v>3.53496527671814</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240172386169</v>
+        <v>3.86240196228027</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446766853333</v>
+        <v>3.81446743011475</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802055358887</v>
+        <v>4.09802103042603</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.00012731552124</v>
+        <v>4.0001277923584</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594927787781</v>
+        <v>3.98594951629639</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761993408203</v>
+        <v>3.42761969566345</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302568435669</v>
+        <v>3.59302592277527</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944169044495</v>
+        <v>3.67944192886353</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952332496643</v>
+        <v>3.57952356338501</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682251930237</v>
+        <v>3.57682275772095</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082757949829</v>
+        <v>3.47082781791687</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.20989108085632</v>
+        <v>3.2098913192749</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724430084229</v>
+        <v>3.55724406242371</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326684951782</v>
+        <v>3.21326661109924</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948274612427</v>
+        <v>3.62948298454285</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488340377808</v>
+        <v>3.63488364219666</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813234329224</v>
+        <v>3.62813258171082</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.5322642326355</v>
+        <v>3.53226447105408</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319842338562</v>
+        <v>3.71319818496704</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894479751587</v>
+        <v>3.95894455909729</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290951728821</v>
+        <v>3.90290927886963</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139656066895</v>
+        <v>4.10139608383179</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126901626587</v>
+        <v>4.09126949310303</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067521095276</v>
+        <v>3.99067544937134</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539095878601</v>
+        <v>3.67539119720459</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648261070251</v>
+        <v>3.49648237228394</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846254348755</v>
+        <v>3.38846230506897</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.4168176651001</v>
+        <v>3.41681742668152</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086839675903</v>
+        <v>3.42086815834045</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086839675903</v>
+        <v>3.42086815834045</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837350845337</v>
+        <v>3.24837327003479</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116032600403</v>
+        <v>3.31116056442261</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786826133728</v>
+        <v>3.28786849975586</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340131759644</v>
+        <v>3.46340155601501</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51065993309021</v>
+        <v>3.51066017150879</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842681884766</v>
+        <v>3.59842705726624</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.6240816116333</v>
+        <v>3.62408185005188</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678217887878</v>
+        <v>3.62678241729736</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577192306519</v>
+        <v>3.70577216148376</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.72400045394897</v>
+        <v>3.7240002155304</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079257011414</v>
+        <v>3.68079233169556</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450824737549</v>
+        <v>3.76450800895691</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527988433838</v>
+        <v>4.14527940750122</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916320800781</v>
+        <v>4.18916273117065</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620826721191</v>
+        <v>4.16620874404907</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106174468994</v>
+        <v>4.18106126785278</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629499435425</v>
+        <v>4.22629547119141</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840732574463</v>
+        <v>4.28840684890747</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562440872192</v>
+        <v>4.38562488555908</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781280517578</v>
+        <v>4.18781232833862</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633581161499</v>
+        <v>4.17633533477783</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.0264573097229</v>
+        <v>4.02645778656006</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033020973206</v>
+        <v>3.75033044815063</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771613121033</v>
+        <v>3.80771589279175</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73682808876038</v>
+        <v>3.7368278503418</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948760032654</v>
+        <v>3.78948783874512</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478179931641</v>
+        <v>4.42478227615356</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605613708496</v>
+        <v>4.68605661392212</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.65972661972046</v>
+        <v>4.6597261428833</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.7353401184082</v>
+        <v>4.73534059524536</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543703079224</v>
+        <v>5.11543750762939</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.03172159194946</v>
+        <v>5.0317211151123</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855890274048</v>
+        <v>5.09855937957764</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902635574341</v>
+        <v>5.18902587890625</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370073318481</v>
+        <v>6.25370025634766</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707626342773</v>
+        <v>6.25707674026489</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926513671875</v>
+        <v>6.05926561355591</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293466567993</v>
+        <v>6.03293418884277</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.19361448287964</v>
+        <v>6.1936149597168</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441213607788</v>
+        <v>6.04441165924072</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836595535278</v>
+        <v>5.66836643218994</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.8661789894104</v>
+        <v>5.86617851257324</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977245330811</v>
+        <v>6.09977293014526</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390434265137</v>
+        <v>6.00390386581421</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748857498169</v>
+        <v>5.91748809814453</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047828674316</v>
+        <v>5.73047733306885</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.30649852752686</v>
+        <v>5.3064980506897</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920904159546</v>
+        <v>5.62920951843262</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672155380249</v>
+        <v>5.69672107696533</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.37536096572876</v>
+        <v>5.3753604888916</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751363754272</v>
+        <v>5.38751316070557</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003128051758</v>
+        <v>4.95003080368042</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809192657471</v>
+        <v>5.00809240341187</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.82175731658936</v>
+        <v>4.8217568397522</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76774644851685</v>
+        <v>4.767746925354</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568559646606</v>
+        <v>4.97568607330322</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26463985443115</v>
+        <v>5.26464033126831</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236616134644</v>
+        <v>5.40236568450928</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080291748047</v>
+        <v>5.33080244064331</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379724502563</v>
+        <v>5.30379772186279</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114839553833</v>
+        <v>5.57114791870117</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578712463379</v>
+        <v>5.51578760147095</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148321151733</v>
+        <v>5.49148273468018</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907735824585</v>
+        <v>5.45907688140869</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.4172191619873</v>
+        <v>5.41721868515015</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562480926514</v>
+        <v>5.71562528610229</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376756668091</v>
+        <v>5.67376804351807</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768613815308</v>
+        <v>5.50768566131592</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460969924927</v>
+        <v>5.63460922241211</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951322555542</v>
+        <v>5.91951274871826</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873180389404</v>
+        <v>6.54873132705688</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044765472412</v>
+        <v>6.10044717788696</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436574935913</v>
+        <v>5.93436622619629</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.82634592056274</v>
+        <v>5.8263463973999</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457906723022</v>
+        <v>6.00457954406738</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631576538086</v>
+        <v>6.19631624221802</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16930961608887</v>
+        <v>6.16931009292603</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002101898193</v>
+        <v>5.96002054214478</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479238510132</v>
+        <v>6.07479286193848</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289384841919</v>
+        <v>6.08289432525635</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770650863647</v>
+        <v>6.14770698547363</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613260269165</v>
+        <v>5.75613307952881</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301630020142</v>
+        <v>5.93301582336426</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748252868652</v>
+        <v>5.75748205184937</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700584411621</v>
+        <v>5.34700536727905</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806177139282</v>
+        <v>5.37806129455566</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36996030807495</v>
+        <v>5.36995983123779</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8285083770752</v>
+        <v>4.82850790023804</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669052124023</v>
+        <v>4.73669099807739</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525991439819</v>
+        <v>4.83525943756104</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893453598022</v>
+        <v>4.96893501281738</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.1417670249939</v>
+        <v>5.14176750183105</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004146575928</v>
+        <v>5.27004194259644</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.3132495880127</v>
+        <v>5.31324911117554</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847726821899</v>
+        <v>5.19847774505615</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26463985443115</v>
+        <v>5.26464033126831</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565591812134</v>
+        <v>5.34565544128418</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076162338257</v>
+        <v>5.38076210021973</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958467483521</v>
+        <v>5.49958419799805</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791982650757</v>
+        <v>6.21792030334473</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.3772497177124</v>
+        <v>6.37725019454956</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492454528809</v>
+        <v>6.24492502212524</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.42450761795044</v>
+        <v>6.4245080947876</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527002334595</v>
+        <v>6.48527050018311</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.58248853683472</v>
+        <v>6.5824875831604</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459991455078</v>
+        <v>6.64459943771362</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751356124878</v>
+        <v>6.71751308441162</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839698791504</v>
+        <v>6.62839651107788</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080331802368</v>
+        <v>6.66080284118652</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320869445801</v>
+        <v>6.69320821762085</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284324645996</v>
+        <v>7.14284372329712</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525514602661</v>
+        <v>7.33525466918945</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989992141724</v>
+        <v>7.43989944458008</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403642654419</v>
+        <v>7.50403690338135</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47028017044067</v>
+        <v>7.47027969360352</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.83147382736206</v>
+        <v>7.8314733505249</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.8483510017395</v>
+        <v>7.84835147857666</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885879516602</v>
+        <v>7.88885927200317</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228485107422</v>
+        <v>8.16228580474854</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053470611572</v>
+        <v>8.82053375244141</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.3235034942627</v>
+        <v>9.32350444793701</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375667572021</v>
+        <v>9.34375762939453</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114307403564</v>
+        <v>9.40114402770996</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253890991211</v>
+        <v>9.51253986358643</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840240478516</v>
+        <v>9.44840145111084</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540760040283</v>
+        <v>9.47540664672852</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297023773193</v>
+        <v>8.48297119140625</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.9527735710144</v>
+        <v>7.95277309417725</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893676757812</v>
+        <v>8.37893772125244</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.1143045425415</v>
+        <v>8.11430358886719</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465784072876</v>
+        <v>7.90465831756592</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809535980225</v>
+        <v>7.90809488296509</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558931350708</v>
+        <v>7.93558979034424</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776195526123</v>
+        <v>8.00776290893555</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.95964765548706</v>
+        <v>7.9596471786499</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.72938108444214</v>
+        <v>7.7293815612793</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621013641357</v>
+        <v>7.95621061325073</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627696990967</v>
+        <v>7.62627744674683</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379367828369</v>
+        <v>7.54379415512085</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250699996948</v>
+        <v>7.72250747680664</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434766769409</v>
+        <v>7.89434814453125</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445858001709</v>
+        <v>7.34445905685425</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758544921875</v>
+        <v>7.33758497238159</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632104873657</v>
+        <v>7.40632057189941</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259611129761</v>
+        <v>7.28259658813477</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.31009101867676</v>
+        <v>7.3100905418396</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982444763184</v>
+        <v>7.07982492446899</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949199676514</v>
+        <v>7.17949151992798</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470287322998</v>
+        <v>7.68470335006714</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.86685371398926</v>
+        <v>7.8668532371521</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.9149694442749</v>
+        <v>7.91496896743774</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122127532959</v>
+        <v>7.90122175216675</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656534194946</v>
+        <v>7.74656581878662</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485786437988</v>
+        <v>6.91485834121704</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946941375732</v>
+        <v>6.35946989059448</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980192184448</v>
+        <v>5.94980239868164</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108764648438</v>
+        <v>5.77108812332153</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255088806152</v>
+        <v>5.95255136489868</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017934799194</v>
+        <v>5.94017887115479</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638805389404</v>
+        <v>6.14638757705688</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199678421021</v>
+        <v>6.22199726104736</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634302139282</v>
+        <v>6.36634349822998</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38009023666382</v>
+        <v>6.38008975982666</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188646316528</v>
+        <v>6.15188598632812</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392608642578</v>
+        <v>5.95392560958862</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28111028671265</v>
+        <v>6.28110980987549</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.30310583114624</v>
+        <v>6.3031063079834</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.49831676483154</v>
+        <v>6.4983172416687</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286195755005</v>
+        <v>6.27286243438721</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536800384521</v>
+        <v>6.24536752700806</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170883178711</v>
+        <v>6.41170930862427</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938089370728</v>
+        <v>6.17938041687012</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441431045532</v>
+        <v>6.01441383361816</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962524414062</v>
+        <v>6.20962476730347</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698612213135</v>
+        <v>6.27698659896851</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450283050537</v>
+        <v>6.19450330734253</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754058837891</v>
+        <v>6.62754011154175</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204170227051</v>
+        <v>6.62204122543335</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.89767360687256</v>
+        <v>6.8976731300354</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088857650757</v>
+        <v>6.76088905334473</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705236434937</v>
+        <v>6.56705284118652</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.01108837127686</v>
+        <v>7.0110878944397</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013515472412</v>
+        <v>6.78013467788696</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729623794556</v>
+        <v>6.59729671478271</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.6467866897583</v>
+        <v>6.64678716659546</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000207901001</v>
+        <v>6.82000160217285</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401544570923</v>
+        <v>6.75401496887207</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.8419976234436</v>
+        <v>6.84199810028076</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093265533447</v>
+        <v>6.54093313217163</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166463851929</v>
+        <v>7.25166511535645</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818351745605</v>
+        <v>7.46818399429321</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933605194092</v>
+        <v>7.94933652877808</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.82904863357544</v>
+        <v>7.8290491104126</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683095932007</v>
+        <v>7.97683143615723</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210674285889</v>
+        <v>10.2210664749146</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341487884521</v>
+        <v>10.4341497421265</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500032424927</v>
+        <v>10.8500022888184</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249475479126</v>
+        <v>11.1249465942383</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953458786011</v>
+        <v>10.6953468322754</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485609054565</v>
+        <v>10.2485618591309</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352586746216</v>
+        <v>11.1352577209473</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029973983765</v>
+        <v>11.5029964447021</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208446502686</v>
+        <v>11.3208456039429</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376964569092</v>
+        <v>11.4376955032349</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414669036865</v>
+        <v>11.3414659500122</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585395812988</v>
+        <v>10.3585386276245</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069868087769</v>
+        <v>10.3069877624512</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634304046631</v>
+        <v>8.84634399414062</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472534179688</v>
+        <v>9.12472438812256</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940307617188</v>
+        <v>9.16940402984619</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -31572,6 +31572,32 @@
         <v>14.1099996566772</v>
       </c>
       <c r="H1200" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>638531</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>14.1099996566772</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>14.1099996566772</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>14.1099996566772</v>
+      </c>
+      <c r="H1201" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -499,7 +499,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634679794312</v>
+        <v>7.15634632110596</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705629348755</v>
+        <v>6.94705677032471</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.859290599823</v>
+        <v>6.85929012298584</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253810882568</v>
+        <v>6.85253858566284</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385883331299</v>
+        <v>7.22385835647583</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010162353516</v>
+        <v>7.19010210037231</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02132081985474</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>7.05507659912109</v>
+        <v>7.05507707595825</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02132081985474</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731090545654</v>
+        <v>6.96730995178223</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47109270095825</v>
+        <v>6.47109222412109</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.625</v>
       </c>
       <c r="G19" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.625</v>
       </c>
       <c r="G20" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956932067871</v>
+        <v>6.34956884384155</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3934531211853</v>
+        <v>6.39345264434814</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>6.43058395385742</v>
+        <v>6.43058443069458</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.75</v>
       </c>
       <c r="G27" t="n">
-        <v>5.90736103057861</v>
+        <v>5.90736150741577</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>5.43477249145508</v>
+        <v>5.43477201461792</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G42" t="n">
-        <v>5.0263204574585</v>
+        <v>5.02631998062134</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850328445435</v>
+        <v>4.66850280761719</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G44" t="n">
-        <v>4.72926473617554</v>
+        <v>4.72926425933838</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>6.875</v>
       </c>
       <c r="G45" t="n">
-        <v>4.64149808883667</v>
+        <v>4.64149761199951</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533088684082</v>
+        <v>4.41533041000366</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44233560562134</v>
+        <v>4.44233512878418</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195487976074</v>
+        <v>4.41195440292358</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4355845451355</v>
+        <v>4.43558406829834</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.94299983978271</v>
       </c>
       <c r="G67" t="n">
-        <v>4.01227998733521</v>
+        <v>4.01227951049805</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.84484839439392</v>
+        <v>3.84484815597534</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754315376282</v>
+        <v>3.68754363059998</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.47300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>3.69497013092041</v>
+        <v>3.69496989250183</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>3.92248749732971</v>
+        <v>3.92248773574829</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>3.85497498512268</v>
+        <v>3.85497522354126</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G75" t="n">
-        <v>4.02240657806396</v>
+        <v>4.02240705490112</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>6.12099981307983</v>
       </c>
       <c r="G77" t="n">
-        <v>4.1324520111084</v>
+        <v>4.13245153427124</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98122382164001</v>
+        <v>3.98122406005859</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822344779968</v>
+        <v>3.84822392463684</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995505332947</v>
+        <v>3.87995529174805</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286313056946</v>
+        <v>3.79286360740662</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045727729797</v>
+        <v>3.76045751571655</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5943763256073</v>
+        <v>3.59437584877014</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496527671814</v>
+        <v>3.53496479988098</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.41900014877319</v>
       </c>
       <c r="G92" t="n">
-        <v>3.65851330757141</v>
+        <v>3.65851306915283</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.39699983596802</v>
       </c>
       <c r="G93" t="n">
-        <v>3.64366030693054</v>
+        <v>3.64366006851196</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395963668823</v>
+        <v>3.77395987510681</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240196228027</v>
+        <v>3.86240148544312</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G98" t="n">
-        <v>3.80231523513794</v>
+        <v>3.80231499671936</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.023756980896</v>
+        <v>4.02375650405884</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0001277923584</v>
+        <v>4.00012731552124</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G107" t="n">
-        <v>4.01430511474609</v>
+        <v>4.01430559158325</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354827880859</v>
+        <v>4.11354875564575</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12029981613159</v>
+        <v>4.12030029296875</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.28900003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24587345123291</v>
+        <v>4.24587392807007</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.10699987411499</v>
       </c>
       <c r="G123" t="n">
-        <v>3.44787335395813</v>
+        <v>3.44787359237671</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091430664062</v>
+        <v>3.53091406822205</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952356338501</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082781791687</v>
+        <v>3.47082757949829</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.74849987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20584058761597</v>
+        <v>3.20584034919739</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326661109924</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.11299991607666</v>
       </c>
       <c r="G140" t="n">
-        <v>3.45192408561707</v>
+        <v>3.45192432403564</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948298454285</v>
+        <v>3.62948274612427</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488364219666</v>
+        <v>3.63488340377808</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>3.64568591117859</v>
+        <v>3.64568567276001</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226447105408</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319818496704</v>
+        <v>3.71319842338562</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>3.89143180847168</v>
+        <v>3.89143204689026</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290927886963</v>
+        <v>3.90290904045105</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387847900391</v>
+        <v>3.87387895584106</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139608383179</v>
+        <v>4.10139656066895</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96772122383118</v>
+        <v>3.9677209854126</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067544937134</v>
+        <v>3.99067568778992</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.75</v>
       </c>
       <c r="G163" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370573997498</v>
+        <v>3.75370621681213</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539143562317</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648237228394</v>
+        <v>3.49648261070251</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.05600023269653</v>
       </c>
       <c r="G171" t="n">
-        <v>3.41344237327576</v>
+        <v>3.41344213485718</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.94549989700317</v>
       </c>
       <c r="G172" t="n">
-        <v>3.33884024620056</v>
+        <v>3.33884048461914</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846230506897</v>
+        <v>3.38846254348755</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681742668152</v>
+        <v>3.4168176651001</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.98750019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.36719608306885</v>
+        <v>3.36719584465027</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437075614929</v>
+        <v>3.43437099456787</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>3.3405282497406</v>
+        <v>3.34052848815918</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837327003479</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116056442261</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>3.3405282497406</v>
+        <v>3.34052848815918</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.14699983596802</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47487854957581</v>
+        <v>3.47487831115723</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>3.48027968406677</v>
+        <v>3.48027992248535</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G201" t="n">
-        <v>3.39858937263489</v>
+        <v>3.39858913421631</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51066017150879</v>
+        <v>3.51066040992737</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842705726624</v>
+        <v>3.59842681884766</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.62408185005188</v>
+        <v>3.6240816116333</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577216148376</v>
+        <v>3.70577192306519</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450800895691</v>
+        <v>3.76450824737549</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>4.20266532897949</v>
+        <v>4.20266580581665</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>6.08300018310547</v>
       </c>
       <c r="G227" t="n">
-        <v>4.10679769515991</v>
+        <v>4.10679721832275</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>6.16200017929077</v>
       </c>
       <c r="G230" t="n">
-        <v>4.16013288497925</v>
+        <v>4.16013240814209</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840637207031</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G236" t="n">
-        <v>4.33566570281982</v>
+        <v>4.33566522598267</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781232833862</v>
+        <v>4.18781280517578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633533477783</v>
+        <v>4.17633581161499</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G246" t="n">
-        <v>4.14257907867432</v>
+        <v>4.14257955551147</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033044815063</v>
+        <v>3.75033020973206</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459449768066</v>
+        <v>3.82459425926208</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771589279175</v>
+        <v>3.80771636962891</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948783874512</v>
+        <v>3.78948760032654</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.87522864341736</v>
+        <v>3.87522888183594</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.79899978637695</v>
       </c>
       <c r="G259" t="n">
-        <v>3.91506147384644</v>
+        <v>3.91506123542786</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604133605957</v>
+        <v>4.20604085922241</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.6597261428833</v>
+        <v>4.65972661972046</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>4.90817308425903</v>
+        <v>4.90817356109619</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>5.11408662796021</v>
+        <v>5.11408710479736</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0317211151123</v>
+        <v>5.03172159194946</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G279" t="n">
-        <v>5.06750345230103</v>
+        <v>5.06750297546387</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855937957764</v>
+        <v>5.09855890274048</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G288" t="n">
-        <v>6.40560483932495</v>
+        <v>6.40560436248779</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370025634766</v>
+        <v>6.25370073318481</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>6.30231046676636</v>
+        <v>6.3023099899292</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G293" t="n">
-        <v>6.09909725189209</v>
+        <v>6.09909772872925</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449281692505</v>
+        <v>5.94449329376221</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G296" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>8.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.90736103057861</v>
+        <v>5.90736150741577</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926561355591</v>
+        <v>6.05926513671875</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293418884277</v>
+        <v>6.03293466567993</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G300" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.11100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>6.15108156204224</v>
+        <v>6.15108203887939</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.8769998550415</v>
       </c>
       <c r="G311" t="n">
-        <v>5.99310255050659</v>
+        <v>5.99310207366943</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977293014526</v>
+        <v>6.09977197647095</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.56700038909912</v>
       </c>
       <c r="G317" t="n">
-        <v>5.7838134765625</v>
+        <v>5.78381299972534</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.85299968719482</v>
       </c>
       <c r="G318" t="n">
-        <v>5.97689914703369</v>
+        <v>5.97689867019653</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390386581421</v>
+        <v>6.00390434265137</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G322" t="n">
-        <v>5.89048337936401</v>
+        <v>5.89048290252686</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047780990601</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G328" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G331" t="n">
-        <v>5.5630464553833</v>
+        <v>5.56304597854614</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920951843262</v>
+        <v>5.62920904159546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.29599952697754</v>
       </c>
       <c r="G333" t="n">
-        <v>5.60085296630859</v>
+        <v>5.60085344314575</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.20600032806396</v>
       </c>
       <c r="G339" t="n">
-        <v>5.54009199142456</v>
+        <v>5.54009246826172</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G340" t="n">
-        <v>5.50228452682495</v>
+        <v>5.50228500366211</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3753604888916</v>
+        <v>5.37536096572876</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.63199996948242</v>
       </c>
       <c r="G354" t="n">
-        <v>5.15256929397583</v>
+        <v>5.15256881713867</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>5.09720897674561</v>
+        <v>5.09720849990845</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910751342773</v>
+        <v>5.08910703659058</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.8217568397522</v>
+        <v>4.82175731658936</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.23600006103516</v>
       </c>
       <c r="G360" t="n">
-        <v>4.88521909713745</v>
+        <v>4.88521862030029</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71643733978271</v>
+        <v>4.71643686294556</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.767746925354</v>
+        <v>4.76774644851685</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543193817139</v>
+        <v>4.95543241500854</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G370" t="n">
-        <v>5.04049825668335</v>
+        <v>5.04049873352051</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.93200016021729</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35510730743408</v>
+        <v>5.35510778427124</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236568450928</v>
+        <v>5.40236616134644</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.95800018310547</v>
       </c>
       <c r="G383" t="n">
-        <v>5.37266063690186</v>
+        <v>5.37266111373901</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907688140869</v>
+        <v>5.45907735824585</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.41721868515015</v>
+        <v>5.4172191619873</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562528610229</v>
+        <v>5.71562480926514</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376804351807</v>
+        <v>5.67376756668091</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>5.72912740707397</v>
+        <v>5.72912788391113</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.56034564971924</v>
+        <v>5.5603461265564</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>8.20600032806396</v>
       </c>
       <c r="G400" t="n">
-        <v>5.54009199142456</v>
+        <v>5.54009246826172</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460922241211</v>
+        <v>5.63461017608643</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.53400039672852</v>
       </c>
       <c r="G407" t="n">
-        <v>6.43666076660156</v>
+        <v>6.43666124343872</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665058135986</v>
+        <v>6.11665105819702</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044717788696</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.97487449645996</v>
+        <v>5.9748740196228</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436622619629</v>
+        <v>5.93436670303345</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.63199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>5.82769584655762</v>
+        <v>5.82769632339478</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.8263463973999</v>
+        <v>5.82634592056274</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97757434844971</v>
+        <v>5.97757482528687</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631624221802</v>
+        <v>6.1963152885437</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16931056976318</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05453872680664</v>
+        <v>6.05453968048096</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002054214478</v>
+        <v>5.96002149581909</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G438" t="n">
-        <v>6.0639910697937</v>
+        <v>6.06399059295654</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G440" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G442" t="n">
-        <v>6.12610292434692</v>
+        <v>6.12610244750977</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G443" t="n">
-        <v>6.15040683746338</v>
+        <v>6.15040636062622</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G444" t="n">
-        <v>6.20711755752563</v>
+        <v>6.20711803436279</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770698547363</v>
+        <v>6.14770650863647</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G448" t="n">
-        <v>5.98297595977783</v>
+        <v>5.98297548294067</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.85599994659424</v>
       </c>
       <c r="G449" t="n">
-        <v>5.97892475128174</v>
+        <v>5.97892427444458</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.9303150177002</v>
+        <v>5.93031597137451</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G455" t="n">
-        <v>5.94246768951416</v>
+        <v>5.94246816635132</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.05453872680664</v>
+        <v>6.05453968048096</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G459" t="n">
-        <v>5.93841600418091</v>
+        <v>5.93841648101807</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984804153442</v>
+        <v>5.83984851837158</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748205184937</v>
+        <v>5.75748300552368</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401056289673</v>
+        <v>5.37401103973389</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29434585571289</v>
+        <v>5.29434537887573</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.83400011062622</v>
       </c>
       <c r="G465" t="n">
-        <v>5.28894472122192</v>
+        <v>5.28894519805908</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409219741821</v>
+        <v>5.27409172058105</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700536727905</v>
+        <v>5.34700584411621</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806129455566</v>
+        <v>5.37806177139282</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36995983123779</v>
+        <v>5.36996030807495</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>4.82715797424316</v>
+        <v>4.82715749740601</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.82850790023804</v>
+        <v>4.8285083770752</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>6.9980001449585</v>
       </c>
       <c r="G474" t="n">
-        <v>4.72453880310059</v>
+        <v>4.72453832626343</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.16599988937378</v>
       </c>
       <c r="G476" t="n">
-        <v>4.8379602432251</v>
+        <v>4.83795976638794</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.8501124382019</v>
+        <v>4.85011196136475</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893501281738</v>
+        <v>4.96893453598022</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.92302560806274</v>
+        <v>4.9230260848999</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.86091423034668</v>
+        <v>4.86091470718384</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.57600021362305</v>
       </c>
       <c r="G494" t="n">
-        <v>5.11476230621338</v>
+        <v>5.11476182937622</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004194259644</v>
+        <v>5.27004146575928</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.31324911117554</v>
+        <v>5.3132495880127</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.43477249145508</v>
+        <v>5.43477201461792</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G512" t="n">
-        <v>5.46852874755859</v>
+        <v>5.46852922439575</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G513" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G514" t="n">
-        <v>5.52928972244263</v>
+        <v>5.52928924560547</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>8.69799995422363</v>
       </c>
       <c r="G518" t="n">
-        <v>5.87225484848022</v>
+        <v>5.87225437164307</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21792030334473</v>
+        <v>6.21791934967041</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37725019454956</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.37454986572266</v>
+        <v>6.3745493888855</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492502212524</v>
+        <v>6.24492454528809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527050018311</v>
+        <v>6.48527002334595</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5824875831604</v>
+        <v>6.58248805999756</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459943771362</v>
+        <v>6.64459991455078</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G533" t="n">
-        <v>6.69185829162598</v>
+        <v>6.69185876846313</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751308441162</v>
+        <v>6.71751356124878</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G539" t="n">
-        <v>6.62974739074707</v>
+        <v>6.62974691390991</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>7.29137182235718</v>
+        <v>7.29137134552002</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403690338135</v>
+        <v>7.50403642654419</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G545" t="n">
-        <v>7.55129528045654</v>
+        <v>7.5512957572937</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.450026512146</v>
+        <v>7.45002603530884</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147287368774</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835147857666</v>
+        <v>7.84835195541382</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885927200317</v>
+        <v>7.88885879516602</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G554" t="n">
-        <v>7.68294525146484</v>
+        <v>7.682945728302</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228580474854</v>
+        <v>8.16228485107422</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>11.9549999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>8.07114315032959</v>
+        <v>8.07114219665527</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G561" t="n">
-        <v>8.36819934844971</v>
+        <v>8.36820030212402</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G567" t="n">
-        <v>9.09396076202393</v>
+        <v>9.09395980834961</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>9.21210861206055</v>
+        <v>9.21210765838623</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114402770996</v>
+        <v>9.40114307403564</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>9.31675243377686</v>
+        <v>9.31675338745117</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G577" t="n">
-        <v>9.45852947235107</v>
+        <v>9.45852851867676</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>13.5649995803833</v>
       </c>
       <c r="G580" t="n">
-        <v>9.15809726715088</v>
+        <v>9.1580982208252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243690490723</v>
+        <v>8.97243785858154</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G583" t="n">
-        <v>8.5471076965332</v>
+        <v>8.54710674285889</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297119140625</v>
+        <v>8.48297023773193</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G586" t="n">
-        <v>8.47621917724609</v>
+        <v>8.47622013092041</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G588" t="n">
-        <v>8.34456920623779</v>
+        <v>8.34457015991211</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -31598,6 +31598,32 @@
         <v>14.1099996566772</v>
       </c>
       <c r="H1201" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>610426</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>14.1199998855591</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>14.0950002670288</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>14.1049995422363</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="H1202" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -31627,6 +31627,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>648464</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>14.1149997711182</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>14.0900001525879</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>14.0900001525879</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>14.0900001525879</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -31653,6 +31653,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>565857</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>14.1149997711182</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>14.0799999237061</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>14.1049995422363</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>14.1049995422363</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418346405029</v>
+        <v>6.82418298721313</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024444580078</v>
+        <v>7.68024492263794</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634679794312</v>
+        <v>7.15634632110596</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.859290599823</v>
+        <v>6.85929012298584</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253810882568</v>
+        <v>6.85253858566284</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411201477051</v>
+        <v>7.24411249160767</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385883331299</v>
+        <v>7.22385835647583</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731090545654</v>
+        <v>6.96731042861938</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956932067871</v>
+        <v>6.34956884384155</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3934531211853</v>
+        <v>6.39345264434814</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08627033233643</v>
+        <v>6.08626985549927</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238653182983</v>
+        <v>6.04238605499268</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284332275391</v>
+        <v>5.81284284591675</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637098312378</v>
+        <v>5.29637145996094</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548294067383</v>
+        <v>5.22548246383667</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850328445435</v>
+        <v>4.66850280761719</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692937850952</v>
+        <v>4.27692985534668</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187881469727</v>
+        <v>4.67187833786011</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347778320312</v>
+        <v>4.53347730636597</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.4052038192749</v>
+        <v>4.40520334243774</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195487976074</v>
+        <v>4.4119553565979</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967052459717</v>
+        <v>4.22967004776001</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667524337769</v>
+        <v>4.25667572021484</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754315376282</v>
+        <v>3.6875433921814</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822344779968</v>
+        <v>3.84822368621826</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286313056946</v>
+        <v>3.79286336898804</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045727729797</v>
+        <v>3.76045751571655</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5943763256073</v>
+        <v>3.59437608718872</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496527671814</v>
+        <v>3.53496503829956</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240196228027</v>
+        <v>3.86240172386169</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446743011475</v>
+        <v>3.81446766853333</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802103042603</v>
+        <v>4.09802055358887</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0001277923584</v>
+        <v>4.00012731552124</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594951629639</v>
+        <v>3.98594927787781</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761969566345</v>
+        <v>3.42761993408203</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302592277527</v>
+        <v>3.59302568435669</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944192886353</v>
+        <v>3.67944169044495</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952356338501</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682275772095</v>
+        <v>3.57682251930237</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082781791687</v>
+        <v>3.47082757949829</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724406242371</v>
+        <v>3.55724430084229</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326661109924</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948298454285</v>
+        <v>3.62948274612427</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488364219666</v>
+        <v>3.63488340377808</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813258171082</v>
+        <v>3.62813234329224</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226447105408</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319818496704</v>
+        <v>3.71319842338562</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894455909729</v>
+        <v>3.95894479751587</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290927886963</v>
+        <v>3.90290951728821</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139608383179</v>
+        <v>4.10139656066895</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126949310303</v>
+        <v>4.09126901626587</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067544937134</v>
+        <v>3.99067521095276</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539095878601</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648237228394</v>
+        <v>3.49648261070251</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846230506897</v>
+        <v>3.38846254348755</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681742668152</v>
+        <v>3.4168176651001</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837327003479</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116056442261</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340155601501</v>
+        <v>3.46340131759644</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51066017150879</v>
+        <v>3.51065993309021</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842705726624</v>
+        <v>3.59842681884766</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.62408185005188</v>
+        <v>3.6240816116333</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678241729736</v>
+        <v>3.62678217887878</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577216148376</v>
+        <v>3.70577192306519</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079233169556</v>
+        <v>3.68079257011414</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450800895691</v>
+        <v>3.76450824737549</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527940750122</v>
+        <v>4.14527988433838</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916273117065</v>
+        <v>4.18916320800781</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620874404907</v>
+        <v>4.16620826721191</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106126785278</v>
+        <v>4.18106174468994</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629547119141</v>
+        <v>4.22629499435425</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840732574463</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562488555908</v>
+        <v>4.38562440872192</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781232833862</v>
+        <v>4.18781280517578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633533477783</v>
+        <v>4.17633581161499</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033044815063</v>
+        <v>3.75033020973206</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771589279175</v>
+        <v>3.80771613121033</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.7368278503418</v>
+        <v>3.73682808876038</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948783874512</v>
+        <v>3.78948760032654</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478227615356</v>
+        <v>4.42478179931641</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.6597261428833</v>
+        <v>4.65972661972046</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.73534059524536</v>
+        <v>4.7353401184082</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543750762939</v>
+        <v>5.11543703079224</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0317211151123</v>
+        <v>5.03172159194946</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855937957764</v>
+        <v>5.09855890274048</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902587890625</v>
+        <v>5.18902635574341</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370025634766</v>
+        <v>6.25370073318481</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707674026489</v>
+        <v>6.25707626342773</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926561355591</v>
+        <v>6.05926513671875</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293418884277</v>
+        <v>6.03293466567993</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441165924072</v>
+        <v>6.04441213607788</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.86617851257324</v>
+        <v>5.8661789894104</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977293014526</v>
+        <v>6.09977245330811</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390386581421</v>
+        <v>6.00390434265137</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748809814453</v>
+        <v>5.91748857498169</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047828674316</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.3064980506897</v>
+        <v>5.30649852752686</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920951843262</v>
+        <v>5.62920904159546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672107696533</v>
+        <v>5.69672155380249</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3753604888916</v>
+        <v>5.37536096572876</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751316070557</v>
+        <v>5.38751363754272</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003080368042</v>
+        <v>4.95003128051758</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809240341187</v>
+        <v>5.00809192657471</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.8217568397522</v>
+        <v>4.82175731658936</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.767746925354</v>
+        <v>4.76774644851685</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568607330322</v>
+        <v>4.97568559646606</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236568450928</v>
+        <v>5.40236616134644</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379772186279</v>
+        <v>5.30379724502563</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114791870117</v>
+        <v>5.57114839553833</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578760147095</v>
+        <v>5.51578712463379</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148273468018</v>
+        <v>5.49148321151733</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907688140869</v>
+        <v>5.45907735824585</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.41721868515015</v>
+        <v>5.4172191619873</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562528610229</v>
+        <v>5.71562480926514</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376804351807</v>
+        <v>5.67376756668091</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460922241211</v>
+        <v>5.63460969924927</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044717788696</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436622619629</v>
+        <v>5.93436574935913</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.8263463973999</v>
+        <v>5.82634592056274</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457954406738</v>
+        <v>6.00457906723022</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631624221802</v>
+        <v>6.19631576538086</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16930961608887</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002054214478</v>
+        <v>5.96002101898193</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479286193848</v>
+        <v>6.07479238510132</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289432525635</v>
+        <v>6.08289384841919</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770698547363</v>
+        <v>6.14770650863647</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301582336426</v>
+        <v>5.93301630020142</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748205184937</v>
+        <v>5.75748252868652</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700536727905</v>
+        <v>5.34700584411621</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806129455566</v>
+        <v>5.37806177139282</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36995983123779</v>
+        <v>5.36996030807495</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.82850790023804</v>
+        <v>4.8285083770752</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669099807739</v>
+        <v>4.73669052124023</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525943756104</v>
+        <v>4.83525991439819</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893501281738</v>
+        <v>4.96893453598022</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004194259644</v>
+        <v>5.27004146575928</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.31324911117554</v>
+        <v>5.3132495880127</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847774505615</v>
+        <v>5.19847726821899</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565544128418</v>
+        <v>5.34565591812134</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076210021973</v>
+        <v>5.38076162338257</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958419799805</v>
+        <v>5.49958467483521</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21792030334473</v>
+        <v>6.21791982650757</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37725019454956</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492502212524</v>
+        <v>6.24492454528809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.4245080947876</v>
+        <v>6.42450761795044</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527050018311</v>
+        <v>6.48527002334595</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5824875831604</v>
+        <v>6.58248853683472</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459943771362</v>
+        <v>6.64459991455078</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751308441162</v>
+        <v>6.71751356124878</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839651107788</v>
+        <v>6.62839698791504</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080284118652</v>
+        <v>6.66080331802368</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320821762085</v>
+        <v>6.69320869445801</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284372329712</v>
+        <v>7.14284324645996</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525466918945</v>
+        <v>7.33525514602661</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989944458008</v>
+        <v>7.43989992141724</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403690338135</v>
+        <v>7.50403642654419</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47027969360352</v>
+        <v>7.47028017044067</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147382736206</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835147857666</v>
+        <v>7.8483510017395</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885927200317</v>
+        <v>7.88885879516602</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228580474854</v>
+        <v>8.16228485107422</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053375244141</v>
+        <v>8.82053470611572</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375762939453</v>
+        <v>9.34375667572021</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114402770996</v>
+        <v>9.40114307403564</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253986358643</v>
+        <v>9.51253890991211</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840145111084</v>
+        <v>9.44840240478516</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297119140625</v>
+        <v>8.48297023773193</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -31728,6 +31728,32 @@
         <v>14.2700004577637</v>
       </c>
       <c r="H1206" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>1166727</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>14.3100004196167</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>14.2550001144409</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>14.2650003433228</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>14.289999961853</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>14.289999961853</v>
+      </c>
+      <c r="H1207" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -28195,8 +28195,31 @@
       <c r="E1210" t="n">
         <v>14.2700004577637</v>
       </c>
-      <c r="F1210"/>
+      <c r="F1210" t="n">
+        <v>14.1750001907349</v>
+      </c>
       <c r="G1210" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>1243336</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>14.2849998474121</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>14.1750001907349</v>
+      </c>
+      <c r="F1211"/>
+      <c r="G1211" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -28210,7 +28210,7 @@
         <v>1243336</v>
       </c>
       <c r="C1211" t="n">
-        <v>14.2849998474121</v>
+        <v>14.3000001907349</v>
       </c>
       <c r="D1211" t="n">
         <v>14.1499996185303</v>
@@ -28218,8 +28218,31 @@
       <c r="E1211" t="n">
         <v>14.1750001907349</v>
       </c>
-      <c r="F1211"/>
+      <c r="F1211" t="n">
+        <v>14.3000001907349</v>
+      </c>
       <c r="G1211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>893612</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>14.2200002670288</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="F1212"/>
+      <c r="G1212" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -28241,8 +28241,31 @@
       <c r="E1212" t="n">
         <v>14.3000001907349</v>
       </c>
-      <c r="F1212"/>
+      <c r="F1212" t="n">
+        <v>14.25</v>
+      </c>
       <c r="G1212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>1663327</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>14.3199996948242</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>14.2349996566772</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>14.2700004577637</v>
+      </c>
+      <c r="F1213"/>
+      <c r="G1213" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -28264,8 +28264,31 @@
       <c r="E1213" t="n">
         <v>14.2700004577637</v>
       </c>
-      <c r="F1213"/>
+      <c r="F1213" t="n">
+        <v>14.3199996948242</v>
+      </c>
       <c r="G1213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1214" t="n">
+        <v>1453584</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>14.5299997329712</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>14.289999961853</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>14.289999961853</v>
+      </c>
+      <c r="F1214"/>
+      <c r="G1214" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -28294,6 +28294,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>1086694</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>14.3299999237061</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>14.335000038147</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418298721313</v>
+        <v>6.82418346405029</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23060989379883</v>
+        <v>7.23061037063599</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024492263794</v>
+        <v>7.68024444580078</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634632110596</v>
+        <v>7.15634679794312</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705677032471</v>
+        <v>6.94705629348755</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8525390625</v>
+        <v>6.85253810882568</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411249160767</v>
+        <v>7.24411201477051</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040723800659</v>
+        <v>7.48040676116943</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385835647583</v>
+        <v>7.22385883331299</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010210037231</v>
+        <v>7.19010162353516</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>7.05507707595825</v>
+        <v>7.05507659912109</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96730995178223</v>
+        <v>6.96731090545654</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47109222412109</v>
+        <v>6.47109270095825</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956884384155</v>
+        <v>6.34956932067871</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.39345264434814</v>
+        <v>6.3934531211853</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>6.43058443069458</v>
+        <v>6.43058395385742</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08626985549927</v>
+        <v>6.08627033233643</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4550256729126</v>
+        <v>5.45502614974976</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>5.43814849853516</v>
+        <v>5.438148021698</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G42" t="n">
-        <v>5.02631998062134</v>
+        <v>5.0263204574585</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850280761719</v>
+        <v>4.66850328445435</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13852787017822</v>
+        <v>4.13852834701538</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13852787017822</v>
+        <v>4.13852834701538</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533041000366</v>
+        <v>4.41533088684082</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187833786011</v>
+        <v>4.67187881469727</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347730636597</v>
+        <v>4.53347778320312</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44233512878418</v>
+        <v>4.44233560562134</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.40520334243774</v>
+        <v>4.4052038192749</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>4.43558406829834</v>
+        <v>4.4355845451355</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.94299983978271</v>
       </c>
       <c r="G67" t="n">
-        <v>4.01227951049805</v>
+        <v>4.01227998733521</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.84484815597534</v>
+        <v>3.84484839439392</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.6875433921814</v>
+        <v>3.68754315376282</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0851936340332</v>
+        <v>4.08519315719604</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G75" t="n">
-        <v>4.02240705490112</v>
+        <v>4.02240657806396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822392463684</v>
+        <v>3.84822344779968</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995529174805</v>
+        <v>3.87995505332947</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286360740662</v>
+        <v>3.79286313056946</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311726570129</v>
+        <v>3.81311678886414</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3.88197994232178</v>
+        <v>3.88198018074036</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045751571655</v>
+        <v>3.76045727729797</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619346618652</v>
+        <v>3.68619322776794</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437584877014</v>
+        <v>3.5943763256073</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496479988098</v>
+        <v>3.53496527671814</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.41900014877319</v>
       </c>
       <c r="G92" t="n">
-        <v>3.65851306915283</v>
+        <v>3.65851330757141</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395987510681</v>
+        <v>3.77395963668823</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240148544312</v>
+        <v>3.86240196228027</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G98" t="n">
-        <v>3.80231499671936</v>
+        <v>3.80231523513794</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354875564575</v>
+        <v>4.11354827880859</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12030029296875</v>
+        <v>4.12029981613159</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594975471497</v>
+        <v>3.98594951629639</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.65716290473938</v>
+        <v>3.6571626663208</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091406822205</v>
+        <v>3.53091430664062</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952332496643</v>
+        <v>3.57952356338501</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.40399026870728</v>
+        <v>3.4039900302887</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082757949829</v>
+        <v>3.47082781791687</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.74849987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20584034919739</v>
+        <v>3.20584058761597</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.20989108085632</v>
+        <v>3.2098913192749</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.45665001869202</v>
+        <v>3.4566502571106</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.2132670879364</v>
+        <v>3.21326661109924</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39183783531189</v>
+        <v>3.39183807373047</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.11299991607666</v>
       </c>
       <c r="G140" t="n">
-        <v>3.45192432403564</v>
+        <v>3.45192408561707</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948274612427</v>
+        <v>3.62948298454285</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319842338562</v>
+        <v>3.71319818496704</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894479751587</v>
+        <v>3.95894455909729</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>3.89143204689026</v>
+        <v>3.89143180847168</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.75899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>3.88805651664734</v>
+        <v>3.88805627822876</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290904045105</v>
+        <v>3.90290927886963</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573643684387</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387871742249</v>
+        <v>3.87387847900391</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139656066895</v>
+        <v>4.10139608383179</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067568778992</v>
+        <v>3.99067544937134</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.75</v>
       </c>
       <c r="G163" t="n">
-        <v>3.88197994232178</v>
+        <v>3.88198018074036</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370597839355</v>
+        <v>3.75370573997498</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648261070251</v>
+        <v>3.49648237228394</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G170" t="n">
-        <v>3.48635601997375</v>
+        <v>3.48635578155518</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.05600023269653</v>
       </c>
       <c r="G171" t="n">
-        <v>3.41344213485718</v>
+        <v>3.41344237327576</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.94549989700317</v>
       </c>
       <c r="G172" t="n">
-        <v>3.33884048461914</v>
+        <v>3.33884024620056</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846254348755</v>
+        <v>3.38846230506897</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.4168176651001</v>
+        <v>3.41681742668152</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538077354431</v>
+        <v>3.35538101196289</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437099456787</v>
+        <v>3.43437075614929</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837350845337</v>
+        <v>3.24837327003479</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116032600403</v>
+        <v>3.31116056442261</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786826133728</v>
+        <v>3.28786849975586</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.10300016403198</v>
       </c>
       <c r="G196" t="n">
-        <v>3.4451732635498</v>
+        <v>3.44517302513123</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340131759644</v>
+        <v>3.46340155601501</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.14699983596802</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47487831115723</v>
+        <v>3.47487854957581</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G201" t="n">
-        <v>3.39858913421631</v>
+        <v>3.39858937263489</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50795984268188</v>
+        <v>3.50796008110046</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842658042908</v>
+        <v>3.59842705726624</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.6240816116333</v>
+        <v>3.62408185005188</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577192306519</v>
+        <v>3.70577216148376</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.72400045394897</v>
+        <v>3.7240002155304</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450824737549</v>
+        <v>3.76450800895691</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573643684387</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>4.20266580581665</v>
+        <v>4.20266532897949</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916320800781</v>
+        <v>4.18916273117065</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620826721191</v>
+        <v>4.16620874404907</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.17903566360474</v>
+        <v>4.17903614044189</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629499435425</v>
+        <v>4.22629547119141</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>4.36807203292847</v>
+        <v>4.36807155609131</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781280517578</v>
+        <v>4.18781232833862</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633581161499</v>
+        <v>4.17633533477783</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G246" t="n">
-        <v>4.14257955551147</v>
+        <v>4.14257907867432</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.0264573097229</v>
+        <v>4.02645778656006</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033020973206</v>
+        <v>3.75033044815063</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459425926208</v>
+        <v>3.82459449768066</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771636962891</v>
+        <v>3.80771589279175</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948760032654</v>
+        <v>3.78948783874512</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.87522888183594</v>
+        <v>3.87522864341736</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604085922241</v>
+        <v>4.20604133605957</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478179931641</v>
+        <v>4.42478227615356</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>4.61786890029907</v>
+        <v>4.61786842346191</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605613708496</v>
+        <v>4.68605661392212</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.65972661972046</v>
+        <v>4.6597261428833</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543703079224</v>
+        <v>5.11543750762939</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.03172159194946</v>
+        <v>5.0317211151123</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7.59299993515015</v>
       </c>
       <c r="G280" t="n">
-        <v>5.12623929977417</v>
+        <v>5.12623882293701</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>7.5310001373291</v>
       </c>
       <c r="G283" t="n">
-        <v>5.08438110351562</v>
+        <v>5.08438158035278</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855890274048</v>
+        <v>5.09855937957764</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370073318481</v>
+        <v>6.25370025634766</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>6.3023099899292</v>
+        <v>6.30231046676636</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>8.95600032806396</v>
       </c>
       <c r="G294" t="n">
-        <v>6.04643774032593</v>
+        <v>6.04643726348877</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449329376221</v>
+        <v>5.94449281692505</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G296" t="n">
-        <v>6.06264019012451</v>
+        <v>6.06263971328735</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926513671875</v>
+        <v>6.05926561355591</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293466567993</v>
+        <v>6.03293418884277</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G300" t="n">
-        <v>6.0450873374939</v>
+        <v>6.04508781433105</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.11100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>6.15108203887939</v>
+        <v>6.15108156204224</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.19361448287964</v>
+        <v>6.1936149597168</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441213607788</v>
+        <v>6.04441165924072</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836595535278</v>
+        <v>5.66836643218994</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.8769998550415</v>
       </c>
       <c r="G311" t="n">
-        <v>5.99310207366943</v>
+        <v>5.99310255050659</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977245330811</v>
+        <v>6.09977293014526</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.56700038909912</v>
       </c>
       <c r="G317" t="n">
-        <v>5.78381299972534</v>
+        <v>5.7838134765625</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.85299968719482</v>
       </c>
       <c r="G318" t="n">
-        <v>5.97689867019653</v>
+        <v>5.97689914703369</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390434265137</v>
+        <v>6.00390386581421</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748857498169</v>
+        <v>5.91748809814453</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047828674316</v>
+        <v>5.73047733306885</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.30649852752686</v>
+        <v>5.3064980506897</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.96799993515015</v>
       </c>
       <c r="G329" t="n">
-        <v>5.37941217422485</v>
+        <v>5.3794116973877</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920904159546</v>
+        <v>5.62920951843262</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.29599952697754</v>
       </c>
       <c r="G333" t="n">
-        <v>5.60085344314575</v>
+        <v>5.60085296630859</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672155380249</v>
+        <v>5.69672107696533</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G337" t="n">
-        <v>5.54144191741943</v>
+        <v>5.54144239425659</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.37536096572876</v>
+        <v>5.3753604888916</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G349" t="n">
-        <v>4.95948266983032</v>
+        <v>4.95948314666748</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003128051758</v>
+        <v>4.95003080368042</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910703659058</v>
+        <v>5.08910751342773</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.82175731658936</v>
+        <v>4.8217568397522</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71643686294556</v>
+        <v>4.71643733978271</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76774644851685</v>
+        <v>4.767746925354</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568559646606</v>
+        <v>4.97568607330322</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543241500854</v>
+        <v>4.95543193817139</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.32600021362305</v>
       </c>
       <c r="G369" t="n">
-        <v>4.94598007202148</v>
+        <v>4.94598054885864</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G373" t="n">
-        <v>5.21603059768677</v>
+        <v>5.21603107452393</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.93200016021729</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35510778427124</v>
+        <v>5.35510730743408</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>5.4550256729126</v>
+        <v>5.45502614974976</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236616134644</v>
+        <v>5.40236568450928</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080291748047</v>
+        <v>5.33080244064331</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578712463379</v>
+        <v>5.51578760147095</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148321151733</v>
+        <v>5.49148273468018</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907735824585</v>
+        <v>5.45907688140869</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.4172191619873</v>
+        <v>5.41721868515015</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G391" t="n">
-        <v>5.54144191741943</v>
+        <v>5.54144239425659</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.6197566986084</v>
+        <v>5.61975717544556</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562433242798</v>
+        <v>5.71562528610229</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376756668091</v>
+        <v>5.67376804351807</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>5.72912788391113</v>
+        <v>5.72912740707397</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.5603461265564</v>
+        <v>5.56034564971924</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768613815308</v>
+        <v>5.50768566131592</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63461017608643</v>
+        <v>5.63460922241211</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951322555542</v>
+        <v>5.91951274871826</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.53400039672852</v>
       </c>
       <c r="G407" t="n">
-        <v>6.43666124343872</v>
+        <v>6.43666076660156</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873180389404</v>
+        <v>6.54873132705688</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.4060001373291</v>
       </c>
       <c r="G410" t="n">
-        <v>6.35024499893188</v>
+        <v>6.35024452209473</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758405685425</v>
+        <v>6.29758453369141</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665105819702</v>
+        <v>6.11665058135986</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044765472412</v>
+        <v>6.10044717788696</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.9748740196228</v>
+        <v>5.97487449645996</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.82634592056274</v>
+        <v>5.8263463973999</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461940765381</v>
+        <v>5.95461988449097</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631576538086</v>
+        <v>6.19631624221802</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002149581909</v>
+        <v>5.96002054214478</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479238510132</v>
+        <v>6.07479286193848</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G439" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G440" t="n">
-        <v>6.0450873374939</v>
+        <v>6.04508781433105</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G442" t="n">
-        <v>6.12610244750977</v>
+        <v>6.12610292434692</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G443" t="n">
-        <v>6.15040636062622</v>
+        <v>6.15040683746338</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G444" t="n">
-        <v>6.20711803436279</v>
+        <v>6.20711755752563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770650863647</v>
+        <v>6.14770698547363</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G448" t="n">
-        <v>5.98297548294067</v>
+        <v>5.98297595977783</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.85599994659424</v>
       </c>
       <c r="G449" t="n">
-        <v>5.97892427444458</v>
+        <v>5.97892475128174</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.93031549453735</v>
+        <v>5.9303150177002</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G451" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613260269165</v>
+        <v>5.75613307952881</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G455" t="n">
-        <v>5.94246816635132</v>
+        <v>5.94246768951416</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.07800006866455</v>
       </c>
       <c r="G456" t="n">
-        <v>6.12880325317383</v>
+        <v>6.12880277633667</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984851837158</v>
+        <v>5.83984804153442</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748300552368</v>
+        <v>5.75748205184937</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401103973389</v>
+        <v>5.37401056289673</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29434537887573</v>
+        <v>5.29434585571289</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.83400011062622</v>
       </c>
       <c r="G465" t="n">
-        <v>5.28894519805908</v>
+        <v>5.28894472122192</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409172058105</v>
+        <v>5.27409219741821</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700632095337</v>
+        <v>5.34700536727905</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806177139282</v>
+        <v>5.37806129455566</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8285083770752</v>
+        <v>4.82850790023804</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.85011196136475</v>
+        <v>4.8501124382019</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669052124023</v>
+        <v>4.73669099807739</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893453598022</v>
+        <v>4.96893501281738</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.25</v>
       </c>
       <c r="G482" t="n">
-        <v>4.89467000961304</v>
+        <v>4.8946704864502</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.9230260848999</v>
+        <v>4.92302560806274</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.86091470718384</v>
+        <v>4.86091423034668</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.1417670249939</v>
+        <v>5.14176750183105</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004098892212</v>
+        <v>5.27004194259644</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.3132495880127</v>
+        <v>5.31324911117554</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847726821899</v>
+        <v>5.19847774505615</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>7.87400007247925</v>
       </c>
       <c r="G504" t="n">
-        <v>5.31595039367676</v>
+        <v>5.3159499168396</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076162338257</v>
+        <v>5.38076210021973</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958467483521</v>
+        <v>5.49958419799805</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>8.69799995422363</v>
       </c>
       <c r="G518" t="n">
-        <v>5.87225437164307</v>
+        <v>5.87225484848022</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791934967041</v>
+        <v>6.21792030334473</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.3772497177124</v>
+        <v>6.37725019454956</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.3745493888855</v>
+        <v>6.37454986572266</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492454528809</v>
+        <v>6.24492502212524</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>6.06264019012451</v>
+        <v>6.06263971328735</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527002334595</v>
+        <v>6.48527050018311</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.58248853683472</v>
+        <v>6.5824875831604</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459991455078</v>
+        <v>6.64459943771362</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G533" t="n">
-        <v>6.69185876846313</v>
+        <v>6.69185829162598</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751356124878</v>
+        <v>6.71751308441162</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080331802368</v>
+        <v>6.66080284118652</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320869445801</v>
+        <v>6.69320821762085</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284324645996</v>
+        <v>7.14284372329712</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403642654419</v>
+        <v>7.50403690338135</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47028017044067</v>
+        <v>7.47027969360352</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.45002603530884</v>
+        <v>7.450026512146</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.83147287368774</v>
+        <v>7.8314733505249</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835195541382</v>
+        <v>7.84835147857666</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885879516602</v>
+        <v>7.88885927200317</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G555" t="n">
-        <v>8.08126926422119</v>
+        <v>8.08127021789551</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228485107422</v>
+        <v>8.16228580474854</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>12.2550001144409</v>
       </c>
       <c r="G560" t="n">
-        <v>8.27368068695068</v>
+        <v>8.273681640625</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G562" t="n">
-        <v>8.26355361938477</v>
+        <v>8.26355457305908</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053470611572</v>
+        <v>8.82053375244141</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.3235034942627</v>
+        <v>9.32350444793701</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375667572021</v>
+        <v>9.34375762939453</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114307403564</v>
+        <v>9.40114402770996</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253890991211</v>
+        <v>9.51253986358643</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840240478516</v>
+        <v>9.44840145111084</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540760040283</v>
+        <v>9.47540664672852</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243785858154</v>
+        <v>8.97243690490723</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G583" t="n">
-        <v>8.54710674285889</v>
+        <v>8.5471076965332</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297023773193</v>
+        <v>8.48297119140625</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G586" t="n">
-        <v>8.47622013092041</v>
+        <v>8.47621917724609</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G587" t="n">
-        <v>8.47284507751465</v>
+        <v>8.47284412384033</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.9527735710144</v>
+        <v>7.95277309417725</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893676757812</v>
+        <v>8.37893772125244</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.1143045425415</v>
+        <v>8.11430358886719</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465784072876</v>
+        <v>7.90465831756592</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809535980225</v>
+        <v>7.90809488296509</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558931350708</v>
+        <v>7.93558979034424</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776195526123</v>
+        <v>8.00776290893555</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.95964765548706</v>
+        <v>7.9596471786499</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.72938108444214</v>
+        <v>7.7293815612793</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621013641357</v>
+        <v>7.95621061325073</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627696990967</v>
+        <v>7.62627744674683</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379367828369</v>
+        <v>7.54379415512085</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250699996948</v>
+        <v>7.72250747680664</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434766769409</v>
+        <v>7.89434814453125</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445858001709</v>
+        <v>7.34445905685425</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758544921875</v>
+        <v>7.33758497238159</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632104873657</v>
+        <v>7.40632057189941</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259611129761</v>
+        <v>7.28259658813477</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.31009101867676</v>
+        <v>7.3100905418396</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982444763184</v>
+        <v>7.07982492446899</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949199676514</v>
+        <v>7.17949151992798</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470287322998</v>
+        <v>7.68470335006714</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.86685371398926</v>
+        <v>7.8668532371521</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.9149694442749</v>
+        <v>7.91496896743774</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122127532959</v>
+        <v>7.90122175216675</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656534194946</v>
+        <v>7.74656581878662</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485786437988</v>
+        <v>6.91485834121704</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946941375732</v>
+        <v>6.35946989059448</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980192184448</v>
+        <v>5.94980239868164</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108764648438</v>
+        <v>5.77108812332153</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255088806152</v>
+        <v>5.95255136489868</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017934799194</v>
+        <v>5.94017887115479</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638805389404</v>
+        <v>6.14638757705688</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199678421021</v>
+        <v>6.22199726104736</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634302139282</v>
+        <v>6.36634349822998</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38009023666382</v>
+        <v>6.38008975982666</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188646316528</v>
+        <v>6.15188598632812</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392608642578</v>
+        <v>5.95392560958862</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28111028671265</v>
+        <v>6.28110980987549</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.30310583114624</v>
+        <v>6.3031063079834</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.49831676483154</v>
+        <v>6.4983172416687</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286195755005</v>
+        <v>6.27286243438721</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536800384521</v>
+        <v>6.24536752700806</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170883178711</v>
+        <v>6.41170930862427</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938089370728</v>
+        <v>6.17938041687012</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441431045532</v>
+        <v>6.01441383361816</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962524414062</v>
+        <v>6.20962476730347</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698612213135</v>
+        <v>6.27698659896851</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450283050537</v>
+        <v>6.19450330734253</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754058837891</v>
+        <v>6.62754011154175</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204170227051</v>
+        <v>6.62204122543335</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.89767360687256</v>
+        <v>6.8976731300354</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088857650757</v>
+        <v>6.76088905334473</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705236434937</v>
+        <v>6.56705284118652</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.01108837127686</v>
+        <v>7.0110878944397</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013515472412</v>
+        <v>6.78013467788696</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729623794556</v>
+        <v>6.59729671478271</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.6467866897583</v>
+        <v>6.64678716659546</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000207901001</v>
+        <v>6.82000160217285</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401544570923</v>
+        <v>6.75401496887207</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.8419976234436</v>
+        <v>6.84199810028076</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093265533447</v>
+        <v>6.54093313217163</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166463851929</v>
+        <v>7.25166511535645</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818351745605</v>
+        <v>7.46818399429321</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933605194092</v>
+        <v>7.94933652877808</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.82904863357544</v>
+        <v>7.8290491104126</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683095932007</v>
+        <v>7.97683143615723</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210674285889</v>
+        <v>10.2210664749146</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341487884521</v>
+        <v>10.4341497421265</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500032424927</v>
+        <v>10.8500022888184</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249475479126</v>
+        <v>11.1249465942383</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953458786011</v>
+        <v>10.6953468322754</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485609054565</v>
+        <v>10.2485618591309</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352586746216</v>
+        <v>11.1352577209473</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029973983765</v>
+        <v>11.5029964447021</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208446502686</v>
+        <v>11.3208456039429</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376964569092</v>
+        <v>11.4376955032349</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414669036865</v>
+        <v>11.3414659500122</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585395812988</v>
+        <v>10.3585386276245</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069868087769</v>
+        <v>10.3069877624512</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634304046631</v>
+        <v>8.84634399414062</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472534179688</v>
+        <v>9.12472438812256</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940307617188</v>
+        <v>9.16940402984619</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -32014,6 +32014,32 @@
         <v>14.3450002670288</v>
       </c>
       <c r="H1217" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>656409</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>14.3450002670288</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>14.3549995422363</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>14.3450002670288</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>14.3450002670288</v>
+      </c>
+      <c r="H1218" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418346405029</v>
+        <v>6.82418298721313</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024444580078</v>
+        <v>7.68024492263794</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634679794312</v>
+        <v>7.15634632110596</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.859290599823</v>
+        <v>6.85929012298584</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253810882568</v>
+        <v>6.85253858566284</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411201477051</v>
+        <v>7.24411249160767</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385883331299</v>
+        <v>7.22385835647583</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731090545654</v>
+        <v>6.96731042861938</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956932067871</v>
+        <v>6.34956884384155</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3934531211853</v>
+        <v>6.39345264434814</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08627033233643</v>
+        <v>6.08626985549927</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238653182983</v>
+        <v>6.04238605499268</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284332275391</v>
+        <v>5.81284284591675</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637098312378</v>
+        <v>5.29637145996094</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548294067383</v>
+        <v>5.22548246383667</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850328445435</v>
+        <v>4.66850280761719</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692937850952</v>
+        <v>4.27692985534668</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187881469727</v>
+        <v>4.67187833786011</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347778320312</v>
+        <v>4.53347730636597</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.4052038192749</v>
+        <v>4.40520334243774</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195487976074</v>
+        <v>4.4119553565979</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967052459717</v>
+        <v>4.22967004776001</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667524337769</v>
+        <v>4.25667572021484</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754315376282</v>
+        <v>3.6875433921814</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822344779968</v>
+        <v>3.84822368621826</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286313056946</v>
+        <v>3.79286336898804</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045727729797</v>
+        <v>3.76045751571655</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5943763256073</v>
+        <v>3.59437608718872</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496527671814</v>
+        <v>3.53496503829956</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240196228027</v>
+        <v>3.86240172386169</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446743011475</v>
+        <v>3.81446766853333</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802103042603</v>
+        <v>4.09802055358887</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0001277923584</v>
+        <v>4.00012731552124</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594951629639</v>
+        <v>3.98594927787781</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761969566345</v>
+        <v>3.42761993408203</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302592277527</v>
+        <v>3.59302568435669</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944192886353</v>
+        <v>3.67944169044495</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952356338501</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682275772095</v>
+        <v>3.57682251930237</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082781791687</v>
+        <v>3.47082757949829</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724406242371</v>
+        <v>3.55724430084229</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326661109924</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948298454285</v>
+        <v>3.62948274612427</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488364219666</v>
+        <v>3.63488340377808</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813258171082</v>
+        <v>3.62813234329224</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226447105408</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319818496704</v>
+        <v>3.71319842338562</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894455909729</v>
+        <v>3.95894479751587</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290927886963</v>
+        <v>3.90290951728821</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139608383179</v>
+        <v>4.10139656066895</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126949310303</v>
+        <v>4.09126901626587</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067544937134</v>
+        <v>3.99067521095276</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539095878601</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648237228394</v>
+        <v>3.49648261070251</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846230506897</v>
+        <v>3.38846254348755</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681742668152</v>
+        <v>3.4168176651001</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837327003479</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116056442261</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340155601501</v>
+        <v>3.46340131759644</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51066017150879</v>
+        <v>3.51065993309021</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842705726624</v>
+        <v>3.59842681884766</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.62408185005188</v>
+        <v>3.6240816116333</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678241729736</v>
+        <v>3.62678217887878</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577216148376</v>
+        <v>3.70577192306519</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079233169556</v>
+        <v>3.68079257011414</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450800895691</v>
+        <v>3.76450824737549</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527940750122</v>
+        <v>4.14527988433838</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916273117065</v>
+        <v>4.18916320800781</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620874404907</v>
+        <v>4.16620826721191</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106126785278</v>
+        <v>4.18106174468994</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629547119141</v>
+        <v>4.22629499435425</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840732574463</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562488555908</v>
+        <v>4.38562440872192</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781232833862</v>
+        <v>4.18781280517578</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633533477783</v>
+        <v>4.17633581161499</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033044815063</v>
+        <v>3.75033020973206</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771589279175</v>
+        <v>3.80771613121033</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.7368278503418</v>
+        <v>3.73682808876038</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948783874512</v>
+        <v>3.78948760032654</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478227615356</v>
+        <v>4.42478179931641</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.6597261428833</v>
+        <v>4.65972661972046</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.73534059524536</v>
+        <v>4.7353401184082</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543750762939</v>
+        <v>5.11543703079224</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0317211151123</v>
+        <v>5.03172159194946</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855937957764</v>
+        <v>5.09855890274048</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902587890625</v>
+        <v>5.18902635574341</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370025634766</v>
+        <v>6.25370073318481</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707674026489</v>
+        <v>6.25707626342773</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926561355591</v>
+        <v>6.05926513671875</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293418884277</v>
+        <v>6.03293466567993</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441165924072</v>
+        <v>6.04441213607788</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.86617851257324</v>
+        <v>5.8661789894104</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977293014526</v>
+        <v>6.09977245330811</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390386581421</v>
+        <v>6.00390434265137</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748809814453</v>
+        <v>5.91748857498169</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047828674316</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.3064980506897</v>
+        <v>5.30649852752686</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920951843262</v>
+        <v>5.62920904159546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672107696533</v>
+        <v>5.69672155380249</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3753604888916</v>
+        <v>5.37536096572876</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751316070557</v>
+        <v>5.38751363754272</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003080368042</v>
+        <v>4.95003128051758</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809240341187</v>
+        <v>5.00809192657471</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.8217568397522</v>
+        <v>4.82175731658936</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.767746925354</v>
+        <v>4.76774644851685</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568607330322</v>
+        <v>4.97568559646606</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236568450928</v>
+        <v>5.40236616134644</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379772186279</v>
+        <v>5.30379724502563</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114791870117</v>
+        <v>5.57114839553833</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578760147095</v>
+        <v>5.51578712463379</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148273468018</v>
+        <v>5.49148321151733</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907688140869</v>
+        <v>5.45907735824585</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.41721868515015</v>
+        <v>5.4172191619873</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562528610229</v>
+        <v>5.71562480926514</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376804351807</v>
+        <v>5.67376756668091</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460922241211</v>
+        <v>5.63460969924927</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044717788696</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436622619629</v>
+        <v>5.93436574935913</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.8263463973999</v>
+        <v>5.82634592056274</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457954406738</v>
+        <v>6.00457906723022</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631624221802</v>
+        <v>6.19631576538086</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16930961608887</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002054214478</v>
+        <v>5.96002101898193</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479286193848</v>
+        <v>6.07479238510132</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289432525635</v>
+        <v>6.08289384841919</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770698547363</v>
+        <v>6.14770650863647</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301582336426</v>
+        <v>5.93301630020142</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748205184937</v>
+        <v>5.75748252868652</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700536727905</v>
+        <v>5.34700584411621</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806129455566</v>
+        <v>5.37806177139282</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36995983123779</v>
+        <v>5.36996030807495</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.82850790023804</v>
+        <v>4.8285083770752</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669099807739</v>
+        <v>4.73669052124023</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525943756104</v>
+        <v>4.83525991439819</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893501281738</v>
+        <v>4.96893453598022</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004194259644</v>
+        <v>5.27004146575928</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.31324911117554</v>
+        <v>5.3132495880127</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847774505615</v>
+        <v>5.19847726821899</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565544128418</v>
+        <v>5.34565591812134</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076210021973</v>
+        <v>5.38076162338257</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958419799805</v>
+        <v>5.49958467483521</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21792030334473</v>
+        <v>6.21791982650757</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37725019454956</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492502212524</v>
+        <v>6.24492454528809</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.4245080947876</v>
+        <v>6.42450761795044</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527050018311</v>
+        <v>6.48527002334595</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5824875831604</v>
+        <v>6.58248853683472</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459943771362</v>
+        <v>6.64459991455078</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751308441162</v>
+        <v>6.71751356124878</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839651107788</v>
+        <v>6.62839698791504</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080284118652</v>
+        <v>6.66080331802368</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320821762085</v>
+        <v>6.69320869445801</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284372329712</v>
+        <v>7.14284324645996</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525466918945</v>
+        <v>7.33525514602661</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989944458008</v>
+        <v>7.43989992141724</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403690338135</v>
+        <v>7.50403642654419</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47027969360352</v>
+        <v>7.47028017044067</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147382736206</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835147857666</v>
+        <v>7.8483510017395</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885927200317</v>
+        <v>7.88885879516602</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228580474854</v>
+        <v>8.16228485107422</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053375244141</v>
+        <v>8.82053470611572</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375762939453</v>
+        <v>9.34375667572021</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114402770996</v>
+        <v>9.40114307403564</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253986358643</v>
+        <v>9.51253890991211</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840145111084</v>
+        <v>9.44840240478516</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297119140625</v>
+        <v>8.48297023773193</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -32040,6 +32040,32 @@
         <v>14.3450002670288</v>
       </c>
       <c r="H1218" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>309428</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>14.3450002670288</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>14.3450002670288</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="H1219" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418346405029</v>
+        <v>6.82418298721313</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -485,7 +485,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024444580078</v>
+        <v>7.68024492263794</v>
       </c>
       <c r="H4" t="n">
         <v>9073446</v>
@@ -514,7 +514,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634679794312</v>
+        <v>7.15634632110596</v>
       </c>
       <c r="H5" t="n">
         <v>8844542</v>
@@ -572,7 +572,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.859290599823</v>
+        <v>6.85929012298584</v>
       </c>
       <c r="H7" t="n">
         <v>6880124</v>
@@ -601,7 +601,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253810882568</v>
+        <v>6.85253858566284</v>
       </c>
       <c r="H8" t="n">
         <v>4472971</v>
@@ -630,7 +630,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411201477051</v>
+        <v>7.24411249160767</v>
       </c>
       <c r="H9" t="n">
         <v>5804326</v>
@@ -659,7 +659,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="n">
         <v>7510382</v>
@@ -688,7 +688,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385883331299</v>
+        <v>7.22385835647583</v>
       </c>
       <c r="H11" t="n">
         <v>4406227</v>
@@ -746,7 +746,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H13" t="n">
         <v>2435262</v>
@@ -804,7 +804,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H15" t="n">
         <v>1535035</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731090545654</v>
+        <v>6.96731042861938</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -891,7 +891,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H18" t="n">
         <v>3251441</v>
@@ -978,7 +978,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956932067871</v>
+        <v>6.34956884384155</v>
       </c>
       <c r="H21" t="n">
         <v>1984383</v>
@@ -1007,7 +1007,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3934531211853</v>
+        <v>6.39345264434814</v>
       </c>
       <c r="H22" t="n">
         <v>1481754</v>
@@ -1210,7 +1210,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08627033233643</v>
+        <v>6.08626985549927</v>
       </c>
       <c r="H29" t="n">
         <v>6081895</v>
@@ -1239,7 +1239,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238653182983</v>
+        <v>6.04238605499268</v>
       </c>
       <c r="H30" t="n">
         <v>4204295</v>
@@ -1268,7 +1268,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284332275391</v>
+        <v>5.81284284591675</v>
       </c>
       <c r="H31" t="n">
         <v>3316128</v>
@@ -1442,7 +1442,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637098312378</v>
+        <v>5.29637145996094</v>
       </c>
       <c r="H37" t="n">
         <v>2369088</v>
@@ -1500,7 +1500,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548294067383</v>
+        <v>5.22548246383667</v>
       </c>
       <c r="H39" t="n">
         <v>1845591</v>
@@ -1616,7 +1616,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850328445435</v>
+        <v>4.66850280761719</v>
       </c>
       <c r="H43" t="n">
         <v>3306233</v>
@@ -1703,7 +1703,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692937850952</v>
+        <v>4.27692985534668</v>
       </c>
       <c r="H46" t="n">
         <v>3684492</v>
@@ -1761,7 +1761,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H48" t="n">
         <v>3779682</v>
@@ -1790,7 +1790,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="n">
         <v>4270764</v>
@@ -1964,7 +1964,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187881469727</v>
+        <v>4.67187833786011</v>
       </c>
       <c r="H55" t="n">
         <v>3556258</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347778320312</v>
+        <v>4.53347730636597</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2051,7 +2051,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="n">
         <v>2735170</v>
@@ -2080,7 +2080,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.4052038192749</v>
+        <v>4.40520334243774</v>
       </c>
       <c r="H59" t="n">
         <v>2749560</v>
@@ -2109,7 +2109,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195487976074</v>
+        <v>4.4119553565979</v>
       </c>
       <c r="H60" t="n">
         <v>1556296</v>
@@ -2138,7 +2138,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967052459717</v>
+        <v>4.22967004776001</v>
       </c>
       <c r="H61" t="n">
         <v>3912970</v>
@@ -2167,7 +2167,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667524337769</v>
+        <v>4.25667572021484</v>
       </c>
       <c r="H62" t="n">
         <v>3017576</v>
@@ -2370,7 +2370,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754315376282</v>
+        <v>3.6875433921814</v>
       </c>
       <c r="H69" t="n">
         <v>4125758</v>
@@ -2399,7 +2399,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H70" t="n">
         <v>2522173</v>
@@ -2515,7 +2515,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="n">
         <v>3445946</v>
@@ -2689,7 +2689,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822344779968</v>
+        <v>3.84822368621826</v>
       </c>
       <c r="H80" t="n">
         <v>1805442</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286313056946</v>
+        <v>3.79286336898804</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2892,7 +2892,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045727729797</v>
+        <v>3.76045751571655</v>
       </c>
       <c r="H87" t="n">
         <v>1422123</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5943763256073</v>
+        <v>3.59437608718872</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496527671814</v>
+        <v>3.53496503829956</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240196228027</v>
+        <v>3.86240172386169</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3269,7 +3269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446743011475</v>
+        <v>3.81446766853333</v>
       </c>
       <c r="H100" t="n">
         <v>1355091</v>
@@ -3356,7 +3356,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="n">
         <v>2495941</v>
@@ -3414,7 +3414,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802103042603</v>
+        <v>4.09802055358887</v>
       </c>
       <c r="H105" t="n">
         <v>1510660</v>
@@ -3443,7 +3443,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0001277923584</v>
+        <v>4.00012731552124</v>
       </c>
       <c r="H106" t="n">
         <v>1710248</v>
@@ -3559,7 +3559,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H110" t="n">
         <v>3321010</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594951629639</v>
+        <v>3.98594927787781</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3675,7 +3675,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="n">
         <v>4779877</v>
@@ -3704,7 +3704,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761969566345</v>
+        <v>3.42761993408203</v>
       </c>
       <c r="H115" t="n">
         <v>4636137</v>
@@ -3791,7 +3791,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H118" t="n">
         <v>2452422</v>
@@ -3820,7 +3820,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302592277527</v>
+        <v>3.59302568435669</v>
       </c>
       <c r="H119" t="n">
         <v>4765434</v>
@@ -3849,7 +3849,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944192886353</v>
+        <v>3.67944169044495</v>
       </c>
       <c r="H120" t="n">
         <v>1265113</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952356338501</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4052,7 +4052,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682275772095</v>
+        <v>3.57682251930237</v>
       </c>
       <c r="H127" t="n">
         <v>1305635</v>
@@ -4139,7 +4139,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082781791687</v>
+        <v>3.47082757949829</v>
       </c>
       <c r="H130" t="n">
         <v>985438</v>
@@ -4197,7 +4197,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="n">
         <v>3036596</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4255,7 +4255,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724406242371</v>
+        <v>3.55724430084229</v>
       </c>
       <c r="H134" t="n">
         <v>2393460</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326661109924</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4458,7 +4458,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948298454285</v>
+        <v>3.62948274612427</v>
       </c>
       <c r="H141" t="n">
         <v>2254990</v>
@@ -4487,7 +4487,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H142" t="n">
         <v>2033903</v>
@@ -4516,7 +4516,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488364219666</v>
+        <v>3.63488340377808</v>
       </c>
       <c r="H143" t="n">
         <v>2301198</v>
@@ -4545,7 +4545,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813258171082</v>
+        <v>3.62813234329224</v>
       </c>
       <c r="H144" t="n">
         <v>1162846</v>
@@ -4603,7 +4603,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226447105408</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="n">
         <v>1532624</v>
@@ -4632,7 +4632,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319818496704</v>
+        <v>3.71319842338562</v>
       </c>
       <c r="H147" t="n">
         <v>2599217</v>
@@ -4661,7 +4661,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894455909729</v>
+        <v>3.95894479751587</v>
       </c>
       <c r="H148" t="n">
         <v>4041376</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290927886963</v>
+        <v>3.90290951728821</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4951,7 +4951,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139608383179</v>
+        <v>4.10139656066895</v>
       </c>
       <c r="H158" t="n">
         <v>1462457</v>
@@ -5009,7 +5009,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126949310303</v>
+        <v>4.09126901626587</v>
       </c>
       <c r="H160" t="n">
         <v>1170223</v>
@@ -5067,7 +5067,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067544937134</v>
+        <v>3.99067521095276</v>
       </c>
       <c r="H162" t="n">
         <v>836698</v>
@@ -5212,7 +5212,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539095878601</v>
       </c>
       <c r="H167" t="n">
         <v>1508487</v>
@@ -5270,7 +5270,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648237228394</v>
+        <v>3.49648261070251</v>
       </c>
       <c r="H169" t="n">
         <v>1228962</v>
@@ -5444,7 +5444,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846230506897</v>
+        <v>3.38846254348755</v>
       </c>
       <c r="H175" t="n">
         <v>951917</v>
@@ -5473,7 +5473,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681742668152</v>
+        <v>3.4168176651001</v>
       </c>
       <c r="H176" t="n">
         <v>743828</v>
@@ -5531,7 +5531,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H178" t="n">
         <v>1113895</v>
@@ -5560,7 +5560,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H179" t="n">
         <v>1218078</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5647,7 +5647,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H182" t="n">
         <v>748112</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837327003479</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116056442261</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -5966,7 +5966,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="n">
         <v>1635754</v>
@@ -6082,7 +6082,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340155601501</v>
+        <v>3.46340131759644</v>
       </c>
       <c r="H197" t="n">
         <v>1022230</v>
@@ -6285,7 +6285,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51066017150879</v>
+        <v>3.51065993309021</v>
       </c>
       <c r="H204" t="n">
         <v>601405</v>
@@ -6343,7 +6343,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842705726624</v>
+        <v>3.59842681884766</v>
       </c>
       <c r="H206" t="n">
         <v>578241</v>
@@ -6372,7 +6372,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.62408185005188</v>
+        <v>3.6240816116333</v>
       </c>
       <c r="H207" t="n">
         <v>1039336</v>
@@ -6401,7 +6401,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678241729736</v>
+        <v>3.62678217887878</v>
       </c>
       <c r="H208" t="n">
         <v>815597</v>
@@ -6430,7 +6430,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H209" t="n">
         <v>1632705</v>
@@ -6459,7 +6459,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H210" t="n">
         <v>1178589</v>
@@ -6546,7 +6546,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577216148376</v>
+        <v>3.70577192306519</v>
       </c>
       <c r="H213" t="n">
         <v>1086736</v>
@@ -6575,7 +6575,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="n">
         <v>561510</v>
@@ -6604,7 +6604,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="n">
         <v>771072</v>
@@ -6633,7 +6633,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079233169556</v>
+        <v>3.68079257011414</v>
       </c>
       <c r="H216" t="n">
         <v>710760</v>
@@ -6691,7 +6691,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450800895691</v>
+        <v>3.76450824737549</v>
       </c>
       <c r="H218" t="n">
         <v>1097994</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6749,7 +6749,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="n">
         <v>1345223</v>
@@ -6778,7 +6778,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527940750122</v>
+        <v>4.14527988433838</v>
       </c>
       <c r="H221" t="n">
         <v>3310511</v>
@@ -6894,7 +6894,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916273117065</v>
+        <v>4.18916320800781</v>
       </c>
       <c r="H225" t="n">
         <v>1148359</v>
@@ -6923,7 +6923,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620874404907</v>
+        <v>4.16620826721191</v>
       </c>
       <c r="H226" t="n">
         <v>1220830</v>
@@ -6981,7 +6981,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H228" t="n">
         <v>1114284</v>
@@ -7068,7 +7068,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106126785278</v>
+        <v>4.18106174468994</v>
       </c>
       <c r="H231" t="n">
         <v>540433</v>
@@ -7097,7 +7097,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="n">
         <v>341527</v>
@@ -7126,7 +7126,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629547119141</v>
+        <v>4.22629499435425</v>
       </c>
       <c r="H233" t="n">
         <v>709890</v>
@@ -7155,7 +7155,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840732574463</v>
       </c>
       <c r="H234" t="n">
         <v>1390641</v>
@@ -7242,7 +7242,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562488555908</v>
+        <v>4.38562440872192</v>
       </c>
       <c r="H237" t="n">
         <v>1118846</v>
@@ -7358,7 +7358,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="n">
         <v>1305794</v>
@@ -7387,7 +7387,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781232833862</v>
+        <v>4.18781280517578</v>
       </c>
       <c r="H242" t="n">
         <v>718598</v>
@@ -7416,7 +7416,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H243" t="n">
         <v>1010763</v>
@@ -7445,7 +7445,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633533477783</v>
+        <v>4.17633581161499</v>
       </c>
       <c r="H244" t="n">
         <v>568662</v>
@@ -7561,7 +7561,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H248" t="n">
         <v>911894</v>
@@ -7590,7 +7590,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="n">
         <v>795631</v>
@@ -7619,7 +7619,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H250" t="n">
         <v>1305048</v>
@@ -7648,7 +7648,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H251" t="n">
         <v>1142347</v>
@@ -7677,7 +7677,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033044815063</v>
+        <v>3.75033020973206</v>
       </c>
       <c r="H252" t="n">
         <v>2220991</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771589279175</v>
+        <v>3.80771613121033</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.7368278503418</v>
+        <v>3.73682808876038</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7793,7 +7793,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948783874512</v>
+        <v>3.78948760032654</v>
       </c>
       <c r="H256" t="n">
         <v>792824</v>
@@ -7938,7 +7938,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H261" t="n">
         <v>1652373</v>
@@ -8054,7 +8054,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478227615356</v>
+        <v>4.42478179931641</v>
       </c>
       <c r="H265" t="n">
         <v>3181061</v>
@@ -8141,7 +8141,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="n">
         <v>2146613</v>
@@ -8199,7 +8199,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.6597261428833</v>
+        <v>4.65972661972046</v>
       </c>
       <c r="H270" t="n">
         <v>1305558</v>
@@ -8228,7 +8228,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.73534059524536</v>
+        <v>4.7353401184082</v>
       </c>
       <c r="H271" t="n">
         <v>2895765</v>
@@ -8315,7 +8315,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H274" t="n">
         <v>1735281</v>
@@ -8373,7 +8373,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543750762939</v>
+        <v>5.11543703079224</v>
       </c>
       <c r="H276" t="n">
         <v>1864510</v>
@@ -8431,7 +8431,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0317211151123</v>
+        <v>5.03172159194946</v>
       </c>
       <c r="H278" t="n">
         <v>1291216</v>
@@ -8605,7 +8605,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855937957764</v>
+        <v>5.09855890274048</v>
       </c>
       <c r="H284" t="n">
         <v>773657</v>
@@ -8663,7 +8663,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902587890625</v>
+        <v>5.18902635574341</v>
       </c>
       <c r="H286" t="n">
         <v>2462672</v>
@@ -8750,7 +8750,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370025634766</v>
+        <v>6.25370073318481</v>
       </c>
       <c r="H289" t="n">
         <v>5659371</v>
@@ -8837,7 +8837,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707674026489</v>
+        <v>6.25707626342773</v>
       </c>
       <c r="H292" t="n">
         <v>1429447</v>
@@ -9011,7 +9011,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926561355591</v>
+        <v>6.05926513671875</v>
       </c>
       <c r="H298" t="n">
         <v>834113</v>
@@ -9040,7 +9040,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293418884277</v>
+        <v>6.03293466567993</v>
       </c>
       <c r="H299" t="n">
         <v>974549</v>
@@ -9098,7 +9098,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H301" t="n">
         <v>740488</v>
@@ -9185,7 +9185,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H304" t="n">
         <v>1512205</v>
@@ -9214,7 +9214,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="n">
         <v>1343595</v>
@@ -9272,7 +9272,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441165924072</v>
+        <v>6.04441213607788</v>
       </c>
       <c r="H307" t="n">
         <v>1036237</v>
@@ -9359,7 +9359,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="n">
         <v>1335804</v>
@@ -9475,7 +9475,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.86617851257324</v>
+        <v>5.8661789894104</v>
       </c>
       <c r="H314" t="n">
         <v>816021</v>
@@ -9504,7 +9504,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977293014526</v>
+        <v>6.09977245330811</v>
       </c>
       <c r="H315" t="n">
         <v>1294330</v>
@@ -9620,7 +9620,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390386581421</v>
+        <v>6.00390434265137</v>
       </c>
       <c r="H319" t="n">
         <v>742878</v>
@@ -9678,7 +9678,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748809814453</v>
+        <v>5.91748857498169</v>
       </c>
       <c r="H321" t="n">
         <v>905026</v>
@@ -9736,7 +9736,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047828674316</v>
       </c>
       <c r="H323" t="n">
         <v>1626293</v>
@@ -9765,7 +9765,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H324" t="n">
         <v>1282373</v>
@@ -9823,7 +9823,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.3064980506897</v>
+        <v>5.30649852752686</v>
       </c>
       <c r="H326" t="n">
         <v>1268089</v>
@@ -9997,7 +9997,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920951843262</v>
+        <v>5.62920904159546</v>
       </c>
       <c r="H332" t="n">
         <v>2007066</v>
@@ -10084,7 +10084,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672107696533</v>
+        <v>5.69672155380249</v>
       </c>
       <c r="H335" t="n">
         <v>1097585</v>
@@ -10403,7 +10403,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3753604888916</v>
+        <v>5.37536096572876</v>
       </c>
       <c r="H346" t="n">
         <v>1300436</v>
@@ -10432,7 +10432,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751316070557</v>
+        <v>5.38751363754272</v>
       </c>
       <c r="H347" t="n">
         <v>1047427</v>
@@ -10519,7 +10519,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003080368042</v>
+        <v>4.95003128051758</v>
       </c>
       <c r="H350" t="n">
         <v>1343262</v>
@@ -10577,7 +10577,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809240341187</v>
+        <v>5.00809192657471</v>
       </c>
       <c r="H352" t="n">
         <v>1123756</v>
@@ -10751,7 +10751,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.8217568397522</v>
+        <v>4.82175731658936</v>
       </c>
       <c r="H358" t="n">
         <v>1382671</v>
@@ -10896,7 +10896,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.767746925354</v>
+        <v>4.76774644851685</v>
       </c>
       <c r="H363" t="n">
         <v>1027763</v>
@@ -10983,7 +10983,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568607330322</v>
+        <v>4.97568559646606</v>
       </c>
       <c r="H366" t="n">
         <v>978343</v>
@@ -11215,7 +11215,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H374" t="n">
         <v>1589421</v>
@@ -11389,7 +11389,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236568450928</v>
+        <v>5.40236616134644</v>
       </c>
       <c r="H380" t="n">
         <v>1291207</v>
@@ -11418,7 +11418,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="n">
         <v>1027240</v>
@@ -11447,7 +11447,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379772186279</v>
+        <v>5.30379724502563</v>
       </c>
       <c r="H382" t="n">
         <v>909012</v>
@@ -11505,7 +11505,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114791870117</v>
+        <v>5.57114839553833</v>
       </c>
       <c r="H384" t="n">
         <v>1867030</v>
@@ -11534,7 +11534,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578760147095</v>
+        <v>5.51578712463379</v>
       </c>
       <c r="H385" t="n">
         <v>1237649</v>
@@ -11563,7 +11563,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148273468018</v>
+        <v>5.49148321151733</v>
       </c>
       <c r="H386" t="n">
         <v>1186915</v>
@@ -11592,7 +11592,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H387" t="n">
         <v>1194785</v>
@@ -11650,7 +11650,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907688140869</v>
+        <v>5.45907735824585</v>
       </c>
       <c r="H389" t="n">
         <v>1552098</v>
@@ -11679,7 +11679,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.41721868515015</v>
+        <v>5.4172191619873</v>
       </c>
       <c r="H390" t="n">
         <v>610844</v>
@@ -11766,7 +11766,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562528610229</v>
+        <v>5.71562480926514</v>
       </c>
       <c r="H393" t="n">
         <v>1448265</v>
@@ -11795,7 +11795,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H394" t="n">
         <v>1342906</v>
@@ -11824,7 +11824,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376804351807</v>
+        <v>5.67376756668091</v>
       </c>
       <c r="H395" t="n">
         <v>1175604</v>
@@ -12027,7 +12027,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="n">
         <v>890149</v>
@@ -12056,7 +12056,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460922241211</v>
+        <v>5.63460969924927</v>
       </c>
       <c r="H403" t="n">
         <v>1808163</v>
@@ -12143,7 +12143,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="n">
         <v>1665434</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="n">
         <v>2733714</v>
@@ -12288,7 +12288,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H411" t="n">
         <v>929420</v>
@@ -12404,7 +12404,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H415" t="n">
         <v>1271542</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044717788696</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12491,7 +12491,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436622619629</v>
+        <v>5.93436574935913</v>
       </c>
       <c r="H418" t="n">
         <v>1220620</v>
@@ -12549,7 +12549,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.8263463973999</v>
+        <v>5.82634592056274</v>
       </c>
       <c r="H420" t="n">
         <v>1409991</v>
@@ -12694,7 +12694,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457954406738</v>
+        <v>6.00457906723022</v>
       </c>
       <c r="H425" t="n">
         <v>1029644</v>
@@ -12752,7 +12752,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631624221802</v>
+        <v>6.19631576538086</v>
       </c>
       <c r="H427" t="n">
         <v>1981669</v>
@@ -12781,7 +12781,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16930961608887</v>
       </c>
       <c r="H428" t="n">
         <v>729053</v>
@@ -12810,7 +12810,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H429" t="n">
         <v>462036</v>
@@ -12868,7 +12868,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H431" t="n">
         <v>1056988</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002054214478</v>
+        <v>5.96002101898193</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -12926,7 +12926,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H433" t="n">
         <v>771857</v>
@@ -12955,7 +12955,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479286193848</v>
+        <v>6.07479238510132</v>
       </c>
       <c r="H434" t="n">
         <v>513724</v>
@@ -12984,7 +12984,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H435" t="n">
         <v>1829397</v>
@@ -13042,7 +13042,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289432525635</v>
+        <v>6.08289384841919</v>
       </c>
       <c r="H437" t="n">
         <v>877361</v>
@@ -13158,7 +13158,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="n">
         <v>1296803</v>
@@ -13303,7 +13303,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770698547363</v>
+        <v>6.14770650863647</v>
       </c>
       <c r="H446" t="n">
         <v>971388</v>
@@ -13535,7 +13535,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="n">
         <v>1565076</v>
@@ -13622,7 +13622,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H457" t="n">
         <v>1441148</v>
@@ -13651,7 +13651,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301582336426</v>
+        <v>5.93301630020142</v>
       </c>
       <c r="H458" t="n">
         <v>867989</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748205184937</v>
+        <v>5.75748252868652</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13912,7 +13912,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700536727905</v>
+        <v>5.34700584411621</v>
       </c>
       <c r="H467" t="n">
         <v>1182375</v>
@@ -13941,7 +13941,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806129455566</v>
+        <v>5.37806177139282</v>
       </c>
       <c r="H468" t="n">
         <v>921952</v>
@@ -13999,7 +13999,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36995983123779</v>
+        <v>5.36996030807495</v>
       </c>
       <c r="H470" t="n">
         <v>1735396</v>
@@ -14028,7 +14028,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H471" t="n">
         <v>13000528</v>
@@ -14086,7 +14086,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.82850790023804</v>
+        <v>4.8285083770752</v>
       </c>
       <c r="H473" t="n">
         <v>4573066</v>
@@ -14231,7 +14231,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669099807739</v>
+        <v>4.73669052124023</v>
       </c>
       <c r="H478" t="n">
         <v>2197891</v>
@@ -14289,7 +14289,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525943756104</v>
+        <v>4.83525991439819</v>
       </c>
       <c r="H480" t="n">
         <v>1773638</v>
@@ -14318,7 +14318,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893501281738</v>
+        <v>4.96893453598022</v>
       </c>
       <c r="H481" t="n">
         <v>3692477</v>
@@ -14666,7 +14666,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="n">
         <v>2819991</v>
@@ -14724,7 +14724,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004194259644</v>
+        <v>5.27004146575928</v>
       </c>
       <c r="H495" t="n">
         <v>2448121</v>
@@ -14753,7 +14753,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H496" t="n">
         <v>2796261</v>
@@ -14782,7 +14782,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.31324911117554</v>
+        <v>5.3132495880127</v>
       </c>
       <c r="H497" t="n">
         <v>1593539</v>
@@ -14898,7 +14898,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847774505615</v>
+        <v>5.19847726821899</v>
       </c>
       <c r="H501" t="n">
         <v>2160367</v>
@@ -14927,7 +14927,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H502" t="n">
         <v>2617256</v>
@@ -14956,7 +14956,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565544128418</v>
+        <v>5.34565591812134</v>
       </c>
       <c r="H503" t="n">
         <v>2644025</v>
@@ -15101,7 +15101,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076210021973</v>
+        <v>5.38076162338257</v>
       </c>
       <c r="H508" t="n">
         <v>821721</v>
@@ -15188,7 +15188,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958419799805</v>
+        <v>5.49958467483521</v>
       </c>
       <c r="H511" t="n">
         <v>928002</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21792030334473</v>
+        <v>6.21791982650757</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37725019454956</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15507,7 +15507,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H522" t="n">
         <v>2967550</v>
@@ -15536,7 +15536,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492502212524</v>
+        <v>6.24492454528809</v>
       </c>
       <c r="H523" t="n">
         <v>1934023</v>
@@ -15565,7 +15565,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="n">
         <v>1721895</v>
@@ -15623,7 +15623,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="n">
         <v>994506</v>
@@ -15652,7 +15652,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H527" t="n">
         <v>1251679</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.4245080947876</v>
+        <v>6.42450761795044</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15739,7 +15739,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527050018311</v>
+        <v>6.48527002334595</v>
       </c>
       <c r="H530" t="n">
         <v>1752325</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5824875831604</v>
+        <v>6.58248853683472</v>
       </c>
       <c r="H531" t="n">
         <v>1252149</v>
@@ -15797,7 +15797,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459943771362</v>
+        <v>6.64459991455078</v>
       </c>
       <c r="H532" t="n">
         <v>1780393</v>
@@ -15855,7 +15855,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751308441162</v>
+        <v>6.71751356124878</v>
       </c>
       <c r="H534" t="n">
         <v>1809327</v>
@@ -15913,7 +15913,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839651107788</v>
+        <v>6.62839698791504</v>
       </c>
       <c r="H536" t="n">
         <v>1797973</v>
@@ -15942,7 +15942,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080284118652</v>
+        <v>6.66080331802368</v>
       </c>
       <c r="H537" t="n">
         <v>956747</v>
@@ -15971,7 +15971,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320821762085</v>
+        <v>6.69320869445801</v>
       </c>
       <c r="H538" t="n">
         <v>1117605</v>
@@ -16029,7 +16029,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284372329712</v>
+        <v>7.14284324645996</v>
       </c>
       <c r="H540" t="n">
         <v>6833320</v>
@@ -16087,7 +16087,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525466918945</v>
+        <v>7.33525514602661</v>
       </c>
       <c r="H542" t="n">
         <v>2008354</v>
@@ -16116,7 +16116,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989944458008</v>
+        <v>7.43989992141724</v>
       </c>
       <c r="H543" t="n">
         <v>1957564</v>
@@ -16145,7 +16145,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403690338135</v>
+        <v>7.50403642654419</v>
       </c>
       <c r="H544" t="n">
         <v>1662762</v>
@@ -16261,7 +16261,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47027969360352</v>
+        <v>7.47028017044067</v>
       </c>
       <c r="H548" t="n">
         <v>2964098</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147382736206</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835147857666</v>
+        <v>7.8483510017395</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16406,7 +16406,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885927200317</v>
+        <v>7.88885879516602</v>
       </c>
       <c r="H553" t="n">
         <v>978481</v>
@@ -16551,7 +16551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228580474854</v>
+        <v>8.16228485107422</v>
       </c>
       <c r="H558" t="n">
         <v>1628712</v>
@@ -16783,7 +16783,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053375244141</v>
+        <v>8.82053470611572</v>
       </c>
       <c r="H566" t="n">
         <v>3617516</v>
@@ -16870,7 +16870,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="n">
         <v>1639116</v>
@@ -16899,7 +16899,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375762939453</v>
+        <v>9.34375667572021</v>
       </c>
       <c r="H570" t="n">
         <v>1437346</v>
@@ -16928,7 +16928,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114402770996</v>
+        <v>9.40114307403564</v>
       </c>
       <c r="H571" t="n">
         <v>1346272</v>
@@ -16986,7 +16986,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253986358643</v>
+        <v>9.51253890991211</v>
       </c>
       <c r="H573" t="n">
         <v>1118116</v>
@@ -17073,7 +17073,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840145111084</v>
+        <v>9.44840240478516</v>
       </c>
       <c r="H576" t="n">
         <v>2197272</v>
@@ -17131,7 +17131,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="n">
         <v>1873488</v>
@@ -17334,7 +17334,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297119140625</v>
+        <v>8.48297023773193</v>
       </c>
       <c r="H585" t="n">
         <v>1264193</v>
@@ -17537,7 +17537,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="n">
         <v>1799211</v>
@@ -17595,7 +17595,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="n">
         <v>1370145</v>
@@ -17624,7 +17624,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="n">
         <v>1343574</v>
@@ -17682,7 +17682,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="n">
         <v>2070634</v>
@@ -17711,7 +17711,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="n">
         <v>1111394</v>
@@ -17740,7 +17740,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="n">
         <v>1144101</v>
@@ -17769,7 +17769,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="n">
         <v>1299934</v>
@@ -17856,7 +17856,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="n">
         <v>4357376</v>
@@ -17943,7 +17943,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="n">
         <v>1233297</v>
@@ -18001,7 +18001,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="n">
         <v>943692</v>
@@ -18059,7 +18059,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="n">
         <v>1482029</v>
@@ -18146,7 +18146,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="n">
         <v>953411</v>
@@ -18233,7 +18233,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="n">
         <v>1263861</v>
@@ -18262,7 +18262,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="n">
         <v>1883401</v>
@@ -18349,7 +18349,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="n">
         <v>1949076</v>
@@ -18407,7 +18407,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="n">
         <v>2466372</v>
@@ -18436,7 +18436,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="n">
         <v>1875863</v>
@@ -18465,7 +18465,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="n">
         <v>2114723</v>
@@ -18494,7 +18494,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="n">
         <v>1003281</v>
@@ -18552,7 +18552,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="n">
         <v>2034035</v>
@@ -18639,7 +18639,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="n">
         <v>961522</v>
@@ -18668,7 +18668,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="n">
         <v>1340364</v>
@@ -18726,7 +18726,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="n">
         <v>1188311</v>
@@ -18755,7 +18755,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="n">
         <v>922139</v>
@@ -18842,7 +18842,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="n">
         <v>1104944</v>
@@ -18871,7 +18871,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="n">
         <v>1477565</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="n">
         <v>1299347</v>
@@ -19016,7 +19016,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="n">
         <v>1807666</v>
@@ -19103,7 +19103,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="n">
         <v>1668673</v>
@@ -19132,7 +19132,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="n">
         <v>1764822</v>
@@ -19161,7 +19161,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="n">
         <v>1235632</v>
@@ -19190,7 +19190,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="n">
         <v>1397538</v>
@@ -19219,7 +19219,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="n">
         <v>1895690</v>
@@ -19277,7 +19277,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="n">
         <v>1855485</v>
@@ -19364,7 +19364,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="n">
         <v>21113678</v>
@@ -19422,7 +19422,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="n">
         <v>4678338</v>
@@ -19451,7 +19451,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="n">
         <v>2619573</v>
@@ -19538,7 +19538,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="n">
         <v>2610988</v>
@@ -19567,7 +19567,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="n">
         <v>4162401</v>
@@ -19596,7 +19596,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="n">
         <v>4859349</v>
@@ -19712,7 +19712,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="n">
         <v>1004735</v>
@@ -19741,7 +19741,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="n">
         <v>997482</v>
@@ -19828,7 +19828,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="n">
         <v>2096737</v>
@@ -19944,7 +19944,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="n">
         <v>1440910</v>
@@ -20031,7 +20031,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="n">
         <v>1366723</v>
@@ -20060,7 +20060,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="n">
         <v>980480</v>
@@ -20176,7 +20176,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="n">
         <v>2106694</v>
@@ -20292,7 +20292,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="n">
         <v>1295054</v>
@@ -20466,7 +20466,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="n">
         <v>2462515</v>
@@ -20495,7 +20495,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="n">
         <v>1410849</v>
@@ -20524,7 +20524,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="n">
         <v>2437479</v>
@@ -20611,7 +20611,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="n">
         <v>3218967</v>
@@ -20640,7 +20640,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="n">
         <v>1981493</v>
@@ -20669,7 +20669,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="n">
         <v>2629183</v>
@@ -20756,7 +20756,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="n">
         <v>3178801</v>
@@ -20785,7 +20785,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="n">
         <v>3618036</v>
@@ -20901,7 +20901,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="n">
         <v>1498085</v>
@@ -20930,7 +20930,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="n">
         <v>2955864</v>
@@ -20959,7 +20959,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="n">
         <v>2554492</v>
@@ -21162,7 +21162,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="n">
         <v>2640643</v>
@@ -21220,7 +21220,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="n">
         <v>1962181</v>
@@ -21278,7 +21278,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="n">
         <v>3961916</v>
@@ -21336,7 +21336,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="n">
         <v>3582670</v>
@@ -21365,7 +21365,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="n">
         <v>2210569</v>
@@ -21423,7 +21423,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="n">
         <v>1858552</v>
@@ -21539,7 +21539,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="n">
         <v>8286642</v>
@@ -21626,7 +21626,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="n">
         <v>4138184</v>
@@ -21713,7 +21713,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="n">
         <v>2990029</v>
@@ -21742,7 +21742,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="n">
         <v>1630942</v>
@@ -21858,7 +21858,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="n">
         <v>1657610</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="n">
         <v>2906567</v>
@@ -22061,7 +22061,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="n">
         <v>1472605</v>
@@ -22119,7 +22119,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="n">
         <v>2428586</v>
@@ -22206,7 +22206,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="n">
         <v>1373245</v>
@@ -22235,7 +22235,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="n">
         <v>1786995</v>
@@ -22293,7 +22293,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="n">
         <v>2943745</v>
@@ -22322,7 +22322,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="n">
         <v>3277617</v>
@@ -22438,7 +22438,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="n">
         <v>2579512</v>
@@ -22467,7 +22467,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="n">
         <v>1442117</v>
@@ -22554,7 +22554,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="n">
         <v>2725833</v>
@@ -22902,7 +22902,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="n">
         <v>3966282</v>
@@ -22989,7 +22989,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="n">
         <v>2399106</v>
@@ -23192,7 +23192,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="n">
         <v>3020927</v>
@@ -23250,7 +23250,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="n">
         <v>2034103</v>
@@ -23279,7 +23279,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="n">
         <v>2487608</v>
@@ -23395,7 +23395,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="n">
         <v>4399432</v>
@@ -23656,7 +23656,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="n">
         <v>1560972</v>
@@ -23830,7 +23830,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="n">
         <v>3171229</v>
@@ -23859,7 +23859,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="n">
         <v>2951875</v>
@@ -23888,7 +23888,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="n">
         <v>2115144</v>
@@ -23946,7 +23946,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="n">
         <v>1560898</v>
@@ -24033,7 +24033,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="n">
         <v>3500840</v>
@@ -24120,7 +24120,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="n">
         <v>2998052</v>
@@ -24207,7 +24207,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="n">
         <v>1495955</v>
@@ -24236,7 +24236,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="n">
         <v>1503927</v>
@@ -24294,7 +24294,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="n">
         <v>1813430</v>
@@ -24352,7 +24352,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="n">
         <v>2267336</v>
@@ -24381,7 +24381,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="n">
         <v>1710958</v>
@@ -24526,7 +24526,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="n">
         <v>2682628</v>
@@ -24584,7 +24584,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="n">
         <v>2895890</v>
@@ -24613,7 +24613,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="n">
         <v>1823500</v>
@@ -35726,6 +35726,64 @@
         <v>309428</v>
       </c>
       <c r="I1219" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1220" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>14.3549995422363</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>957861</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1221" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>14.3549995422363</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="G1221" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="H1221" t="n">
+        <v>834996</v>
+      </c>
+      <c r="I1221" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418298721313</v>
+        <v>6.82418394088745</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23061037063599</v>
+        <v>7.23060941696167</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -543,7 +543,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705629348755</v>
+        <v>6.94705677032471</v>
       </c>
       <c r="H6" t="n">
         <v>11941139</v>
@@ -572,7 +572,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.85929012298584</v>
+        <v>6.859290599823</v>
       </c>
       <c r="H7" t="n">
         <v>6880124</v>
@@ -601,7 +601,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253858566284</v>
+        <v>6.8525390625</v>
       </c>
       <c r="H8" t="n">
         <v>4472971</v>
@@ -630,7 +630,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411249160767</v>
+        <v>7.24411201477051</v>
       </c>
       <c r="H9" t="n">
         <v>5804326</v>
@@ -659,7 +659,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040723800659</v>
+        <v>7.48040676116943</v>
       </c>
       <c r="H10" t="n">
         <v>7510382</v>
@@ -717,7 +717,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010162353516</v>
+        <v>7.19010257720947</v>
       </c>
       <c r="H12" t="n">
         <v>3165422</v>
@@ -746,7 +746,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132034301758</v>
       </c>
       <c r="H13" t="n">
         <v>2435262</v>
@@ -804,7 +804,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132034301758</v>
       </c>
       <c r="H15" t="n">
         <v>1535035</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731042861938</v>
+        <v>6.96730995178223</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -891,7 +891,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H18" t="n">
         <v>3251441</v>
@@ -920,7 +920,7 @@
         <v>9.625</v>
       </c>
       <c r="G19" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H19" t="n">
         <v>3546202</v>
@@ -949,7 +949,7 @@
         <v>9.625</v>
       </c>
       <c r="G20" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H20" t="n">
         <v>2484688</v>
@@ -978,7 +978,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956884384155</v>
+        <v>6.34956932067871</v>
       </c>
       <c r="H21" t="n">
         <v>1984383</v>
@@ -1065,7 +1065,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G24" t="n">
-        <v>6.29218339920044</v>
+        <v>6.29218292236328</v>
       </c>
       <c r="H24" t="n">
         <v>2785789</v>
@@ -1123,7 +1123,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>5.91411209106445</v>
+        <v>5.91411256790161</v>
       </c>
       <c r="H26" t="n">
         <v>3367791</v>
@@ -1181,7 +1181,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>5.69132041931152</v>
+        <v>5.69132089614868</v>
       </c>
       <c r="H28" t="n">
         <v>6011852</v>
@@ -1239,7 +1239,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238605499268</v>
+        <v>6.04238653182983</v>
       </c>
       <c r="H30" t="n">
         <v>4204295</v>
@@ -1268,7 +1268,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284284591675</v>
+        <v>5.81284332275391</v>
       </c>
       <c r="H31" t="n">
         <v>3316128</v>
@@ -1442,7 +1442,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637145996094</v>
+        <v>5.29637098312378</v>
       </c>
       <c r="H37" t="n">
         <v>2369088</v>
@@ -1500,7 +1500,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548246383667</v>
+        <v>5.22548294067383</v>
       </c>
       <c r="H39" t="n">
         <v>1845591</v>
@@ -1761,7 +1761,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H48" t="n">
         <v>3779682</v>
@@ -1790,7 +1790,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H49" t="n">
         <v>4270764</v>
@@ -1906,7 +1906,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533088684082</v>
+        <v>4.41533041000366</v>
       </c>
       <c r="H53" t="n">
         <v>2670255</v>
@@ -1964,7 +1964,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187833786011</v>
+        <v>4.67187881469727</v>
       </c>
       <c r="H55" t="n">
         <v>3556258</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347730636597</v>
+        <v>4.53347826004028</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2051,7 +2051,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H58" t="n">
         <v>2735170</v>
@@ -2080,7 +2080,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.40520334243774</v>
+        <v>4.4052038192749</v>
       </c>
       <c r="H59" t="n">
         <v>2749560</v>
@@ -2109,7 +2109,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.4119553565979</v>
+        <v>4.41195440292358</v>
       </c>
       <c r="H60" t="n">
         <v>1556296</v>
@@ -2138,7 +2138,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967004776001</v>
+        <v>4.22967052459717</v>
       </c>
       <c r="H61" t="n">
         <v>3912970</v>
@@ -2167,7 +2167,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667572021484</v>
+        <v>4.25667524337769</v>
       </c>
       <c r="H62" t="n">
         <v>3017576</v>
@@ -2370,7 +2370,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.6875433921814</v>
+        <v>3.68754363059998</v>
       </c>
       <c r="H69" t="n">
         <v>4125758</v>
@@ -2486,7 +2486,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>3.85497498512268</v>
+        <v>3.85497522354126</v>
       </c>
       <c r="H73" t="n">
         <v>2825138</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995505332947</v>
+        <v>3.87995481491089</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286336898804</v>
+        <v>3.79286360740662</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311702728271</v>
+        <v>3.81311678886414</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2892,7 +2892,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045751571655</v>
+        <v>3.76045775413513</v>
       </c>
       <c r="H87" t="n">
         <v>1422123</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619322776794</v>
+        <v>3.68619346618652</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437608718872</v>
+        <v>3.59437584877014</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496503829956</v>
+        <v>3.53496479988098</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395963668823</v>
+        <v>3.77396011352539</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240172386169</v>
+        <v>3.86240148544312</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3240,7 +3240,7 @@
         <v>5.5939998626709</v>
       </c>
       <c r="G99" t="n">
-        <v>3.77666020393372</v>
+        <v>3.77666044235229</v>
       </c>
       <c r="H99" t="n">
         <v>1773866</v>
@@ -3269,7 +3269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446766853333</v>
+        <v>3.8144679069519</v>
       </c>
       <c r="H100" t="n">
         <v>1355091</v>
@@ -3327,7 +3327,7 @@
         <v>5.72300004959106</v>
       </c>
       <c r="G102" t="n">
-        <v>3.86375188827515</v>
+        <v>3.86375164985657</v>
       </c>
       <c r="H102" t="n">
         <v>1984827</v>
@@ -3356,7 +3356,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H103" t="n">
         <v>2495941</v>
@@ -3414,7 +3414,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802055358887</v>
+        <v>4.09802103042603</v>
       </c>
       <c r="H105" t="n">
         <v>1510660</v>
@@ -3472,7 +3472,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G107" t="n">
-        <v>4.01430511474609</v>
+        <v>4.01430463790894</v>
       </c>
       <c r="H107" t="n">
         <v>1985267</v>
@@ -3501,7 +3501,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354827880859</v>
+        <v>4.11354875564575</v>
       </c>
       <c r="H108" t="n">
         <v>1792655</v>
@@ -3530,7 +3530,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12029981613159</v>
+        <v>4.12030029296875</v>
       </c>
       <c r="H109" t="n">
         <v>2831477</v>
@@ -3559,7 +3559,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406116485596</v>
+        <v>4.31406164169312</v>
       </c>
       <c r="H110" t="n">
         <v>3321010</v>
@@ -3588,7 +3588,7 @@
         <v>6.28900003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24587345123291</v>
+        <v>4.24587392807007</v>
       </c>
       <c r="H111" t="n">
         <v>2320257</v>
@@ -3617,7 +3617,7 @@
         <v>6.32600021362305</v>
       </c>
       <c r="G112" t="n">
-        <v>4.2708535194397</v>
+        <v>4.27085304260254</v>
       </c>
       <c r="H112" t="n">
         <v>1704261</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594927787781</v>
+        <v>3.98594975471497</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3675,7 +3675,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H114" t="n">
         <v>4779877</v>
@@ -3704,7 +3704,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761993408203</v>
+        <v>3.42761969566345</v>
       </c>
       <c r="H115" t="n">
         <v>4636137</v>
@@ -3733,7 +3733,7 @@
         <v>5.09700012207031</v>
       </c>
       <c r="G116" t="n">
-        <v>3.44112229347229</v>
+        <v>3.44112253189087</v>
       </c>
       <c r="H116" t="n">
         <v>2818082</v>
@@ -3791,7 +3791,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H118" t="n">
         <v>2452422</v>
@@ -3820,7 +3820,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302568435669</v>
+        <v>3.59302592277527</v>
       </c>
       <c r="H119" t="n">
         <v>4765434</v>
@@ -3849,7 +3849,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944169044495</v>
+        <v>3.67944192886353</v>
       </c>
       <c r="H120" t="n">
         <v>1265113</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.6571626663208</v>
+        <v>3.65716290473938</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3994,7 +3994,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091430664062</v>
+        <v>3.53091406822205</v>
       </c>
       <c r="H125" t="n">
         <v>1761818</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952332496643</v>
+        <v>3.57952308654785</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4052,7 +4052,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682251930237</v>
+        <v>3.57682275772095</v>
       </c>
       <c r="H127" t="n">
         <v>1305635</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.4039900302887</v>
+        <v>3.40399050712585</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4139,7 +4139,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082757949829</v>
+        <v>3.47082781791687</v>
       </c>
       <c r="H130" t="n">
         <v>985438</v>
@@ -4197,7 +4197,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.20989108085632</v>
+        <v>3.2098913192749</v>
       </c>
       <c r="H132" t="n">
         <v>3036596</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044709205627</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4255,7 +4255,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724430084229</v>
+        <v>3.55724406242371</v>
       </c>
       <c r="H134" t="n">
         <v>2393460</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.4566502571106</v>
+        <v>3.45665001869202</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4342,7 +4342,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>3.34187841415405</v>
+        <v>3.34187865257263</v>
       </c>
       <c r="H137" t="n">
         <v>1981838</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326684951782</v>
+        <v>3.2132670879364</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4458,7 +4458,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948274612427</v>
+        <v>3.62948298454285</v>
       </c>
       <c r="H141" t="n">
         <v>2254990</v>
@@ -4545,7 +4545,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813234329224</v>
+        <v>3.62813210487366</v>
       </c>
       <c r="H144" t="n">
         <v>1162846</v>
@@ -4632,7 +4632,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319842338562</v>
+        <v>3.71319818496704</v>
       </c>
       <c r="H147" t="n">
         <v>2599217</v>
@@ -4661,7 +4661,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894479751587</v>
+        <v>3.95894455909729</v>
       </c>
       <c r="H148" t="n">
         <v>4041376</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290951728821</v>
+        <v>3.90290904045105</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4922,7 +4922,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G157" t="n">
-        <v>4.02510690689087</v>
+        <v>4.02510738372803</v>
       </c>
       <c r="H157" t="n">
         <v>1266112</v>
@@ -5009,7 +5009,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126901626587</v>
+        <v>4.09126949310303</v>
       </c>
       <c r="H160" t="n">
         <v>1170223</v>
@@ -5067,7 +5067,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067521095276</v>
+        <v>3.99067544937134</v>
       </c>
       <c r="H162" t="n">
         <v>836698</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370573997498</v>
+        <v>3.75370621681213</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5212,7 +5212,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539095878601</v>
+        <v>3.67539119720459</v>
       </c>
       <c r="H167" t="n">
         <v>1508487</v>
@@ -5270,7 +5270,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648261070251</v>
+        <v>3.49648284912109</v>
       </c>
       <c r="H169" t="n">
         <v>1228962</v>
@@ -5444,7 +5444,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846254348755</v>
+        <v>3.38846230506897</v>
       </c>
       <c r="H175" t="n">
         <v>951917</v>
@@ -5473,7 +5473,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.4168176651001</v>
+        <v>3.41681790351868</v>
       </c>
       <c r="H176" t="n">
         <v>743828</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538101196289</v>
+        <v>3.35538077354431</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5531,7 +5531,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086839675903</v>
+        <v>3.42086815834045</v>
       </c>
       <c r="H178" t="n">
         <v>1113895</v>
@@ -5560,7 +5560,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H179" t="n">
         <v>1218078</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044709205627</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5647,7 +5647,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086839675903</v>
+        <v>3.42086815834045</v>
       </c>
       <c r="H182" t="n">
         <v>748112</v>
@@ -5705,7 +5705,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437075614929</v>
+        <v>3.43437099456787</v>
       </c>
       <c r="H184" t="n">
         <v>1118182</v>
@@ -5792,7 +5792,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>3.36213254928589</v>
+        <v>3.36213231086731</v>
       </c>
       <c r="H187" t="n">
         <v>1010793</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837350845337</v>
+        <v>3.24837374687195</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116032600403</v>
+        <v>3.31116008758545</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -5966,7 +5966,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786826133728</v>
+        <v>3.28786849975586</v>
       </c>
       <c r="H193" t="n">
         <v>1635754</v>
@@ -6082,7 +6082,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340131759644</v>
+        <v>3.46340155601501</v>
       </c>
       <c r="H197" t="n">
         <v>1022230</v>
@@ -6140,7 +6140,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>3.48027968406677</v>
+        <v>3.48027992248535</v>
       </c>
       <c r="H199" t="n">
         <v>734627</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50796008110046</v>
+        <v>3.50795984268188</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6285,7 +6285,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51065993309021</v>
+        <v>3.51066017150879</v>
       </c>
       <c r="H204" t="n">
         <v>601405</v>
@@ -6314,7 +6314,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.608553647995</v>
+        <v>3.60855340957642</v>
       </c>
       <c r="H205" t="n">
         <v>1822628</v>
@@ -6343,7 +6343,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842681884766</v>
+        <v>3.59842705726624</v>
       </c>
       <c r="H206" t="n">
         <v>578241</v>
@@ -6372,7 +6372,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.6240816116333</v>
+        <v>3.62408185005188</v>
       </c>
       <c r="H207" t="n">
         <v>1039336</v>
@@ -6546,7 +6546,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577192306519</v>
+        <v>3.70577216148376</v>
       </c>
       <c r="H213" t="n">
         <v>1086736</v>
@@ -6575,7 +6575,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H214" t="n">
         <v>561510</v>
@@ -6604,7 +6604,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.72400045394897</v>
+        <v>3.7240002155304</v>
       </c>
       <c r="H215" t="n">
         <v>771072</v>
@@ -6633,7 +6633,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079257011414</v>
+        <v>3.68079233169556</v>
       </c>
       <c r="H216" t="n">
         <v>710760</v>
@@ -6662,7 +6662,7 @@
         <v>5.37900018692017</v>
       </c>
       <c r="G217" t="n">
-        <v>3.63150835037231</v>
+        <v>3.63150787353516</v>
       </c>
       <c r="H217" t="n">
         <v>1446118</v>
@@ -6691,7 +6691,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450824737549</v>
+        <v>3.76450800895691</v>
       </c>
       <c r="H218" t="n">
         <v>1097994</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6749,7 +6749,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324942588806</v>
       </c>
       <c r="H220" t="n">
         <v>1345223</v>
@@ -6778,7 +6778,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527988433838</v>
+        <v>4.14527940750122</v>
       </c>
       <c r="H221" t="n">
         <v>3310511</v>
@@ -6865,7 +6865,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19928979873657</v>
+        <v>4.19928932189941</v>
       </c>
       <c r="H224" t="n">
         <v>1230545</v>
@@ -6894,7 +6894,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916320800781</v>
+        <v>4.18916273117065</v>
       </c>
       <c r="H225" t="n">
         <v>1148359</v>
@@ -6923,7 +6923,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620826721191</v>
+        <v>4.16620874404907</v>
       </c>
       <c r="H226" t="n">
         <v>1220830</v>
@@ -6981,7 +6981,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H228" t="n">
         <v>1114284</v>
@@ -7068,7 +7068,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106174468994</v>
+        <v>4.18106126785278</v>
       </c>
       <c r="H231" t="n">
         <v>540433</v>
@@ -7097,7 +7097,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H232" t="n">
         <v>341527</v>
@@ -7126,7 +7126,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629499435425</v>
+        <v>4.22629547119141</v>
       </c>
       <c r="H233" t="n">
         <v>709890</v>
@@ -7155,7 +7155,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840732574463</v>
+        <v>4.28840684890747</v>
       </c>
       <c r="H234" t="n">
         <v>1390641</v>
@@ -7213,7 +7213,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G236" t="n">
-        <v>4.33566570281982</v>
+        <v>4.33566522598267</v>
       </c>
       <c r="H236" t="n">
         <v>986833</v>
@@ -7242,7 +7242,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562440872192</v>
+        <v>4.38562488555908</v>
       </c>
       <c r="H237" t="n">
         <v>1118846</v>
@@ -7271,7 +7271,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>4.36807155609131</v>
+        <v>4.36807107925415</v>
       </c>
       <c r="H238" t="n">
         <v>855642</v>
@@ -7329,7 +7329,7 @@
         <v>6.31300020217896</v>
       </c>
       <c r="G240" t="n">
-        <v>4.26207637786865</v>
+        <v>4.26207685470581</v>
       </c>
       <c r="H240" t="n">
         <v>1219252</v>
@@ -7358,7 +7358,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H241" t="n">
         <v>1305794</v>
@@ -7416,7 +7416,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H243" t="n">
         <v>1010763</v>
@@ -7445,7 +7445,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633581161499</v>
+        <v>4.17633533477783</v>
       </c>
       <c r="H244" t="n">
         <v>568662</v>
@@ -7561,7 +7561,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H248" t="n">
         <v>911894</v>
@@ -7590,7 +7590,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.0264573097229</v>
+        <v>4.02645778656006</v>
       </c>
       <c r="H249" t="n">
         <v>795631</v>
@@ -7619,7 +7619,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H250" t="n">
         <v>1305048</v>
@@ -7648,7 +7648,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H251" t="n">
         <v>1142347</v>
@@ -7677,7 +7677,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033020973206</v>
+        <v>3.75033044815063</v>
       </c>
       <c r="H252" t="n">
         <v>2220991</v>
@@ -7706,7 +7706,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459449768066</v>
+        <v>3.82459402084351</v>
       </c>
       <c r="H253" t="n">
         <v>1270112</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771613121033</v>
+        <v>3.80771636962891</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73682808876038</v>
+        <v>3.73682761192322</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7793,7 +7793,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948760032654</v>
+        <v>3.78948783874512</v>
       </c>
       <c r="H256" t="n">
         <v>792824</v>
@@ -7822,7 +7822,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G257" t="n">
-        <v>3.7523558139801</v>
+        <v>3.75235605239868</v>
       </c>
       <c r="H257" t="n">
         <v>475168</v>
@@ -7938,7 +7938,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434569358826</v>
       </c>
       <c r="H261" t="n">
         <v>1652373</v>
@@ -7967,7 +7967,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G262" t="n">
-        <v>4.06156396865845</v>
+        <v>4.06156349182129</v>
       </c>
       <c r="H262" t="n">
         <v>1735246</v>
@@ -8025,7 +8025,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604133605957</v>
+        <v>4.20604085922241</v>
       </c>
       <c r="H264" t="n">
         <v>1003317</v>
@@ -8054,7 +8054,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478179931641</v>
+        <v>4.42478227615356</v>
       </c>
       <c r="H265" t="n">
         <v>3181061</v>
@@ -8083,7 +8083,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>4.61786842346191</v>
+        <v>4.61786890029907</v>
       </c>
       <c r="H266" t="n">
         <v>4637628</v>
@@ -8141,7 +8141,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605613708496</v>
+        <v>4.68605661392212</v>
       </c>
       <c r="H268" t="n">
         <v>2146613</v>
@@ -8228,7 +8228,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.7353401184082</v>
+        <v>4.73534059524536</v>
       </c>
       <c r="H271" t="n">
         <v>2895765</v>
@@ -8286,7 +8286,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>4.90817308425903</v>
+        <v>4.90817356109619</v>
       </c>
       <c r="H273" t="n">
         <v>2063203</v>
@@ -8373,7 +8373,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543703079224</v>
+        <v>5.11543750762939</v>
       </c>
       <c r="H276" t="n">
         <v>1864510</v>
@@ -8402,7 +8402,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>5.11408662796021</v>
+        <v>5.11408710479736</v>
       </c>
       <c r="H277" t="n">
         <v>2333721</v>
@@ -8634,7 +8634,7 @@
         <v>7.48199987411499</v>
       </c>
       <c r="G285" t="n">
-        <v>5.05130004882812</v>
+        <v>5.05129957199097</v>
       </c>
       <c r="H285" t="n">
         <v>1023863</v>
@@ -8663,7 +8663,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902635574341</v>
+        <v>5.18902587890625</v>
       </c>
       <c r="H286" t="n">
         <v>2462672</v>
@@ -8750,7 +8750,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370073318481</v>
+        <v>6.25370121002197</v>
       </c>
       <c r="H289" t="n">
         <v>5659371</v>
@@ -8779,7 +8779,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G290" t="n">
-        <v>6.17943716049194</v>
+        <v>6.1794376373291</v>
       </c>
       <c r="H290" t="n">
         <v>1832776</v>
@@ -8837,7 +8837,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707626342773</v>
+        <v>6.25707674026489</v>
       </c>
       <c r="H292" t="n">
         <v>1429447</v>
@@ -8924,7 +8924,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449281692505</v>
+        <v>5.94449377059937</v>
       </c>
       <c r="H295" t="n">
         <v>1414060</v>
@@ -9011,7 +9011,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926513671875</v>
+        <v>6.05926465988159</v>
       </c>
       <c r="H298" t="n">
         <v>834113</v>
@@ -9040,7 +9040,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293466567993</v>
+        <v>6.03293418884277</v>
       </c>
       <c r="H299" t="n">
         <v>974549</v>
@@ -9098,7 +9098,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698539733887</v>
       </c>
       <c r="H301" t="n">
         <v>740488</v>
@@ -9185,7 +9185,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124992370605</v>
       </c>
       <c r="H304" t="n">
         <v>1512205</v>
@@ -9214,7 +9214,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.19361448287964</v>
+        <v>6.1936149597168</v>
       </c>
       <c r="H305" t="n">
         <v>1343595</v>
@@ -9243,7 +9243,7 @@
         <v>9.07299995422363</v>
       </c>
       <c r="G306" t="n">
-        <v>6.12542724609375</v>
+        <v>6.12542676925659</v>
       </c>
       <c r="H306" t="n">
         <v>1336985</v>
@@ -9272,7 +9272,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441213607788</v>
+        <v>6.04441165924072</v>
       </c>
       <c r="H307" t="n">
         <v>1036237</v>
@@ -9301,7 +9301,7 @@
         <v>8.50899982452393</v>
       </c>
       <c r="G308" t="n">
-        <v>5.7446551322937</v>
+        <v>5.74465608596802</v>
       </c>
       <c r="H308" t="n">
         <v>1509651</v>
@@ -9359,7 +9359,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836595535278</v>
+        <v>5.66836643218994</v>
       </c>
       <c r="H310" t="n">
         <v>1335804</v>
@@ -9475,7 +9475,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.8661789894104</v>
+        <v>5.86617803573608</v>
       </c>
       <c r="H314" t="n">
         <v>816021</v>
@@ -9504,7 +9504,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977245330811</v>
+        <v>6.09977197647095</v>
       </c>
       <c r="H315" t="n">
         <v>1294330</v>
@@ -9620,7 +9620,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390434265137</v>
+        <v>6.00390386581421</v>
       </c>
       <c r="H319" t="n">
         <v>742878</v>
@@ -9649,7 +9649,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G320" t="n">
-        <v>5.91411209106445</v>
+        <v>5.91411256790161</v>
       </c>
       <c r="H320" t="n">
         <v>1043632</v>
@@ -9678,7 +9678,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748857498169</v>
+        <v>5.91748809814453</v>
       </c>
       <c r="H321" t="n">
         <v>905026</v>
@@ -9736,7 +9736,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047828674316</v>
+        <v>5.73047733306885</v>
       </c>
       <c r="H323" t="n">
         <v>1626293</v>
@@ -9765,7 +9765,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H324" t="n">
         <v>1282373</v>
@@ -9823,7 +9823,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.30649852752686</v>
+        <v>5.3064980506897</v>
       </c>
       <c r="H326" t="n">
         <v>1268089</v>
@@ -9881,7 +9881,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G328" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H328" t="n">
         <v>2329069</v>
@@ -9968,7 +9968,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G331" t="n">
-        <v>5.5630464553833</v>
+        <v>5.56304597854614</v>
       </c>
       <c r="H331" t="n">
         <v>1403612</v>
@@ -9997,7 +9997,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920904159546</v>
+        <v>5.62920951843262</v>
       </c>
       <c r="H332" t="n">
         <v>2007066</v>
@@ -10084,7 +10084,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672155380249</v>
+        <v>5.69672107696533</v>
       </c>
       <c r="H335" t="n">
         <v>1097585</v>
@@ -10258,7 +10258,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30784845352173</v>
+        <v>5.30784797668457</v>
       </c>
       <c r="H341" t="n">
         <v>1370858</v>
@@ -10287,7 +10287,7 @@
         <v>7.86399984359741</v>
       </c>
       <c r="G342" t="n">
-        <v>5.3091983795166</v>
+        <v>5.30919885635376</v>
       </c>
       <c r="H342" t="n">
         <v>806647</v>
@@ -10316,7 +10316,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G343" t="n">
-        <v>5.14581823348999</v>
+        <v>5.14581775665283</v>
       </c>
       <c r="H343" t="n">
         <v>1174384</v>
@@ -10374,7 +10374,7 @@
         <v>7.93599987030029</v>
       </c>
       <c r="G345" t="n">
-        <v>5.35780763626099</v>
+        <v>5.35780811309814</v>
       </c>
       <c r="H345" t="n">
         <v>557874</v>
@@ -10432,7 +10432,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751363754272</v>
+        <v>5.38751316070557</v>
       </c>
       <c r="H347" t="n">
         <v>1047427</v>
@@ -10490,7 +10490,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G349" t="n">
-        <v>4.95948314666748</v>
+        <v>4.95948266983032</v>
       </c>
       <c r="H349" t="n">
         <v>3108681</v>
@@ -10519,7 +10519,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003128051758</v>
+        <v>4.95003080368042</v>
       </c>
       <c r="H350" t="n">
         <v>1343262</v>
@@ -10548,7 +10548,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G351" t="n">
-        <v>4.90547275543213</v>
+        <v>4.90547227859497</v>
       </c>
       <c r="H351" t="n">
         <v>1070151</v>
@@ -10577,7 +10577,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809192657471</v>
+        <v>5.00809240341187</v>
       </c>
       <c r="H352" t="n">
         <v>1123756</v>
@@ -10635,7 +10635,7 @@
         <v>7.63199996948242</v>
       </c>
       <c r="G354" t="n">
-        <v>5.15256929397583</v>
+        <v>5.15256881713867</v>
       </c>
       <c r="H354" t="n">
         <v>1115525</v>
@@ -10693,7 +10693,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910751342773</v>
+        <v>5.08910703659058</v>
       </c>
       <c r="H356" t="n">
         <v>721988</v>
@@ -10722,7 +10722,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G357" t="n">
-        <v>4.90547275543213</v>
+        <v>4.90547227859497</v>
       </c>
       <c r="H357" t="n">
         <v>1284720</v>
@@ -10780,7 +10780,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.91492462158203</v>
+        <v>4.91492509841919</v>
       </c>
       <c r="H359" t="n">
         <v>837846</v>
@@ -10896,7 +10896,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.76774644851685</v>
+        <v>4.767746925354</v>
       </c>
       <c r="H363" t="n">
         <v>1027763</v>
@@ -11041,7 +11041,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543193817139</v>
+        <v>4.95543241500854</v>
       </c>
       <c r="H368" t="n">
         <v>1136830</v>
@@ -11157,7 +11157,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G372" t="n">
-        <v>5.21198034286499</v>
+        <v>5.21197986602783</v>
       </c>
       <c r="H372" t="n">
         <v>1028465</v>
@@ -11215,7 +11215,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26463985443115</v>
+        <v>5.26464033126831</v>
       </c>
       <c r="H374" t="n">
         <v>1589421</v>
@@ -11244,7 +11244,7 @@
         <v>7.82600021362305</v>
       </c>
       <c r="G375" t="n">
-        <v>5.28354406356812</v>
+        <v>5.28354358673096</v>
       </c>
       <c r="H375" t="n">
         <v>584900</v>
@@ -11273,7 +11273,7 @@
         <v>7.81400012969971</v>
       </c>
       <c r="G376" t="n">
-        <v>5.27544260025024</v>
+        <v>5.27544212341309</v>
       </c>
       <c r="H376" t="n">
         <v>879423</v>
@@ -11418,7 +11418,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080291748047</v>
+        <v>5.33080244064331</v>
       </c>
       <c r="H381" t="n">
         <v>1027240</v>
@@ -11447,7 +11447,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379724502563</v>
+        <v>5.30379772186279</v>
       </c>
       <c r="H382" t="n">
         <v>909012</v>
@@ -11505,7 +11505,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114839553833</v>
+        <v>5.57114791870117</v>
       </c>
       <c r="H384" t="n">
         <v>1867030</v>
@@ -11534,7 +11534,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578712463379</v>
+        <v>5.51578760147095</v>
       </c>
       <c r="H385" t="n">
         <v>1237649</v>
@@ -11563,7 +11563,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148321151733</v>
+        <v>5.49148273468018</v>
       </c>
       <c r="H386" t="n">
         <v>1186915</v>
@@ -11592,7 +11592,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H387" t="n">
         <v>1194785</v>
@@ -11650,7 +11650,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907735824585</v>
+        <v>5.45907688140869</v>
       </c>
       <c r="H389" t="n">
         <v>1552098</v>
@@ -11679,7 +11679,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.4172191619873</v>
+        <v>5.41721868515015</v>
       </c>
       <c r="H390" t="n">
         <v>610844</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.61975717544556</v>
+        <v>5.61975765228271</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -11766,7 +11766,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562480926514</v>
+        <v>5.71562528610229</v>
       </c>
       <c r="H393" t="n">
         <v>1448265</v>
@@ -11795,7 +11795,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H394" t="n">
         <v>1342906</v>
@@ -11824,7 +11824,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376756668091</v>
+        <v>5.67376708984375</v>
       </c>
       <c r="H395" t="n">
         <v>1175604</v>
@@ -11882,7 +11882,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G397" t="n">
-        <v>5.60355424880981</v>
+        <v>5.60355472564697</v>
       </c>
       <c r="H397" t="n">
         <v>1898927</v>
@@ -11911,7 +11911,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.56034564971924</v>
+        <v>5.5603461265564</v>
       </c>
       <c r="H398" t="n">
         <v>1662385</v>
@@ -12027,7 +12027,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768613815308</v>
+        <v>5.50768566131592</v>
       </c>
       <c r="H402" t="n">
         <v>890149</v>
@@ -12143,7 +12143,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951322555542</v>
+        <v>5.91951274871826</v>
       </c>
       <c r="H406" t="n">
         <v>1665434</v>
@@ -12201,7 +12201,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G408" t="n">
-        <v>6.56088399887085</v>
+        <v>6.56088447570801</v>
       </c>
       <c r="H408" t="n">
         <v>3234067</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873180389404</v>
+        <v>6.54873132705688</v>
       </c>
       <c r="H409" t="n">
         <v>2733714</v>
@@ -12288,7 +12288,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H411" t="n">
         <v>929420</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758453369141</v>
+        <v>6.29758501052856</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12375,7 +12375,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665058135986</v>
+        <v>6.11665105819702</v>
       </c>
       <c r="H414" t="n">
         <v>900855</v>
@@ -12404,7 +12404,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H415" t="n">
         <v>1271542</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044765472412</v>
+        <v>6.10044813156128</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12462,7 +12462,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.97487449645996</v>
+        <v>5.9748740196228</v>
       </c>
       <c r="H417" t="n">
         <v>839338</v>
@@ -12491,7 +12491,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436574935913</v>
+        <v>5.93436670303345</v>
       </c>
       <c r="H418" t="n">
         <v>1220620</v>
@@ -12520,7 +12520,7 @@
         <v>8.63199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>5.82769584655762</v>
+        <v>5.82769632339478</v>
       </c>
       <c r="H419" t="n">
         <v>1609287</v>
@@ -12549,7 +12549,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.82634592056274</v>
+        <v>5.8263463973999</v>
       </c>
       <c r="H420" t="n">
         <v>1409991</v>
@@ -12607,7 +12607,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>5.59005117416382</v>
+        <v>5.59005165100098</v>
       </c>
       <c r="H422" t="n">
         <v>2610359</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461988449097</v>
+        <v>5.95461940765381</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12694,7 +12694,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457906723022</v>
+        <v>6.00457954406738</v>
       </c>
       <c r="H425" t="n">
         <v>1029644</v>
@@ -12723,7 +12723,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97757434844971</v>
+        <v>5.97757387161255</v>
       </c>
       <c r="H426" t="n">
         <v>685213</v>
@@ -12752,7 +12752,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631576538086</v>
+        <v>6.19631624221802</v>
       </c>
       <c r="H427" t="n">
         <v>1981669</v>
@@ -12781,7 +12781,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16930961608887</v>
+        <v>6.16931009292603</v>
       </c>
       <c r="H428" t="n">
         <v>729053</v>
@@ -12810,7 +12810,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124992370605</v>
       </c>
       <c r="H429" t="n">
         <v>462036</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002101898193</v>
+        <v>5.96002149581909</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -12926,7 +12926,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698539733887</v>
       </c>
       <c r="H433" t="n">
         <v>771857</v>
@@ -12955,7 +12955,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479238510132</v>
+        <v>6.07479286193848</v>
       </c>
       <c r="H434" t="n">
         <v>513724</v>
@@ -12984,7 +12984,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023433685303</v>
+        <v>6.03023386001587</v>
       </c>
       <c r="H435" t="n">
         <v>1829397</v>
@@ -13042,7 +13042,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289384841919</v>
+        <v>6.08289432525635</v>
       </c>
       <c r="H437" t="n">
         <v>877361</v>
@@ -13100,7 +13100,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G439" t="n">
-        <v>5.97352313995361</v>
+        <v>5.97352361679077</v>
       </c>
       <c r="H439" t="n">
         <v>745131</v>
@@ -13158,7 +13158,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H441" t="n">
         <v>1296803</v>
@@ -13303,7 +13303,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770650863647</v>
+        <v>6.14770603179932</v>
       </c>
       <c r="H446" t="n">
         <v>971388</v>
@@ -13419,7 +13419,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.9303150177002</v>
+        <v>5.93031597137451</v>
       </c>
       <c r="H450" t="n">
         <v>988269</v>
@@ -13448,7 +13448,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G451" t="n">
-        <v>5.97352313995361</v>
+        <v>5.97352361679077</v>
       </c>
       <c r="H451" t="n">
         <v>722064</v>
@@ -13535,7 +13535,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613260269165</v>
+        <v>5.75613307952881</v>
       </c>
       <c r="H454" t="n">
         <v>1565076</v>
@@ -13651,7 +13651,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301630020142</v>
+        <v>5.93301582336426</v>
       </c>
       <c r="H458" t="n">
         <v>867989</v>
@@ -13709,7 +13709,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984804153442</v>
+        <v>5.83984851837158</v>
       </c>
       <c r="H460" t="n">
         <v>2271949</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748252868652</v>
+        <v>5.75748300552368</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13767,7 +13767,7 @@
         <v>8.34799957275391</v>
       </c>
       <c r="G462" t="n">
-        <v>5.63595962524414</v>
+        <v>5.6359601020813</v>
       </c>
       <c r="H462" t="n">
         <v>1243781</v>
@@ -13796,7 +13796,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401056289673</v>
+        <v>5.37401103973389</v>
       </c>
       <c r="H463" t="n">
         <v>2564625</v>
@@ -13883,7 +13883,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409219741821</v>
+        <v>5.27409172058105</v>
       </c>
       <c r="H466" t="n">
         <v>851531</v>
@@ -13912,7 +13912,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700584411621</v>
+        <v>5.34700536727905</v>
       </c>
       <c r="H467" t="n">
         <v>1182375</v>
@@ -13941,7 +13941,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806177139282</v>
+        <v>5.37806129455566</v>
       </c>
       <c r="H468" t="n">
         <v>921952</v>
@@ -13970,7 +13970,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H469" t="n">
         <v>812307</v>
@@ -13999,7 +13999,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36996030807495</v>
+        <v>5.36995983123779</v>
       </c>
       <c r="H470" t="n">
         <v>1735396</v>
@@ -14086,7 +14086,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.8285083770752</v>
+        <v>4.82850790023804</v>
       </c>
       <c r="H473" t="n">
         <v>4573066</v>
@@ -14202,7 +14202,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.8501124382019</v>
+        <v>4.85011196136475</v>
       </c>
       <c r="H477" t="n">
         <v>2148643</v>
@@ -14231,7 +14231,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669052124023</v>
+        <v>4.73669099807739</v>
       </c>
       <c r="H478" t="n">
         <v>2197891</v>
@@ -14289,7 +14289,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525991439819</v>
+        <v>4.83525943756104</v>
       </c>
       <c r="H480" t="n">
         <v>1773638</v>
@@ -14318,7 +14318,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893453598022</v>
+        <v>4.96893501281738</v>
       </c>
       <c r="H481" t="n">
         <v>3692477</v>
@@ -14376,7 +14376,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G483" t="n">
-        <v>4.93922901153564</v>
+        <v>4.9392294883728</v>
       </c>
       <c r="H483" t="n">
         <v>1326009</v>
@@ -14492,7 +14492,7 @@
         <v>7.23199987411499</v>
       </c>
       <c r="G487" t="n">
-        <v>4.88251829147339</v>
+        <v>4.88251781463623</v>
       </c>
       <c r="H487" t="n">
         <v>1282850</v>
@@ -14521,7 +14521,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.92302560806274</v>
+        <v>4.9230260848999</v>
       </c>
       <c r="H488" t="n">
         <v>1062819</v>
@@ -14608,7 +14608,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G491" t="n">
-        <v>5.04319858551025</v>
+        <v>5.0431981086731</v>
       </c>
       <c r="H491" t="n">
         <v>2706817</v>
@@ -14666,7 +14666,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.1417670249939</v>
+        <v>5.14176750183105</v>
       </c>
       <c r="H493" t="n">
         <v>2819991</v>
@@ -14695,7 +14695,7 @@
         <v>7.57600021362305</v>
       </c>
       <c r="G494" t="n">
-        <v>5.11476230621338</v>
+        <v>5.11476182937622</v>
       </c>
       <c r="H494" t="n">
         <v>1479490</v>
@@ -14753,7 +14753,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H496" t="n">
         <v>2796261</v>
@@ -14782,7 +14782,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.3132495880127</v>
+        <v>5.31324911117554</v>
       </c>
       <c r="H497" t="n">
         <v>1593539</v>
@@ -14811,7 +14811,7 @@
         <v>7.93599987030029</v>
       </c>
       <c r="G498" t="n">
-        <v>5.35780763626099</v>
+        <v>5.35780811309814</v>
       </c>
       <c r="H498" t="n">
         <v>1351028</v>
@@ -14840,7 +14840,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G499" t="n">
-        <v>5.33350324630737</v>
+        <v>5.33350372314453</v>
       </c>
       <c r="H499" t="n">
         <v>999232</v>
@@ -14898,7 +14898,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847726821899</v>
+        <v>5.19847774505615</v>
       </c>
       <c r="H501" t="n">
         <v>2160367</v>
@@ -14927,7 +14927,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26463985443115</v>
+        <v>5.26464033126831</v>
       </c>
       <c r="H502" t="n">
         <v>2617256</v>
@@ -14956,7 +14956,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565591812134</v>
+        <v>5.34565544128418</v>
       </c>
       <c r="H503" t="n">
         <v>2644025</v>
@@ -15072,7 +15072,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G507" t="n">
-        <v>5.40641689300537</v>
+        <v>5.40641736984253</v>
       </c>
       <c r="H507" t="n">
         <v>1345581</v>
@@ -15101,7 +15101,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076162338257</v>
+        <v>5.38076210021973</v>
       </c>
       <c r="H508" t="n">
         <v>821721</v>
@@ -15130,7 +15130,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H509" t="n">
         <v>1443560</v>
@@ -15188,7 +15188,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958467483521</v>
+        <v>5.49958419799805</v>
       </c>
       <c r="H511" t="n">
         <v>928002</v>
@@ -15246,7 +15246,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G513" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H513" t="n">
         <v>1395334</v>
@@ -15333,7 +15333,7 @@
         <v>8.45600032806396</v>
       </c>
       <c r="G516" t="n">
-        <v>5.7088737487793</v>
+        <v>5.70887422561646</v>
       </c>
       <c r="H516" t="n">
         <v>1752740</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791982650757</v>
+        <v>6.21791934967041</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.3772497177124</v>
+        <v>6.37724924087524</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15478,7 +15478,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.37454986572266</v>
+        <v>6.3745493888855</v>
       </c>
       <c r="H521" t="n">
         <v>4282126</v>
@@ -15507,7 +15507,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H522" t="n">
         <v>2967550</v>
@@ -15536,7 +15536,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492454528809</v>
+        <v>6.24492502212524</v>
       </c>
       <c r="H523" t="n">
         <v>1934023</v>
@@ -15565,7 +15565,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H524" t="n">
         <v>1721895</v>
@@ -15623,7 +15623,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H526" t="n">
         <v>994506</v>
@@ -15652,7 +15652,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H527" t="n">
         <v>1251679</v>
@@ -15681,7 +15681,7 @@
         <v>9.53800010681152</v>
       </c>
       <c r="G528" t="n">
-        <v>6.43936157226562</v>
+        <v>6.43936109542847</v>
       </c>
       <c r="H528" t="n">
         <v>1494558</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.42450761795044</v>
+        <v>6.42450857162476</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15739,7 +15739,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527002334595</v>
+        <v>6.48526954650879</v>
       </c>
       <c r="H530" t="n">
         <v>1752325</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.58248853683472</v>
+        <v>6.5824875831604</v>
       </c>
       <c r="H531" t="n">
         <v>1252149</v>
@@ -15797,7 +15797,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459991455078</v>
+        <v>6.64459943771362</v>
       </c>
       <c r="H532" t="n">
         <v>1780393</v>
@@ -15855,7 +15855,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751356124878</v>
+        <v>6.71751308441162</v>
       </c>
       <c r="H534" t="n">
         <v>1809327</v>
@@ -15913,7 +15913,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839698791504</v>
+        <v>6.62839651107788</v>
       </c>
       <c r="H536" t="n">
         <v>1797973</v>
@@ -15971,7 +15971,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320869445801</v>
+        <v>6.69320917129517</v>
       </c>
       <c r="H538" t="n">
         <v>1117605</v>
@@ -16000,7 +16000,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G539" t="n">
-        <v>6.62974739074707</v>
+        <v>6.62974643707275</v>
       </c>
       <c r="H539" t="n">
         <v>1373635</v>
@@ -16087,7 +16087,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525514602661</v>
+        <v>7.33525466918945</v>
       </c>
       <c r="H542" t="n">
         <v>2008354</v>
@@ -16116,7 +16116,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989992141724</v>
+        <v>7.43989944458008</v>
       </c>
       <c r="H543" t="n">
         <v>1957564</v>
@@ -16145,7 +16145,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403642654419</v>
+        <v>7.50403690338135</v>
       </c>
       <c r="H544" t="n">
         <v>1662762</v>
@@ -16232,7 +16232,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G547" t="n">
-        <v>7.11246299743652</v>
+        <v>7.11246204376221</v>
       </c>
       <c r="H547" t="n">
         <v>2425730</v>
@@ -16261,7 +16261,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47028017044067</v>
+        <v>7.47027969360352</v>
       </c>
       <c r="H548" t="n">
         <v>2964098</v>
@@ -16290,7 +16290,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.450026512146</v>
+        <v>7.45002603530884</v>
       </c>
       <c r="H549" t="n">
         <v>2293340</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.83147382736206</v>
+        <v>7.8314733505249</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.8483510017395</v>
+        <v>7.84835052490234</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16406,7 +16406,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885879516602</v>
+        <v>7.88885927200317</v>
       </c>
       <c r="H553" t="n">
         <v>978481</v>
@@ -16609,7 +16609,7 @@
         <v>12.2550001144409</v>
       </c>
       <c r="G560" t="n">
-        <v>8.273681640625</v>
+        <v>8.27368068695068</v>
       </c>
       <c r="H560" t="n">
         <v>3458397</v>
@@ -16696,7 +16696,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G563" t="n">
-        <v>8.21629524230957</v>
+        <v>8.21629619598389</v>
       </c>
       <c r="H563" t="n">
         <v>1551305</v>
@@ -16783,7 +16783,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053470611572</v>
+        <v>8.82053375244141</v>
       </c>
       <c r="H566" t="n">
         <v>3617516</v>
@@ -16841,7 +16841,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>9.21210861206055</v>
+        <v>9.21210765838623</v>
       </c>
       <c r="H568" t="n">
         <v>1870794</v>
@@ -16870,7 +16870,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.3235034942627</v>
+        <v>9.32350444793701</v>
       </c>
       <c r="H569" t="n">
         <v>1639116</v>
@@ -16899,7 +16899,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375667572021</v>
+        <v>9.34375762939453</v>
       </c>
       <c r="H570" t="n">
         <v>1437346</v>
@@ -16928,7 +16928,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114307403564</v>
+        <v>9.40114402770996</v>
       </c>
       <c r="H571" t="n">
         <v>1346272</v>
@@ -16957,7 +16957,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G572" t="n">
-        <v>9.47878265380859</v>
+        <v>9.47878360748291</v>
       </c>
       <c r="H572" t="n">
         <v>1791246</v>
@@ -16986,7 +16986,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253890991211</v>
+        <v>9.51253986358643</v>
       </c>
       <c r="H573" t="n">
         <v>1118116</v>
@@ -17131,7 +17131,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540760040283</v>
+        <v>9.47540664672852</v>
       </c>
       <c r="H578" t="n">
         <v>1873488</v>
@@ -17160,7 +17160,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G579" t="n">
-        <v>9.84335136413574</v>
+        <v>9.84335041046143</v>
       </c>
       <c r="H579" t="n">
         <v>2092638</v>
@@ -17218,7 +17218,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243690490723</v>
+        <v>8.97243785858154</v>
       </c>
       <c r="H581" t="n">
         <v>4533092</v>
@@ -17537,7 +17537,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.9527735710144</v>
+        <v>7.95277309417725</v>
       </c>
       <c r="H592" t="n">
         <v>1799211</v>
@@ -17595,7 +17595,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893676757812</v>
+        <v>8.37893772125244</v>
       </c>
       <c r="H594" t="n">
         <v>1370145</v>
@@ -17624,7 +17624,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.1143045425415</v>
+        <v>8.11430358886719</v>
       </c>
       <c r="H595" t="n">
         <v>1343574</v>
@@ -17682,7 +17682,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465784072876</v>
+        <v>7.90465831756592</v>
       </c>
       <c r="H597" t="n">
         <v>2070634</v>
@@ -17711,7 +17711,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809535980225</v>
+        <v>7.90809488296509</v>
       </c>
       <c r="H598" t="n">
         <v>1111394</v>
@@ -17740,7 +17740,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558931350708</v>
+        <v>7.93558979034424</v>
       </c>
       <c r="H599" t="n">
         <v>1144101</v>
@@ -17769,7 +17769,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776195526123</v>
+        <v>8.00776290893555</v>
       </c>
       <c r="H600" t="n">
         <v>1299934</v>
@@ -17856,7 +17856,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H603" t="n">
         <v>4357376</v>
@@ -17943,7 +17943,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.95964765548706</v>
+        <v>7.9596471786499</v>
       </c>
       <c r="H606" t="n">
         <v>1233297</v>
@@ -18001,7 +18001,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H608" t="n">
         <v>943692</v>
@@ -18059,7 +18059,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.72938108444214</v>
+        <v>7.7293815612793</v>
       </c>
       <c r="H610" t="n">
         <v>1482029</v>
@@ -18146,7 +18146,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621013641357</v>
+        <v>7.95621061325073</v>
       </c>
       <c r="H613" t="n">
         <v>953411</v>
@@ -18233,7 +18233,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627696990967</v>
+        <v>7.62627744674683</v>
       </c>
       <c r="H616" t="n">
         <v>1263861</v>
@@ -18262,7 +18262,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379367828369</v>
+        <v>7.54379415512085</v>
       </c>
       <c r="H617" t="n">
         <v>1883401</v>
@@ -18349,7 +18349,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250699996948</v>
+        <v>7.72250747680664</v>
       </c>
       <c r="H620" t="n">
         <v>1949076</v>
@@ -18407,7 +18407,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434766769409</v>
+        <v>7.89434814453125</v>
       </c>
       <c r="H622" t="n">
         <v>2466372</v>
@@ -18436,7 +18436,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H623" t="n">
         <v>1875863</v>
@@ -18465,7 +18465,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H624" t="n">
         <v>2114723</v>
@@ -18494,7 +18494,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H625" t="n">
         <v>1003281</v>
@@ -18552,7 +18552,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H627" t="n">
         <v>2034035</v>
@@ -18639,7 +18639,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445858001709</v>
+        <v>7.34445905685425</v>
       </c>
       <c r="H630" t="n">
         <v>961522</v>
@@ -18668,7 +18668,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758544921875</v>
+        <v>7.33758497238159</v>
       </c>
       <c r="H631" t="n">
         <v>1340364</v>
@@ -18726,7 +18726,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632104873657</v>
+        <v>7.40632057189941</v>
       </c>
       <c r="H633" t="n">
         <v>1188311</v>
@@ -18755,7 +18755,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259611129761</v>
+        <v>7.28259658813477</v>
       </c>
       <c r="H634" t="n">
         <v>922139</v>
@@ -18842,7 +18842,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H637" t="n">
         <v>1104944</v>
@@ -18871,7 +18871,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.31009101867676</v>
+        <v>7.3100905418396</v>
       </c>
       <c r="H638" t="n">
         <v>1477565</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982444763184</v>
+        <v>7.07982492446899</v>
       </c>
       <c r="H642" t="n">
         <v>1299347</v>
@@ -19016,7 +19016,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949199676514</v>
+        <v>7.17949151992798</v>
       </c>
       <c r="H643" t="n">
         <v>1807666</v>
@@ -19103,7 +19103,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470287322998</v>
+        <v>7.68470335006714</v>
       </c>
       <c r="H646" t="n">
         <v>1668673</v>
@@ -19132,7 +19132,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.86685371398926</v>
+        <v>7.8668532371521</v>
       </c>
       <c r="H647" t="n">
         <v>1764822</v>
@@ -19161,7 +19161,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.9149694442749</v>
+        <v>7.91496896743774</v>
       </c>
       <c r="H648" t="n">
         <v>1235632</v>
@@ -19190,7 +19190,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122127532959</v>
+        <v>7.90122175216675</v>
       </c>
       <c r="H649" t="n">
         <v>1397538</v>
@@ -19219,7 +19219,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656534194946</v>
+        <v>7.74656581878662</v>
       </c>
       <c r="H650" t="n">
         <v>1895690</v>
@@ -19277,7 +19277,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H652" t="n">
         <v>1855485</v>
@@ -19364,7 +19364,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485786437988</v>
+        <v>6.91485834121704</v>
       </c>
       <c r="H655" t="n">
         <v>21113678</v>
@@ -19422,7 +19422,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946941375732</v>
+        <v>6.35946989059448</v>
       </c>
       <c r="H657" t="n">
         <v>4678338</v>
@@ -19451,7 +19451,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H658" t="n">
         <v>2619573</v>
@@ -19538,7 +19538,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H661" t="n">
         <v>2610988</v>
@@ -19567,7 +19567,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980192184448</v>
+        <v>5.94980239868164</v>
       </c>
       <c r="H662" t="n">
         <v>4162401</v>
@@ -19596,7 +19596,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108764648438</v>
+        <v>5.77108812332153</v>
       </c>
       <c r="H663" t="n">
         <v>4859349</v>
@@ -19712,7 +19712,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255088806152</v>
+        <v>5.95255136489868</v>
       </c>
       <c r="H667" t="n">
         <v>1004735</v>
@@ -19741,7 +19741,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017934799194</v>
+        <v>5.94017887115479</v>
       </c>
       <c r="H668" t="n">
         <v>997482</v>
@@ -19828,7 +19828,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638805389404</v>
+        <v>6.14638757705688</v>
       </c>
       <c r="H671" t="n">
         <v>2096737</v>
@@ -19944,7 +19944,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199678421021</v>
+        <v>6.22199726104736</v>
       </c>
       <c r="H675" t="n">
         <v>1440910</v>
@@ -20031,7 +20031,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634302139282</v>
+        <v>6.36634349822998</v>
       </c>
       <c r="H678" t="n">
         <v>1366723</v>
@@ -20060,7 +20060,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38009023666382</v>
+        <v>6.38008975982666</v>
       </c>
       <c r="H679" t="n">
         <v>980480</v>
@@ -20176,7 +20176,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188646316528</v>
+        <v>6.15188598632812</v>
       </c>
       <c r="H683" t="n">
         <v>2106694</v>
@@ -20292,7 +20292,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392608642578</v>
+        <v>5.95392560958862</v>
       </c>
       <c r="H687" t="n">
         <v>1295054</v>
@@ -20466,7 +20466,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28111028671265</v>
+        <v>6.28110980987549</v>
       </c>
       <c r="H693" t="n">
         <v>2462515</v>
@@ -20495,7 +20495,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.30310583114624</v>
+        <v>6.3031063079834</v>
       </c>
       <c r="H694" t="n">
         <v>1410849</v>
@@ -20524,7 +20524,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.49831676483154</v>
+        <v>6.4983172416687</v>
       </c>
       <c r="H695" t="n">
         <v>2437479</v>
@@ -20611,7 +20611,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286195755005</v>
+        <v>6.27286243438721</v>
       </c>
       <c r="H698" t="n">
         <v>3218967</v>
@@ -20640,7 +20640,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536800384521</v>
+        <v>6.24536752700806</v>
       </c>
       <c r="H699" t="n">
         <v>1981493</v>
@@ -20669,7 +20669,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170883178711</v>
+        <v>6.41170930862427</v>
       </c>
       <c r="H700" t="n">
         <v>2629183</v>
@@ -20756,7 +20756,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938089370728</v>
+        <v>6.17938041687012</v>
       </c>
       <c r="H703" t="n">
         <v>3178801</v>
@@ -20785,7 +20785,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441431045532</v>
+        <v>6.01441383361816</v>
       </c>
       <c r="H704" t="n">
         <v>3618036</v>
@@ -20901,7 +20901,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962524414062</v>
+        <v>6.20962476730347</v>
       </c>
       <c r="H708" t="n">
         <v>1498085</v>
@@ -20930,7 +20930,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698612213135</v>
+        <v>6.27698659896851</v>
       </c>
       <c r="H709" t="n">
         <v>2955864</v>
@@ -20959,7 +20959,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450283050537</v>
+        <v>6.19450330734253</v>
       </c>
       <c r="H710" t="n">
         <v>2554492</v>
@@ -21162,7 +21162,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754058837891</v>
+        <v>6.62754011154175</v>
       </c>
       <c r="H717" t="n">
         <v>2640643</v>
@@ -21220,7 +21220,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204170227051</v>
+        <v>6.62204122543335</v>
       </c>
       <c r="H719" t="n">
         <v>1962181</v>
@@ -21278,7 +21278,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.89767360687256</v>
+        <v>6.8976731300354</v>
       </c>
       <c r="H721" t="n">
         <v>3961916</v>
@@ -21336,7 +21336,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088857650757</v>
+        <v>6.76088905334473</v>
       </c>
       <c r="H723" t="n">
         <v>3582670</v>
@@ -21365,7 +21365,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705236434937</v>
+        <v>6.56705284118652</v>
       </c>
       <c r="H724" t="n">
         <v>2210569</v>
@@ -21423,7 +21423,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H726" t="n">
         <v>1858552</v>
@@ -21539,7 +21539,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.01108837127686</v>
+        <v>7.0110878944397</v>
       </c>
       <c r="H730" t="n">
         <v>8286642</v>
@@ -21626,7 +21626,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013515472412</v>
+        <v>6.78013467788696</v>
       </c>
       <c r="H733" t="n">
         <v>4138184</v>
@@ -21713,7 +21713,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729623794556</v>
+        <v>6.59729671478271</v>
       </c>
       <c r="H736" t="n">
         <v>2990029</v>
@@ -21742,7 +21742,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H737" t="n">
         <v>1630942</v>
@@ -21858,7 +21858,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H741" t="n">
         <v>1657610</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H745" t="n">
         <v>2906567</v>
@@ -22061,7 +22061,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.6467866897583</v>
+        <v>6.64678716659546</v>
       </c>
       <c r="H748" t="n">
         <v>1472605</v>
@@ -22119,7 +22119,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000207901001</v>
+        <v>6.82000160217285</v>
       </c>
       <c r="H750" t="n">
         <v>2428586</v>
@@ -22206,7 +22206,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H753" t="n">
         <v>1373245</v>
@@ -22235,7 +22235,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401544570923</v>
+        <v>6.75401496887207</v>
       </c>
       <c r="H754" t="n">
         <v>1786995</v>
@@ -22293,7 +22293,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.8419976234436</v>
+        <v>6.84199810028076</v>
       </c>
       <c r="H756" t="n">
         <v>2943745</v>
@@ -22322,7 +22322,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093265533447</v>
+        <v>6.54093313217163</v>
       </c>
       <c r="H757" t="n">
         <v>3277617</v>
@@ -22438,7 +22438,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H761" t="n">
         <v>2579512</v>
@@ -22467,7 +22467,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H762" t="n">
         <v>1442117</v>
@@ -22554,7 +22554,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H765" t="n">
         <v>2725833</v>
@@ -22902,7 +22902,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166463851929</v>
+        <v>7.25166511535645</v>
       </c>
       <c r="H777" t="n">
         <v>3966282</v>
@@ -22989,7 +22989,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818351745605</v>
+        <v>7.46818399429321</v>
       </c>
       <c r="H780" t="n">
         <v>2399106</v>
@@ -23192,7 +23192,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933605194092</v>
+        <v>7.94933652877808</v>
       </c>
       <c r="H787" t="n">
         <v>3020927</v>
@@ -23250,7 +23250,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.82904863357544</v>
+        <v>7.8290491104126</v>
       </c>
       <c r="H789" t="n">
         <v>2034103</v>
@@ -23279,7 +23279,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683095932007</v>
+        <v>7.97683143615723</v>
       </c>
       <c r="H790" t="n">
         <v>2487608</v>
@@ -23395,7 +23395,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210674285889</v>
+        <v>10.2210664749146</v>
       </c>
       <c r="H794" t="n">
         <v>4399432</v>
@@ -23656,7 +23656,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341487884521</v>
+        <v>10.4341497421265</v>
       </c>
       <c r="H803" t="n">
         <v>1560972</v>
@@ -23830,7 +23830,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500032424927</v>
+        <v>10.8500022888184</v>
       </c>
       <c r="H809" t="n">
         <v>3171229</v>
@@ -23859,7 +23859,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249475479126</v>
+        <v>11.1249465942383</v>
       </c>
       <c r="H810" t="n">
         <v>2951875</v>
@@ -23888,7 +23888,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953458786011</v>
+        <v>10.6953468322754</v>
       </c>
       <c r="H811" t="n">
         <v>2115144</v>
@@ -23946,7 +23946,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485609054565</v>
+        <v>10.2485618591309</v>
       </c>
       <c r="H813" t="n">
         <v>1560898</v>
@@ -24033,7 +24033,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352586746216</v>
+        <v>11.1352577209473</v>
       </c>
       <c r="H816" t="n">
         <v>3500840</v>
@@ -24120,7 +24120,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029973983765</v>
+        <v>11.5029964447021</v>
       </c>
       <c r="H819" t="n">
         <v>2998052</v>
@@ -24207,7 +24207,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208446502686</v>
+        <v>11.3208456039429</v>
       </c>
       <c r="H822" t="n">
         <v>1495955</v>
@@ -24236,7 +24236,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376964569092</v>
+        <v>11.4376955032349</v>
       </c>
       <c r="H823" t="n">
         <v>1503927</v>
@@ -24294,7 +24294,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414669036865</v>
+        <v>11.3414659500122</v>
       </c>
       <c r="H825" t="n">
         <v>1813430</v>
@@ -24352,7 +24352,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585395812988</v>
+        <v>10.3585386276245</v>
       </c>
       <c r="H827" t="n">
         <v>2267336</v>
@@ -24381,7 +24381,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069868087769</v>
+        <v>10.3069877624512</v>
       </c>
       <c r="H828" t="n">
         <v>1710958</v>
@@ -24526,7 +24526,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634304046631</v>
+        <v>8.84634399414062</v>
       </c>
       <c r="H833" t="n">
         <v>2682628</v>
@@ -24584,7 +24584,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472534179688</v>
+        <v>9.12472438812256</v>
       </c>
       <c r="H835" t="n">
         <v>2895890</v>
@@ -24613,7 +24613,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940307617188</v>
+        <v>9.16940402984619</v>
       </c>
       <c r="H836" t="n">
         <v>1823500</v>
@@ -35784,6 +35784,35 @@
         <v>834996</v>
       </c>
       <c r="I1221" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1222" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>14.3500003814697</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="G1222" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="H1222" t="n">
+        <v>1037371</v>
+      </c>
+      <c r="I1222" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418394088745</v>
+        <v>6.82418346405029</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23060941696167</v>
+        <v>7.23061037063599</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -485,7 +485,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024492263794</v>
+        <v>7.68024444580078</v>
       </c>
       <c r="H4" t="n">
         <v>9073446</v>
@@ -514,7 +514,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634632110596</v>
+        <v>7.15634679794312</v>
       </c>
       <c r="H5" t="n">
         <v>8844542</v>
@@ -543,7 +543,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705677032471</v>
+        <v>6.94705629348755</v>
       </c>
       <c r="H6" t="n">
         <v>11941139</v>
@@ -601,7 +601,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8525390625</v>
+        <v>6.85253810882568</v>
       </c>
       <c r="H8" t="n">
         <v>4472971</v>
@@ -688,7 +688,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385835647583</v>
+        <v>7.22385883331299</v>
       </c>
       <c r="H11" t="n">
         <v>4406227</v>
@@ -717,7 +717,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010257720947</v>
+        <v>7.19010162353516</v>
       </c>
       <c r="H12" t="n">
         <v>3165422</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96730995178223</v>
+        <v>6.96731090545654</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -920,7 +920,7 @@
         <v>9.625</v>
       </c>
       <c r="G19" t="n">
-        <v>6.49809694290161</v>
+        <v>6.49809741973877</v>
       </c>
       <c r="H19" t="n">
         <v>3546202</v>
@@ -949,7 +949,7 @@
         <v>9.625</v>
       </c>
       <c r="G20" t="n">
-        <v>6.49809694290161</v>
+        <v>6.49809741973877</v>
       </c>
       <c r="H20" t="n">
         <v>2484688</v>
@@ -1007,7 +1007,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.39345264434814</v>
+        <v>6.3934531211853</v>
       </c>
       <c r="H22" t="n">
         <v>1481754</v>
@@ -1065,7 +1065,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G24" t="n">
-        <v>6.29218292236328</v>
+        <v>6.29218339920044</v>
       </c>
       <c r="H24" t="n">
         <v>2785789</v>
@@ -1123,7 +1123,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>5.91411256790161</v>
+        <v>5.91411209106445</v>
       </c>
       <c r="H26" t="n">
         <v>3367791</v>
@@ -1181,7 +1181,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>5.69132089614868</v>
+        <v>5.69132041931152</v>
       </c>
       <c r="H28" t="n">
         <v>6011852</v>
@@ -1210,7 +1210,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08626985549927</v>
+        <v>6.08627033233643</v>
       </c>
       <c r="H29" t="n">
         <v>6081895</v>
@@ -1616,7 +1616,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850280761719</v>
+        <v>4.66850328445435</v>
       </c>
       <c r="H43" t="n">
         <v>3306233</v>
@@ -1703,7 +1703,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692985534668</v>
+        <v>4.27692937850952</v>
       </c>
       <c r="H46" t="n">
         <v>3684492</v>
@@ -1906,7 +1906,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533041000366</v>
+        <v>4.41533088684082</v>
       </c>
       <c r="H53" t="n">
         <v>2670255</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347826004028</v>
+        <v>4.53347778320312</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2109,7 +2109,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195440292358</v>
+        <v>4.41195487976074</v>
       </c>
       <c r="H60" t="n">
         <v>1556296</v>
@@ -2370,7 +2370,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754363059998</v>
+        <v>3.68754315376282</v>
       </c>
       <c r="H69" t="n">
         <v>4125758</v>
@@ -2399,7 +2399,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H70" t="n">
         <v>2522173</v>
@@ -2486,7 +2486,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>3.85497522354126</v>
+        <v>3.85497498512268</v>
       </c>
       <c r="H73" t="n">
         <v>2825138</v>
@@ -2515,7 +2515,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0851936340332</v>
+        <v>4.08519315719604</v>
       </c>
       <c r="H74" t="n">
         <v>3445946</v>
@@ -2689,7 +2689,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822368621826</v>
+        <v>3.84822344779968</v>
       </c>
       <c r="H80" t="n">
         <v>1805442</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995481491089</v>
+        <v>3.87995505332947</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286360740662</v>
+        <v>3.79286313056946</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2892,7 +2892,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045775413513</v>
+        <v>3.76045727729797</v>
       </c>
       <c r="H87" t="n">
         <v>1422123</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619346618652</v>
+        <v>3.68619322776794</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437584877014</v>
+        <v>3.5943763256073</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496479988098</v>
+        <v>3.53496527671814</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77396011352539</v>
+        <v>3.77395963668823</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240148544312</v>
+        <v>3.86240196228027</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3240,7 +3240,7 @@
         <v>5.5939998626709</v>
       </c>
       <c r="G99" t="n">
-        <v>3.77666044235229</v>
+        <v>3.77666020393372</v>
       </c>
       <c r="H99" t="n">
         <v>1773866</v>
@@ -3269,7 +3269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.8144679069519</v>
+        <v>3.81446743011475</v>
       </c>
       <c r="H100" t="n">
         <v>1355091</v>
@@ -3327,7 +3327,7 @@
         <v>5.72300004959106</v>
       </c>
       <c r="G102" t="n">
-        <v>3.86375164985657</v>
+        <v>3.86375188827515</v>
       </c>
       <c r="H102" t="n">
         <v>1984827</v>
@@ -3443,7 +3443,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.00012731552124</v>
+        <v>4.0001277923584</v>
       </c>
       <c r="H106" t="n">
         <v>1710248</v>
@@ -3472,7 +3472,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G107" t="n">
-        <v>4.01430463790894</v>
+        <v>4.01430511474609</v>
       </c>
       <c r="H107" t="n">
         <v>1985267</v>
@@ -3501,7 +3501,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354875564575</v>
+        <v>4.11354827880859</v>
       </c>
       <c r="H108" t="n">
         <v>1792655</v>
@@ -3530,7 +3530,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12030029296875</v>
+        <v>4.12029981613159</v>
       </c>
       <c r="H109" t="n">
         <v>2831477</v>
@@ -3588,7 +3588,7 @@
         <v>6.28900003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24587392807007</v>
+        <v>4.24587345123291</v>
       </c>
       <c r="H111" t="n">
         <v>2320257</v>
@@ -3617,7 +3617,7 @@
         <v>6.32600021362305</v>
       </c>
       <c r="G112" t="n">
-        <v>4.27085304260254</v>
+        <v>4.2708535194397</v>
       </c>
       <c r="H112" t="n">
         <v>1704261</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594975471497</v>
+        <v>3.98594951629639</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3733,7 +3733,7 @@
         <v>5.09700012207031</v>
       </c>
       <c r="G116" t="n">
-        <v>3.44112253189087</v>
+        <v>3.44112229347229</v>
       </c>
       <c r="H116" t="n">
         <v>2818082</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.65716290473938</v>
+        <v>3.6571626663208</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3994,7 +3994,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091406822205</v>
+        <v>3.53091430664062</v>
       </c>
       <c r="H125" t="n">
         <v>1761818</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952308654785</v>
+        <v>3.57952356338501</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.40399050712585</v>
+        <v>3.4039900302887</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044709205627</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.45665001869202</v>
+        <v>3.4566502571106</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4342,7 +4342,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>3.34187865257263</v>
+        <v>3.34187841415405</v>
       </c>
       <c r="H137" t="n">
         <v>1981838</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.2132670879364</v>
+        <v>3.21326661109924</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4487,7 +4487,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192917823792</v>
+        <v>3.61192941665649</v>
       </c>
       <c r="H142" t="n">
         <v>2033903</v>
@@ -4516,7 +4516,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488340377808</v>
+        <v>3.63488364219666</v>
       </c>
       <c r="H143" t="n">
         <v>2301198</v>
@@ -4545,7 +4545,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813210487366</v>
+        <v>3.62813258171082</v>
       </c>
       <c r="H144" t="n">
         <v>1162846</v>
@@ -4603,7 +4603,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.5322642326355</v>
+        <v>3.53226447105408</v>
       </c>
       <c r="H146" t="n">
         <v>1532624</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290904045105</v>
+        <v>3.90290927886963</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4922,7 +4922,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G157" t="n">
-        <v>4.02510738372803</v>
+        <v>4.02510690689087</v>
       </c>
       <c r="H157" t="n">
         <v>1266112</v>
@@ -4951,7 +4951,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139656066895</v>
+        <v>4.10139608383179</v>
       </c>
       <c r="H158" t="n">
         <v>1462457</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370621681213</v>
+        <v>3.75370573997498</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5270,7 +5270,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648284912109</v>
+        <v>3.49648237228394</v>
       </c>
       <c r="H169" t="n">
         <v>1228962</v>
@@ -5473,7 +5473,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681790351868</v>
+        <v>3.41681742668152</v>
       </c>
       <c r="H176" t="n">
         <v>743828</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538077354431</v>
+        <v>3.35538101196289</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044709205627</v>
+        <v>3.44044756889343</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5705,7 +5705,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437099456787</v>
+        <v>3.43437075614929</v>
       </c>
       <c r="H184" t="n">
         <v>1118182</v>
@@ -5792,7 +5792,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>3.36213231086731</v>
+        <v>3.36213254928589</v>
       </c>
       <c r="H187" t="n">
         <v>1010793</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837374687195</v>
+        <v>3.24837327003479</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116008758545</v>
+        <v>3.31116056442261</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -6140,7 +6140,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>3.48027992248535</v>
+        <v>3.48027968406677</v>
       </c>
       <c r="H199" t="n">
         <v>734627</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50795984268188</v>
+        <v>3.50796008110046</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6314,7 +6314,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.60855340957642</v>
+        <v>3.608553647995</v>
       </c>
       <c r="H205" t="n">
         <v>1822628</v>
@@ -6401,7 +6401,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678217887878</v>
+        <v>3.62678241729736</v>
       </c>
       <c r="H208" t="n">
         <v>815597</v>
@@ -6430,7 +6430,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H209" t="n">
         <v>1632705</v>
@@ -6459,7 +6459,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535085678101</v>
+        <v>3.72535061836243</v>
       </c>
       <c r="H210" t="n">
         <v>1178589</v>
@@ -6662,7 +6662,7 @@
         <v>5.37900018692017</v>
       </c>
       <c r="G217" t="n">
-        <v>3.63150787353516</v>
+        <v>3.63150835037231</v>
       </c>
       <c r="H217" t="n">
         <v>1446118</v>
@@ -6865,7 +6865,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19928932189941</v>
+        <v>4.19928979873657</v>
       </c>
       <c r="H224" t="n">
         <v>1230545</v>
@@ -7213,7 +7213,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G236" t="n">
-        <v>4.33566522598267</v>
+        <v>4.33566570281982</v>
       </c>
       <c r="H236" t="n">
         <v>986833</v>
@@ -7271,7 +7271,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>4.36807107925415</v>
+        <v>4.36807155609131</v>
       </c>
       <c r="H238" t="n">
         <v>855642</v>
@@ -7329,7 +7329,7 @@
         <v>6.31300020217896</v>
       </c>
       <c r="G240" t="n">
-        <v>4.26207685470581</v>
+        <v>4.26207637786865</v>
       </c>
       <c r="H240" t="n">
         <v>1219252</v>
@@ -7387,7 +7387,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781280517578</v>
+        <v>4.18781232833862</v>
       </c>
       <c r="H242" t="n">
         <v>718598</v>
@@ -7706,7 +7706,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459402084351</v>
+        <v>3.82459449768066</v>
       </c>
       <c r="H253" t="n">
         <v>1270112</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771636962891</v>
+        <v>3.80771589279175</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73682761192322</v>
+        <v>3.7368278503418</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7822,7 +7822,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G257" t="n">
-        <v>3.75235605239868</v>
+        <v>3.7523558139801</v>
       </c>
       <c r="H257" t="n">
         <v>475168</v>
@@ -7967,7 +7967,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G262" t="n">
-        <v>4.06156349182129</v>
+        <v>4.06156396865845</v>
       </c>
       <c r="H262" t="n">
         <v>1735246</v>
@@ -8025,7 +8025,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604085922241</v>
+        <v>4.20604133605957</v>
       </c>
       <c r="H264" t="n">
         <v>1003317</v>
@@ -8083,7 +8083,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>4.61786890029907</v>
+        <v>4.61786842346191</v>
       </c>
       <c r="H266" t="n">
         <v>4637628</v>
@@ -8199,7 +8199,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.65972661972046</v>
+        <v>4.6597261428833</v>
       </c>
       <c r="H270" t="n">
         <v>1305558</v>
@@ -8286,7 +8286,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>4.90817356109619</v>
+        <v>4.90817308425903</v>
       </c>
       <c r="H273" t="n">
         <v>2063203</v>
@@ -8315,7 +8315,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H274" t="n">
         <v>1735281</v>
@@ -8402,7 +8402,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>5.11408710479736</v>
+        <v>5.11408662796021</v>
       </c>
       <c r="H277" t="n">
         <v>2333721</v>
@@ -8431,7 +8431,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.03172159194946</v>
+        <v>5.0317211151123</v>
       </c>
       <c r="H278" t="n">
         <v>1291216</v>
@@ -8605,7 +8605,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855890274048</v>
+        <v>5.09855937957764</v>
       </c>
       <c r="H284" t="n">
         <v>773657</v>
@@ -8634,7 +8634,7 @@
         <v>7.48199987411499</v>
       </c>
       <c r="G285" t="n">
-        <v>5.05129957199097</v>
+        <v>5.05130004882812</v>
       </c>
       <c r="H285" t="n">
         <v>1023863</v>
@@ -8750,7 +8750,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370121002197</v>
+        <v>6.25370025634766</v>
       </c>
       <c r="H289" t="n">
         <v>5659371</v>
@@ -8779,7 +8779,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G290" t="n">
-        <v>6.1794376373291</v>
+        <v>6.17943716049194</v>
       </c>
       <c r="H290" t="n">
         <v>1832776</v>
@@ -8924,7 +8924,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449377059937</v>
+        <v>5.94449281692505</v>
       </c>
       <c r="H295" t="n">
         <v>1414060</v>
@@ -9011,7 +9011,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926465988159</v>
+        <v>6.05926561355591</v>
       </c>
       <c r="H298" t="n">
         <v>834113</v>
@@ -9098,7 +9098,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698539733887</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H301" t="n">
         <v>740488</v>
@@ -9185,7 +9185,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.11124992370605</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H304" t="n">
         <v>1512205</v>
@@ -9243,7 +9243,7 @@
         <v>9.07299995422363</v>
       </c>
       <c r="G306" t="n">
-        <v>6.12542676925659</v>
+        <v>6.12542724609375</v>
       </c>
       <c r="H306" t="n">
         <v>1336985</v>
@@ -9301,7 +9301,7 @@
         <v>8.50899982452393</v>
       </c>
       <c r="G308" t="n">
-        <v>5.74465608596802</v>
+        <v>5.7446551322937</v>
       </c>
       <c r="H308" t="n">
         <v>1509651</v>
@@ -9475,7 +9475,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.86617803573608</v>
+        <v>5.86617851257324</v>
       </c>
       <c r="H314" t="n">
         <v>816021</v>
@@ -9504,7 +9504,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977197647095</v>
+        <v>6.09977293014526</v>
       </c>
       <c r="H315" t="n">
         <v>1294330</v>
@@ -9649,7 +9649,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G320" t="n">
-        <v>5.91411256790161</v>
+        <v>5.91411209106445</v>
       </c>
       <c r="H320" t="n">
         <v>1043632</v>
@@ -9881,7 +9881,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G328" t="n">
-        <v>5.43747282028198</v>
+        <v>5.43747234344482</v>
       </c>
       <c r="H328" t="n">
         <v>2329069</v>
@@ -9968,7 +9968,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G331" t="n">
-        <v>5.56304597854614</v>
+        <v>5.5630464553833</v>
       </c>
       <c r="H331" t="n">
         <v>1403612</v>
@@ -10258,7 +10258,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30784797668457</v>
+        <v>5.30784845352173</v>
       </c>
       <c r="H341" t="n">
         <v>1370858</v>
@@ -10287,7 +10287,7 @@
         <v>7.86399984359741</v>
       </c>
       <c r="G342" t="n">
-        <v>5.30919885635376</v>
+        <v>5.3091983795166</v>
       </c>
       <c r="H342" t="n">
         <v>806647</v>
@@ -10316,7 +10316,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G343" t="n">
-        <v>5.14581775665283</v>
+        <v>5.14581823348999</v>
       </c>
       <c r="H343" t="n">
         <v>1174384</v>
@@ -10374,7 +10374,7 @@
         <v>7.93599987030029</v>
       </c>
       <c r="G345" t="n">
-        <v>5.35780811309814</v>
+        <v>5.35780763626099</v>
       </c>
       <c r="H345" t="n">
         <v>557874</v>
@@ -10403,7 +10403,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.37536096572876</v>
+        <v>5.3753604888916</v>
       </c>
       <c r="H346" t="n">
         <v>1300436</v>
@@ -10490,7 +10490,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G349" t="n">
-        <v>4.95948266983032</v>
+        <v>4.95948314666748</v>
       </c>
       <c r="H349" t="n">
         <v>3108681</v>
@@ -10548,7 +10548,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G351" t="n">
-        <v>4.90547227859497</v>
+        <v>4.90547275543213</v>
       </c>
       <c r="H351" t="n">
         <v>1070151</v>
@@ -10635,7 +10635,7 @@
         <v>7.63199996948242</v>
       </c>
       <c r="G354" t="n">
-        <v>5.15256881713867</v>
+        <v>5.15256929397583</v>
       </c>
       <c r="H354" t="n">
         <v>1115525</v>
@@ -10693,7 +10693,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910703659058</v>
+        <v>5.08910751342773</v>
       </c>
       <c r="H356" t="n">
         <v>721988</v>
@@ -10722,7 +10722,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G357" t="n">
-        <v>4.90547227859497</v>
+        <v>4.90547275543213</v>
       </c>
       <c r="H357" t="n">
         <v>1284720</v>
@@ -10751,7 +10751,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.82175731658936</v>
+        <v>4.8217568397522</v>
       </c>
       <c r="H358" t="n">
         <v>1382671</v>
@@ -10780,7 +10780,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G359" t="n">
-        <v>4.91492509841919</v>
+        <v>4.91492462158203</v>
       </c>
       <c r="H359" t="n">
         <v>837846</v>
@@ -10983,7 +10983,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568559646606</v>
+        <v>4.97568607330322</v>
       </c>
       <c r="H366" t="n">
         <v>978343</v>
@@ -11041,7 +11041,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543241500854</v>
+        <v>4.95543193817139</v>
       </c>
       <c r="H368" t="n">
         <v>1136830</v>
@@ -11157,7 +11157,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G372" t="n">
-        <v>5.21197986602783</v>
+        <v>5.21198034286499</v>
       </c>
       <c r="H372" t="n">
         <v>1028465</v>
@@ -11244,7 +11244,7 @@
         <v>7.82600021362305</v>
       </c>
       <c r="G375" t="n">
-        <v>5.28354358673096</v>
+        <v>5.28354406356812</v>
       </c>
       <c r="H375" t="n">
         <v>584900</v>
@@ -11273,7 +11273,7 @@
         <v>7.81400012969971</v>
       </c>
       <c r="G376" t="n">
-        <v>5.27544212341309</v>
+        <v>5.27544260025024</v>
       </c>
       <c r="H376" t="n">
         <v>879423</v>
@@ -11389,7 +11389,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236616134644</v>
+        <v>5.40236568450928</v>
       </c>
       <c r="H380" t="n">
         <v>1291207</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.61975765228271</v>
+        <v>5.61975717544556</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -11824,7 +11824,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376708984375</v>
+        <v>5.67376804351807</v>
       </c>
       <c r="H395" t="n">
         <v>1175604</v>
@@ -11882,7 +11882,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G397" t="n">
-        <v>5.60355472564697</v>
+        <v>5.60355424880981</v>
       </c>
       <c r="H397" t="n">
         <v>1898927</v>
@@ -11911,7 +11911,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.5603461265564</v>
+        <v>5.56034564971924</v>
       </c>
       <c r="H398" t="n">
         <v>1662385</v>
@@ -12056,7 +12056,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460969924927</v>
+        <v>5.63460922241211</v>
       </c>
       <c r="H403" t="n">
         <v>1808163</v>
@@ -12201,7 +12201,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G408" t="n">
-        <v>6.56088447570801</v>
+        <v>6.56088399887085</v>
       </c>
       <c r="H408" t="n">
         <v>3234067</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758501052856</v>
+        <v>6.29758453369141</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12375,7 +12375,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665105819702</v>
+        <v>6.11665058135986</v>
       </c>
       <c r="H414" t="n">
         <v>900855</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044813156128</v>
+        <v>6.10044717788696</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12462,7 +12462,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.9748740196228</v>
+        <v>5.97487449645996</v>
       </c>
       <c r="H417" t="n">
         <v>839338</v>
@@ -12491,7 +12491,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436670303345</v>
+        <v>5.93436622619629</v>
       </c>
       <c r="H418" t="n">
         <v>1220620</v>
@@ -12520,7 +12520,7 @@
         <v>8.63199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>5.82769632339478</v>
+        <v>5.82769584655762</v>
       </c>
       <c r="H419" t="n">
         <v>1609287</v>
@@ -12607,7 +12607,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G422" t="n">
-        <v>5.59005165100098</v>
+        <v>5.59005117416382</v>
       </c>
       <c r="H422" t="n">
         <v>2610359</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461940765381</v>
+        <v>5.95461988449097</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12723,7 +12723,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97757387161255</v>
+        <v>5.97757434844971</v>
       </c>
       <c r="H426" t="n">
         <v>685213</v>
@@ -12810,7 +12810,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.11124992370605</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H429" t="n">
         <v>462036</v>
@@ -12868,7 +12868,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H431" t="n">
         <v>1056988</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002149581909</v>
+        <v>5.96002054214478</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -12926,7 +12926,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698539733887</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H433" t="n">
         <v>771857</v>
@@ -13100,7 +13100,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G439" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H439" t="n">
         <v>745131</v>
@@ -13303,7 +13303,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770603179932</v>
+        <v>6.14770698547363</v>
       </c>
       <c r="H446" t="n">
         <v>971388</v>
@@ -13419,7 +13419,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.93031597137451</v>
+        <v>5.9303150177002</v>
       </c>
       <c r="H450" t="n">
         <v>988269</v>
@@ -13448,7 +13448,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G451" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H451" t="n">
         <v>722064</v>
@@ -13622,7 +13622,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453872680664</v>
       </c>
       <c r="H457" t="n">
         <v>1441148</v>
@@ -13709,7 +13709,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984851837158</v>
+        <v>5.83984804153442</v>
       </c>
       <c r="H460" t="n">
         <v>2271949</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748300552368</v>
+        <v>5.75748205184937</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13767,7 +13767,7 @@
         <v>8.34799957275391</v>
       </c>
       <c r="G462" t="n">
-        <v>5.6359601020813</v>
+        <v>5.63595962524414</v>
       </c>
       <c r="H462" t="n">
         <v>1243781</v>
@@ -13796,7 +13796,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401103973389</v>
+        <v>5.37401056289673</v>
       </c>
       <c r="H463" t="n">
         <v>2564625</v>
@@ -13883,7 +13883,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409172058105</v>
+        <v>5.27409219741821</v>
       </c>
       <c r="H466" t="n">
         <v>851531</v>
@@ -13970,7 +13970,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H469" t="n">
         <v>812307</v>
@@ -14028,7 +14028,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H471" t="n">
         <v>13000528</v>
@@ -14202,7 +14202,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.85011196136475</v>
+        <v>4.8501124382019</v>
       </c>
       <c r="H477" t="n">
         <v>2148643</v>
@@ -14376,7 +14376,7 @@
         <v>7.31599998474121</v>
       </c>
       <c r="G483" t="n">
-        <v>4.9392294883728</v>
+        <v>4.93922901153564</v>
       </c>
       <c r="H483" t="n">
         <v>1326009</v>
@@ -14492,7 +14492,7 @@
         <v>7.23199987411499</v>
       </c>
       <c r="G487" t="n">
-        <v>4.88251781463623</v>
+        <v>4.88251829147339</v>
       </c>
       <c r="H487" t="n">
         <v>1282850</v>
@@ -14521,7 +14521,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.9230260848999</v>
+        <v>4.92302560806274</v>
       </c>
       <c r="H488" t="n">
         <v>1062819</v>
@@ -14608,7 +14608,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G491" t="n">
-        <v>5.0431981086731</v>
+        <v>5.04319858551025</v>
       </c>
       <c r="H491" t="n">
         <v>2706817</v>
@@ -14695,7 +14695,7 @@
         <v>7.57600021362305</v>
       </c>
       <c r="G494" t="n">
-        <v>5.11476182937622</v>
+        <v>5.11476230621338</v>
       </c>
       <c r="H494" t="n">
         <v>1479490</v>
@@ -14724,7 +14724,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004146575928</v>
+        <v>5.27004194259644</v>
       </c>
       <c r="H495" t="n">
         <v>2448121</v>
@@ -14811,7 +14811,7 @@
         <v>7.93599987030029</v>
       </c>
       <c r="G498" t="n">
-        <v>5.35780811309814</v>
+        <v>5.35780763626099</v>
       </c>
       <c r="H498" t="n">
         <v>1351028</v>
@@ -14840,7 +14840,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G499" t="n">
-        <v>5.33350372314453</v>
+        <v>5.33350324630737</v>
       </c>
       <c r="H499" t="n">
         <v>999232</v>
@@ -15072,7 +15072,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G507" t="n">
-        <v>5.40641736984253</v>
+        <v>5.40641689300537</v>
       </c>
       <c r="H507" t="n">
         <v>1345581</v>
@@ -15130,7 +15130,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H509" t="n">
         <v>1443560</v>
@@ -15246,7 +15246,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G513" t="n">
-        <v>5.43747282028198</v>
+        <v>5.43747234344482</v>
       </c>
       <c r="H513" t="n">
         <v>1395334</v>
@@ -15333,7 +15333,7 @@
         <v>8.45600032806396</v>
       </c>
       <c r="G516" t="n">
-        <v>5.70887422561646</v>
+        <v>5.7088737487793</v>
       </c>
       <c r="H516" t="n">
         <v>1752740</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791934967041</v>
+        <v>6.21792030334473</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37724924087524</v>
+        <v>6.37725019454956</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15478,7 +15478,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.3745493888855</v>
+        <v>6.37454986572266</v>
       </c>
       <c r="H521" t="n">
         <v>4282126</v>
@@ -15681,7 +15681,7 @@
         <v>9.53800010681152</v>
       </c>
       <c r="G528" t="n">
-        <v>6.43936109542847</v>
+        <v>6.43936157226562</v>
       </c>
       <c r="H528" t="n">
         <v>1494558</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.42450857162476</v>
+        <v>6.4245080947876</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15739,7 +15739,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48526954650879</v>
+        <v>6.48527050018311</v>
       </c>
       <c r="H530" t="n">
         <v>1752325</v>
@@ -15942,7 +15942,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080331802368</v>
+        <v>6.66080284118652</v>
       </c>
       <c r="H537" t="n">
         <v>956747</v>
@@ -15971,7 +15971,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320917129517</v>
+        <v>6.69320821762085</v>
       </c>
       <c r="H538" t="n">
         <v>1117605</v>
@@ -16000,7 +16000,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G539" t="n">
-        <v>6.62974643707275</v>
+        <v>6.62974739074707</v>
       </c>
       <c r="H539" t="n">
         <v>1373635</v>
@@ -16029,7 +16029,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284324645996</v>
+        <v>7.14284372329712</v>
       </c>
       <c r="H540" t="n">
         <v>6833320</v>
@@ -16232,7 +16232,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G547" t="n">
-        <v>7.11246204376221</v>
+        <v>7.11246299743652</v>
       </c>
       <c r="H547" t="n">
         <v>2425730</v>
@@ -16290,7 +16290,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.45002603530884</v>
+        <v>7.450026512146</v>
       </c>
       <c r="H549" t="n">
         <v>2293340</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835052490234</v>
+        <v>7.84835147857666</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16551,7 +16551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228485107422</v>
+        <v>8.16228580474854</v>
       </c>
       <c r="H558" t="n">
         <v>1628712</v>
@@ -16609,7 +16609,7 @@
         <v>12.2550001144409</v>
       </c>
       <c r="G560" t="n">
-        <v>8.27368068695068</v>
+        <v>8.273681640625</v>
       </c>
       <c r="H560" t="n">
         <v>3458397</v>
@@ -16696,7 +16696,7 @@
         <v>12.1700000762939</v>
       </c>
       <c r="G563" t="n">
-        <v>8.21629619598389</v>
+        <v>8.21629524230957</v>
       </c>
       <c r="H563" t="n">
         <v>1551305</v>
@@ -16841,7 +16841,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>9.21210765838623</v>
+        <v>9.21210861206055</v>
       </c>
       <c r="H568" t="n">
         <v>1870794</v>
@@ -16957,7 +16957,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G572" t="n">
-        <v>9.47878360748291</v>
+        <v>9.47878265380859</v>
       </c>
       <c r="H572" t="n">
         <v>1791246</v>
@@ -17073,7 +17073,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840240478516</v>
+        <v>9.44840145111084</v>
       </c>
       <c r="H576" t="n">
         <v>2197272</v>
@@ -17160,7 +17160,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G579" t="n">
-        <v>9.84335041046143</v>
+        <v>9.84335136413574</v>
       </c>
       <c r="H579" t="n">
         <v>2092638</v>
@@ -17218,7 +17218,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243785858154</v>
+        <v>8.97243690490723</v>
       </c>
       <c r="H581" t="n">
         <v>4533092</v>
@@ -17334,7 +17334,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297023773193</v>
+        <v>8.48297119140625</v>
       </c>
       <c r="H585" t="n">
         <v>1264193</v>
@@ -35813,6 +35813,35 @@
         <v>1037371</v>
       </c>
       <c r="I1222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1223" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>14.2449998855591</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>14.3199996948242</v>
+      </c>
+      <c r="G1223" t="n">
+        <v>14.3199996948242</v>
+      </c>
+      <c r="H1223" t="n">
+        <v>2329667</v>
+      </c>
+      <c r="I1223" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418346405029</v>
+        <v>6.82418298721313</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23061037063599</v>
+        <v>7.23060989379883</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -485,7 +485,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024444580078</v>
+        <v>7.68024492263794</v>
       </c>
       <c r="H4" t="n">
         <v>9073446</v>
@@ -514,7 +514,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>7.15634679794312</v>
+        <v>7.15634632110596</v>
       </c>
       <c r="H5" t="n">
         <v>8844542</v>
@@ -543,7 +543,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705629348755</v>
+        <v>6.94705677032471</v>
       </c>
       <c r="H6" t="n">
         <v>11941139</v>
@@ -601,7 +601,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.85253810882568</v>
+        <v>6.8525390625</v>
       </c>
       <c r="H8" t="n">
         <v>4472971</v>
@@ -630,7 +630,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411201477051</v>
+        <v>7.24411249160767</v>
       </c>
       <c r="H9" t="n">
         <v>5804326</v>
@@ -659,7 +659,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="n">
         <v>7510382</v>
@@ -688,7 +688,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>7.22385883331299</v>
+        <v>7.22385835647583</v>
       </c>
       <c r="H11" t="n">
         <v>4406227</v>
@@ -717,7 +717,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010162353516</v>
+        <v>7.19010210037231</v>
       </c>
       <c r="H12" t="n">
         <v>3165422</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>7.05507659912109</v>
+        <v>7.05507707595825</v>
       </c>
       <c r="H14" t="n">
         <v>2413549</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731090545654</v>
+        <v>6.96730995178223</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -862,7 +862,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47109270095825</v>
+        <v>6.47109222412109</v>
       </c>
       <c r="H17" t="n">
         <v>4229589</v>
@@ -978,7 +978,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G21" t="n">
-        <v>6.34956932067871</v>
+        <v>6.34956884384155</v>
       </c>
       <c r="H21" t="n">
         <v>1984383</v>
@@ -1007,7 +1007,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3934531211853</v>
+        <v>6.39345264434814</v>
       </c>
       <c r="H22" t="n">
         <v>1481754</v>
@@ -1036,7 +1036,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>6.43058395385742</v>
+        <v>6.43058443069458</v>
       </c>
       <c r="H23" t="n">
         <v>3182466</v>
@@ -1210,7 +1210,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08627033233643</v>
+        <v>6.08626985549927</v>
       </c>
       <c r="H29" t="n">
         <v>6081895</v>
@@ -1384,7 +1384,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45502614974976</v>
+        <v>5.4550256729126</v>
       </c>
       <c r="H35" t="n">
         <v>3404051</v>
@@ -1413,7 +1413,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>5.438148021698</v>
+        <v>5.43814849853516</v>
       </c>
       <c r="H36" t="n">
         <v>2313680</v>
@@ -1587,7 +1587,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G42" t="n">
-        <v>5.0263204574585</v>
+        <v>5.02631998062134</v>
       </c>
       <c r="H42" t="n">
         <v>2532581</v>
@@ -1616,7 +1616,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>4.66850328445435</v>
+        <v>4.66850280761719</v>
       </c>
       <c r="H43" t="n">
         <v>3306233</v>
@@ -1732,7 +1732,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H47" t="n">
         <v>5966204</v>
@@ -1761,7 +1761,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G48" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H48" t="n">
         <v>3779682</v>
@@ -1790,7 +1790,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="n">
         <v>4270764</v>
@@ -1819,7 +1819,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H50" t="n">
         <v>5312212</v>
@@ -1906,7 +1906,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533088684082</v>
+        <v>4.41533041000366</v>
       </c>
       <c r="H53" t="n">
         <v>2670255</v>
@@ -1964,7 +1964,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187881469727</v>
+        <v>4.67187833786011</v>
       </c>
       <c r="H55" t="n">
         <v>3556258</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347778320312</v>
+        <v>4.53347730636597</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2022,7 +2022,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44233560562134</v>
+        <v>4.44233512878418</v>
       </c>
       <c r="H57" t="n">
         <v>2303616</v>
@@ -2051,7 +2051,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="n">
         <v>2735170</v>
@@ -2080,7 +2080,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.4052038192749</v>
+        <v>4.40520334243774</v>
       </c>
       <c r="H59" t="n">
         <v>2749560</v>
@@ -2196,7 +2196,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4355845451355</v>
+        <v>4.43558406829834</v>
       </c>
       <c r="H63" t="n">
         <v>4427308</v>
@@ -2312,7 +2312,7 @@
         <v>5.94299983978271</v>
       </c>
       <c r="G67" t="n">
-        <v>4.01227998733521</v>
+        <v>4.01227951049805</v>
       </c>
       <c r="H67" t="n">
         <v>2524391</v>
@@ -2341,7 +2341,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.84484839439392</v>
+        <v>3.84484815597534</v>
       </c>
       <c r="H68" t="n">
         <v>4549813</v>
@@ -2370,7 +2370,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.68754315376282</v>
+        <v>3.6875433921814</v>
       </c>
       <c r="H69" t="n">
         <v>4125758</v>
@@ -2399,7 +2399,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G70" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H70" t="n">
         <v>2522173</v>
@@ -2515,7 +2515,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="n">
         <v>3445946</v>
@@ -2544,7 +2544,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G75" t="n">
-        <v>4.02240657806396</v>
+        <v>4.02240705490112</v>
       </c>
       <c r="H75" t="n">
         <v>2815887</v>
@@ -2689,7 +2689,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822344779968</v>
+        <v>3.84822392463684</v>
       </c>
       <c r="H80" t="n">
         <v>1805442</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995505332947</v>
+        <v>3.87995529174805</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286313056946</v>
+        <v>3.79286360740662</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311726570129</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2863,7 +2863,7 @@
         <v>5.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H86" t="n">
         <v>1785095</v>
@@ -2892,7 +2892,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G87" t="n">
-        <v>3.76045727729797</v>
+        <v>3.76045751571655</v>
       </c>
       <c r="H87" t="n">
         <v>1422123</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619322776794</v>
+        <v>3.68619346618652</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.5943763256073</v>
+        <v>3.59437584877014</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496527671814</v>
+        <v>3.53496479988098</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3037,7 +3037,7 @@
         <v>5.41900014877319</v>
       </c>
       <c r="G92" t="n">
-        <v>3.65851330757141</v>
+        <v>3.65851306915283</v>
       </c>
       <c r="H92" t="n">
         <v>1860265</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395963668823</v>
+        <v>3.77395987510681</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240196228027</v>
+        <v>3.86240148544312</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3211,7 +3211,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G98" t="n">
-        <v>3.80231523513794</v>
+        <v>3.80231499671936</v>
       </c>
       <c r="H98" t="n">
         <v>1569339</v>
@@ -3356,7 +3356,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="n">
         <v>2495941</v>
@@ -3501,7 +3501,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354827880859</v>
+        <v>4.11354875564575</v>
       </c>
       <c r="H108" t="n">
         <v>1792655</v>
@@ -3530,7 +3530,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12029981613159</v>
+        <v>4.12030029296875</v>
       </c>
       <c r="H109" t="n">
         <v>2831477</v>
@@ -3559,7 +3559,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>4.31406164169312</v>
+        <v>4.31406116485596</v>
       </c>
       <c r="H110" t="n">
         <v>3321010</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594951629639</v>
+        <v>3.98594975471497</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3675,7 +3675,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="n">
         <v>4779877</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.6571626663208</v>
+        <v>3.65716290473938</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3994,7 +3994,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091430664062</v>
+        <v>3.53091406822205</v>
       </c>
       <c r="H125" t="n">
         <v>1761818</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952356338501</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.4039900302887</v>
+        <v>3.40399026870728</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4139,7 +4139,7 @@
         <v>5.14099979400635</v>
       </c>
       <c r="G130" t="n">
-        <v>3.47082781791687</v>
+        <v>3.47082757949829</v>
       </c>
       <c r="H130" t="n">
         <v>985438</v>
@@ -4168,7 +4168,7 @@
         <v>4.74849987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20584058761597</v>
+        <v>3.20584034919739</v>
       </c>
       <c r="H131" t="n">
         <v>3762380</v>
@@ -4197,7 +4197,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="n">
         <v>3036596</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.4566502571106</v>
+        <v>3.45665001869202</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326661109924</v>
+        <v>3.2132670879364</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4400,7 +4400,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39183807373047</v>
+        <v>3.39183783531189</v>
       </c>
       <c r="H139" t="n">
         <v>1947099</v>
@@ -4429,7 +4429,7 @@
         <v>5.11299991607666</v>
       </c>
       <c r="G140" t="n">
-        <v>3.45192408561707</v>
+        <v>3.45192432403564</v>
       </c>
       <c r="H140" t="n">
         <v>1625180</v>
@@ -4458,7 +4458,7 @@
         <v>5.37599992752075</v>
       </c>
       <c r="G141" t="n">
-        <v>3.62948298454285</v>
+        <v>3.62948274612427</v>
       </c>
       <c r="H141" t="n">
         <v>2254990</v>
@@ -4487,7 +4487,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>3.61192941665649</v>
+        <v>3.61192917823792</v>
       </c>
       <c r="H142" t="n">
         <v>2033903</v>
@@ -4632,7 +4632,7 @@
         <v>5.5</v>
       </c>
       <c r="G147" t="n">
-        <v>3.71319818496704</v>
+        <v>3.71319842338562</v>
       </c>
       <c r="H147" t="n">
         <v>2599217</v>
@@ -4661,7 +4661,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894455909729</v>
+        <v>3.95894479751587</v>
       </c>
       <c r="H148" t="n">
         <v>4041376</v>
@@ -4719,7 +4719,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>3.89143180847168</v>
+        <v>3.89143204689026</v>
       </c>
       <c r="H150" t="n">
         <v>1641881</v>
@@ -4806,7 +4806,7 @@
         <v>5.75899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>3.88805627822876</v>
+        <v>3.88805651664734</v>
       </c>
       <c r="H153" t="n">
         <v>2138183</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290927886963</v>
+        <v>3.90290904045105</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4893,7 +4893,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387847900391</v>
+        <v>3.87387871742249</v>
       </c>
       <c r="H156" t="n">
         <v>947624</v>
@@ -4951,7 +4951,7 @@
         <v>6.07499980926514</v>
       </c>
       <c r="G158" t="n">
-        <v>4.10139608383179</v>
+        <v>4.10139656066895</v>
       </c>
       <c r="H158" t="n">
         <v>1462457</v>
@@ -5067,7 +5067,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067544937134</v>
+        <v>3.99067568778992</v>
       </c>
       <c r="H162" t="n">
         <v>836698</v>
@@ -5096,7 +5096,7 @@
         <v>5.75</v>
       </c>
       <c r="G163" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H163" t="n">
         <v>830988</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370573997498</v>
+        <v>3.75370597839355</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5270,7 +5270,7 @@
         <v>5.17899990081787</v>
       </c>
       <c r="G169" t="n">
-        <v>3.49648237228394</v>
+        <v>3.49648261070251</v>
       </c>
       <c r="H169" t="n">
         <v>1228962</v>
@@ -5299,7 +5299,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G170" t="n">
-        <v>3.48635578155518</v>
+        <v>3.48635601997375</v>
       </c>
       <c r="H170" t="n">
         <v>1032447</v>
@@ -5328,7 +5328,7 @@
         <v>5.05600023269653</v>
       </c>
       <c r="G171" t="n">
-        <v>3.41344237327576</v>
+        <v>3.41344213485718</v>
       </c>
       <c r="H171" t="n">
         <v>1569176</v>
@@ -5357,7 +5357,7 @@
         <v>4.94549989700317</v>
       </c>
       <c r="G172" t="n">
-        <v>3.33884024620056</v>
+        <v>3.33884048461914</v>
       </c>
       <c r="H172" t="n">
         <v>1226903</v>
@@ -5386,7 +5386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H173" t="n">
         <v>1536086</v>
@@ -5444,7 +5444,7 @@
         <v>5.01900005340576</v>
       </c>
       <c r="G175" t="n">
-        <v>3.38846230506897</v>
+        <v>3.38846254348755</v>
       </c>
       <c r="H175" t="n">
         <v>951917</v>
@@ -5473,7 +5473,7 @@
         <v>5.06099987030029</v>
       </c>
       <c r="G176" t="n">
-        <v>3.41681742668152</v>
+        <v>3.4168176651001</v>
       </c>
       <c r="H176" t="n">
         <v>743828</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538101196289</v>
+        <v>3.35538077354431</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044756889343</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5705,7 +5705,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437075614929</v>
+        <v>3.43437099456787</v>
       </c>
       <c r="H184" t="n">
         <v>1118182</v>
@@ -5763,7 +5763,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H186" t="n">
         <v>1032448</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837327003479</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116056442261</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -5966,7 +5966,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="n">
         <v>1635754</v>
@@ -6024,7 +6024,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H195" t="n">
         <v>1707922</v>
@@ -6053,7 +6053,7 @@
         <v>5.10300016403198</v>
       </c>
       <c r="G196" t="n">
-        <v>3.44517302513123</v>
+        <v>3.4451732635498</v>
       </c>
       <c r="H196" t="n">
         <v>1313665</v>
@@ -6082,7 +6082,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340155601501</v>
+        <v>3.46340131759644</v>
       </c>
       <c r="H197" t="n">
         <v>1022230</v>
@@ -6111,7 +6111,7 @@
         <v>5.14699983596802</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47487854957581</v>
+        <v>3.47487831115723</v>
       </c>
       <c r="H198" t="n">
         <v>1005472</v>
@@ -6198,7 +6198,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G201" t="n">
-        <v>3.39858937263489</v>
+        <v>3.39858913421631</v>
       </c>
       <c r="H201" t="n">
         <v>960763</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50796008110046</v>
+        <v>3.50795984268188</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6343,7 +6343,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842705726624</v>
+        <v>3.59842658042908</v>
       </c>
       <c r="H206" t="n">
         <v>578241</v>
@@ -6372,7 +6372,7 @@
         <v>5.36800003051758</v>
       </c>
       <c r="G207" t="n">
-        <v>3.62408185005188</v>
+        <v>3.6240816116333</v>
       </c>
       <c r="H207" t="n">
         <v>1039336</v>
@@ -6430,7 +6430,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G209" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H209" t="n">
         <v>1632705</v>
@@ -6459,7 +6459,7 @@
         <v>5.51800012588501</v>
       </c>
       <c r="G210" t="n">
-        <v>3.72535061836243</v>
+        <v>3.72535085678101</v>
       </c>
       <c r="H210" t="n">
         <v>1178589</v>
@@ -6546,7 +6546,7 @@
         <v>5.48899984359741</v>
       </c>
       <c r="G213" t="n">
-        <v>3.70577216148376</v>
+        <v>3.70577192306519</v>
       </c>
       <c r="H213" t="n">
         <v>1086736</v>
@@ -6575,7 +6575,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="n">
         <v>561510</v>
@@ -6604,7 +6604,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="n">
         <v>771072</v>
@@ -6691,7 +6691,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G218" t="n">
-        <v>3.76450800895691</v>
+        <v>3.76450824737549</v>
       </c>
       <c r="H218" t="n">
         <v>1097994</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6749,7 +6749,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324942588806</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="n">
         <v>1345223</v>
@@ -6807,7 +6807,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>4.20266532897949</v>
+        <v>4.20266580581665</v>
       </c>
       <c r="H222" t="n">
         <v>2465306</v>
@@ -6894,7 +6894,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916273117065</v>
+        <v>4.18916320800781</v>
       </c>
       <c r="H225" t="n">
         <v>1148359</v>
@@ -6923,7 +6923,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620874404907</v>
+        <v>4.16620826721191</v>
       </c>
       <c r="H226" t="n">
         <v>1220830</v>
@@ -7010,7 +7010,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.17903614044189</v>
+        <v>4.17903566360474</v>
       </c>
       <c r="H229" t="n">
         <v>548307</v>
@@ -7097,7 +7097,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="n">
         <v>341527</v>
@@ -7126,7 +7126,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629547119141</v>
+        <v>4.22629499435425</v>
       </c>
       <c r="H233" t="n">
         <v>709890</v>
@@ -7271,7 +7271,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>4.36807155609131</v>
+        <v>4.36807203292847</v>
       </c>
       <c r="H238" t="n">
         <v>855642</v>
@@ -7358,7 +7358,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="n">
         <v>1305794</v>
@@ -7387,7 +7387,7 @@
         <v>6.20300006866455</v>
       </c>
       <c r="G242" t="n">
-        <v>4.18781232833862</v>
+        <v>4.18781280517578</v>
       </c>
       <c r="H242" t="n">
         <v>718598</v>
@@ -7445,7 +7445,7 @@
         <v>6.18599987030029</v>
       </c>
       <c r="G244" t="n">
-        <v>4.17633533477783</v>
+        <v>4.17633581161499</v>
       </c>
       <c r="H244" t="n">
         <v>568662</v>
@@ -7503,7 +7503,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G246" t="n">
-        <v>4.14257907867432</v>
+        <v>4.14257955551147</v>
       </c>
       <c r="H246" t="n">
         <v>1169428</v>
@@ -7561,7 +7561,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H248" t="n">
         <v>911894</v>
@@ -7590,7 +7590,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="n">
         <v>795631</v>
@@ -7619,7 +7619,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H250" t="n">
         <v>1305048</v>
@@ -7648,7 +7648,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788863182068</v>
+        <v>3.92788887023926</v>
       </c>
       <c r="H251" t="n">
         <v>1142347</v>
@@ -7677,7 +7677,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G252" t="n">
-        <v>3.75033044815063</v>
+        <v>3.75033020973206</v>
       </c>
       <c r="H252" t="n">
         <v>2220991</v>
@@ -7706,7 +7706,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459449768066</v>
+        <v>3.82459425926208</v>
       </c>
       <c r="H253" t="n">
         <v>1270112</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771589279175</v>
+        <v>3.80771636962891</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7793,7 +7793,7 @@
         <v>5.61299991607666</v>
       </c>
       <c r="G256" t="n">
-        <v>3.78948783874512</v>
+        <v>3.78948760032654</v>
       </c>
       <c r="H256" t="n">
         <v>792824</v>
@@ -7851,7 +7851,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.87522864341736</v>
+        <v>3.87522888183594</v>
       </c>
       <c r="H258" t="n">
         <v>683671</v>
@@ -7938,7 +7938,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434569358826</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H261" t="n">
         <v>1652373</v>
@@ -8025,7 +8025,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604133605957</v>
+        <v>4.20604085922241</v>
       </c>
       <c r="H264" t="n">
         <v>1003317</v>
@@ -8054,7 +8054,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478227615356</v>
+        <v>4.42478179931641</v>
       </c>
       <c r="H265" t="n">
         <v>3181061</v>
@@ -8083,7 +8083,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>4.61786842346191</v>
+        <v>4.61786890029907</v>
       </c>
       <c r="H266" t="n">
         <v>4637628</v>
@@ -8141,7 +8141,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="n">
         <v>2146613</v>
@@ -8199,7 +8199,7 @@
         <v>6.90199995040894</v>
       </c>
       <c r="G270" t="n">
-        <v>4.6597261428833</v>
+        <v>4.65972661972046</v>
       </c>
       <c r="H270" t="n">
         <v>1305558</v>
@@ -8315,7 +8315,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H274" t="n">
         <v>1735281</v>
@@ -8373,7 +8373,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543750762939</v>
+        <v>5.11543703079224</v>
       </c>
       <c r="H276" t="n">
         <v>1864510</v>
@@ -8431,7 +8431,7 @@
         <v>7.45300006866455</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0317211151123</v>
+        <v>5.03172159194946</v>
       </c>
       <c r="H278" t="n">
         <v>1291216</v>
@@ -8489,7 +8489,7 @@
         <v>7.59299993515015</v>
       </c>
       <c r="G280" t="n">
-        <v>5.12623882293701</v>
+        <v>5.12623929977417</v>
       </c>
       <c r="H280" t="n">
         <v>1294165</v>
@@ -8576,7 +8576,7 @@
         <v>7.5310001373291</v>
       </c>
       <c r="G283" t="n">
-        <v>5.08438158035278</v>
+        <v>5.08438110351562</v>
       </c>
       <c r="H283" t="n">
         <v>1340387</v>
@@ -8605,7 +8605,7 @@
         <v>7.55200004577637</v>
       </c>
       <c r="G284" t="n">
-        <v>5.09855937957764</v>
+        <v>5.09855890274048</v>
       </c>
       <c r="H284" t="n">
         <v>773657</v>
@@ -8750,7 +8750,7 @@
         <v>9.26299953460693</v>
       </c>
       <c r="G289" t="n">
-        <v>6.25370025634766</v>
+        <v>6.25370073318481</v>
       </c>
       <c r="H289" t="n">
         <v>5659371</v>
@@ -8808,7 +8808,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>6.30231046676636</v>
+        <v>6.3023099899292</v>
       </c>
       <c r="H291" t="n">
         <v>1551590</v>
@@ -8895,7 +8895,7 @@
         <v>8.95600032806396</v>
       </c>
       <c r="G294" t="n">
-        <v>6.04643726348877</v>
+        <v>6.04643774032593</v>
       </c>
       <c r="H294" t="n">
         <v>1037804</v>
@@ -8924,7 +8924,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449281692505</v>
+        <v>5.94449329376221</v>
       </c>
       <c r="H295" t="n">
         <v>1414060</v>
@@ -8953,7 +8953,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G296" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H296" t="n">
         <v>990544</v>
@@ -9011,7 +9011,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>6.05926561355591</v>
+        <v>6.05926513671875</v>
       </c>
       <c r="H298" t="n">
         <v>834113</v>
@@ -9040,7 +9040,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G299" t="n">
-        <v>6.03293418884277</v>
+        <v>6.03293466567993</v>
       </c>
       <c r="H299" t="n">
         <v>974549</v>
@@ -9069,7 +9069,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G300" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H300" t="n">
         <v>774116</v>
@@ -9098,7 +9098,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H301" t="n">
         <v>740488</v>
@@ -9127,7 +9127,7 @@
         <v>9.11100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>6.15108156204224</v>
+        <v>6.15108203887939</v>
       </c>
       <c r="H302" t="n">
         <v>850913</v>
@@ -9185,7 +9185,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H304" t="n">
         <v>1512205</v>
@@ -9214,7 +9214,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="n">
         <v>1343595</v>
@@ -9272,7 +9272,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441165924072</v>
+        <v>6.04441213607788</v>
       </c>
       <c r="H307" t="n">
         <v>1036237</v>
@@ -9359,7 +9359,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="n">
         <v>1335804</v>
@@ -9388,7 +9388,7 @@
         <v>8.8769998550415</v>
       </c>
       <c r="G311" t="n">
-        <v>5.99310255050659</v>
+        <v>5.99310207366943</v>
       </c>
       <c r="H311" t="n">
         <v>1769031</v>
@@ -9504,7 +9504,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977293014526</v>
+        <v>6.09977245330811</v>
       </c>
       <c r="H315" t="n">
         <v>1294330</v>
@@ -9562,7 +9562,7 @@
         <v>8.56700038909912</v>
       </c>
       <c r="G317" t="n">
-        <v>5.7838134765625</v>
+        <v>5.78381299972534</v>
       </c>
       <c r="H317" t="n">
         <v>1777741</v>
@@ -9591,7 +9591,7 @@
         <v>8.85299968719482</v>
       </c>
       <c r="G318" t="n">
-        <v>5.97689914703369</v>
+        <v>5.97689867019653</v>
       </c>
       <c r="H318" t="n">
         <v>757013</v>
@@ -9620,7 +9620,7 @@
         <v>8.89299964904785</v>
       </c>
       <c r="G319" t="n">
-        <v>6.00390386581421</v>
+        <v>6.00390434265137</v>
       </c>
       <c r="H319" t="n">
         <v>742878</v>
@@ -9678,7 +9678,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748809814453</v>
+        <v>5.91748857498169</v>
       </c>
       <c r="H321" t="n">
         <v>905026</v>
@@ -9736,7 +9736,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047828674316</v>
       </c>
       <c r="H323" t="n">
         <v>1626293</v>
@@ -9765,7 +9765,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H324" t="n">
         <v>1282373</v>
@@ -9823,7 +9823,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.3064980506897</v>
+        <v>5.30649852752686</v>
       </c>
       <c r="H326" t="n">
         <v>1268089</v>
@@ -9910,7 +9910,7 @@
         <v>7.96799993515015</v>
       </c>
       <c r="G329" t="n">
-        <v>5.3794116973877</v>
+        <v>5.37941217422485</v>
       </c>
       <c r="H329" t="n">
         <v>756992</v>
@@ -9997,7 +9997,7 @@
         <v>8.33800029754639</v>
       </c>
       <c r="G332" t="n">
-        <v>5.62920951843262</v>
+        <v>5.62920904159546</v>
       </c>
       <c r="H332" t="n">
         <v>2007066</v>
@@ -10026,7 +10026,7 @@
         <v>8.29599952697754</v>
       </c>
       <c r="G333" t="n">
-        <v>5.60085296630859</v>
+        <v>5.60085344314575</v>
       </c>
       <c r="H333" t="n">
         <v>1137057</v>
@@ -10084,7 +10084,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672107696533</v>
+        <v>5.69672155380249</v>
       </c>
       <c r="H335" t="n">
         <v>1097585</v>
@@ -10142,7 +10142,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G337" t="n">
-        <v>5.54144239425659</v>
+        <v>5.54144191741943</v>
       </c>
       <c r="H337" t="n">
         <v>731614</v>
@@ -10403,7 +10403,7 @@
         <v>7.96199989318848</v>
       </c>
       <c r="G346" t="n">
-        <v>5.3753604888916</v>
+        <v>5.37536096572876</v>
       </c>
       <c r="H346" t="n">
         <v>1300436</v>
@@ -10490,7 +10490,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G349" t="n">
-        <v>4.95948314666748</v>
+        <v>4.95948266983032</v>
       </c>
       <c r="H349" t="n">
         <v>3108681</v>
@@ -10519,7 +10519,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003080368042</v>
+        <v>4.95003128051758</v>
       </c>
       <c r="H350" t="n">
         <v>1343262</v>
@@ -10693,7 +10693,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910751342773</v>
+        <v>5.08910703659058</v>
       </c>
       <c r="H356" t="n">
         <v>721988</v>
@@ -10751,7 +10751,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G358" t="n">
-        <v>4.8217568397522</v>
+        <v>4.82175731658936</v>
       </c>
       <c r="H358" t="n">
         <v>1382671</v>
@@ -10867,7 +10867,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71643733978271</v>
+        <v>4.71643686294556</v>
       </c>
       <c r="H362" t="n">
         <v>2613625</v>
@@ -10896,7 +10896,7 @@
         <v>7.06199979782104</v>
       </c>
       <c r="G363" t="n">
-        <v>4.767746925354</v>
+        <v>4.76774644851685</v>
       </c>
       <c r="H363" t="n">
         <v>1027763</v>
@@ -10983,7 +10983,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568607330322</v>
+        <v>4.97568559646606</v>
       </c>
       <c r="H366" t="n">
         <v>978343</v>
@@ -11041,7 +11041,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543193817139</v>
+        <v>4.95543241500854</v>
       </c>
       <c r="H368" t="n">
         <v>1136830</v>
@@ -11070,7 +11070,7 @@
         <v>7.32600021362305</v>
       </c>
       <c r="G369" t="n">
-        <v>4.94598054885864</v>
+        <v>4.94598007202148</v>
       </c>
       <c r="H369" t="n">
         <v>618100</v>
@@ -11186,7 +11186,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G373" t="n">
-        <v>5.21603107452393</v>
+        <v>5.21603059768677</v>
       </c>
       <c r="H373" t="n">
         <v>584786</v>
@@ -11302,7 +11302,7 @@
         <v>7.93200016021729</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35510730743408</v>
+        <v>5.35510778427124</v>
       </c>
       <c r="H377" t="n">
         <v>3080122</v>
@@ -11360,7 +11360,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>5.45502614974976</v>
+        <v>5.4550256729126</v>
       </c>
       <c r="H379" t="n">
         <v>1476056</v>
@@ -11389,7 +11389,7 @@
         <v>8.0019998550415</v>
       </c>
       <c r="G380" t="n">
-        <v>5.40236568450928</v>
+        <v>5.40236616134644</v>
       </c>
       <c r="H380" t="n">
         <v>1291207</v>
@@ -11418,7 +11418,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="n">
         <v>1027240</v>
@@ -11534,7 +11534,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578760147095</v>
+        <v>5.51578712463379</v>
       </c>
       <c r="H385" t="n">
         <v>1237649</v>
@@ -11563,7 +11563,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148273468018</v>
+        <v>5.49148321151733</v>
       </c>
       <c r="H386" t="n">
         <v>1186915</v>
@@ -11650,7 +11650,7 @@
         <v>8.08600044250488</v>
       </c>
       <c r="G389" t="n">
-        <v>5.45907688140869</v>
+        <v>5.45907735824585</v>
       </c>
       <c r="H389" t="n">
         <v>1552098</v>
@@ -11679,7 +11679,7 @@
         <v>8.02400016784668</v>
       </c>
       <c r="G390" t="n">
-        <v>5.41721868515015</v>
+        <v>5.4172191619873</v>
       </c>
       <c r="H390" t="n">
         <v>610844</v>
@@ -11708,7 +11708,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G391" t="n">
-        <v>5.54144239425659</v>
+        <v>5.54144191741943</v>
       </c>
       <c r="H391" t="n">
         <v>1149636</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.61975717544556</v>
+        <v>5.6197566986084</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -11766,7 +11766,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562528610229</v>
+        <v>5.71562433242798</v>
       </c>
       <c r="H393" t="n">
         <v>1448265</v>
@@ -11795,7 +11795,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456935882568</v>
+        <v>5.68456888198853</v>
       </c>
       <c r="H394" t="n">
         <v>1342906</v>
@@ -11824,7 +11824,7 @@
         <v>8.4040002822876</v>
       </c>
       <c r="G395" t="n">
-        <v>5.67376804351807</v>
+        <v>5.67376756668091</v>
       </c>
       <c r="H395" t="n">
         <v>1175604</v>
@@ -11853,7 +11853,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>5.72912740707397</v>
+        <v>5.72912788391113</v>
       </c>
       <c r="H396" t="n">
         <v>1166669</v>
@@ -11911,7 +11911,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.56034564971924</v>
+        <v>5.5603461265564</v>
       </c>
       <c r="H398" t="n">
         <v>1662385</v>
@@ -12027,7 +12027,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="n">
         <v>890149</v>
@@ -12056,7 +12056,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460922241211</v>
+        <v>5.63461017608643</v>
       </c>
       <c r="H403" t="n">
         <v>1808163</v>
@@ -12143,7 +12143,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="n">
         <v>1665434</v>
@@ -12172,7 +12172,7 @@
         <v>9.53400039672852</v>
       </c>
       <c r="G407" t="n">
-        <v>6.43666076660156</v>
+        <v>6.43666124343872</v>
       </c>
       <c r="H407" t="n">
         <v>10634260</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="n">
         <v>2733714</v>
@@ -12259,7 +12259,7 @@
         <v>9.4060001373291</v>
       </c>
       <c r="G410" t="n">
-        <v>6.35024452209473</v>
+        <v>6.35024499893188</v>
       </c>
       <c r="H410" t="n">
         <v>1595872</v>
@@ -12288,7 +12288,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H411" t="n">
         <v>929420</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758453369141</v>
+        <v>6.29758405685425</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12375,7 +12375,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665058135986</v>
+        <v>6.11665105819702</v>
       </c>
       <c r="H414" t="n">
         <v>900855</v>
@@ -12404,7 +12404,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G415" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H415" t="n">
         <v>1271542</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044717788696</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12462,7 +12462,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.97487449645996</v>
+        <v>5.9748740196228</v>
       </c>
       <c r="H417" t="n">
         <v>839338</v>
@@ -12549,7 +12549,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>5.8263463973999</v>
+        <v>5.82634592056274</v>
       </c>
       <c r="H420" t="n">
         <v>1409991</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461988449097</v>
+        <v>5.95461940765381</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12752,7 +12752,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631624221802</v>
+        <v>6.19631576538086</v>
       </c>
       <c r="H427" t="n">
         <v>1981669</v>
@@ -12810,7 +12810,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.11124897003174</v>
+        <v>6.1112494468689</v>
       </c>
       <c r="H429" t="n">
         <v>462036</v>
@@ -12868,7 +12868,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H431" t="n">
         <v>1056988</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002054214478</v>
+        <v>5.96002149581909</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -12926,7 +12926,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698635101318</v>
+        <v>6.03698587417603</v>
       </c>
       <c r="H433" t="n">
         <v>771857</v>
@@ -12955,7 +12955,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479286193848</v>
+        <v>6.07479238510132</v>
       </c>
       <c r="H434" t="n">
         <v>513724</v>
@@ -12984,7 +12984,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G435" t="n">
-        <v>6.03023386001587</v>
+        <v>6.03023433685303</v>
       </c>
       <c r="H435" t="n">
         <v>1829397</v>
@@ -13100,7 +13100,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G439" t="n">
-        <v>5.97352313995361</v>
+        <v>5.97352361679077</v>
       </c>
       <c r="H439" t="n">
         <v>745131</v>
@@ -13129,7 +13129,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G440" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H440" t="n">
         <v>556517</v>
@@ -13158,7 +13158,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="n">
         <v>1296803</v>
@@ -13187,7 +13187,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G442" t="n">
-        <v>6.12610292434692</v>
+        <v>6.12610244750977</v>
       </c>
       <c r="H442" t="n">
         <v>812225</v>
@@ -13216,7 +13216,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G443" t="n">
-        <v>6.15040683746338</v>
+        <v>6.15040636062622</v>
       </c>
       <c r="H443" t="n">
         <v>1030117</v>
@@ -13245,7 +13245,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G444" t="n">
-        <v>6.20711755752563</v>
+        <v>6.20711803436279</v>
       </c>
       <c r="H444" t="n">
         <v>1671458</v>
@@ -13303,7 +13303,7 @@
         <v>9.10599994659424</v>
       </c>
       <c r="G446" t="n">
-        <v>6.14770698547363</v>
+        <v>6.14770650863647</v>
       </c>
       <c r="H446" t="n">
         <v>971388</v>
@@ -13361,7 +13361,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G448" t="n">
-        <v>5.98297595977783</v>
+        <v>5.98297548294067</v>
       </c>
       <c r="H448" t="n">
         <v>1062778</v>
@@ -13390,7 +13390,7 @@
         <v>8.85599994659424</v>
       </c>
       <c r="G449" t="n">
-        <v>5.97892475128174</v>
+        <v>5.97892427444458</v>
       </c>
       <c r="H449" t="n">
         <v>746956</v>
@@ -13419,7 +13419,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.9303150177002</v>
+        <v>5.93031549453735</v>
       </c>
       <c r="H450" t="n">
         <v>988269</v>
@@ -13448,7 +13448,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G451" t="n">
-        <v>5.97352313995361</v>
+        <v>5.97352361679077</v>
       </c>
       <c r="H451" t="n">
         <v>722064</v>
@@ -13535,7 +13535,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="n">
         <v>1565076</v>
@@ -13564,7 +13564,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G455" t="n">
-        <v>5.94246768951416</v>
+        <v>5.94246816635132</v>
       </c>
       <c r="H455" t="n">
         <v>1173522</v>
@@ -13593,7 +13593,7 @@
         <v>9.07800006866455</v>
       </c>
       <c r="G456" t="n">
-        <v>6.12880277633667</v>
+        <v>6.12880325317383</v>
       </c>
       <c r="H456" t="n">
         <v>2123712</v>
@@ -13622,7 +13622,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.05453872680664</v>
+        <v>6.0545392036438</v>
       </c>
       <c r="H457" t="n">
         <v>1441148</v>
@@ -13709,7 +13709,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984804153442</v>
+        <v>5.83984851837158</v>
       </c>
       <c r="H460" t="n">
         <v>2271949</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748205184937</v>
+        <v>5.75748300552368</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13796,7 +13796,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401056289673</v>
+        <v>5.37401103973389</v>
       </c>
       <c r="H463" t="n">
         <v>2564625</v>
@@ -13825,7 +13825,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29434585571289</v>
+        <v>5.29434537887573</v>
       </c>
       <c r="H464" t="n">
         <v>1025453</v>
@@ -13854,7 +13854,7 @@
         <v>7.83400011062622</v>
       </c>
       <c r="G465" t="n">
-        <v>5.28894472122192</v>
+        <v>5.28894519805908</v>
       </c>
       <c r="H465" t="n">
         <v>1213624</v>
@@ -13883,7 +13883,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409219741821</v>
+        <v>5.27409172058105</v>
       </c>
       <c r="H466" t="n">
         <v>851531</v>
@@ -13912,7 +13912,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700536727905</v>
+        <v>5.34700632095337</v>
       </c>
       <c r="H467" t="n">
         <v>1182375</v>
@@ -13941,7 +13941,7 @@
         <v>7.96600008010864</v>
       </c>
       <c r="G468" t="n">
-        <v>5.37806129455566</v>
+        <v>5.37806177139282</v>
       </c>
       <c r="H468" t="n">
         <v>921952</v>
@@ -13970,7 +13970,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H469" t="n">
         <v>812307</v>
@@ -14028,7 +14028,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89196968078613</v>
+        <v>4.89197015762329</v>
       </c>
       <c r="H471" t="n">
         <v>13000528</v>
@@ -14086,7 +14086,7 @@
         <v>7.15199995040894</v>
       </c>
       <c r="G473" t="n">
-        <v>4.82850790023804</v>
+        <v>4.8285083770752</v>
       </c>
       <c r="H473" t="n">
         <v>4573066</v>
@@ -14202,7 +14202,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.8501124382019</v>
+        <v>4.85011196136475</v>
       </c>
       <c r="H477" t="n">
         <v>2148643</v>
@@ -14231,7 +14231,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669099807739</v>
+        <v>4.73669052124023</v>
       </c>
       <c r="H478" t="n">
         <v>2197891</v>
@@ -14318,7 +14318,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G481" t="n">
-        <v>4.96893501281738</v>
+        <v>4.96893453598022</v>
       </c>
       <c r="H481" t="n">
         <v>3692477</v>
@@ -14347,7 +14347,7 @@
         <v>7.25</v>
       </c>
       <c r="G482" t="n">
-        <v>4.8946704864502</v>
+        <v>4.89467000961304</v>
       </c>
       <c r="H482" t="n">
         <v>2096743</v>
@@ -14521,7 +14521,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.92302560806274</v>
+        <v>4.9230260848999</v>
       </c>
       <c r="H488" t="n">
         <v>1062819</v>
@@ -14550,7 +14550,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.86091423034668</v>
+        <v>4.86091470718384</v>
       </c>
       <c r="H489" t="n">
         <v>997609</v>
@@ -14666,7 +14666,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="n">
         <v>2819991</v>
@@ -14724,7 +14724,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004194259644</v>
+        <v>5.27004098892212</v>
       </c>
       <c r="H495" t="n">
         <v>2448121</v>
@@ -14782,7 +14782,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>5.31324911117554</v>
+        <v>5.3132495880127</v>
       </c>
       <c r="H497" t="n">
         <v>1593539</v>
@@ -14898,7 +14898,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847774505615</v>
+        <v>5.19847726821899</v>
       </c>
       <c r="H501" t="n">
         <v>2160367</v>
@@ -14985,7 +14985,7 @@
         <v>7.87400007247925</v>
       </c>
       <c r="G504" t="n">
-        <v>5.3159499168396</v>
+        <v>5.31595039367676</v>
       </c>
       <c r="H504" t="n">
         <v>1319000</v>
@@ -15101,7 +15101,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076210021973</v>
+        <v>5.38076162338257</v>
       </c>
       <c r="H508" t="n">
         <v>821721</v>
@@ -15130,7 +15130,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H509" t="n">
         <v>1443560</v>
@@ -15188,7 +15188,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958419799805</v>
+        <v>5.49958467483521</v>
       </c>
       <c r="H511" t="n">
         <v>928002</v>
@@ -15391,7 +15391,7 @@
         <v>8.69799995422363</v>
       </c>
       <c r="G518" t="n">
-        <v>5.87225484848022</v>
+        <v>5.87225437164307</v>
       </c>
       <c r="H518" t="n">
         <v>1992357</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21792030334473</v>
+        <v>6.21791934967041</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37725019454956</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15478,7 +15478,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.37454986572266</v>
+        <v>6.3745493888855</v>
       </c>
       <c r="H521" t="n">
         <v>4282126</v>
@@ -15507,7 +15507,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914825439453</v>
+        <v>6.36914777755737</v>
       </c>
       <c r="H522" t="n">
         <v>2967550</v>
@@ -15536,7 +15536,7 @@
         <v>9.25</v>
       </c>
       <c r="G523" t="n">
-        <v>6.24492502212524</v>
+        <v>6.24492454528809</v>
       </c>
       <c r="H523" t="n">
         <v>1934023</v>
@@ -15565,7 +15565,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="n">
         <v>1721895</v>
@@ -15594,7 +15594,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H525" t="n">
         <v>1802779</v>
@@ -15623,7 +15623,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="n">
         <v>994506</v>
@@ -15739,7 +15739,7 @@
         <v>9.60599994659424</v>
       </c>
       <c r="G530" t="n">
-        <v>6.48527050018311</v>
+        <v>6.48527002334595</v>
       </c>
       <c r="H530" t="n">
         <v>1752325</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5824875831604</v>
+        <v>6.58248853683472</v>
       </c>
       <c r="H531" t="n">
         <v>1252149</v>
@@ -15797,7 +15797,7 @@
         <v>9.84200000762939</v>
       </c>
       <c r="G532" t="n">
-        <v>6.64459943771362</v>
+        <v>6.64459991455078</v>
       </c>
       <c r="H532" t="n">
         <v>1780393</v>
@@ -15826,7 +15826,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G533" t="n">
-        <v>6.69185829162598</v>
+        <v>6.69185876846313</v>
       </c>
       <c r="H533" t="n">
         <v>2342231</v>
@@ -15855,7 +15855,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>6.71751308441162</v>
+        <v>6.71751356124878</v>
       </c>
       <c r="H534" t="n">
         <v>1809327</v>
@@ -15942,7 +15942,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080284118652</v>
+        <v>6.66080331802368</v>
       </c>
       <c r="H537" t="n">
         <v>956747</v>
@@ -15971,7 +15971,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320821762085</v>
+        <v>6.69320869445801</v>
       </c>
       <c r="H538" t="n">
         <v>1117605</v>
@@ -16029,7 +16029,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284372329712</v>
+        <v>7.14284324645996</v>
       </c>
       <c r="H540" t="n">
         <v>6833320</v>
@@ -16145,7 +16145,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>7.50403690338135</v>
+        <v>7.50403642654419</v>
       </c>
       <c r="H544" t="n">
         <v>1662762</v>
@@ -16261,7 +16261,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47027969360352</v>
+        <v>7.47028017044067</v>
       </c>
       <c r="H548" t="n">
         <v>2964098</v>
@@ -16290,7 +16290,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.450026512146</v>
+        <v>7.45002603530884</v>
       </c>
       <c r="H549" t="n">
         <v>2293340</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147287368774</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835147857666</v>
+        <v>7.84835195541382</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16406,7 +16406,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G553" t="n">
-        <v>7.88885927200317</v>
+        <v>7.88885879516602</v>
       </c>
       <c r="H553" t="n">
         <v>978481</v>
@@ -16464,7 +16464,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G555" t="n">
-        <v>8.08127021789551</v>
+        <v>8.08126926422119</v>
       </c>
       <c r="H555" t="n">
         <v>2829914</v>
@@ -16551,7 +16551,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G558" t="n">
-        <v>8.16228580474854</v>
+        <v>8.16228485107422</v>
       </c>
       <c r="H558" t="n">
         <v>1628712</v>
@@ -16609,7 +16609,7 @@
         <v>12.2550001144409</v>
       </c>
       <c r="G560" t="n">
-        <v>8.273681640625</v>
+        <v>8.27368068695068</v>
       </c>
       <c r="H560" t="n">
         <v>3458397</v>
@@ -16667,7 +16667,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G562" t="n">
-        <v>8.26355457305908</v>
+        <v>8.26355361938477</v>
       </c>
       <c r="H562" t="n">
         <v>2570522</v>
@@ -16783,7 +16783,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053375244141</v>
+        <v>8.82053470611572</v>
       </c>
       <c r="H566" t="n">
         <v>3617516</v>
@@ -16870,7 +16870,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="n">
         <v>1639116</v>
@@ -16899,7 +16899,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375762939453</v>
+        <v>9.34375667572021</v>
       </c>
       <c r="H570" t="n">
         <v>1437346</v>
@@ -16928,7 +16928,7 @@
         <v>13.9250001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>9.40114402770996</v>
+        <v>9.40114307403564</v>
       </c>
       <c r="H571" t="n">
         <v>1346272</v>
@@ -16986,7 +16986,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253986358643</v>
+        <v>9.51253890991211</v>
       </c>
       <c r="H573" t="n">
         <v>1118116</v>
@@ -17073,7 +17073,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840145111084</v>
+        <v>9.44840240478516</v>
       </c>
       <c r="H576" t="n">
         <v>2197272</v>
@@ -17131,7 +17131,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="n">
         <v>1873488</v>
@@ -17218,7 +17218,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243690490723</v>
+        <v>8.97243785858154</v>
       </c>
       <c r="H581" t="n">
         <v>4533092</v>
@@ -17276,7 +17276,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G583" t="n">
-        <v>8.5471076965332</v>
+        <v>8.54710674285889</v>
       </c>
       <c r="H583" t="n">
         <v>2183078</v>
@@ -17334,7 +17334,7 @@
         <v>12.5649995803833</v>
       </c>
       <c r="G585" t="n">
-        <v>8.48297119140625</v>
+        <v>8.48297023773193</v>
       </c>
       <c r="H585" t="n">
         <v>1264193</v>
@@ -17363,7 +17363,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G586" t="n">
-        <v>8.47621917724609</v>
+        <v>8.47622013092041</v>
       </c>
       <c r="H586" t="n">
         <v>1149074</v>
@@ -17392,7 +17392,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G587" t="n">
-        <v>8.47284412384033</v>
+        <v>8.47284507751465</v>
       </c>
       <c r="H587" t="n">
         <v>883840</v>
@@ -17537,7 +17537,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="n">
         <v>1799211</v>
@@ -17595,7 +17595,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="n">
         <v>1370145</v>
@@ -17624,7 +17624,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="n">
         <v>1343574</v>
@@ -17682,7 +17682,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="n">
         <v>2070634</v>
@@ -17711,7 +17711,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="n">
         <v>1111394</v>
@@ -17740,7 +17740,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="n">
         <v>1144101</v>
@@ -17769,7 +17769,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="n">
         <v>1299934</v>
@@ -17856,7 +17856,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="n">
         <v>4357376</v>
@@ -17943,7 +17943,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="n">
         <v>1233297</v>
@@ -18001,7 +18001,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="n">
         <v>943692</v>
@@ -18059,7 +18059,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="n">
         <v>1482029</v>
@@ -18146,7 +18146,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="n">
         <v>953411</v>
@@ -18233,7 +18233,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="n">
         <v>1263861</v>
@@ -18262,7 +18262,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="n">
         <v>1883401</v>
@@ -18349,7 +18349,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="n">
         <v>1949076</v>
@@ -18407,7 +18407,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="n">
         <v>2466372</v>
@@ -18436,7 +18436,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="n">
         <v>1875863</v>
@@ -18465,7 +18465,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="n">
         <v>2114723</v>
@@ -18494,7 +18494,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="n">
         <v>1003281</v>
@@ -18552,7 +18552,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="n">
         <v>2034035</v>
@@ -18639,7 +18639,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="n">
         <v>961522</v>
@@ -18668,7 +18668,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="n">
         <v>1340364</v>
@@ -18726,7 +18726,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="n">
         <v>1188311</v>
@@ -18755,7 +18755,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="n">
         <v>922139</v>
@@ -18842,7 +18842,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="n">
         <v>1104944</v>
@@ -18871,7 +18871,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="n">
         <v>1477565</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="n">
         <v>1299347</v>
@@ -19016,7 +19016,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="n">
         <v>1807666</v>
@@ -19103,7 +19103,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="n">
         <v>1668673</v>
@@ -19132,7 +19132,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="n">
         <v>1764822</v>
@@ -19161,7 +19161,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="n">
         <v>1235632</v>
@@ -19190,7 +19190,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="n">
         <v>1397538</v>
@@ -19219,7 +19219,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="n">
         <v>1895690</v>
@@ -19277,7 +19277,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="n">
         <v>1855485</v>
@@ -19364,7 +19364,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="n">
         <v>21113678</v>
@@ -19422,7 +19422,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="n">
         <v>4678338</v>
@@ -19451,7 +19451,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="n">
         <v>2619573</v>
@@ -19538,7 +19538,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="n">
         <v>2610988</v>
@@ -19567,7 +19567,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="n">
         <v>4162401</v>
@@ -19596,7 +19596,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="n">
         <v>4859349</v>
@@ -19712,7 +19712,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="n">
         <v>1004735</v>
@@ -19741,7 +19741,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="n">
         <v>997482</v>
@@ -19828,7 +19828,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="n">
         <v>2096737</v>
@@ -19944,7 +19944,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="n">
         <v>1440910</v>
@@ -20031,7 +20031,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="n">
         <v>1366723</v>
@@ -20060,7 +20060,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="n">
         <v>980480</v>
@@ -20176,7 +20176,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="n">
         <v>2106694</v>
@@ -20292,7 +20292,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="n">
         <v>1295054</v>
@@ -20466,7 +20466,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="n">
         <v>2462515</v>
@@ -20495,7 +20495,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="n">
         <v>1410849</v>
@@ -20524,7 +20524,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="n">
         <v>2437479</v>
@@ -20611,7 +20611,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="n">
         <v>3218967</v>
@@ -20640,7 +20640,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="n">
         <v>1981493</v>
@@ -20669,7 +20669,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="n">
         <v>2629183</v>
@@ -20756,7 +20756,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="n">
         <v>3178801</v>
@@ -20785,7 +20785,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="n">
         <v>3618036</v>
@@ -20901,7 +20901,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="n">
         <v>1498085</v>
@@ -20930,7 +20930,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="n">
         <v>2955864</v>
@@ -20959,7 +20959,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="n">
         <v>2554492</v>
@@ -21162,7 +21162,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="n">
         <v>2640643</v>
@@ -21220,7 +21220,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="n">
         <v>1962181</v>
@@ -21278,7 +21278,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="n">
         <v>3961916</v>
@@ -21336,7 +21336,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="n">
         <v>3582670</v>
@@ -21365,7 +21365,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="n">
         <v>2210569</v>
@@ -21423,7 +21423,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="n">
         <v>1858552</v>
@@ -21539,7 +21539,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="n">
         <v>8286642</v>
@@ -21626,7 +21626,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="n">
         <v>4138184</v>
@@ -21713,7 +21713,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="n">
         <v>2990029</v>
@@ -21742,7 +21742,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="n">
         <v>1630942</v>
@@ -21858,7 +21858,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="n">
         <v>1657610</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="n">
         <v>2906567</v>
@@ -22061,7 +22061,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="n">
         <v>1472605</v>
@@ -22119,7 +22119,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="n">
         <v>2428586</v>
@@ -22206,7 +22206,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="n">
         <v>1373245</v>
@@ -22235,7 +22235,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="n">
         <v>1786995</v>
@@ -22293,7 +22293,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="n">
         <v>2943745</v>
@@ -22322,7 +22322,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="n">
         <v>3277617</v>
@@ -22438,7 +22438,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="n">
         <v>2579512</v>
@@ -22467,7 +22467,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="n">
         <v>1442117</v>
@@ -22554,7 +22554,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="n">
         <v>2725833</v>
@@ -22902,7 +22902,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="n">
         <v>3966282</v>
@@ -22989,7 +22989,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="n">
         <v>2399106</v>
@@ -23192,7 +23192,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="n">
         <v>3020927</v>
@@ -23250,7 +23250,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="n">
         <v>2034103</v>
@@ -23279,7 +23279,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="n">
         <v>2487608</v>
@@ -23395,7 +23395,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="n">
         <v>4399432</v>
@@ -23656,7 +23656,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="n">
         <v>1560972</v>
@@ -23830,7 +23830,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="n">
         <v>3171229</v>
@@ -23859,7 +23859,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="n">
         <v>2951875</v>
@@ -23888,7 +23888,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="n">
         <v>2115144</v>
@@ -23946,7 +23946,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="n">
         <v>1560898</v>
@@ -24033,7 +24033,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="n">
         <v>3500840</v>
@@ -24120,7 +24120,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="n">
         <v>2998052</v>
@@ -24207,7 +24207,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="n">
         <v>1495955</v>
@@ -24236,7 +24236,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="n">
         <v>1503927</v>
@@ -24294,7 +24294,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="n">
         <v>1813430</v>
@@ -24352,7 +24352,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="n">
         <v>2267336</v>
@@ -24381,7 +24381,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="n">
         <v>1710958</v>
@@ -24526,7 +24526,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="n">
         <v>2682628</v>
@@ -24584,7 +24584,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="n">
         <v>2895890</v>
@@ -24613,7 +24613,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="n">
         <v>1823500</v>
@@ -35842,6 +35842,35 @@
         <v>2329667</v>
       </c>
       <c r="I1223" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1224" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>14.2250003814697</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>14.3149995803833</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>14.1925001144409</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>14.2749996185303</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>14.2749996185303</v>
+      </c>
+      <c r="H1224" t="n">
+        <v>1078143</v>
+      </c>
+      <c r="I1224" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23060989379883</v>
+        <v>7.23061037063599</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -543,7 +543,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705677032471</v>
+        <v>6.94705629348755</v>
       </c>
       <c r="H6" t="n">
         <v>11941139</v>
@@ -572,7 +572,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>6.859290599823</v>
+        <v>6.85929012298584</v>
       </c>
       <c r="H7" t="n">
         <v>6880124</v>
@@ -601,7 +601,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8525390625</v>
+        <v>6.85253858566284</v>
       </c>
       <c r="H8" t="n">
         <v>4472971</v>
@@ -717,7 +717,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010210037231</v>
+        <v>7.19010162353516</v>
       </c>
       <c r="H12" t="n">
         <v>3165422</v>
@@ -746,7 +746,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H13" t="n">
         <v>2435262</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>7.05507707595825</v>
+        <v>7.05507659912109</v>
       </c>
       <c r="H14" t="n">
         <v>2413549</v>
@@ -804,7 +804,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02132034301758</v>
+        <v>7.02131986618042</v>
       </c>
       <c r="H15" t="n">
         <v>1535035</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96730995178223</v>
+        <v>6.96731042861938</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -862,7 +862,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47109222412109</v>
+        <v>6.47109270095825</v>
       </c>
       <c r="H17" t="n">
         <v>4229589</v>
@@ -891,7 +891,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H18" t="n">
         <v>3251441</v>
@@ -1036,7 +1036,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>6.43058443069458</v>
+        <v>6.43058395385742</v>
       </c>
       <c r="H23" t="n">
         <v>3182466</v>
@@ -1239,7 +1239,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238653182983</v>
+        <v>6.04238605499268</v>
       </c>
       <c r="H30" t="n">
         <v>4204295</v>
@@ -1268,7 +1268,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284332275391</v>
+        <v>5.81284284591675</v>
       </c>
       <c r="H31" t="n">
         <v>3316128</v>
@@ -1384,7 +1384,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4550256729126</v>
+        <v>5.45502614974976</v>
       </c>
       <c r="H35" t="n">
         <v>3404051</v>
@@ -1413,7 +1413,7 @@
         <v>8.05500030517578</v>
       </c>
       <c r="G36" t="n">
-        <v>5.43814849853516</v>
+        <v>5.438148021698</v>
       </c>
       <c r="H36" t="n">
         <v>2313680</v>
@@ -1442,7 +1442,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637098312378</v>
+        <v>5.29637145996094</v>
       </c>
       <c r="H37" t="n">
         <v>2369088</v>
@@ -1500,7 +1500,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548294067383</v>
+        <v>5.22548246383667</v>
       </c>
       <c r="H39" t="n">
         <v>1845591</v>
@@ -1587,7 +1587,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G42" t="n">
-        <v>5.02631998062134</v>
+        <v>5.0263204574585</v>
       </c>
       <c r="H42" t="n">
         <v>2532581</v>
@@ -1703,7 +1703,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692937850952</v>
+        <v>4.27692985534668</v>
       </c>
       <c r="H46" t="n">
         <v>3684492</v>
@@ -1732,7 +1732,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13852787017822</v>
+        <v>4.13852834701538</v>
       </c>
       <c r="H47" t="n">
         <v>5966204</v>
@@ -1819,7 +1819,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13852787017822</v>
+        <v>4.13852834701538</v>
       </c>
       <c r="H50" t="n">
         <v>5312212</v>
@@ -1906,7 +1906,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533041000366</v>
+        <v>4.41533088684082</v>
       </c>
       <c r="H53" t="n">
         <v>2670255</v>
@@ -2022,7 +2022,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44233512878418</v>
+        <v>4.44233560562134</v>
       </c>
       <c r="H57" t="n">
         <v>2303616</v>
@@ -2109,7 +2109,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.41195487976074</v>
+        <v>4.4119553565979</v>
       </c>
       <c r="H60" t="n">
         <v>1556296</v>
@@ -2138,7 +2138,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967052459717</v>
+        <v>4.22967004776001</v>
       </c>
       <c r="H61" t="n">
         <v>3912970</v>
@@ -2167,7 +2167,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667524337769</v>
+        <v>4.25667572021484</v>
       </c>
       <c r="H62" t="n">
         <v>3017576</v>
@@ -2196,7 +2196,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>4.43558406829834</v>
+        <v>4.4355845451355</v>
       </c>
       <c r="H63" t="n">
         <v>4427308</v>
@@ -2312,7 +2312,7 @@
         <v>5.94299983978271</v>
       </c>
       <c r="G67" t="n">
-        <v>4.01227951049805</v>
+        <v>4.01227998733521</v>
       </c>
       <c r="H67" t="n">
         <v>2524391</v>
@@ -2341,7 +2341,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.84484815597534</v>
+        <v>3.84484839439392</v>
       </c>
       <c r="H68" t="n">
         <v>4549813</v>
@@ -2544,7 +2544,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G75" t="n">
-        <v>4.02240705490112</v>
+        <v>4.02240657806396</v>
       </c>
       <c r="H75" t="n">
         <v>2815887</v>
@@ -2689,7 +2689,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822392463684</v>
+        <v>3.84822368621826</v>
       </c>
       <c r="H80" t="n">
         <v>1805442</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995529174805</v>
+        <v>3.87995505332947</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286360740662</v>
+        <v>3.79286336898804</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311726570129</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2863,7 +2863,7 @@
         <v>5.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3.88197994232178</v>
+        <v>3.88198018074036</v>
       </c>
       <c r="H86" t="n">
         <v>1785095</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619346618652</v>
+        <v>3.68619322776794</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437584877014</v>
+        <v>3.59437608718872</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496479988098</v>
+        <v>3.53496503829956</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3037,7 +3037,7 @@
         <v>5.41900014877319</v>
       </c>
       <c r="G92" t="n">
-        <v>3.65851306915283</v>
+        <v>3.65851330757141</v>
       </c>
       <c r="H92" t="n">
         <v>1860265</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395987510681</v>
+        <v>3.77395963668823</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240148544312</v>
+        <v>3.86240172386169</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3211,7 +3211,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G98" t="n">
-        <v>3.80231499671936</v>
+        <v>3.80231523513794</v>
       </c>
       <c r="H98" t="n">
         <v>1569339</v>
@@ -3269,7 +3269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446743011475</v>
+        <v>3.81446766853333</v>
       </c>
       <c r="H100" t="n">
         <v>1355091</v>
@@ -3414,7 +3414,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802103042603</v>
+        <v>4.09802055358887</v>
       </c>
       <c r="H105" t="n">
         <v>1510660</v>
@@ -3443,7 +3443,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>4.0001277923584</v>
+        <v>4.00012731552124</v>
       </c>
       <c r="H106" t="n">
         <v>1710248</v>
@@ -3501,7 +3501,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354875564575</v>
+        <v>4.11354827880859</v>
       </c>
       <c r="H108" t="n">
         <v>1792655</v>
@@ -3530,7 +3530,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12030029296875</v>
+        <v>4.12029981613159</v>
       </c>
       <c r="H109" t="n">
         <v>2831477</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594975471497</v>
+        <v>3.98594927787781</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3704,7 +3704,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761969566345</v>
+        <v>3.42761993408203</v>
       </c>
       <c r="H115" t="n">
         <v>4636137</v>
@@ -3791,7 +3791,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H118" t="n">
         <v>2452422</v>
@@ -3820,7 +3820,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302592277527</v>
+        <v>3.59302568435669</v>
       </c>
       <c r="H119" t="n">
         <v>4765434</v>
@@ -3849,7 +3849,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944192886353</v>
+        <v>3.67944169044495</v>
       </c>
       <c r="H120" t="n">
         <v>1265113</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.65716290473938</v>
+        <v>3.6571626663208</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3994,7 +3994,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091406822205</v>
+        <v>3.53091430664062</v>
       </c>
       <c r="H125" t="n">
         <v>1761818</v>
@@ -4052,7 +4052,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682275772095</v>
+        <v>3.57682251930237</v>
       </c>
       <c r="H127" t="n">
         <v>1305635</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.40399026870728</v>
+        <v>3.4039900302887</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4168,7 +4168,7 @@
         <v>4.74849987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20584034919739</v>
+        <v>3.20584058761597</v>
       </c>
       <c r="H131" t="n">
         <v>3762380</v>
@@ -4255,7 +4255,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724406242371</v>
+        <v>3.55724430084229</v>
       </c>
       <c r="H134" t="n">
         <v>2393460</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.45665001869202</v>
+        <v>3.4566502571106</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.2132670879364</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4400,7 +4400,7 @@
         <v>5.02400016784668</v>
       </c>
       <c r="G139" t="n">
-        <v>3.39183783531189</v>
+        <v>3.39183807373047</v>
       </c>
       <c r="H139" t="n">
         <v>1947099</v>
@@ -4429,7 +4429,7 @@
         <v>5.11299991607666</v>
       </c>
       <c r="G140" t="n">
-        <v>3.45192432403564</v>
+        <v>3.45192408561707</v>
       </c>
       <c r="H140" t="n">
         <v>1625180</v>
@@ -4516,7 +4516,7 @@
         <v>5.38399982452393</v>
       </c>
       <c r="G143" t="n">
-        <v>3.63488364219666</v>
+        <v>3.63488340377808</v>
       </c>
       <c r="H143" t="n">
         <v>2301198</v>
@@ -4545,7 +4545,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813258171082</v>
+        <v>3.62813234329224</v>
       </c>
       <c r="H144" t="n">
         <v>1162846</v>
@@ -4603,7 +4603,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226447105408</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="n">
         <v>1532624</v>
@@ -4719,7 +4719,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>3.89143204689026</v>
+        <v>3.89143180847168</v>
       </c>
       <c r="H150" t="n">
         <v>1641881</v>
@@ -4806,7 +4806,7 @@
         <v>5.75899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>3.88805651664734</v>
+        <v>3.88805627822876</v>
       </c>
       <c r="H153" t="n">
         <v>2138183</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290904045105</v>
+        <v>3.90290951728821</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573643684387</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4893,7 +4893,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387871742249</v>
+        <v>3.87387847900391</v>
       </c>
       <c r="H156" t="n">
         <v>947624</v>
@@ -5009,7 +5009,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126949310303</v>
+        <v>4.09126901626587</v>
       </c>
       <c r="H160" t="n">
         <v>1170223</v>
@@ -5067,7 +5067,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067568778992</v>
+        <v>3.99067521095276</v>
       </c>
       <c r="H162" t="n">
         <v>836698</v>
@@ -5096,7 +5096,7 @@
         <v>5.75</v>
       </c>
       <c r="G163" t="n">
-        <v>3.88197994232178</v>
+        <v>3.88198018074036</v>
       </c>
       <c r="H163" t="n">
         <v>830988</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370597839355</v>
+        <v>3.75370573997498</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5212,7 +5212,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539095878601</v>
       </c>
       <c r="H167" t="n">
         <v>1508487</v>
@@ -5299,7 +5299,7 @@
         <v>5.16400003433228</v>
       </c>
       <c r="G170" t="n">
-        <v>3.48635601997375</v>
+        <v>3.48635578155518</v>
       </c>
       <c r="H170" t="n">
         <v>1032447</v>
@@ -5328,7 +5328,7 @@
         <v>5.05600023269653</v>
       </c>
       <c r="G171" t="n">
-        <v>3.41344213485718</v>
+        <v>3.41344237327576</v>
       </c>
       <c r="H171" t="n">
         <v>1569176</v>
@@ -5357,7 +5357,7 @@
         <v>4.94549989700317</v>
       </c>
       <c r="G172" t="n">
-        <v>3.33884048461914</v>
+        <v>3.33884024620056</v>
       </c>
       <c r="H172" t="n">
         <v>1226903</v>
@@ -5386,7 +5386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H173" t="n">
         <v>1536086</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538077354431</v>
+        <v>3.35538101196289</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5531,7 +5531,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G178" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H178" t="n">
         <v>1113895</v>
@@ -5560,7 +5560,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.52483820915222</v>
+        <v>3.5248384475708</v>
       </c>
       <c r="H179" t="n">
         <v>1218078</v>
@@ -5647,7 +5647,7 @@
         <v>5.06699991226196</v>
       </c>
       <c r="G182" t="n">
-        <v>3.42086815834045</v>
+        <v>3.42086839675903</v>
       </c>
       <c r="H182" t="n">
         <v>748112</v>
@@ -5705,7 +5705,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437099456787</v>
+        <v>3.43437075614929</v>
       </c>
       <c r="H184" t="n">
         <v>1118182</v>
@@ -5763,7 +5763,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H186" t="n">
         <v>1032448</v>
@@ -6024,7 +6024,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>3.47690391540527</v>
+        <v>3.47690415382385</v>
       </c>
       <c r="H195" t="n">
         <v>1707922</v>
@@ -6053,7 +6053,7 @@
         <v>5.10300016403198</v>
       </c>
       <c r="G196" t="n">
-        <v>3.4451732635498</v>
+        <v>3.44517302513123</v>
       </c>
       <c r="H196" t="n">
         <v>1313665</v>
@@ -6111,7 +6111,7 @@
         <v>5.14699983596802</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47487831115723</v>
+        <v>3.47487854957581</v>
       </c>
       <c r="H198" t="n">
         <v>1005472</v>
@@ -6198,7 +6198,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G201" t="n">
-        <v>3.39858913421631</v>
+        <v>3.39858937263489</v>
       </c>
       <c r="H201" t="n">
         <v>960763</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50795984268188</v>
+        <v>3.50796008110046</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6285,7 +6285,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51066017150879</v>
+        <v>3.51065993309021</v>
       </c>
       <c r="H204" t="n">
         <v>601405</v>
@@ -6343,7 +6343,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G206" t="n">
-        <v>3.59842658042908</v>
+        <v>3.59842681884766</v>
       </c>
       <c r="H206" t="n">
         <v>578241</v>
@@ -6401,7 +6401,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678241729736</v>
+        <v>3.62678217887878</v>
       </c>
       <c r="H208" t="n">
         <v>815597</v>
@@ -6633,7 +6633,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079233169556</v>
+        <v>3.68079257011414</v>
       </c>
       <c r="H216" t="n">
         <v>710760</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573643684387</v>
+        <v>3.91573691368103</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6778,7 +6778,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527940750122</v>
+        <v>4.14527988433838</v>
       </c>
       <c r="H221" t="n">
         <v>3310511</v>
@@ -6807,7 +6807,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>4.20266580581665</v>
+        <v>4.20266532897949</v>
       </c>
       <c r="H222" t="n">
         <v>2465306</v>
@@ -6981,7 +6981,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H228" t="n">
         <v>1114284</v>
@@ -7010,7 +7010,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G229" t="n">
-        <v>4.17903566360474</v>
+        <v>4.17903614044189</v>
       </c>
       <c r="H229" t="n">
         <v>548307</v>
@@ -7068,7 +7068,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106126785278</v>
+        <v>4.18106174468994</v>
       </c>
       <c r="H231" t="n">
         <v>540433</v>
@@ -7155,7 +7155,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840732574463</v>
       </c>
       <c r="H234" t="n">
         <v>1390641</v>
@@ -7242,7 +7242,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562488555908</v>
+        <v>4.38562440872192</v>
       </c>
       <c r="H237" t="n">
         <v>1118846</v>
@@ -7271,7 +7271,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>4.36807203292847</v>
+        <v>4.36807155609131</v>
       </c>
       <c r="H238" t="n">
         <v>855642</v>
@@ -7416,7 +7416,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886825561523</v>
+        <v>4.21886873245239</v>
       </c>
       <c r="H243" t="n">
         <v>1010763</v>
@@ -7503,7 +7503,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G246" t="n">
-        <v>4.14257955551147</v>
+        <v>4.14257907867432</v>
       </c>
       <c r="H246" t="n">
         <v>1169428</v>
@@ -7706,7 +7706,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459425926208</v>
+        <v>3.82459449768066</v>
       </c>
       <c r="H253" t="n">
         <v>1270112</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771636962891</v>
+        <v>3.80771613121033</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.7368278503418</v>
+        <v>3.73682808876038</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7851,7 +7851,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.87522888183594</v>
+        <v>3.87522864341736</v>
       </c>
       <c r="H258" t="n">
         <v>683671</v>
@@ -8025,7 +8025,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604085922241</v>
+        <v>4.20604133605957</v>
       </c>
       <c r="H264" t="n">
         <v>1003317</v>
@@ -8083,7 +8083,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G266" t="n">
-        <v>4.61786890029907</v>
+        <v>4.61786842346191</v>
       </c>
       <c r="H266" t="n">
         <v>4637628</v>
@@ -8228,7 +8228,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.73534059524536</v>
+        <v>4.7353401184082</v>
       </c>
       <c r="H271" t="n">
         <v>2895765</v>
@@ -8489,7 +8489,7 @@
         <v>7.59299993515015</v>
       </c>
       <c r="G280" t="n">
-        <v>5.12623929977417</v>
+        <v>5.12623882293701</v>
       </c>
       <c r="H280" t="n">
         <v>1294165</v>
@@ -8576,7 +8576,7 @@
         <v>7.5310001373291</v>
       </c>
       <c r="G283" t="n">
-        <v>5.08438110351562</v>
+        <v>5.08438158035278</v>
       </c>
       <c r="H283" t="n">
         <v>1340387</v>
@@ -8663,7 +8663,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902587890625</v>
+        <v>5.18902635574341</v>
       </c>
       <c r="H286" t="n">
         <v>2462672</v>
@@ -8808,7 +8808,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>6.3023099899292</v>
+        <v>6.30231046676636</v>
       </c>
       <c r="H291" t="n">
         <v>1551590</v>
@@ -8837,7 +8837,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707674026489</v>
+        <v>6.25707626342773</v>
       </c>
       <c r="H292" t="n">
         <v>1429447</v>
@@ -8895,7 +8895,7 @@
         <v>8.95600032806396</v>
       </c>
       <c r="G294" t="n">
-        <v>6.04643774032593</v>
+        <v>6.04643726348877</v>
       </c>
       <c r="H294" t="n">
         <v>1037804</v>
@@ -8924,7 +8924,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449329376221</v>
+        <v>5.94449281692505</v>
       </c>
       <c r="H295" t="n">
         <v>1414060</v>
@@ -8953,7 +8953,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G296" t="n">
-        <v>6.06264019012451</v>
+        <v>6.06263971328735</v>
       </c>
       <c r="H296" t="n">
         <v>990544</v>
@@ -9069,7 +9069,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G300" t="n">
-        <v>6.0450873374939</v>
+        <v>6.04508781433105</v>
       </c>
       <c r="H300" t="n">
         <v>774116</v>
@@ -9127,7 +9127,7 @@
         <v>9.11100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>6.15108203887939</v>
+        <v>6.15108156204224</v>
       </c>
       <c r="H302" t="n">
         <v>850913</v>
@@ -9388,7 +9388,7 @@
         <v>8.8769998550415</v>
       </c>
       <c r="G311" t="n">
-        <v>5.99310207366943</v>
+        <v>5.99310255050659</v>
       </c>
       <c r="H311" t="n">
         <v>1769031</v>
@@ -9475,7 +9475,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.86617851257324</v>
+        <v>5.8661789894104</v>
       </c>
       <c r="H314" t="n">
         <v>816021</v>
@@ -9562,7 +9562,7 @@
         <v>8.56700038909912</v>
       </c>
       <c r="G317" t="n">
-        <v>5.78381299972534</v>
+        <v>5.7838134765625</v>
       </c>
       <c r="H317" t="n">
         <v>1777741</v>
@@ -9591,7 +9591,7 @@
         <v>8.85299968719482</v>
       </c>
       <c r="G318" t="n">
-        <v>5.97689867019653</v>
+        <v>5.97689914703369</v>
       </c>
       <c r="H318" t="n">
         <v>757013</v>
@@ -9910,7 +9910,7 @@
         <v>7.96799993515015</v>
       </c>
       <c r="G329" t="n">
-        <v>5.37941217422485</v>
+        <v>5.3794116973877</v>
       </c>
       <c r="H329" t="n">
         <v>756992</v>
@@ -10026,7 +10026,7 @@
         <v>8.29599952697754</v>
       </c>
       <c r="G333" t="n">
-        <v>5.60085344314575</v>
+        <v>5.60085296630859</v>
       </c>
       <c r="H333" t="n">
         <v>1137057</v>
@@ -10142,7 +10142,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G337" t="n">
-        <v>5.54144191741943</v>
+        <v>5.54144239425659</v>
       </c>
       <c r="H337" t="n">
         <v>731614</v>
@@ -10432,7 +10432,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751316070557</v>
+        <v>5.38751363754272</v>
       </c>
       <c r="H347" t="n">
         <v>1047427</v>
@@ -10490,7 +10490,7 @@
         <v>7.34600019454956</v>
       </c>
       <c r="G349" t="n">
-        <v>4.95948266983032</v>
+        <v>4.95948314666748</v>
       </c>
       <c r="H349" t="n">
         <v>3108681</v>
@@ -10577,7 +10577,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809240341187</v>
+        <v>5.00809192657471</v>
       </c>
       <c r="H352" t="n">
         <v>1123756</v>
@@ -10693,7 +10693,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910703659058</v>
+        <v>5.08910751342773</v>
       </c>
       <c r="H356" t="n">
         <v>721988</v>
@@ -10867,7 +10867,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71643686294556</v>
+        <v>4.71643733978271</v>
       </c>
       <c r="H362" t="n">
         <v>2613625</v>
@@ -11041,7 +11041,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543241500854</v>
+        <v>4.95543193817139</v>
       </c>
       <c r="H368" t="n">
         <v>1136830</v>
@@ -11070,7 +11070,7 @@
         <v>7.32600021362305</v>
       </c>
       <c r="G369" t="n">
-        <v>4.94598007202148</v>
+        <v>4.94598054885864</v>
       </c>
       <c r="H369" t="n">
         <v>618100</v>
@@ -11186,7 +11186,7 @@
         <v>7.72599983215332</v>
       </c>
       <c r="G373" t="n">
-        <v>5.21603059768677</v>
+        <v>5.21603107452393</v>
       </c>
       <c r="H373" t="n">
         <v>584786</v>
@@ -11215,7 +11215,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G374" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H374" t="n">
         <v>1589421</v>
@@ -11302,7 +11302,7 @@
         <v>7.93200016021729</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35510778427124</v>
+        <v>5.35510730743408</v>
       </c>
       <c r="H377" t="n">
         <v>3080122</v>
@@ -11360,7 +11360,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G379" t="n">
-        <v>5.4550256729126</v>
+        <v>5.45502614974976</v>
       </c>
       <c r="H379" t="n">
         <v>1476056</v>
@@ -11447,7 +11447,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379772186279</v>
+        <v>5.30379724502563</v>
       </c>
       <c r="H382" t="n">
         <v>909012</v>
@@ -11505,7 +11505,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114791870117</v>
+        <v>5.57114839553833</v>
       </c>
       <c r="H384" t="n">
         <v>1867030</v>
@@ -11592,7 +11592,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H387" t="n">
         <v>1194785</v>
@@ -11708,7 +11708,7 @@
         <v>8.20800018310547</v>
       </c>
       <c r="G391" t="n">
-        <v>5.54144191741943</v>
+        <v>5.54144239425659</v>
       </c>
       <c r="H391" t="n">
         <v>1149636</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.6197566986084</v>
+        <v>5.61975717544556</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -11766,7 +11766,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G393" t="n">
-        <v>5.71562433242798</v>
+        <v>5.71562480926514</v>
       </c>
       <c r="H393" t="n">
         <v>1448265</v>
@@ -11853,7 +11853,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>5.72912788391113</v>
+        <v>5.72912740707397</v>
       </c>
       <c r="H396" t="n">
         <v>1166669</v>
@@ -11911,7 +11911,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.5603461265564</v>
+        <v>5.56034564971924</v>
       </c>
       <c r="H398" t="n">
         <v>1662385</v>
@@ -12056,7 +12056,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63461017608643</v>
+        <v>5.63460969924927</v>
       </c>
       <c r="H403" t="n">
         <v>1808163</v>
@@ -12172,7 +12172,7 @@
         <v>9.53400039672852</v>
       </c>
       <c r="G407" t="n">
-        <v>6.43666124343872</v>
+        <v>6.43666076660156</v>
       </c>
       <c r="H407" t="n">
         <v>10634260</v>
@@ -12259,7 +12259,7 @@
         <v>9.4060001373291</v>
       </c>
       <c r="G410" t="n">
-        <v>6.35024499893188</v>
+        <v>6.35024452209473</v>
       </c>
       <c r="H410" t="n">
         <v>1595872</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758405685425</v>
+        <v>6.29758453369141</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12375,7 +12375,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665105819702</v>
+        <v>6.11665058135986</v>
       </c>
       <c r="H414" t="n">
         <v>900855</v>
@@ -12462,7 +12462,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.9748740196228</v>
+        <v>5.97487449645996</v>
       </c>
       <c r="H417" t="n">
         <v>839338</v>
@@ -12491,7 +12491,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436622619629</v>
+        <v>5.93436574935913</v>
       </c>
       <c r="H418" t="n">
         <v>1220620</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461940765381</v>
+        <v>5.95461988449097</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12694,7 +12694,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457954406738</v>
+        <v>6.00457906723022</v>
       </c>
       <c r="H425" t="n">
         <v>1029644</v>
@@ -12781,7 +12781,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16930961608887</v>
       </c>
       <c r="H428" t="n">
         <v>729053</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002149581909</v>
+        <v>5.96002101898193</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -13042,7 +13042,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289432525635</v>
+        <v>6.08289384841919</v>
       </c>
       <c r="H437" t="n">
         <v>877361</v>
@@ -13100,7 +13100,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G439" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H439" t="n">
         <v>745131</v>
@@ -13129,7 +13129,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G440" t="n">
-        <v>6.0450873374939</v>
+        <v>6.04508781433105</v>
       </c>
       <c r="H440" t="n">
         <v>556517</v>
@@ -13187,7 +13187,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G442" t="n">
-        <v>6.12610244750977</v>
+        <v>6.12610292434692</v>
       </c>
       <c r="H442" t="n">
         <v>812225</v>
@@ -13216,7 +13216,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G443" t="n">
-        <v>6.15040636062622</v>
+        <v>6.15040683746338</v>
       </c>
       <c r="H443" t="n">
         <v>1030117</v>
@@ -13245,7 +13245,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G444" t="n">
-        <v>6.20711803436279</v>
+        <v>6.20711755752563</v>
       </c>
       <c r="H444" t="n">
         <v>1671458</v>
@@ -13361,7 +13361,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G448" t="n">
-        <v>5.98297548294067</v>
+        <v>5.98297595977783</v>
       </c>
       <c r="H448" t="n">
         <v>1062778</v>
@@ -13390,7 +13390,7 @@
         <v>8.85599994659424</v>
       </c>
       <c r="G449" t="n">
-        <v>5.97892427444458</v>
+        <v>5.97892475128174</v>
       </c>
       <c r="H449" t="n">
         <v>746956</v>
@@ -13419,7 +13419,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.93031549453735</v>
+        <v>5.9303150177002</v>
       </c>
       <c r="H450" t="n">
         <v>988269</v>
@@ -13448,7 +13448,7 @@
         <v>8.84799957275391</v>
       </c>
       <c r="G451" t="n">
-        <v>5.97352361679077</v>
+        <v>5.97352313995361</v>
       </c>
       <c r="H451" t="n">
         <v>722064</v>
@@ -13564,7 +13564,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G455" t="n">
-        <v>5.94246816635132</v>
+        <v>5.94246768951416</v>
       </c>
       <c r="H455" t="n">
         <v>1173522</v>
@@ -13593,7 +13593,7 @@
         <v>9.07800006866455</v>
       </c>
       <c r="G456" t="n">
-        <v>6.12880325317383</v>
+        <v>6.12880277633667</v>
       </c>
       <c r="H456" t="n">
         <v>2123712</v>
@@ -13651,7 +13651,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301582336426</v>
+        <v>5.93301630020142</v>
       </c>
       <c r="H458" t="n">
         <v>867989</v>
@@ -13709,7 +13709,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984851837158</v>
+        <v>5.83984804153442</v>
       </c>
       <c r="H460" t="n">
         <v>2271949</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748300552368</v>
+        <v>5.75748252868652</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13796,7 +13796,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401103973389</v>
+        <v>5.37401056289673</v>
       </c>
       <c r="H463" t="n">
         <v>2564625</v>
@@ -13825,7 +13825,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29434537887573</v>
+        <v>5.29434585571289</v>
       </c>
       <c r="H464" t="n">
         <v>1025453</v>
@@ -13854,7 +13854,7 @@
         <v>7.83400011062622</v>
       </c>
       <c r="G465" t="n">
-        <v>5.28894519805908</v>
+        <v>5.28894472122192</v>
       </c>
       <c r="H465" t="n">
         <v>1213624</v>
@@ -13883,7 +13883,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409172058105</v>
+        <v>5.27409219741821</v>
       </c>
       <c r="H466" t="n">
         <v>851531</v>
@@ -13912,7 +13912,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34700632095337</v>
+        <v>5.34700584411621</v>
       </c>
       <c r="H467" t="n">
         <v>1182375</v>
@@ -13970,7 +13970,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H469" t="n">
         <v>812307</v>
@@ -13999,7 +13999,7 @@
         <v>7.9539999961853</v>
       </c>
       <c r="G470" t="n">
-        <v>5.36995983123779</v>
+        <v>5.36996030807495</v>
       </c>
       <c r="H470" t="n">
         <v>1735396</v>
@@ -14202,7 +14202,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.85011196136475</v>
+        <v>4.8501124382019</v>
       </c>
       <c r="H477" t="n">
         <v>2148643</v>
@@ -14289,7 +14289,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525943756104</v>
+        <v>4.83525991439819</v>
       </c>
       <c r="H480" t="n">
         <v>1773638</v>
@@ -14347,7 +14347,7 @@
         <v>7.25</v>
       </c>
       <c r="G482" t="n">
-        <v>4.89467000961304</v>
+        <v>4.8946704864502</v>
       </c>
       <c r="H482" t="n">
         <v>2096743</v>
@@ -14521,7 +14521,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.9230260848999</v>
+        <v>4.92302560806274</v>
       </c>
       <c r="H488" t="n">
         <v>1062819</v>
@@ -14550,7 +14550,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.86091470718384</v>
+        <v>4.86091423034668</v>
       </c>
       <c r="H489" t="n">
         <v>997609</v>
@@ -14724,7 +14724,7 @@
         <v>7.80600023269653</v>
       </c>
       <c r="G495" t="n">
-        <v>5.27004098892212</v>
+        <v>5.27004146575928</v>
       </c>
       <c r="H495" t="n">
         <v>2448121</v>
@@ -14753,7 +14753,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346242904663</v>
+        <v>5.38346290588379</v>
       </c>
       <c r="H496" t="n">
         <v>2796261</v>
@@ -14927,7 +14927,7 @@
         <v>7.7979998588562</v>
       </c>
       <c r="G502" t="n">
-        <v>5.26464033126831</v>
+        <v>5.26463985443115</v>
       </c>
       <c r="H502" t="n">
         <v>2617256</v>
@@ -14956,7 +14956,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565544128418</v>
+        <v>5.34565591812134</v>
       </c>
       <c r="H503" t="n">
         <v>2644025</v>
@@ -14985,7 +14985,7 @@
         <v>7.87400007247925</v>
       </c>
       <c r="G504" t="n">
-        <v>5.31595039367676</v>
+        <v>5.3159499168396</v>
       </c>
       <c r="H504" t="n">
         <v>1319000</v>
@@ -15130,7 +15130,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342256546021</v>
+        <v>5.43342208862305</v>
       </c>
       <c r="H509" t="n">
         <v>1443560</v>
@@ -15391,7 +15391,7 @@
         <v>8.69799995422363</v>
       </c>
       <c r="G518" t="n">
-        <v>5.87225437164307</v>
+        <v>5.87225484848022</v>
       </c>
       <c r="H518" t="n">
         <v>1992357</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791934967041</v>
+        <v>6.21791982650757</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15478,7 +15478,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.3745493888855</v>
+        <v>6.37454986572266</v>
       </c>
       <c r="H521" t="n">
         <v>4282126</v>
@@ -15594,7 +15594,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>6.06264019012451</v>
+        <v>6.06263971328735</v>
       </c>
       <c r="H525" t="n">
         <v>1802779</v>
@@ -15652,7 +15652,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.28543281555176</v>
+        <v>6.2854323387146</v>
       </c>
       <c r="H527" t="n">
         <v>1251679</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.4245080947876</v>
+        <v>6.42450761795044</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15826,7 +15826,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G533" t="n">
-        <v>6.69185876846313</v>
+        <v>6.69185829162598</v>
       </c>
       <c r="H533" t="n">
         <v>2342231</v>
@@ -15913,7 +15913,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839651107788</v>
+        <v>6.62839698791504</v>
       </c>
       <c r="H536" t="n">
         <v>1797973</v>
@@ -16087,7 +16087,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525466918945</v>
+        <v>7.33525514602661</v>
       </c>
       <c r="H542" t="n">
         <v>2008354</v>
@@ -16116,7 +16116,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989944458008</v>
+        <v>7.43989992141724</v>
       </c>
       <c r="H543" t="n">
         <v>1957564</v>
@@ -16290,7 +16290,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.45002603530884</v>
+        <v>7.450026512146</v>
       </c>
       <c r="H549" t="n">
         <v>2293340</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.83147287368774</v>
+        <v>7.83147382736206</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.84835195541382</v>
+        <v>7.8483510017395</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16464,7 +16464,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G555" t="n">
-        <v>8.08126926422119</v>
+        <v>8.08127021789551</v>
       </c>
       <c r="H555" t="n">
         <v>2829914</v>
@@ -16609,7 +16609,7 @@
         <v>12.2550001144409</v>
       </c>
       <c r="G560" t="n">
-        <v>8.27368068695068</v>
+        <v>8.273681640625</v>
       </c>
       <c r="H560" t="n">
         <v>3458397</v>
@@ -16667,7 +16667,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G562" t="n">
-        <v>8.26355361938477</v>
+        <v>8.26355457305908</v>
       </c>
       <c r="H562" t="n">
         <v>2570522</v>
@@ -17218,7 +17218,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243785858154</v>
+        <v>8.97243690490723</v>
       </c>
       <c r="H581" t="n">
         <v>4533092</v>
@@ -17276,7 +17276,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G583" t="n">
-        <v>8.54710674285889</v>
+        <v>8.5471076965332</v>
       </c>
       <c r="H583" t="n">
         <v>2183078</v>
@@ -17363,7 +17363,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G586" t="n">
-        <v>8.47622013092041</v>
+        <v>8.47621917724609</v>
       </c>
       <c r="H586" t="n">
         <v>1149074</v>
@@ -17392,7 +17392,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G587" t="n">
-        <v>8.47284507751465</v>
+        <v>8.47284412384033</v>
       </c>
       <c r="H587" t="n">
         <v>883840</v>
@@ -35871,6 +35871,35 @@
         <v>1078143</v>
       </c>
       <c r="I1224" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1225" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>14.2849998474121</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>14.3249998092651</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>14.2550001144409</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>14.2799997329712</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>14.2799997329712</v>
+      </c>
+      <c r="H1225" t="n">
+        <v>401989</v>
+      </c>
+      <c r="I1225" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -35903,6 +35903,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1226" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>14.3950004577637</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>1052322</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418298721313</v>
+        <v>6.82418394088745</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23061037063599</v>
+        <v>7.23060989379883</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -543,7 +543,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G6" t="n">
-        <v>6.94705629348755</v>
+        <v>6.94705677032471</v>
       </c>
       <c r="H6" t="n">
         <v>11941139</v>
@@ -630,7 +630,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G9" t="n">
-        <v>7.24411249160767</v>
+        <v>7.24411201477051</v>
       </c>
       <c r="H9" t="n">
         <v>5804326</v>
@@ -659,7 +659,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040723800659</v>
+        <v>7.48040676116943</v>
       </c>
       <c r="H10" t="n">
         <v>7510382</v>
@@ -717,7 +717,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.19010162353516</v>
+        <v>7.19010210037231</v>
       </c>
       <c r="H12" t="n">
         <v>3165422</v>
@@ -746,7 +746,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G13" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132081985474</v>
       </c>
       <c r="H13" t="n">
         <v>2435262</v>
@@ -804,7 +804,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.02131986618042</v>
+        <v>7.02132081985474</v>
       </c>
       <c r="H15" t="n">
         <v>1535035</v>
@@ -833,7 +833,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96731042861938</v>
+        <v>6.96730995178223</v>
       </c>
       <c r="H16" t="n">
         <v>1777164</v>
@@ -891,7 +891,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543329238892</v>
       </c>
       <c r="H18" t="n">
         <v>3251441</v>
@@ -920,7 +920,7 @@
         <v>9.625</v>
       </c>
       <c r="G19" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H19" t="n">
         <v>3546202</v>
@@ -949,7 +949,7 @@
         <v>9.625</v>
       </c>
       <c r="G20" t="n">
-        <v>6.49809741973877</v>
+        <v>6.49809694290161</v>
       </c>
       <c r="H20" t="n">
         <v>2484688</v>
@@ -1065,7 +1065,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G24" t="n">
-        <v>6.29218339920044</v>
+        <v>6.29218292236328</v>
       </c>
       <c r="H24" t="n">
         <v>2785789</v>
@@ -1123,7 +1123,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>5.91411209106445</v>
+        <v>5.91411256790161</v>
       </c>
       <c r="H26" t="n">
         <v>3367791</v>
@@ -1181,7 +1181,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>5.69132041931152</v>
+        <v>5.69132089614868</v>
       </c>
       <c r="H28" t="n">
         <v>6011852</v>
@@ -1355,7 +1355,7 @@
         <v>8.375</v>
       </c>
       <c r="G34" t="n">
-        <v>5.65418863296509</v>
+        <v>5.65418910980225</v>
       </c>
       <c r="H34" t="n">
         <v>2299262</v>
@@ -1442,7 +1442,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G37" t="n">
-        <v>5.29637145996094</v>
+        <v>5.29637098312378</v>
       </c>
       <c r="H37" t="n">
         <v>2369088</v>
@@ -1471,7 +1471,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G38" t="n">
-        <v>5.43477249145508</v>
+        <v>5.43477201461792</v>
       </c>
       <c r="H38" t="n">
         <v>3062742</v>
@@ -1790,7 +1790,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H49" t="n">
         <v>4270764</v>
@@ -1877,7 +1877,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G52" t="n">
-        <v>4.53685331344604</v>
+        <v>4.53685283660889</v>
       </c>
       <c r="H52" t="n">
         <v>2581341</v>
@@ -1906,7 +1906,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>4.41533088684082</v>
+        <v>4.41533041000366</v>
       </c>
       <c r="H53" t="n">
         <v>2670255</v>
@@ -1964,7 +1964,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>4.67187833786011</v>
+        <v>4.67187881469727</v>
       </c>
       <c r="H55" t="n">
         <v>3556258</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347730636597</v>
+        <v>4.53347826004028</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2051,7 +2051,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284292221069</v>
+        <v>4.48284339904785</v>
       </c>
       <c r="H58" t="n">
         <v>2735170</v>
@@ -2080,7 +2080,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>4.40520334243774</v>
+        <v>4.4052038192749</v>
       </c>
       <c r="H59" t="n">
         <v>2749560</v>
@@ -2109,7 +2109,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>4.4119553565979</v>
+        <v>4.41195440292358</v>
       </c>
       <c r="H60" t="n">
         <v>1556296</v>
@@ -2138,7 +2138,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G61" t="n">
-        <v>4.22967004776001</v>
+        <v>4.22967052459717</v>
       </c>
       <c r="H61" t="n">
         <v>3912970</v>
@@ -2167,7 +2167,7 @@
         <v>6.30499982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>4.25667572021484</v>
+        <v>4.25667524337769</v>
       </c>
       <c r="H62" t="n">
         <v>3017576</v>
@@ -2312,7 +2312,7 @@
         <v>5.94299983978271</v>
       </c>
       <c r="G67" t="n">
-        <v>4.01227998733521</v>
+        <v>4.01227951049805</v>
       </c>
       <c r="H67" t="n">
         <v>2524391</v>
@@ -2370,7 +2370,7 @@
         <v>5.46199989318848</v>
       </c>
       <c r="G69" t="n">
-        <v>3.6875433921814</v>
+        <v>3.68754363059998</v>
       </c>
       <c r="H69" t="n">
         <v>4125758</v>
@@ -2428,7 +2428,7 @@
         <v>5.47300004959106</v>
       </c>
       <c r="G71" t="n">
-        <v>3.69497013092041</v>
+        <v>3.69496989250183</v>
       </c>
       <c r="H71" t="n">
         <v>2794856</v>
@@ -2457,7 +2457,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>3.92248749732971</v>
+        <v>3.92248773574829</v>
       </c>
       <c r="H72" t="n">
         <v>4160054</v>
@@ -2486,7 +2486,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>3.85497498512268</v>
+        <v>3.85497546195984</v>
       </c>
       <c r="H73" t="n">
         <v>2825138</v>
@@ -2515,7 +2515,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.0851936340332</v>
+        <v>4.08519315719604</v>
       </c>
       <c r="H74" t="n">
         <v>3445946</v>
@@ -2631,7 +2631,7 @@
         <v>6.13100004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>4.1392035484314</v>
+        <v>4.13920402526855</v>
       </c>
       <c r="H78" t="n">
         <v>1800303</v>
@@ -2660,7 +2660,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98122382164001</v>
+        <v>3.98122406005859</v>
       </c>
       <c r="H79" t="n">
         <v>2997914</v>
@@ -2689,7 +2689,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G80" t="n">
-        <v>3.84822368621826</v>
+        <v>3.84822392463684</v>
       </c>
       <c r="H80" t="n">
         <v>1805442</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995505332947</v>
+        <v>3.87995481491089</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2747,7 +2747,7 @@
         <v>5.63100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>3.80164003372192</v>
+        <v>3.8016402721405</v>
       </c>
       <c r="H82" t="n">
         <v>2732328</v>
@@ -2776,7 +2776,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G83" t="n">
-        <v>3.79286336898804</v>
+        <v>3.79286360740662</v>
       </c>
       <c r="H83" t="n">
         <v>1663580</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311702728271</v>
+        <v>3.81311678886414</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2834,7 +2834,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.76720857620239</v>
+        <v>3.76720881462097</v>
       </c>
       <c r="H85" t="n">
         <v>1773043</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619322776794</v>
+        <v>3.68619346618652</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -2979,7 +2979,7 @@
         <v>5.32399988174438</v>
       </c>
       <c r="G90" t="n">
-        <v>3.59437608718872</v>
+        <v>3.59437584877014</v>
       </c>
       <c r="H90" t="n">
         <v>2313101</v>
@@ -3124,7 +3124,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>3.65581274032593</v>
+        <v>3.65581250190735</v>
       </c>
       <c r="H95" t="n">
         <v>1002502</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77395963668823</v>
+        <v>3.77396011352539</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3182,7 +3182,7 @@
         <v>5.72100019454956</v>
       </c>
       <c r="G97" t="n">
-        <v>3.86240172386169</v>
+        <v>3.86240148544312</v>
       </c>
       <c r="H97" t="n">
         <v>2097766</v>
@@ -3211,7 +3211,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G98" t="n">
-        <v>3.80231523513794</v>
+        <v>3.80231499671936</v>
       </c>
       <c r="H98" t="n">
         <v>1569339</v>
@@ -3327,7 +3327,7 @@
         <v>5.72300004959106</v>
       </c>
       <c r="G102" t="n">
-        <v>3.86375188827515</v>
+        <v>3.86375164985657</v>
       </c>
       <c r="H102" t="n">
         <v>1984827</v>
@@ -3356,7 +3356,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324966430664</v>
       </c>
       <c r="H103" t="n">
         <v>2495941</v>
@@ -3414,7 +3414,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>4.09802055358887</v>
+        <v>4.09802103042603</v>
       </c>
       <c r="H105" t="n">
         <v>1510660</v>
@@ -3501,7 +3501,7 @@
         <v>6.09299993515015</v>
       </c>
       <c r="G108" t="n">
-        <v>4.11354827880859</v>
+        <v>4.11354875564575</v>
       </c>
       <c r="H108" t="n">
         <v>1792655</v>
@@ -3588,7 +3588,7 @@
         <v>6.28900003433228</v>
       </c>
       <c r="G111" t="n">
-        <v>4.24587345123291</v>
+        <v>4.24587392807007</v>
       </c>
       <c r="H111" t="n">
         <v>2320257</v>
@@ -3646,7 +3646,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G113" t="n">
-        <v>3.98594927787781</v>
+        <v>3.98594951629639</v>
       </c>
       <c r="H113" t="n">
         <v>4583558</v>
@@ -3675,7 +3675,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H114" t="n">
         <v>4779877</v>
@@ -3704,7 +3704,7 @@
         <v>5.0770001411438</v>
       </c>
       <c r="G115" t="n">
-        <v>3.42761993408203</v>
+        <v>3.42761969566345</v>
       </c>
       <c r="H115" t="n">
         <v>4636137</v>
@@ -3733,7 +3733,7 @@
         <v>5.09700012207031</v>
       </c>
       <c r="G116" t="n">
-        <v>3.44112229347229</v>
+        <v>3.44112253189087</v>
       </c>
       <c r="H116" t="n">
         <v>2818082</v>
@@ -3791,7 +3791,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G118" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H118" t="n">
         <v>2452422</v>
@@ -3820,7 +3820,7 @@
         <v>5.32200002670288</v>
       </c>
       <c r="G119" t="n">
-        <v>3.59302568435669</v>
+        <v>3.59302592277527</v>
       </c>
       <c r="H119" t="n">
         <v>4765434</v>
@@ -3849,7 +3849,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.67944169044495</v>
+        <v>3.6794421672821</v>
       </c>
       <c r="H120" t="n">
         <v>1265113</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.6571626663208</v>
+        <v>3.65716290473938</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3965,7 +3965,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G124" t="n">
-        <v>3.50728464126587</v>
+        <v>3.50728487968445</v>
       </c>
       <c r="H124" t="n">
         <v>1933194</v>
@@ -3994,7 +3994,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>3.53091430664062</v>
+        <v>3.53091406822205</v>
       </c>
       <c r="H125" t="n">
         <v>1761818</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952332496643</v>
+        <v>3.57952308654785</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4052,7 +4052,7 @@
         <v>5.2979998588562</v>
       </c>
       <c r="G127" t="n">
-        <v>3.57682251930237</v>
+        <v>3.57682275772095</v>
       </c>
       <c r="H127" t="n">
         <v>1305635</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.4039900302887</v>
+        <v>3.40399026870728</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4110,7 +4110,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>3.4289698600769</v>
+        <v>3.42897009849548</v>
       </c>
       <c r="H129" t="n">
         <v>1535360</v>
@@ -4197,7 +4197,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.20989108085632</v>
+        <v>3.2098913192749</v>
       </c>
       <c r="H132" t="n">
         <v>3036596</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044709205627</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4255,7 +4255,7 @@
         <v>5.26900005340576</v>
       </c>
       <c r="G134" t="n">
-        <v>3.55724430084229</v>
+        <v>3.55724406242371</v>
       </c>
       <c r="H134" t="n">
         <v>2393460</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.4566502571106</v>
+        <v>3.45665001869202</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.21326684951782</v>
+        <v>3.2132670879364</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4429,7 +4429,7 @@
         <v>5.11299991607666</v>
       </c>
       <c r="G140" t="n">
-        <v>3.45192408561707</v>
+        <v>3.45192432403564</v>
       </c>
       <c r="H140" t="n">
         <v>1625180</v>
@@ -4603,7 +4603,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.5322642326355</v>
+        <v>3.53226399421692</v>
       </c>
       <c r="H146" t="n">
         <v>1532624</v>
@@ -4661,7 +4661,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95894479751587</v>
+        <v>3.95894455909729</v>
       </c>
       <c r="H148" t="n">
         <v>4041376</v>
@@ -4806,7 +4806,7 @@
         <v>5.75899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>3.88805627822876</v>
+        <v>3.88805603981018</v>
       </c>
       <c r="H153" t="n">
         <v>2138183</v>
@@ -4835,7 +4835,7 @@
         <v>5.7810001373291</v>
       </c>
       <c r="G154" t="n">
-        <v>3.90290951728821</v>
+        <v>3.90290904045105</v>
       </c>
       <c r="H154" t="n">
         <v>1418521</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4893,7 +4893,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387847900391</v>
+        <v>3.87387871742249</v>
       </c>
       <c r="H156" t="n">
         <v>947624</v>
@@ -5009,7 +5009,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G160" t="n">
-        <v>4.09126901626587</v>
+        <v>4.09126949310303</v>
       </c>
       <c r="H160" t="n">
         <v>1170223</v>
@@ -5038,7 +5038,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96772122383118</v>
+        <v>3.9677209854126</v>
       </c>
       <c r="H161" t="n">
         <v>1665740</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370573997498</v>
+        <v>3.75370597839355</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5212,7 +5212,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539095878601</v>
+        <v>3.67539119720459</v>
       </c>
       <c r="H167" t="n">
         <v>1508487</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538101196289</v>
+        <v>3.35538077354431</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5560,7 +5560,7 @@
         <v>5.22100019454956</v>
       </c>
       <c r="G179" t="n">
-        <v>3.5248384475708</v>
+        <v>3.52483820915222</v>
       </c>
       <c r="H179" t="n">
         <v>1218078</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044733047485</v>
+        <v>3.44044709205627</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5705,7 +5705,7 @@
         <v>5.08699989318848</v>
       </c>
       <c r="G184" t="n">
-        <v>3.43437075614929</v>
+        <v>3.43437099456787</v>
       </c>
       <c r="H184" t="n">
         <v>1118182</v>
@@ -5734,7 +5734,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G185" t="n">
-        <v>3.3405282497406</v>
+        <v>3.34052848815918</v>
       </c>
       <c r="H185" t="n">
         <v>1049480</v>
@@ -5792,7 +5792,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>3.36213254928589</v>
+        <v>3.36213231086731</v>
       </c>
       <c r="H187" t="n">
         <v>1010793</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837350845337</v>
+        <v>3.24837374687195</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116032600403</v>
+        <v>3.31116008758545</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -5966,7 +5966,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786826133728</v>
+        <v>3.28786849975586</v>
       </c>
       <c r="H193" t="n">
         <v>1635754</v>
@@ -5995,7 +5995,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G194" t="n">
-        <v>3.3405282497406</v>
+        <v>3.34052848815918</v>
       </c>
       <c r="H194" t="n">
         <v>1105812</v>
@@ -6082,7 +6082,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G197" t="n">
-        <v>3.46340131759644</v>
+        <v>3.46340155601501</v>
       </c>
       <c r="H197" t="n">
         <v>1022230</v>
@@ -6140,7 +6140,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G199" t="n">
-        <v>3.48027968406677</v>
+        <v>3.48027992248535</v>
       </c>
       <c r="H199" t="n">
         <v>734627</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50796008110046</v>
+        <v>3.50795984268188</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6256,7 +6256,7 @@
         <v>5.11899995803833</v>
       </c>
       <c r="G203" t="n">
-        <v>3.45597505569458</v>
+        <v>3.455974817276</v>
       </c>
       <c r="H203" t="n">
         <v>1003543</v>
@@ -6285,7 +6285,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G204" t="n">
-        <v>3.51065993309021</v>
+        <v>3.51066040992737</v>
       </c>
       <c r="H204" t="n">
         <v>601405</v>
@@ -6314,7 +6314,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.608553647995</v>
+        <v>3.60855340957642</v>
       </c>
       <c r="H205" t="n">
         <v>1822628</v>
@@ -6517,7 +6517,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G212" t="n">
-        <v>3.78206157684326</v>
+        <v>3.78206181526184</v>
       </c>
       <c r="H212" t="n">
         <v>1401317</v>
@@ -6575,7 +6575,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294452667236</v>
+        <v>3.69294428825378</v>
       </c>
       <c r="H214" t="n">
         <v>561510</v>
@@ -6604,7 +6604,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.72400045394897</v>
+        <v>3.7240002155304</v>
       </c>
       <c r="H215" t="n">
         <v>771072</v>
@@ -6662,7 +6662,7 @@
         <v>5.37900018692017</v>
       </c>
       <c r="G217" t="n">
-        <v>3.63150835037231</v>
+        <v>3.63150811195374</v>
       </c>
       <c r="H217" t="n">
         <v>1446118</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573691368103</v>
+        <v>3.91573667526245</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6749,7 +6749,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324918746948</v>
+        <v>3.98324966430664</v>
       </c>
       <c r="H220" t="n">
         <v>1345223</v>
@@ -6836,7 +6836,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G223" t="n">
-        <v>4.23979759216309</v>
+        <v>4.23979806900024</v>
       </c>
       <c r="H223" t="n">
         <v>1940924</v>
@@ -6865,7 +6865,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19928979873657</v>
+        <v>4.19928932189941</v>
       </c>
       <c r="H224" t="n">
         <v>1230545</v>
@@ -6894,7 +6894,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18916320800781</v>
+        <v>4.18916273117065</v>
       </c>
       <c r="H225" t="n">
         <v>1148359</v>
@@ -6923,7 +6923,7 @@
         <v>6.1710000038147</v>
       </c>
       <c r="G226" t="n">
-        <v>4.16620826721191</v>
+        <v>4.16620874404907</v>
       </c>
       <c r="H226" t="n">
         <v>1220830</v>
@@ -6952,7 +6952,7 @@
         <v>6.08300018310547</v>
       </c>
       <c r="G227" t="n">
-        <v>4.10679769515991</v>
+        <v>4.10679721832275</v>
       </c>
       <c r="H227" t="n">
         <v>1183007</v>
@@ -6981,7 +6981,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G228" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H228" t="n">
         <v>1114284</v>
@@ -7039,7 +7039,7 @@
         <v>6.16200017929077</v>
       </c>
       <c r="G230" t="n">
-        <v>4.16013288497925</v>
+        <v>4.16013240814209</v>
       </c>
       <c r="H230" t="n">
         <v>421479</v>
@@ -7068,7 +7068,7 @@
         <v>6.19299983978271</v>
       </c>
       <c r="G231" t="n">
-        <v>4.18106174468994</v>
+        <v>4.18106126785278</v>
       </c>
       <c r="H231" t="n">
         <v>540433</v>
@@ -7097,7 +7097,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H232" t="n">
         <v>341527</v>
@@ -7155,7 +7155,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840732574463</v>
+        <v>4.28840684890747</v>
       </c>
       <c r="H234" t="n">
         <v>1390641</v>
@@ -7213,7 +7213,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G236" t="n">
-        <v>4.33566570281982</v>
+        <v>4.33566522598267</v>
       </c>
       <c r="H236" t="n">
         <v>986833</v>
@@ -7242,7 +7242,7 @@
         <v>6.49599981307983</v>
       </c>
       <c r="G237" t="n">
-        <v>4.38562440872192</v>
+        <v>4.38562488555908</v>
       </c>
       <c r="H237" t="n">
         <v>1118846</v>
@@ -7329,7 +7329,7 @@
         <v>6.31300020217896</v>
       </c>
       <c r="G240" t="n">
-        <v>4.26207637786865</v>
+        <v>4.26207685470581</v>
       </c>
       <c r="H240" t="n">
         <v>1219252</v>
@@ -7358,7 +7358,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.18848752975464</v>
+        <v>4.1884880065918</v>
       </c>
       <c r="H241" t="n">
         <v>1305794</v>
@@ -7416,7 +7416,7 @@
         <v>6.24900007247925</v>
       </c>
       <c r="G243" t="n">
-        <v>4.21886873245239</v>
+        <v>4.21886825561523</v>
       </c>
       <c r="H243" t="n">
         <v>1010763</v>
@@ -7474,7 +7474,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.23979759216309</v>
+        <v>4.23979806900024</v>
       </c>
       <c r="H245" t="n">
         <v>1194931</v>
@@ -7503,7 +7503,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G246" t="n">
-        <v>4.14257907867432</v>
+        <v>4.14257955551147</v>
       </c>
       <c r="H246" t="n">
         <v>1169428</v>
@@ -7561,7 +7561,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434545516968</v>
       </c>
       <c r="H248" t="n">
         <v>911894</v>
@@ -7590,7 +7590,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.0264573097229</v>
+        <v>4.02645778656006</v>
       </c>
       <c r="H249" t="n">
         <v>795631</v>
@@ -7619,7 +7619,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G250" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H250" t="n">
         <v>1305048</v>
@@ -7648,7 +7648,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G251" t="n">
-        <v>3.92788887023926</v>
+        <v>3.92788863182068</v>
       </c>
       <c r="H251" t="n">
         <v>1142347</v>
@@ -7706,7 +7706,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>3.82459449768066</v>
+        <v>3.82459425926208</v>
       </c>
       <c r="H253" t="n">
         <v>1270112</v>
@@ -7735,7 +7735,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G254" t="n">
-        <v>3.80771613121033</v>
+        <v>3.80771636962891</v>
       </c>
       <c r="H254" t="n">
         <v>708248</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73682808876038</v>
+        <v>3.73682761192322</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7822,7 +7822,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G257" t="n">
-        <v>3.7523558139801</v>
+        <v>3.75235605239868</v>
       </c>
       <c r="H257" t="n">
         <v>475168</v>
@@ -7880,7 +7880,7 @@
         <v>5.79899978637695</v>
       </c>
       <c r="G259" t="n">
-        <v>3.91506147384644</v>
+        <v>3.91506123542786</v>
       </c>
       <c r="H259" t="n">
         <v>1139125</v>
@@ -7938,7 +7938,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434617042542</v>
+        <v>3.96434545516968</v>
       </c>
       <c r="H261" t="n">
         <v>1652373</v>
@@ -7967,7 +7967,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G262" t="n">
-        <v>4.06156396865845</v>
+        <v>4.06156349182129</v>
       </c>
       <c r="H262" t="n">
         <v>1735246</v>
@@ -8054,7 +8054,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478179931641</v>
+        <v>4.42478275299072</v>
       </c>
       <c r="H265" t="n">
         <v>3181061</v>
@@ -8141,7 +8141,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605613708496</v>
+        <v>4.68605661392212</v>
       </c>
       <c r="H268" t="n">
         <v>2146613</v>
@@ -8228,7 +8228,7 @@
         <v>7.01399993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>4.7353401184082</v>
+        <v>4.73534059524536</v>
       </c>
       <c r="H271" t="n">
         <v>2895765</v>
@@ -8286,7 +8286,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>4.90817308425903</v>
+        <v>4.90817356109619</v>
       </c>
       <c r="H273" t="n">
         <v>2063203</v>
@@ -8344,7 +8344,7 @@
         <v>7.47300004959106</v>
       </c>
       <c r="G275" t="n">
-        <v>5.0452241897583</v>
+        <v>5.04522371292114</v>
       </c>
       <c r="H275" t="n">
         <v>3618760</v>
@@ -8373,7 +8373,7 @@
         <v>7.5770001411438</v>
       </c>
       <c r="G276" t="n">
-        <v>5.11543703079224</v>
+        <v>5.11543750762939</v>
       </c>
       <c r="H276" t="n">
         <v>1864510</v>
@@ -8402,7 +8402,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G277" t="n">
-        <v>5.11408662796021</v>
+        <v>5.11408710479736</v>
       </c>
       <c r="H277" t="n">
         <v>2333721</v>
@@ -8721,7 +8721,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G288" t="n">
-        <v>6.40560483932495</v>
+        <v>6.40560436248779</v>
       </c>
       <c r="H288" t="n">
         <v>8785274</v>
@@ -8779,7 +8779,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G290" t="n">
-        <v>6.17943716049194</v>
+        <v>6.1794376373291</v>
       </c>
       <c r="H290" t="n">
         <v>1832776</v>
@@ -8924,7 +8924,7 @@
         <v>8.80500030517578</v>
       </c>
       <c r="G295" t="n">
-        <v>5.94449281692505</v>
+        <v>5.94449329376221</v>
       </c>
       <c r="H295" t="n">
         <v>1414060</v>
@@ -8953,7 +8953,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G296" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H296" t="n">
         <v>990544</v>
@@ -9214,7 +9214,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.19361448287964</v>
+        <v>6.1936149597168</v>
       </c>
       <c r="H305" t="n">
         <v>1343595</v>
@@ -9243,7 +9243,7 @@
         <v>9.07299995422363</v>
       </c>
       <c r="G306" t="n">
-        <v>6.12542724609375</v>
+        <v>6.12542676925659</v>
       </c>
       <c r="H306" t="n">
         <v>1336985</v>
@@ -9272,7 +9272,7 @@
         <v>8.95300006866455</v>
       </c>
       <c r="G307" t="n">
-        <v>6.04441213607788</v>
+        <v>6.04441165924072</v>
       </c>
       <c r="H307" t="n">
         <v>1036237</v>
@@ -9301,7 +9301,7 @@
         <v>8.50899982452393</v>
       </c>
       <c r="G308" t="n">
-        <v>5.7446551322937</v>
+        <v>5.74465560913086</v>
       </c>
       <c r="H308" t="n">
         <v>1509651</v>
@@ -9359,7 +9359,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836595535278</v>
+        <v>5.66836643218994</v>
       </c>
       <c r="H310" t="n">
         <v>1335804</v>
@@ -9388,7 +9388,7 @@
         <v>8.8769998550415</v>
       </c>
       <c r="G311" t="n">
-        <v>5.99310255050659</v>
+        <v>5.99310207366943</v>
       </c>
       <c r="H311" t="n">
         <v>1769031</v>
@@ -9417,7 +9417,7 @@
         <v>8.49300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>5.73385381698608</v>
+        <v>5.73385334014893</v>
       </c>
       <c r="H312" t="n">
         <v>2412855</v>
@@ -9475,7 +9475,7 @@
         <v>8.68900012969971</v>
       </c>
       <c r="G314" t="n">
-        <v>5.8661789894104</v>
+        <v>5.86617851257324</v>
       </c>
       <c r="H314" t="n">
         <v>816021</v>
@@ -9504,7 +9504,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G315" t="n">
-        <v>6.09977245330811</v>
+        <v>6.09977197647095</v>
       </c>
       <c r="H315" t="n">
         <v>1294330</v>
@@ -9533,7 +9533,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>6.08897018432617</v>
+        <v>6.08897066116333</v>
       </c>
       <c r="H316" t="n">
         <v>1068724</v>
@@ -9591,7 +9591,7 @@
         <v>8.85299968719482</v>
       </c>
       <c r="G318" t="n">
-        <v>5.97689914703369</v>
+        <v>5.97689867019653</v>
       </c>
       <c r="H318" t="n">
         <v>757013</v>
@@ -9649,7 +9649,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G320" t="n">
-        <v>5.91411209106445</v>
+        <v>5.91411256790161</v>
       </c>
       <c r="H320" t="n">
         <v>1043632</v>
@@ -9678,7 +9678,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G321" t="n">
-        <v>5.91748857498169</v>
+        <v>5.91748809814453</v>
       </c>
       <c r="H321" t="n">
         <v>905026</v>
@@ -9736,7 +9736,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047828674316</v>
+        <v>5.73047733306885</v>
       </c>
       <c r="H323" t="n">
         <v>1626293</v>
@@ -9765,7 +9765,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H324" t="n">
         <v>1282373</v>
@@ -9823,7 +9823,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.30649852752686</v>
+        <v>5.3064980506897</v>
       </c>
       <c r="H326" t="n">
         <v>1268089</v>
@@ -9881,7 +9881,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G328" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H328" t="n">
         <v>2329069</v>
@@ -9968,7 +9968,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G331" t="n">
-        <v>5.5630464553833</v>
+        <v>5.56304597854614</v>
       </c>
       <c r="H331" t="n">
         <v>1403612</v>
@@ -10084,7 +10084,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G335" t="n">
-        <v>5.69672155380249</v>
+        <v>5.69672107696533</v>
       </c>
       <c r="H335" t="n">
         <v>1097585</v>
@@ -10113,7 +10113,7 @@
         <v>8.35400009155273</v>
       </c>
       <c r="G336" t="n">
-        <v>5.64001083374023</v>
+        <v>5.64001035690308</v>
       </c>
       <c r="H336" t="n">
         <v>610594</v>
@@ -10200,7 +10200,7 @@
         <v>8.20600032806396</v>
       </c>
       <c r="G339" t="n">
-        <v>5.54009199142456</v>
+        <v>5.54009246826172</v>
       </c>
       <c r="H339" t="n">
         <v>797257</v>
@@ -10229,7 +10229,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G340" t="n">
-        <v>5.50228452682495</v>
+        <v>5.50228500366211</v>
       </c>
       <c r="H340" t="n">
         <v>1247923</v>
@@ -10258,7 +10258,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30784845352173</v>
+        <v>5.30784797668457</v>
       </c>
       <c r="H341" t="n">
         <v>1370858</v>
@@ -10287,7 +10287,7 @@
         <v>7.86399984359741</v>
       </c>
       <c r="G342" t="n">
-        <v>5.3091983795166</v>
+        <v>5.30919885635376</v>
       </c>
       <c r="H342" t="n">
         <v>806647</v>
@@ -10316,7 +10316,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G343" t="n">
-        <v>5.14581823348999</v>
+        <v>5.14581775665283</v>
       </c>
       <c r="H343" t="n">
         <v>1174384</v>
@@ -10432,7 +10432,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>5.38751363754272</v>
+        <v>5.38751316070557</v>
       </c>
       <c r="H347" t="n">
         <v>1047427</v>
@@ -10548,7 +10548,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G351" t="n">
-        <v>4.90547275543213</v>
+        <v>4.90547227859497</v>
       </c>
       <c r="H351" t="n">
         <v>1070151</v>
@@ -10635,7 +10635,7 @@
         <v>7.63199996948242</v>
       </c>
       <c r="G354" t="n">
-        <v>5.15256929397583</v>
+        <v>5.15256881713867</v>
       </c>
       <c r="H354" t="n">
         <v>1115525</v>
@@ -10664,7 +10664,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>5.09720897674561</v>
+        <v>5.09720849990845</v>
       </c>
       <c r="H355" t="n">
         <v>1249783</v>
@@ -10693,7 +10693,7 @@
         <v>7.53800010681152</v>
       </c>
       <c r="G356" t="n">
-        <v>5.08910751342773</v>
+        <v>5.08910703659058</v>
       </c>
       <c r="H356" t="n">
         <v>721988</v>
@@ -10722,7 +10722,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G357" t="n">
-        <v>4.90547275543213</v>
+        <v>4.90547227859497</v>
       </c>
       <c r="H357" t="n">
         <v>1284720</v>
@@ -10867,7 +10867,7 @@
         <v>6.98600006103516</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71643733978271</v>
+        <v>4.71643686294556</v>
       </c>
       <c r="H362" t="n">
         <v>2613625</v>
@@ -10983,7 +10983,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>4.97568559646606</v>
+        <v>4.97568607330322</v>
       </c>
       <c r="H366" t="n">
         <v>978343</v>
@@ -11418,7 +11418,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080291748047</v>
+        <v>5.33080244064331</v>
       </c>
       <c r="H381" t="n">
         <v>1027240</v>
@@ -11447,7 +11447,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G382" t="n">
-        <v>5.30379724502563</v>
+        <v>5.30379772186279</v>
       </c>
       <c r="H382" t="n">
         <v>909012</v>
@@ -11534,7 +11534,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>5.51578712463379</v>
+        <v>5.51578760147095</v>
       </c>
       <c r="H385" t="n">
         <v>1237649</v>
@@ -11563,7 +11563,7 @@
         <v>8.13399982452393</v>
       </c>
       <c r="G386" t="n">
-        <v>5.49148321151733</v>
+        <v>5.49148273468018</v>
       </c>
       <c r="H386" t="n">
         <v>1186915</v>
@@ -11592,7 +11592,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H387" t="n">
         <v>1194785</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.61975717544556</v>
+        <v>5.61975765228271</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -11795,7 +11795,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>5.68456888198853</v>
+        <v>5.68456935882568</v>
       </c>
       <c r="H394" t="n">
         <v>1342906</v>
@@ -11853,7 +11853,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G396" t="n">
-        <v>5.72912740707397</v>
+        <v>5.72912788391113</v>
       </c>
       <c r="H396" t="n">
         <v>1166669</v>
@@ -11911,7 +11911,7 @@
         <v>8.23600006103516</v>
       </c>
       <c r="G398" t="n">
-        <v>5.56034564971924</v>
+        <v>5.5603461265564</v>
       </c>
       <c r="H398" t="n">
         <v>1662385</v>
@@ -11969,7 +11969,7 @@
         <v>8.20600032806396</v>
       </c>
       <c r="G400" t="n">
-        <v>5.54009199142456</v>
+        <v>5.54009246826172</v>
       </c>
       <c r="H400" t="n">
         <v>775903</v>
@@ -12027,7 +12027,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768613815308</v>
+        <v>5.50768566131592</v>
       </c>
       <c r="H402" t="n">
         <v>890149</v>
@@ -12114,7 +12114,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G405" t="n">
-        <v>5.82364559173584</v>
+        <v>5.823646068573</v>
       </c>
       <c r="H405" t="n">
         <v>1357346</v>
@@ -12143,7 +12143,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951322555542</v>
+        <v>5.91951274871826</v>
       </c>
       <c r="H406" t="n">
         <v>1665434</v>
@@ -12201,7 +12201,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G408" t="n">
-        <v>6.56088399887085</v>
+        <v>6.56088447570801</v>
       </c>
       <c r="H408" t="n">
         <v>3234067</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873180389404</v>
+        <v>6.54873132705688</v>
       </c>
       <c r="H409" t="n">
         <v>2733714</v>
@@ -12288,7 +12288,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G411" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H411" t="n">
         <v>929420</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758453369141</v>
+        <v>6.29758501052856</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12346,7 +12346,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>6.27192974090576</v>
+        <v>6.27193021774292</v>
       </c>
       <c r="H413" t="n">
         <v>817793</v>
@@ -12375,7 +12375,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G414" t="n">
-        <v>6.11665058135986</v>
+        <v>6.11665105819702</v>
       </c>
       <c r="H414" t="n">
         <v>900855</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044765472412</v>
+        <v>6.10044813156128</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12462,7 +12462,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>5.97487449645996</v>
+        <v>5.9748740196228</v>
       </c>
       <c r="H417" t="n">
         <v>839338</v>
@@ -12491,7 +12491,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G418" t="n">
-        <v>5.93436574935913</v>
+        <v>5.93436670303345</v>
       </c>
       <c r="H418" t="n">
         <v>1220620</v>
@@ -12520,7 +12520,7 @@
         <v>8.63199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>5.82769584655762</v>
+        <v>5.82769680023193</v>
       </c>
       <c r="H419" t="n">
         <v>1609287</v>
@@ -12636,7 +12636,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G423" t="n">
-        <v>5.82364559173584</v>
+        <v>5.823646068573</v>
       </c>
       <c r="H423" t="n">
         <v>2422377</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461988449097</v>
+        <v>5.95461940765381</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12694,7 +12694,7 @@
         <v>8.89400005340576</v>
       </c>
       <c r="G425" t="n">
-        <v>6.00457906723022</v>
+        <v>6.00457954406738</v>
       </c>
       <c r="H425" t="n">
         <v>1029644</v>
@@ -12781,7 +12781,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16930961608887</v>
+        <v>6.16931009292603</v>
       </c>
       <c r="H428" t="n">
         <v>729053</v>
@@ -12868,7 +12868,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G431" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453968048096</v>
       </c>
       <c r="H431" t="n">
         <v>1056988</v>
@@ -12897,7 +12897,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G432" t="n">
-        <v>5.96002101898193</v>
+        <v>5.96002149581909</v>
       </c>
       <c r="H432" t="n">
         <v>533030</v>
@@ -13013,7 +13013,7 @@
         <v>8.88599967956543</v>
       </c>
       <c r="G436" t="n">
-        <v>5.99917840957642</v>
+        <v>5.99917793273926</v>
       </c>
       <c r="H436" t="n">
         <v>954787</v>
@@ -13042,7 +13042,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08289384841919</v>
+        <v>6.08289432525635</v>
       </c>
       <c r="H437" t="n">
         <v>877361</v>
@@ -13158,7 +13158,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H441" t="n">
         <v>1296803</v>
@@ -13216,7 +13216,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G443" t="n">
-        <v>6.15040683746338</v>
+        <v>6.15040636062622</v>
       </c>
       <c r="H443" t="n">
         <v>1030117</v>
@@ -13245,7 +13245,7 @@
         <v>9.19400024414062</v>
       </c>
       <c r="G444" t="n">
-        <v>6.20711755752563</v>
+        <v>6.20711803436279</v>
       </c>
       <c r="H444" t="n">
         <v>1671458</v>
@@ -13390,7 +13390,7 @@
         <v>8.85599994659424</v>
       </c>
       <c r="G449" t="n">
-        <v>5.97892475128174</v>
+        <v>5.97892427444458</v>
       </c>
       <c r="H449" t="n">
         <v>746956</v>
@@ -13419,7 +13419,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G450" t="n">
-        <v>5.9303150177002</v>
+        <v>5.93031597137451</v>
       </c>
       <c r="H450" t="n">
         <v>988269</v>
@@ -13506,7 +13506,7 @@
         <v>8.88599967956543</v>
       </c>
       <c r="G453" t="n">
-        <v>5.99917840957642</v>
+        <v>5.99917793273926</v>
       </c>
       <c r="H453" t="n">
         <v>1027395</v>
@@ -13535,7 +13535,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613260269165</v>
+        <v>5.75613307952881</v>
       </c>
       <c r="H454" t="n">
         <v>1565076</v>
@@ -13622,7 +13622,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G457" t="n">
-        <v>6.0545392036438</v>
+        <v>6.05453968048096</v>
       </c>
       <c r="H457" t="n">
         <v>1441148</v>
@@ -13651,7 +13651,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G458" t="n">
-        <v>5.93301630020142</v>
+        <v>5.93301582336426</v>
       </c>
       <c r="H458" t="n">
         <v>867989</v>
@@ -13680,7 +13680,7 @@
         <v>8.79599952697754</v>
       </c>
       <c r="G459" t="n">
-        <v>5.93841600418091</v>
+        <v>5.93841648101807</v>
       </c>
       <c r="H459" t="n">
         <v>727028</v>
@@ -13709,7 +13709,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G460" t="n">
-        <v>5.83984804153442</v>
+        <v>5.83984851837158</v>
       </c>
       <c r="H460" t="n">
         <v>2271949</v>
@@ -13796,7 +13796,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>5.37401056289673</v>
+        <v>5.37401103973389</v>
       </c>
       <c r="H463" t="n">
         <v>2564625</v>
@@ -13854,7 +13854,7 @@
         <v>7.83400011062622</v>
       </c>
       <c r="G465" t="n">
-        <v>5.28894472122192</v>
+        <v>5.28894519805908</v>
       </c>
       <c r="H465" t="n">
         <v>1213624</v>
@@ -13883,7 +13883,7 @@
         <v>7.81199979782104</v>
       </c>
       <c r="G466" t="n">
-        <v>5.27409219741821</v>
+        <v>5.27409172058105</v>
       </c>
       <c r="H466" t="n">
         <v>851531</v>
@@ -13970,7 +13970,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G469" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H469" t="n">
         <v>812307</v>
@@ -14173,7 +14173,7 @@
         <v>7.16599988937378</v>
       </c>
       <c r="G476" t="n">
-        <v>4.8379602432251</v>
+        <v>4.83795976638794</v>
       </c>
       <c r="H476" t="n">
         <v>3509239</v>
@@ -14202,7 +14202,7 @@
         <v>7.18400001525879</v>
       </c>
       <c r="G477" t="n">
-        <v>4.8501124382019</v>
+        <v>4.85011196136475</v>
       </c>
       <c r="H477" t="n">
         <v>2148643</v>
@@ -14231,7 +14231,7 @@
         <v>7.01599979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>4.73669052124023</v>
+        <v>4.73669099807739</v>
       </c>
       <c r="H478" t="n">
         <v>2197891</v>
@@ -14347,7 +14347,7 @@
         <v>7.25</v>
       </c>
       <c r="G482" t="n">
-        <v>4.8946704864502</v>
+        <v>4.89467096328735</v>
       </c>
       <c r="H482" t="n">
         <v>2096743</v>
@@ -14521,7 +14521,7 @@
         <v>7.29199981689453</v>
       </c>
       <c r="G488" t="n">
-        <v>4.92302560806274</v>
+        <v>4.9230260848999</v>
       </c>
       <c r="H488" t="n">
         <v>1062819</v>
@@ -14608,7 +14608,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G491" t="n">
-        <v>5.04319858551025</v>
+        <v>5.0431981086731</v>
       </c>
       <c r="H491" t="n">
         <v>2706817</v>
@@ -14666,7 +14666,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.1417670249939</v>
+        <v>5.14176750183105</v>
       </c>
       <c r="H493" t="n">
         <v>2819991</v>
@@ -14695,7 +14695,7 @@
         <v>7.57600021362305</v>
       </c>
       <c r="G494" t="n">
-        <v>5.11476230621338</v>
+        <v>5.11476182937622</v>
       </c>
       <c r="H494" t="n">
         <v>1479490</v>
@@ -14753,7 +14753,7 @@
         <v>7.97399997711182</v>
       </c>
       <c r="G496" t="n">
-        <v>5.38346290588379</v>
+        <v>5.38346242904663</v>
       </c>
       <c r="H496" t="n">
         <v>2796261</v>
@@ -14898,7 +14898,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>5.19847726821899</v>
+        <v>5.19847774505615</v>
       </c>
       <c r="H501" t="n">
         <v>2160367</v>
@@ -14956,7 +14956,7 @@
         <v>7.91800022125244</v>
       </c>
       <c r="G503" t="n">
-        <v>5.34565591812134</v>
+        <v>5.34565544128418</v>
       </c>
       <c r="H503" t="n">
         <v>2644025</v>
@@ -15043,7 +15043,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.43477249145508</v>
+        <v>5.43477201461792</v>
       </c>
       <c r="H506" t="n">
         <v>1280179</v>
@@ -15072,7 +15072,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G507" t="n">
-        <v>5.40641689300537</v>
+        <v>5.40641736984253</v>
       </c>
       <c r="H507" t="n">
         <v>1345581</v>
@@ -15130,7 +15130,7 @@
         <v>8.04800033569336</v>
       </c>
       <c r="G509" t="n">
-        <v>5.43342208862305</v>
+        <v>5.43342256546021</v>
       </c>
       <c r="H509" t="n">
         <v>1443560</v>
@@ -15188,7 +15188,7 @@
         <v>8.14599990844727</v>
       </c>
       <c r="G511" t="n">
-        <v>5.49958467483521</v>
+        <v>5.49958419799805</v>
       </c>
       <c r="H511" t="n">
         <v>928002</v>
@@ -15246,7 +15246,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G513" t="n">
-        <v>5.43747234344482</v>
+        <v>5.43747282028198</v>
       </c>
       <c r="H513" t="n">
         <v>1395334</v>
@@ -15391,7 +15391,7 @@
         <v>8.69799995422363</v>
       </c>
       <c r="G518" t="n">
-        <v>5.87225484848022</v>
+        <v>5.87225437164307</v>
       </c>
       <c r="H518" t="n">
         <v>1992357</v>
@@ -15420,7 +15420,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>6.21791982650757</v>
+        <v>6.21791934967041</v>
       </c>
       <c r="H519" t="n">
         <v>8210065</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.3772497177124</v>
+        <v>6.37724924087524</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15478,7 +15478,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G521" t="n">
-        <v>6.37454986572266</v>
+        <v>6.3745493888855</v>
       </c>
       <c r="H521" t="n">
         <v>4282126</v>
@@ -15507,7 +15507,7 @@
         <v>9.43400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>6.36914777755737</v>
+        <v>6.36914825439453</v>
       </c>
       <c r="H522" t="n">
         <v>2967550</v>
@@ -15565,7 +15565,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H524" t="n">
         <v>1721895</v>
@@ -15594,7 +15594,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G525" t="n">
-        <v>6.06263971328735</v>
+        <v>6.06264019012451</v>
       </c>
       <c r="H525" t="n">
         <v>1802779</v>
@@ -15623,7 +15623,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500570297241</v>
+        <v>6.14500617980957</v>
       </c>
       <c r="H526" t="n">
         <v>994506</v>
@@ -15652,7 +15652,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.2854323387146</v>
+        <v>6.28543329238892</v>
       </c>
       <c r="H527" t="n">
         <v>1251679</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.42450761795044</v>
+        <v>6.42450857162476</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>6.58248853683472</v>
+        <v>6.58248805999756</v>
       </c>
       <c r="H531" t="n">
         <v>1252149</v>
@@ -15913,7 +15913,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G536" t="n">
-        <v>6.62839698791504</v>
+        <v>6.62839651107788</v>
       </c>
       <c r="H536" t="n">
         <v>1797973</v>
@@ -16000,7 +16000,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G539" t="n">
-        <v>6.62974739074707</v>
+        <v>6.62974643707275</v>
       </c>
       <c r="H539" t="n">
         <v>1373635</v>
@@ -16174,7 +16174,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G545" t="n">
-        <v>7.55129528045654</v>
+        <v>7.5512957572937</v>
       </c>
       <c r="H545" t="n">
         <v>1308976</v>
@@ -16232,7 +16232,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G547" t="n">
-        <v>7.11246299743652</v>
+        <v>7.11246252059937</v>
       </c>
       <c r="H547" t="n">
         <v>2425730</v>
@@ -16261,7 +16261,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G548" t="n">
-        <v>7.47028017044067</v>
+        <v>7.47027969360352</v>
       </c>
       <c r="H548" t="n">
         <v>2964098</v>
@@ -16290,7 +16290,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G549" t="n">
-        <v>7.450026512146</v>
+        <v>7.45002603530884</v>
       </c>
       <c r="H549" t="n">
         <v>2293340</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.83147382736206</v>
+        <v>7.8314733505249</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16667,7 +16667,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G562" t="n">
-        <v>8.26355457305908</v>
+        <v>8.26355361938477</v>
       </c>
       <c r="H562" t="n">
         <v>2570522</v>
@@ -16783,7 +16783,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>8.82053470611572</v>
+        <v>8.82053375244141</v>
       </c>
       <c r="H566" t="n">
         <v>3617516</v>
@@ -16812,7 +16812,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G567" t="n">
-        <v>9.09396076202393</v>
+        <v>9.09395980834961</v>
       </c>
       <c r="H567" t="n">
         <v>2613180</v>
@@ -16841,7 +16841,7 @@
         <v>13.6450004577637</v>
       </c>
       <c r="G568" t="n">
-        <v>9.21210861206055</v>
+        <v>9.21210765838623</v>
       </c>
       <c r="H568" t="n">
         <v>1870794</v>
@@ -16870,7 +16870,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.3235034942627</v>
+        <v>9.32350444793701</v>
       </c>
       <c r="H569" t="n">
         <v>1639116</v>
@@ -16899,7 +16899,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>9.34375667572021</v>
+        <v>9.34375762939453</v>
       </c>
       <c r="H570" t="n">
         <v>1437346</v>
@@ -16986,7 +16986,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>9.51253890991211</v>
+        <v>9.51253986358643</v>
       </c>
       <c r="H573" t="n">
         <v>1118116</v>
@@ -17131,7 +17131,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540760040283</v>
+        <v>9.47540664672852</v>
       </c>
       <c r="H578" t="n">
         <v>1873488</v>
@@ -17160,7 +17160,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G579" t="n">
-        <v>9.84335136413574</v>
+        <v>9.84335041046143</v>
       </c>
       <c r="H579" t="n">
         <v>2092638</v>
@@ -17218,7 +17218,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G581" t="n">
-        <v>8.97243690490723</v>
+        <v>8.97243785858154</v>
       </c>
       <c r="H581" t="n">
         <v>4533092</v>
@@ -17537,7 +17537,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.9527735710144</v>
+        <v>7.95277309417725</v>
       </c>
       <c r="H592" t="n">
         <v>1799211</v>
@@ -17595,7 +17595,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893676757812</v>
+        <v>8.37893772125244</v>
       </c>
       <c r="H594" t="n">
         <v>1370145</v>
@@ -17624,7 +17624,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.1143045425415</v>
+        <v>8.11430358886719</v>
       </c>
       <c r="H595" t="n">
         <v>1343574</v>
@@ -17682,7 +17682,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465784072876</v>
+        <v>7.90465831756592</v>
       </c>
       <c r="H597" t="n">
         <v>2070634</v>
@@ -17711,7 +17711,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809535980225</v>
+        <v>7.90809488296509</v>
       </c>
       <c r="H598" t="n">
         <v>1111394</v>
@@ -17740,7 +17740,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558931350708</v>
+        <v>7.93558979034424</v>
       </c>
       <c r="H599" t="n">
         <v>1144101</v>
@@ -17769,7 +17769,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776195526123</v>
+        <v>8.00776290893555</v>
       </c>
       <c r="H600" t="n">
         <v>1299934</v>
@@ -17856,7 +17856,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H603" t="n">
         <v>4357376</v>
@@ -17943,7 +17943,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.95964765548706</v>
+        <v>7.9596471786499</v>
       </c>
       <c r="H606" t="n">
         <v>1233297</v>
@@ -18001,7 +18001,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873798370361</v>
+        <v>7.81873846054077</v>
       </c>
       <c r="H608" t="n">
         <v>943692</v>
@@ -18059,7 +18059,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.72938108444214</v>
+        <v>7.7293815612793</v>
       </c>
       <c r="H610" t="n">
         <v>1482029</v>
@@ -18146,7 +18146,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621013641357</v>
+        <v>7.95621061325073</v>
       </c>
       <c r="H613" t="n">
         <v>953411</v>
@@ -18233,7 +18233,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627696990967</v>
+        <v>7.62627744674683</v>
       </c>
       <c r="H616" t="n">
         <v>1263861</v>
@@ -18262,7 +18262,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379367828369</v>
+        <v>7.54379415512085</v>
       </c>
       <c r="H617" t="n">
         <v>1883401</v>
@@ -18349,7 +18349,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250699996948</v>
+        <v>7.72250747680664</v>
       </c>
       <c r="H620" t="n">
         <v>1949076</v>
@@ -18407,7 +18407,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434766769409</v>
+        <v>7.89434814453125</v>
       </c>
       <c r="H622" t="n">
         <v>2466372</v>
@@ -18436,7 +18436,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H623" t="n">
         <v>1875863</v>
@@ -18465,7 +18465,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H624" t="n">
         <v>2114723</v>
@@ -18494,7 +18494,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745178222656</v>
+        <v>7.99745225906372</v>
       </c>
       <c r="H625" t="n">
         <v>1003281</v>
@@ -18552,7 +18552,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H627" t="n">
         <v>2034035</v>
@@ -18639,7 +18639,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445858001709</v>
+        <v>7.34445905685425</v>
       </c>
       <c r="H630" t="n">
         <v>961522</v>
@@ -18668,7 +18668,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758544921875</v>
+        <v>7.33758497238159</v>
       </c>
       <c r="H631" t="n">
         <v>1340364</v>
@@ -18726,7 +18726,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632104873657</v>
+        <v>7.40632057189941</v>
       </c>
       <c r="H633" t="n">
         <v>1188311</v>
@@ -18755,7 +18755,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259611129761</v>
+        <v>7.28259658813477</v>
       </c>
       <c r="H634" t="n">
         <v>922139</v>
@@ -18842,7 +18842,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.19667625427246</v>
+        <v>7.1966757774353</v>
       </c>
       <c r="H637" t="n">
         <v>1104944</v>
@@ -18871,7 +18871,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.31009101867676</v>
+        <v>7.3100905418396</v>
       </c>
       <c r="H638" t="n">
         <v>1477565</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982444763184</v>
+        <v>7.07982492446899</v>
       </c>
       <c r="H642" t="n">
         <v>1299347</v>
@@ -19016,7 +19016,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949199676514</v>
+        <v>7.17949151992798</v>
       </c>
       <c r="H643" t="n">
         <v>1807666</v>
@@ -19103,7 +19103,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470287322998</v>
+        <v>7.68470335006714</v>
       </c>
       <c r="H646" t="n">
         <v>1668673</v>
@@ -19132,7 +19132,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.86685371398926</v>
+        <v>7.8668532371521</v>
       </c>
       <c r="H647" t="n">
         <v>1764822</v>
@@ -19161,7 +19161,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.9149694442749</v>
+        <v>7.91496896743774</v>
       </c>
       <c r="H648" t="n">
         <v>1235632</v>
@@ -19190,7 +19190,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122127532959</v>
+        <v>7.90122175216675</v>
       </c>
       <c r="H649" t="n">
         <v>1397538</v>
@@ -19219,7 +19219,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656534194946</v>
+        <v>7.74656581878662</v>
       </c>
       <c r="H650" t="n">
         <v>1895690</v>
@@ -19277,7 +19277,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995782852173</v>
+        <v>7.96995830535889</v>
       </c>
       <c r="H652" t="n">
         <v>1855485</v>
@@ -19364,7 +19364,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485786437988</v>
+        <v>6.91485834121704</v>
       </c>
       <c r="H655" t="n">
         <v>21113678</v>
@@ -19422,7 +19422,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946941375732</v>
+        <v>6.35946989059448</v>
       </c>
       <c r="H657" t="n">
         <v>4678338</v>
@@ -19451,7 +19451,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H658" t="n">
         <v>2619573</v>
@@ -19538,7 +19538,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736307144165</v>
+        <v>6.26736259460449</v>
       </c>
       <c r="H661" t="n">
         <v>2610988</v>
@@ -19567,7 +19567,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980192184448</v>
+        <v>5.94980239868164</v>
       </c>
       <c r="H662" t="n">
         <v>4162401</v>
@@ -19596,7 +19596,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108764648438</v>
+        <v>5.77108812332153</v>
       </c>
       <c r="H663" t="n">
         <v>4859349</v>
@@ -19712,7 +19712,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255088806152</v>
+        <v>5.95255136489868</v>
       </c>
       <c r="H667" t="n">
         <v>1004735</v>
@@ -19741,7 +19741,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017934799194</v>
+        <v>5.94017887115479</v>
       </c>
       <c r="H668" t="n">
         <v>997482</v>
@@ -19828,7 +19828,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638805389404</v>
+        <v>6.14638757705688</v>
       </c>
       <c r="H671" t="n">
         <v>2096737</v>
@@ -19944,7 +19944,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199678421021</v>
+        <v>6.22199726104736</v>
       </c>
       <c r="H675" t="n">
         <v>1440910</v>
@@ -20031,7 +20031,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634302139282</v>
+        <v>6.36634349822998</v>
       </c>
       <c r="H678" t="n">
         <v>1366723</v>
@@ -20060,7 +20060,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38009023666382</v>
+        <v>6.38008975982666</v>
       </c>
       <c r="H679" t="n">
         <v>980480</v>
@@ -20176,7 +20176,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188646316528</v>
+        <v>6.15188598632812</v>
       </c>
       <c r="H683" t="n">
         <v>2106694</v>
@@ -20292,7 +20292,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392608642578</v>
+        <v>5.95392560958862</v>
       </c>
       <c r="H687" t="n">
         <v>1295054</v>
@@ -20466,7 +20466,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28111028671265</v>
+        <v>6.28110980987549</v>
       </c>
       <c r="H693" t="n">
         <v>2462515</v>
@@ -20495,7 +20495,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.30310583114624</v>
+        <v>6.3031063079834</v>
       </c>
       <c r="H694" t="n">
         <v>1410849</v>
@@ -20524,7 +20524,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.49831676483154</v>
+        <v>6.4983172416687</v>
       </c>
       <c r="H695" t="n">
         <v>2437479</v>
@@ -20611,7 +20611,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286195755005</v>
+        <v>6.27286243438721</v>
       </c>
       <c r="H698" t="n">
         <v>3218967</v>
@@ -20640,7 +20640,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536800384521</v>
+        <v>6.24536752700806</v>
       </c>
       <c r="H699" t="n">
         <v>1981493</v>
@@ -20669,7 +20669,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170883178711</v>
+        <v>6.41170930862427</v>
       </c>
       <c r="H700" t="n">
         <v>2629183</v>
@@ -20756,7 +20756,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938089370728</v>
+        <v>6.17938041687012</v>
       </c>
       <c r="H703" t="n">
         <v>3178801</v>
@@ -20785,7 +20785,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441431045532</v>
+        <v>6.01441383361816</v>
       </c>
       <c r="H704" t="n">
         <v>3618036</v>
@@ -20901,7 +20901,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962524414062</v>
+        <v>6.20962476730347</v>
       </c>
       <c r="H708" t="n">
         <v>1498085</v>
@@ -20930,7 +20930,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698612213135</v>
+        <v>6.27698659896851</v>
       </c>
       <c r="H709" t="n">
         <v>2955864</v>
@@ -20959,7 +20959,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450283050537</v>
+        <v>6.19450330734253</v>
       </c>
       <c r="H710" t="n">
         <v>2554492</v>
@@ -21162,7 +21162,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754058837891</v>
+        <v>6.62754011154175</v>
       </c>
       <c r="H717" t="n">
         <v>2640643</v>
@@ -21220,7 +21220,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204170227051</v>
+        <v>6.62204122543335</v>
       </c>
       <c r="H719" t="n">
         <v>1962181</v>
@@ -21278,7 +21278,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.89767360687256</v>
+        <v>6.8976731300354</v>
       </c>
       <c r="H721" t="n">
         <v>3961916</v>
@@ -21336,7 +21336,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088857650757</v>
+        <v>6.76088905334473</v>
       </c>
       <c r="H723" t="n">
         <v>3582670</v>
@@ -21365,7 +21365,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705236434937</v>
+        <v>6.56705284118652</v>
       </c>
       <c r="H724" t="n">
         <v>2210569</v>
@@ -21423,7 +21423,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H726" t="n">
         <v>1858552</v>
@@ -21539,7 +21539,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.01108837127686</v>
+        <v>7.0110878944397</v>
       </c>
       <c r="H730" t="n">
         <v>8286642</v>
@@ -21626,7 +21626,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013515472412</v>
+        <v>6.78013467788696</v>
       </c>
       <c r="H733" t="n">
         <v>4138184</v>
@@ -21713,7 +21713,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729623794556</v>
+        <v>6.59729671478271</v>
       </c>
       <c r="H736" t="n">
         <v>2990029</v>
@@ -21742,7 +21742,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H737" t="n">
         <v>1630942</v>
@@ -21858,7 +21858,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H741" t="n">
         <v>1657610</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53130960464478</v>
+        <v>6.53131008148193</v>
       </c>
       <c r="H745" t="n">
         <v>2906567</v>
@@ -22061,7 +22061,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.6467866897583</v>
+        <v>6.64678716659546</v>
       </c>
       <c r="H748" t="n">
         <v>1472605</v>
@@ -22119,7 +22119,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000207901001</v>
+        <v>6.82000160217285</v>
       </c>
       <c r="H750" t="n">
         <v>2428586</v>
@@ -22206,7 +22206,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.66465854644775</v>
+        <v>6.6646580696106</v>
       </c>
       <c r="H753" t="n">
         <v>1373245</v>
@@ -22235,7 +22235,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401544570923</v>
+        <v>6.75401496887207</v>
       </c>
       <c r="H754" t="n">
         <v>1786995</v>
@@ -22293,7 +22293,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.8419976234436</v>
+        <v>6.84199810028076</v>
       </c>
       <c r="H756" t="n">
         <v>2943745</v>
@@ -22322,7 +22322,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093265533447</v>
+        <v>6.54093313217163</v>
       </c>
       <c r="H757" t="n">
         <v>3277617</v>
@@ -22438,7 +22438,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H761" t="n">
         <v>2579512</v>
@@ -22467,7 +22467,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472442626953</v>
+        <v>6.33472394943237</v>
       </c>
       <c r="H762" t="n">
         <v>1442117</v>
@@ -22554,7 +22554,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046718597412</v>
+        <v>6.37046670913696</v>
       </c>
       <c r="H765" t="n">
         <v>2725833</v>
@@ -22902,7 +22902,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166463851929</v>
+        <v>7.25166511535645</v>
       </c>
       <c r="H777" t="n">
         <v>3966282</v>
@@ -22989,7 +22989,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818351745605</v>
+        <v>7.46818399429321</v>
       </c>
       <c r="H780" t="n">
         <v>2399106</v>
@@ -23192,7 +23192,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933605194092</v>
+        <v>7.94933652877808</v>
       </c>
       <c r="H787" t="n">
         <v>3020927</v>
@@ -23250,7 +23250,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.82904863357544</v>
+        <v>7.8290491104126</v>
       </c>
       <c r="H789" t="n">
         <v>2034103</v>
@@ -23279,7 +23279,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683095932007</v>
+        <v>7.97683143615723</v>
       </c>
       <c r="H790" t="n">
         <v>2487608</v>
@@ -23395,7 +23395,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210674285889</v>
+        <v>10.2210664749146</v>
       </c>
       <c r="H794" t="n">
         <v>4399432</v>
@@ -23656,7 +23656,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341487884521</v>
+        <v>10.4341497421265</v>
       </c>
       <c r="H803" t="n">
         <v>1560972</v>
@@ -23830,7 +23830,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500032424927</v>
+        <v>10.8500022888184</v>
       </c>
       <c r="H809" t="n">
         <v>3171229</v>
@@ -23859,7 +23859,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249475479126</v>
+        <v>11.1249465942383</v>
       </c>
       <c r="H810" t="n">
         <v>2951875</v>
@@ -23888,7 +23888,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953458786011</v>
+        <v>10.6953468322754</v>
       </c>
       <c r="H811" t="n">
         <v>2115144</v>
@@ -23946,7 +23946,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485609054565</v>
+        <v>10.2485618591309</v>
       </c>
       <c r="H813" t="n">
         <v>1560898</v>
@@ -24033,7 +24033,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352586746216</v>
+        <v>11.1352577209473</v>
       </c>
       <c r="H816" t="n">
         <v>3500840</v>
@@ -24120,7 +24120,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029973983765</v>
+        <v>11.5029964447021</v>
       </c>
       <c r="H819" t="n">
         <v>2998052</v>
@@ -24207,7 +24207,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208446502686</v>
+        <v>11.3208456039429</v>
       </c>
       <c r="H822" t="n">
         <v>1495955</v>
@@ -24236,7 +24236,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376964569092</v>
+        <v>11.4376955032349</v>
       </c>
       <c r="H823" t="n">
         <v>1503927</v>
@@ -24294,7 +24294,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414669036865</v>
+        <v>11.3414659500122</v>
       </c>
       <c r="H825" t="n">
         <v>1813430</v>
@@ -24352,7 +24352,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585395812988</v>
+        <v>10.3585386276245</v>
       </c>
       <c r="H827" t="n">
         <v>2267336</v>
@@ -24381,7 +24381,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069868087769</v>
+        <v>10.3069877624512</v>
       </c>
       <c r="H828" t="n">
         <v>1710958</v>
@@ -24526,7 +24526,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634304046631</v>
+        <v>8.84634399414062</v>
       </c>
       <c r="H833" t="n">
         <v>2682628</v>
@@ -24584,7 +24584,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472534179688</v>
+        <v>9.12472438812256</v>
       </c>
       <c r="H835" t="n">
         <v>2895890</v>
@@ -24613,7 +24613,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940307617188</v>
+        <v>9.16940402984619</v>
       </c>
       <c r="H836" t="n">
         <v>1823500</v>
@@ -35926,9 +35926,38 @@
         <v>14.3699998855591</v>
       </c>
       <c r="H1226" t="n">
-        <v>1052322</v>
+        <v>1060056</v>
       </c>
       <c r="I1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1227" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>14.4049997329712</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>463212</v>
+      </c>
+      <c r="I1227" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>10.1079998016357</v>
       </c>
       <c r="G2" t="n">
-        <v>6.82418394088745</v>
+        <v>6.82418346405029</v>
       </c>
       <c r="H2" t="n">
         <v>23323315</v>
@@ -456,7 +456,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G3" t="n">
-        <v>7.23060989379883</v>
+        <v>7.23061037063599</v>
       </c>
       <c r="H3" t="n">
         <v>11315628</v>
@@ -485,7 +485,7 @@
         <v>11.3760004043579</v>
       </c>
       <c r="G4" t="n">
-        <v>7.68024492263794</v>
+        <v>7.68024444580078</v>
       </c>
       <c r="H4" t="n">
         <v>9073446</v>
@@ -659,7 +659,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>7.48040676116943</v>
+        <v>7.48040723800659</v>
       </c>
       <c r="H10" t="n">
         <v>7510382</v>
@@ -775,7 +775,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>7.05507659912109</v>
+        <v>7.05507707595825</v>
       </c>
       <c r="H14" t="n">
         <v>2413549</v>
@@ -862,7 +862,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>6.47109270095825</v>
+        <v>6.47109222412109</v>
       </c>
       <c r="H17" t="n">
         <v>4229589</v>
@@ -891,7 +891,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>6.28543329238892</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H18" t="n">
         <v>3251441</v>
@@ -1036,7 +1036,7 @@
         <v>9.52499961853027</v>
       </c>
       <c r="G23" t="n">
-        <v>6.43058395385742</v>
+        <v>6.43058443069458</v>
       </c>
       <c r="H23" t="n">
         <v>3182466</v>
@@ -1065,7 +1065,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G24" t="n">
-        <v>6.29218292236328</v>
+        <v>6.29218339920044</v>
       </c>
       <c r="H24" t="n">
         <v>2785789</v>
@@ -1123,7 +1123,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>5.91411256790161</v>
+        <v>5.91411209106445</v>
       </c>
       <c r="H26" t="n">
         <v>3367791</v>
@@ -1152,7 +1152,7 @@
         <v>8.75</v>
       </c>
       <c r="G27" t="n">
-        <v>5.90736103057861</v>
+        <v>5.90736150741577</v>
       </c>
       <c r="H27" t="n">
         <v>3275204</v>
@@ -1181,7 +1181,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G28" t="n">
-        <v>5.69132089614868</v>
+        <v>5.69132041931152</v>
       </c>
       <c r="H28" t="n">
         <v>6011852</v>
@@ -1210,7 +1210,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G29" t="n">
-        <v>6.08626985549927</v>
+        <v>6.08627033233643</v>
       </c>
       <c r="H29" t="n">
         <v>6081895</v>
@@ -1239,7 +1239,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>6.04238605499268</v>
+        <v>6.04238653182983</v>
       </c>
       <c r="H30" t="n">
         <v>4204295</v>
@@ -1268,7 +1268,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>5.81284284591675</v>
+        <v>5.81284332275391</v>
       </c>
       <c r="H31" t="n">
         <v>3316128</v>
@@ -1355,7 +1355,7 @@
         <v>8.375</v>
       </c>
       <c r="G34" t="n">
-        <v>5.65418910980225</v>
+        <v>5.65418863296509</v>
       </c>
       <c r="H34" t="n">
         <v>2299262</v>
@@ -1500,7 +1500,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22548246383667</v>
+        <v>5.22548294067383</v>
       </c>
       <c r="H39" t="n">
         <v>1845591</v>
@@ -1587,7 +1587,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G42" t="n">
-        <v>5.0263204574585</v>
+        <v>5.02631998062134</v>
       </c>
       <c r="H42" t="n">
         <v>2532581</v>
@@ -1645,7 +1645,7 @@
         <v>7.00500011444092</v>
       </c>
       <c r="G44" t="n">
-        <v>4.72926473617554</v>
+        <v>4.72926425933838</v>
       </c>
       <c r="H44" t="n">
         <v>3447231</v>
@@ -1674,7 +1674,7 @@
         <v>6.875</v>
       </c>
       <c r="G45" t="n">
-        <v>4.64149808883667</v>
+        <v>4.64149761199951</v>
       </c>
       <c r="H45" t="n">
         <v>1906095</v>
@@ -1703,7 +1703,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>4.27692985534668</v>
+        <v>4.27692937850952</v>
       </c>
       <c r="H46" t="n">
         <v>3684492</v>
@@ -1732,7 +1732,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H47" t="n">
         <v>5966204</v>
@@ -1790,7 +1790,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H49" t="n">
         <v>4270764</v>
@@ -1819,7 +1819,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G50" t="n">
-        <v>4.13852834701538</v>
+        <v>4.13852787017822</v>
       </c>
       <c r="H50" t="n">
         <v>5312212</v>
@@ -1877,7 +1877,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G52" t="n">
-        <v>4.53685283660889</v>
+        <v>4.53685331344604</v>
       </c>
       <c r="H52" t="n">
         <v>2581341</v>
@@ -1993,7 +1993,7 @@
         <v>6.71500015258789</v>
       </c>
       <c r="G56" t="n">
-        <v>4.53347826004028</v>
+        <v>4.53347778320312</v>
       </c>
       <c r="H56" t="n">
         <v>4400032</v>
@@ -2022,7 +2022,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>4.44233560562134</v>
+        <v>4.44233512878418</v>
       </c>
       <c r="H57" t="n">
         <v>2303616</v>
@@ -2051,7 +2051,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G58" t="n">
-        <v>4.48284339904785</v>
+        <v>4.48284292221069</v>
       </c>
       <c r="H58" t="n">
         <v>2735170</v>
@@ -2196,7 +2196,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>4.4355845451355</v>
+        <v>4.43558406829834</v>
       </c>
       <c r="H63" t="n">
         <v>4427308</v>
@@ -2341,7 +2341,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G68" t="n">
-        <v>3.84484839439392</v>
+        <v>3.84484815597534</v>
       </c>
       <c r="H68" t="n">
         <v>4549813</v>
@@ -2486,7 +2486,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>3.85497546195984</v>
+        <v>3.85497522354126</v>
       </c>
       <c r="H73" t="n">
         <v>2825138</v>
@@ -2515,7 +2515,7 @@
         <v>6.05100011825562</v>
       </c>
       <c r="G74" t="n">
-        <v>4.08519315719604</v>
+        <v>4.0851936340332</v>
       </c>
       <c r="H74" t="n">
         <v>3445946</v>
@@ -2544,7 +2544,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G75" t="n">
-        <v>4.02240657806396</v>
+        <v>4.02240705490112</v>
       </c>
       <c r="H75" t="n">
         <v>2815887</v>
@@ -2602,7 +2602,7 @@
         <v>6.12099981307983</v>
       </c>
       <c r="G77" t="n">
-        <v>4.1324520111084</v>
+        <v>4.13245153427124</v>
       </c>
       <c r="H77" t="n">
         <v>1758895</v>
@@ -2631,7 +2631,7 @@
         <v>6.13100004196167</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13920402526855</v>
+        <v>4.1392035484314</v>
       </c>
       <c r="H78" t="n">
         <v>1800303</v>
@@ -2718,7 +2718,7 @@
         <v>5.74700021743774</v>
       </c>
       <c r="G81" t="n">
-        <v>3.87995481491089</v>
+        <v>3.87995529174805</v>
       </c>
       <c r="H81" t="n">
         <v>4118445</v>
@@ -2747,7 +2747,7 @@
         <v>5.63100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>3.8016402721405</v>
+        <v>3.80164003372192</v>
       </c>
       <c r="H82" t="n">
         <v>2732328</v>
@@ -2805,7 +2805,7 @@
         <v>5.64799976348877</v>
       </c>
       <c r="G84" t="n">
-        <v>3.81311678886414</v>
+        <v>3.81311702728271</v>
       </c>
       <c r="H84" t="n">
         <v>1099010</v>
@@ -2834,7 +2834,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.76720881462097</v>
+        <v>3.76720857620239</v>
       </c>
       <c r="H85" t="n">
         <v>1773043</v>
@@ -2863,7 +2863,7 @@
         <v>5.75</v>
       </c>
       <c r="G86" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H86" t="n">
         <v>1785095</v>
@@ -2950,7 +2950,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>3.68619346618652</v>
+        <v>3.68619322776794</v>
       </c>
       <c r="H89" t="n">
         <v>1944723</v>
@@ -3008,7 +3008,7 @@
         <v>5.23600006103516</v>
       </c>
       <c r="G91" t="n">
-        <v>3.53496503829956</v>
+        <v>3.53496479988098</v>
       </c>
       <c r="H91" t="n">
         <v>1768139</v>
@@ -3037,7 +3037,7 @@
         <v>5.41900014877319</v>
       </c>
       <c r="G92" t="n">
-        <v>3.65851330757141</v>
+        <v>3.65851306915283</v>
       </c>
       <c r="H92" t="n">
         <v>1860265</v>
@@ -3066,7 +3066,7 @@
         <v>5.39699983596802</v>
       </c>
       <c r="G93" t="n">
-        <v>3.64366030693054</v>
+        <v>3.64366006851196</v>
       </c>
       <c r="H93" t="n">
         <v>1936176</v>
@@ -3124,7 +3124,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>3.65581250190735</v>
+        <v>3.65581274032593</v>
       </c>
       <c r="H95" t="n">
         <v>1002502</v>
@@ -3153,7 +3153,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G96" t="n">
-        <v>3.77396011352539</v>
+        <v>3.77395987510681</v>
       </c>
       <c r="H96" t="n">
         <v>3413741</v>
@@ -3269,7 +3269,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>3.81446766853333</v>
+        <v>3.81446743011475</v>
       </c>
       <c r="H100" t="n">
         <v>1355091</v>
@@ -3327,7 +3327,7 @@
         <v>5.72300004959106</v>
       </c>
       <c r="G102" t="n">
-        <v>3.86375164985657</v>
+        <v>3.86375188827515</v>
       </c>
       <c r="H102" t="n">
         <v>1984827</v>
@@ -3356,7 +3356,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>3.98324966430664</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H103" t="n">
         <v>2495941</v>
@@ -3385,7 +3385,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.023756980896</v>
+        <v>4.02375650405884</v>
       </c>
       <c r="H104" t="n">
         <v>1583023</v>
@@ -3472,7 +3472,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G107" t="n">
-        <v>4.01430511474609</v>
+        <v>4.01430559158325</v>
       </c>
       <c r="H107" t="n">
         <v>1985267</v>
@@ -3530,7 +3530,7 @@
         <v>6.10300016403198</v>
       </c>
       <c r="G109" t="n">
-        <v>4.12029981613159</v>
+        <v>4.12030029296875</v>
       </c>
       <c r="H109" t="n">
         <v>2831477</v>
@@ -3675,7 +3675,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G114" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H114" t="n">
         <v>4779877</v>
@@ -3733,7 +3733,7 @@
         <v>5.09700012207031</v>
       </c>
       <c r="G116" t="n">
-        <v>3.44112253189087</v>
+        <v>3.44112229347229</v>
       </c>
       <c r="H116" t="n">
         <v>2818082</v>
@@ -3849,7 +3849,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G120" t="n">
-        <v>3.6794421672821</v>
+        <v>3.67944192886353</v>
       </c>
       <c r="H120" t="n">
         <v>1265113</v>
@@ -3878,7 +3878,7 @@
         <v>5.41699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>3.65716290473938</v>
+        <v>3.6571626663208</v>
       </c>
       <c r="H121" t="n">
         <v>1367658</v>
@@ -3936,7 +3936,7 @@
         <v>5.10699987411499</v>
       </c>
       <c r="G123" t="n">
-        <v>3.44787335395813</v>
+        <v>3.44787359237671</v>
       </c>
       <c r="H123" t="n">
         <v>1778269</v>
@@ -3965,7 +3965,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G124" t="n">
-        <v>3.50728487968445</v>
+        <v>3.50728464126587</v>
       </c>
       <c r="H124" t="n">
         <v>1933194</v>
@@ -4023,7 +4023,7 @@
         <v>5.30200004577637</v>
       </c>
       <c r="G126" t="n">
-        <v>3.57952308654785</v>
+        <v>3.57952332496643</v>
       </c>
       <c r="H126" t="n">
         <v>1556955</v>
@@ -4081,7 +4081,7 @@
         <v>5.04199981689453</v>
       </c>
       <c r="G128" t="n">
-        <v>3.40399026870728</v>
+        <v>3.4039900302887</v>
       </c>
       <c r="H128" t="n">
         <v>3072185</v>
@@ -4110,7 +4110,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>3.42897009849548</v>
+        <v>3.4289698600769</v>
       </c>
       <c r="H129" t="n">
         <v>1535360</v>
@@ -4168,7 +4168,7 @@
         <v>4.74849987030029</v>
       </c>
       <c r="G131" t="n">
-        <v>3.20584058761597</v>
+        <v>3.20584034919739</v>
       </c>
       <c r="H131" t="n">
         <v>3762380</v>
@@ -4197,7 +4197,7 @@
         <v>4.75449991226196</v>
       </c>
       <c r="G132" t="n">
-        <v>3.2098913192749</v>
+        <v>3.20989108085632</v>
       </c>
       <c r="H132" t="n">
         <v>3036596</v>
@@ -4226,7 +4226,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G133" t="n">
-        <v>3.44044709205627</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H133" t="n">
         <v>3052499</v>
@@ -4313,7 +4313,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G136" t="n">
-        <v>3.45665001869202</v>
+        <v>3.4566502571106</v>
       </c>
       <c r="H136" t="n">
         <v>1560900</v>
@@ -4371,7 +4371,7 @@
         <v>4.75950002670288</v>
       </c>
       <c r="G138" t="n">
-        <v>3.2132670879364</v>
+        <v>3.21326684951782</v>
       </c>
       <c r="H138" t="n">
         <v>2312800</v>
@@ -4545,7 +4545,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G144" t="n">
-        <v>3.62813234329224</v>
+        <v>3.62813258171082</v>
       </c>
       <c r="H144" t="n">
         <v>1162846</v>
@@ -4574,7 +4574,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G145" t="n">
-        <v>3.64568591117859</v>
+        <v>3.64568567276001</v>
       </c>
       <c r="H145" t="n">
         <v>1157899</v>
@@ -4603,7 +4603,7 @@
         <v>5.23199987411499</v>
       </c>
       <c r="G146" t="n">
-        <v>3.53226399421692</v>
+        <v>3.5322642326355</v>
       </c>
       <c r="H146" t="n">
         <v>1532624</v>
@@ -4719,7 +4719,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G150" t="n">
-        <v>3.89143180847168</v>
+        <v>3.89143204689026</v>
       </c>
       <c r="H150" t="n">
         <v>1641881</v>
@@ -4806,7 +4806,7 @@
         <v>5.75899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>3.88805603981018</v>
+        <v>3.88805627822876</v>
       </c>
       <c r="H153" t="n">
         <v>2138183</v>
@@ -4864,7 +4864,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G155" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H155" t="n">
         <v>695578</v>
@@ -4893,7 +4893,7 @@
         <v>5.73799991607666</v>
       </c>
       <c r="G156" t="n">
-        <v>3.87387871742249</v>
+        <v>3.87387895584106</v>
       </c>
       <c r="H156" t="n">
         <v>947624</v>
@@ -5067,7 +5067,7 @@
         <v>5.91099977493286</v>
       </c>
       <c r="G162" t="n">
-        <v>3.99067521095276</v>
+        <v>3.99067568778992</v>
       </c>
       <c r="H162" t="n">
         <v>836698</v>
@@ -5096,7 +5096,7 @@
         <v>5.75</v>
       </c>
       <c r="G163" t="n">
-        <v>3.88198018074036</v>
+        <v>3.88197994232178</v>
       </c>
       <c r="H163" t="n">
         <v>830988</v>
@@ -5183,7 +5183,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G166" t="n">
-        <v>3.75370597839355</v>
+        <v>3.75370621681213</v>
       </c>
       <c r="H166" t="n">
         <v>1306839</v>
@@ -5212,7 +5212,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G167" t="n">
-        <v>3.67539119720459</v>
+        <v>3.67539143562317</v>
       </c>
       <c r="H167" t="n">
         <v>1508487</v>
@@ -5328,7 +5328,7 @@
         <v>5.05600023269653</v>
       </c>
       <c r="G171" t="n">
-        <v>3.41344237327576</v>
+        <v>3.41344213485718</v>
       </c>
       <c r="H171" t="n">
         <v>1569176</v>
@@ -5357,7 +5357,7 @@
         <v>4.94549989700317</v>
       </c>
       <c r="G172" t="n">
-        <v>3.33884024620056</v>
+        <v>3.33884048461914</v>
       </c>
       <c r="H172" t="n">
         <v>1226903</v>
@@ -5386,7 +5386,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G173" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H173" t="n">
         <v>1536086</v>
@@ -5502,7 +5502,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G177" t="n">
-        <v>3.35538077354431</v>
+        <v>3.35538101196289</v>
       </c>
       <c r="H177" t="n">
         <v>1462223</v>
@@ -5589,7 +5589,7 @@
         <v>5.09600019454956</v>
       </c>
       <c r="G180" t="n">
-        <v>3.44044709205627</v>
+        <v>3.44044733047485</v>
       </c>
       <c r="H180" t="n">
         <v>1415013</v>
@@ -5676,7 +5676,7 @@
         <v>4.98750019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.36719608306885</v>
+        <v>3.36719584465027</v>
       </c>
       <c r="H183" t="n">
         <v>1585033</v>
@@ -5763,7 +5763,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H186" t="n">
         <v>1032448</v>
@@ -5792,7 +5792,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G187" t="n">
-        <v>3.36213231086731</v>
+        <v>3.36213254928589</v>
       </c>
       <c r="H187" t="n">
         <v>1010793</v>
@@ -5879,7 +5879,7 @@
         <v>4.81150007247925</v>
       </c>
       <c r="G190" t="n">
-        <v>3.24837374687195</v>
+        <v>3.24837350845337</v>
       </c>
       <c r="H190" t="n">
         <v>891838</v>
@@ -5908,7 +5908,7 @@
         <v>4.90450000762939</v>
       </c>
       <c r="G191" t="n">
-        <v>3.31116008758545</v>
+        <v>3.31116032600403</v>
       </c>
       <c r="H191" t="n">
         <v>1348230</v>
@@ -5966,7 +5966,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>3.28786849975586</v>
+        <v>3.28786826133728</v>
       </c>
       <c r="H193" t="n">
         <v>1635754</v>
@@ -6024,7 +6024,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>3.47690415382385</v>
+        <v>3.47690391540527</v>
       </c>
       <c r="H195" t="n">
         <v>1707922</v>
@@ -6111,7 +6111,7 @@
         <v>5.14699983596802</v>
       </c>
       <c r="G198" t="n">
-        <v>3.47487854957581</v>
+        <v>3.47487831115723</v>
       </c>
       <c r="H198" t="n">
         <v>1005472</v>
@@ -6198,7 +6198,7 @@
         <v>5.03399991989136</v>
       </c>
       <c r="G201" t="n">
-        <v>3.39858937263489</v>
+        <v>3.39858913421631</v>
       </c>
       <c r="H201" t="n">
         <v>960763</v>
@@ -6227,7 +6227,7 @@
         <v>5.19600009918213</v>
       </c>
       <c r="G202" t="n">
-        <v>3.50795984268188</v>
+        <v>3.50796008110046</v>
       </c>
       <c r="H202" t="n">
         <v>1007357</v>
@@ -6256,7 +6256,7 @@
         <v>5.11899995803833</v>
       </c>
       <c r="G203" t="n">
-        <v>3.455974817276</v>
+        <v>3.45597505569458</v>
       </c>
       <c r="H203" t="n">
         <v>1003543</v>
@@ -6314,7 +6314,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G205" t="n">
-        <v>3.60855340957642</v>
+        <v>3.608553647995</v>
       </c>
       <c r="H205" t="n">
         <v>1822628</v>
@@ -6401,7 +6401,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G208" t="n">
-        <v>3.62678217887878</v>
+        <v>3.62678241729736</v>
       </c>
       <c r="H208" t="n">
         <v>815597</v>
@@ -6517,7 +6517,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G212" t="n">
-        <v>3.78206181526184</v>
+        <v>3.78206157684326</v>
       </c>
       <c r="H212" t="n">
         <v>1401317</v>
@@ -6575,7 +6575,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G214" t="n">
-        <v>3.69294428825378</v>
+        <v>3.69294452667236</v>
       </c>
       <c r="H214" t="n">
         <v>561510</v>
@@ -6604,7 +6604,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G215" t="n">
-        <v>3.7240002155304</v>
+        <v>3.72400045394897</v>
       </c>
       <c r="H215" t="n">
         <v>771072</v>
@@ -6633,7 +6633,7 @@
         <v>5.4520001411438</v>
       </c>
       <c r="G216" t="n">
-        <v>3.68079257011414</v>
+        <v>3.68079233169556</v>
       </c>
       <c r="H216" t="n">
         <v>710760</v>
@@ -6662,7 +6662,7 @@
         <v>5.37900018692017</v>
       </c>
       <c r="G217" t="n">
-        <v>3.63150811195374</v>
+        <v>3.63150835037231</v>
       </c>
       <c r="H217" t="n">
         <v>1446118</v>
@@ -6720,7 +6720,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>3.91573667526245</v>
+        <v>3.91573643684387</v>
       </c>
       <c r="H219" t="n">
         <v>1966146</v>
@@ -6749,7 +6749,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.98324966430664</v>
+        <v>3.98324918746948</v>
       </c>
       <c r="H220" t="n">
         <v>1345223</v>
@@ -6778,7 +6778,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>4.14527988433838</v>
+        <v>4.14527940750122</v>
       </c>
       <c r="H221" t="n">
         <v>3310511</v>
@@ -6807,7 +6807,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G222" t="n">
-        <v>4.20266532897949</v>
+        <v>4.20266580581665</v>
       </c>
       <c r="H222" t="n">
         <v>2465306</v>
@@ -6836,7 +6836,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G223" t="n">
-        <v>4.23979806900024</v>
+        <v>4.23979759216309</v>
       </c>
       <c r="H223" t="n">
         <v>1940924</v>
@@ -6865,7 +6865,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19928932189941</v>
+        <v>4.19928979873657</v>
       </c>
       <c r="H224" t="n">
         <v>1230545</v>
@@ -7097,7 +7097,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G232" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H232" t="n">
         <v>341527</v>
@@ -7126,7 +7126,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G233" t="n">
-        <v>4.22629499435425</v>
+        <v>4.22629547119141</v>
       </c>
       <c r="H233" t="n">
         <v>709890</v>
@@ -7155,7 +7155,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G234" t="n">
-        <v>4.28840684890747</v>
+        <v>4.28840637207031</v>
       </c>
       <c r="H234" t="n">
         <v>1390641</v>
@@ -7329,7 +7329,7 @@
         <v>6.31300020217896</v>
       </c>
       <c r="G240" t="n">
-        <v>4.26207685470581</v>
+        <v>4.26207637786865</v>
       </c>
       <c r="H240" t="n">
         <v>1219252</v>
@@ -7358,7 +7358,7 @@
         <v>6.2039999961853</v>
       </c>
       <c r="G241" t="n">
-        <v>4.1884880065918</v>
+        <v>4.18848752975464</v>
       </c>
       <c r="H241" t="n">
         <v>1305794</v>
@@ -7474,7 +7474,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G245" t="n">
-        <v>4.23979806900024</v>
+        <v>4.23979759216309</v>
       </c>
       <c r="H245" t="n">
         <v>1194931</v>
@@ -7561,7 +7561,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G248" t="n">
-        <v>3.96434545516968</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H248" t="n">
         <v>911894</v>
@@ -7590,7 +7590,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G249" t="n">
-        <v>4.02645778656006</v>
+        <v>4.0264573097229</v>
       </c>
       <c r="H249" t="n">
         <v>795631</v>
@@ -7764,7 +7764,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>3.73682761192322</v>
+        <v>3.7368278503418</v>
       </c>
       <c r="H255" t="n">
         <v>892336</v>
@@ -7822,7 +7822,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G257" t="n">
-        <v>3.75235605239868</v>
+        <v>3.7523558139801</v>
       </c>
       <c r="H257" t="n">
         <v>475168</v>
@@ -7851,7 +7851,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G258" t="n">
-        <v>3.87522864341736</v>
+        <v>3.87522888183594</v>
       </c>
       <c r="H258" t="n">
         <v>683671</v>
@@ -7938,7 +7938,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G261" t="n">
-        <v>3.96434545516968</v>
+        <v>3.96434593200684</v>
       </c>
       <c r="H261" t="n">
         <v>1652373</v>
@@ -7967,7 +7967,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G262" t="n">
-        <v>4.06156349182129</v>
+        <v>4.06156396865845</v>
       </c>
       <c r="H262" t="n">
         <v>1735246</v>
@@ -8025,7 +8025,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>4.20604133605957</v>
+        <v>4.20604085922241</v>
       </c>
       <c r="H264" t="n">
         <v>1003317</v>
@@ -8054,7 +8054,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G265" t="n">
-        <v>4.42478275299072</v>
+        <v>4.42478227615356</v>
       </c>
       <c r="H265" t="n">
         <v>3181061</v>
@@ -8141,7 +8141,7 @@
         <v>6.94099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>4.68605661392212</v>
+        <v>4.68605613708496</v>
       </c>
       <c r="H268" t="n">
         <v>2146613</v>
@@ -8315,7 +8315,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G274" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H274" t="n">
         <v>1735281</v>
@@ -8344,7 +8344,7 @@
         <v>7.47300004959106</v>
       </c>
       <c r="G275" t="n">
-        <v>5.04522371292114</v>
+        <v>5.0452241897583</v>
       </c>
       <c r="H275" t="n">
         <v>3618760</v>
@@ -8460,7 +8460,7 @@
         <v>7.50600004196167</v>
       </c>
       <c r="G279" t="n">
-        <v>5.06750345230103</v>
+        <v>5.06750297546387</v>
       </c>
       <c r="H279" t="n">
         <v>1448874</v>
@@ -8663,7 +8663,7 @@
         <v>7.68599987030029</v>
       </c>
       <c r="G286" t="n">
-        <v>5.18902635574341</v>
+        <v>5.18902587890625</v>
       </c>
       <c r="H286" t="n">
         <v>2462672</v>
@@ -8779,7 +8779,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G290" t="n">
-        <v>6.1794376373291</v>
+        <v>6.17943716049194</v>
       </c>
       <c r="H290" t="n">
         <v>1832776</v>
@@ -8808,7 +8808,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>6.30231046676636</v>
+        <v>6.3023099899292</v>
       </c>
       <c r="H291" t="n">
         <v>1551590</v>
@@ -8837,7 +8837,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G292" t="n">
-        <v>6.25707626342773</v>
+        <v>6.25707674026489</v>
       </c>
       <c r="H292" t="n">
         <v>1429447</v>
@@ -8866,7 +8866,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G293" t="n">
-        <v>6.09909725189209</v>
+        <v>6.09909772872925</v>
       </c>
       <c r="H293" t="n">
         <v>1649945</v>
@@ -8982,7 +8982,7 @@
         <v>8.75</v>
       </c>
       <c r="G297" t="n">
-        <v>5.90736103057861</v>
+        <v>5.90736150741577</v>
       </c>
       <c r="H297" t="n">
         <v>1065274</v>
@@ -9069,7 +9069,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G300" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H300" t="n">
         <v>774116</v>
@@ -9098,7 +9098,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G301" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H301" t="n">
         <v>740488</v>
@@ -9127,7 +9127,7 @@
         <v>9.11100006103516</v>
       </c>
       <c r="G302" t="n">
-        <v>6.15108156204224</v>
+        <v>6.15108203887939</v>
       </c>
       <c r="H302" t="n">
         <v>850913</v>
@@ -9185,7 +9185,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G304" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H304" t="n">
         <v>1512205</v>
@@ -9214,7 +9214,7 @@
         <v>9.17399978637695</v>
       </c>
       <c r="G305" t="n">
-        <v>6.1936149597168</v>
+        <v>6.19361448287964</v>
       </c>
       <c r="H305" t="n">
         <v>1343595</v>
@@ -9243,7 +9243,7 @@
         <v>9.07299995422363</v>
       </c>
       <c r="G306" t="n">
-        <v>6.12542676925659</v>
+        <v>6.12542724609375</v>
       </c>
       <c r="H306" t="n">
         <v>1336985</v>
@@ -9301,7 +9301,7 @@
         <v>8.50899982452393</v>
       </c>
       <c r="G308" t="n">
-        <v>5.74465560913086</v>
+        <v>5.7446551322937</v>
       </c>
       <c r="H308" t="n">
         <v>1509651</v>
@@ -9359,7 +9359,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G310" t="n">
-        <v>5.66836643218994</v>
+        <v>5.66836595535278</v>
       </c>
       <c r="H310" t="n">
         <v>1335804</v>
@@ -9417,7 +9417,7 @@
         <v>8.49300003051758</v>
       </c>
       <c r="G312" t="n">
-        <v>5.73385334014893</v>
+        <v>5.73385381698608</v>
       </c>
       <c r="H312" t="n">
         <v>2412855</v>
@@ -9533,7 +9533,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G316" t="n">
-        <v>6.08897066116333</v>
+        <v>6.08897018432617</v>
       </c>
       <c r="H316" t="n">
         <v>1068724</v>
@@ -9562,7 +9562,7 @@
         <v>8.56700038909912</v>
       </c>
       <c r="G317" t="n">
-        <v>5.7838134765625</v>
+        <v>5.78381299972534</v>
       </c>
       <c r="H317" t="n">
         <v>1777741</v>
@@ -9649,7 +9649,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G320" t="n">
-        <v>5.91411256790161</v>
+        <v>5.91411209106445</v>
       </c>
       <c r="H320" t="n">
         <v>1043632</v>
@@ -9707,7 +9707,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G322" t="n">
-        <v>5.89048337936401</v>
+        <v>5.89048290252686</v>
       </c>
       <c r="H322" t="n">
         <v>967814</v>
@@ -9736,7 +9736,7 @@
         <v>8.48799991607666</v>
       </c>
       <c r="G323" t="n">
-        <v>5.73047733306885</v>
+        <v>5.73047780990601</v>
       </c>
       <c r="H323" t="n">
         <v>1626293</v>
@@ -10026,7 +10026,7 @@
         <v>8.29599952697754</v>
       </c>
       <c r="G333" t="n">
-        <v>5.60085296630859</v>
+        <v>5.60085344314575</v>
       </c>
       <c r="H333" t="n">
         <v>1137057</v>
@@ -10113,7 +10113,7 @@
         <v>8.35400009155273</v>
       </c>
       <c r="G336" t="n">
-        <v>5.64001035690308</v>
+        <v>5.64001083374023</v>
       </c>
       <c r="H336" t="n">
         <v>610594</v>
@@ -10258,7 +10258,7 @@
         <v>7.86199998855591</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30784797668457</v>
+        <v>5.30784845352173</v>
       </c>
       <c r="H341" t="n">
         <v>1370858</v>
@@ -10287,7 +10287,7 @@
         <v>7.86399984359741</v>
       </c>
       <c r="G342" t="n">
-        <v>5.30919885635376</v>
+        <v>5.3091983795166</v>
       </c>
       <c r="H342" t="n">
         <v>806647</v>
@@ -10316,7 +10316,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G343" t="n">
-        <v>5.14581775665283</v>
+        <v>5.14581823348999</v>
       </c>
       <c r="H343" t="n">
         <v>1174384</v>
@@ -10519,7 +10519,7 @@
         <v>7.33199977874756</v>
       </c>
       <c r="G350" t="n">
-        <v>4.95003128051758</v>
+        <v>4.95003080368042</v>
       </c>
       <c r="H350" t="n">
         <v>1343262</v>
@@ -10548,7 +10548,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G351" t="n">
-        <v>4.90547227859497</v>
+        <v>4.90547275543213</v>
       </c>
       <c r="H351" t="n">
         <v>1070151</v>
@@ -10577,7 +10577,7 @@
         <v>7.41800022125244</v>
       </c>
       <c r="G352" t="n">
-        <v>5.00809192657471</v>
+        <v>5.00809240341187</v>
       </c>
       <c r="H352" t="n">
         <v>1123756</v>
@@ -10722,7 +10722,7 @@
         <v>7.26599979400635</v>
       </c>
       <c r="G357" t="n">
-        <v>4.90547227859497</v>
+        <v>4.90547275543213</v>
       </c>
       <c r="H357" t="n">
         <v>1284720</v>
@@ -10809,7 +10809,7 @@
         <v>7.23600006103516</v>
       </c>
       <c r="G360" t="n">
-        <v>4.88521909713745</v>
+        <v>4.88521862030029</v>
       </c>
       <c r="H360" t="n">
         <v>443396</v>
@@ -11041,7 +11041,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G368" t="n">
-        <v>4.95543193817139</v>
+        <v>4.95543241500854</v>
       </c>
       <c r="H368" t="n">
         <v>1136830</v>
@@ -11099,7 +11099,7 @@
         <v>7.46600008010864</v>
       </c>
       <c r="G370" t="n">
-        <v>5.04049825668335</v>
+        <v>5.04049873352051</v>
       </c>
       <c r="H370" t="n">
         <v>872450</v>
@@ -11302,7 +11302,7 @@
         <v>7.93200016021729</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35510730743408</v>
+        <v>5.35510778427124</v>
       </c>
       <c r="H377" t="n">
         <v>3080122</v>
@@ -11418,7 +11418,7 @@
         <v>7.89599990844727</v>
       </c>
       <c r="G381" t="n">
-        <v>5.33080244064331</v>
+        <v>5.33080291748047</v>
       </c>
       <c r="H381" t="n">
         <v>1027240</v>
@@ -11476,7 +11476,7 @@
         <v>7.95800018310547</v>
       </c>
       <c r="G383" t="n">
-        <v>5.37266063690186</v>
+        <v>5.37266111373901</v>
       </c>
       <c r="H383" t="n">
         <v>997333</v>
@@ -11505,7 +11505,7 @@
         <v>8.2519998550415</v>
       </c>
       <c r="G384" t="n">
-        <v>5.57114839553833</v>
+        <v>5.57114791870117</v>
       </c>
       <c r="H384" t="n">
         <v>1867030</v>
@@ -11737,7 +11737,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G392" t="n">
-        <v>5.61975765228271</v>
+        <v>5.61975717544556</v>
       </c>
       <c r="H392" t="n">
         <v>2069415</v>
@@ -12027,7 +12027,7 @@
         <v>8.15799999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>5.50768566131592</v>
+        <v>5.50768613815308</v>
       </c>
       <c r="H402" t="n">
         <v>890149</v>
@@ -12056,7 +12056,7 @@
         <v>8.3459997177124</v>
       </c>
       <c r="G403" t="n">
-        <v>5.63460969924927</v>
+        <v>5.63461017608643</v>
       </c>
       <c r="H403" t="n">
         <v>1808163</v>
@@ -12114,7 +12114,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G405" t="n">
-        <v>5.823646068573</v>
+        <v>5.82364559173584</v>
       </c>
       <c r="H405" t="n">
         <v>1357346</v>
@@ -12143,7 +12143,7 @@
         <v>8.76799964904785</v>
       </c>
       <c r="G406" t="n">
-        <v>5.91951274871826</v>
+        <v>5.91951322555542</v>
       </c>
       <c r="H406" t="n">
         <v>1665434</v>
@@ -12172,7 +12172,7 @@
         <v>9.53400039672852</v>
       </c>
       <c r="G407" t="n">
-        <v>6.43666076660156</v>
+        <v>6.43666124343872</v>
       </c>
       <c r="H407" t="n">
         <v>10634260</v>
@@ -12201,7 +12201,7 @@
         <v>9.7180004119873</v>
       </c>
       <c r="G408" t="n">
-        <v>6.56088447570801</v>
+        <v>6.56088399887085</v>
       </c>
       <c r="H408" t="n">
         <v>3234067</v>
@@ -12230,7 +12230,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>6.54873132705688</v>
+        <v>6.54873180389404</v>
       </c>
       <c r="H409" t="n">
         <v>2733714</v>
@@ -12317,7 +12317,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G412" t="n">
-        <v>6.29758501052856</v>
+        <v>6.29758453369141</v>
       </c>
       <c r="H412" t="n">
         <v>951090</v>
@@ -12346,7 +12346,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G413" t="n">
-        <v>6.27193021774292</v>
+        <v>6.27192974090576</v>
       </c>
       <c r="H413" t="n">
         <v>817793</v>
@@ -12433,7 +12433,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G416" t="n">
-        <v>6.10044813156128</v>
+        <v>6.10044765472412</v>
       </c>
       <c r="H416" t="n">
         <v>989526</v>
@@ -12520,7 +12520,7 @@
         <v>8.63199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>5.82769680023193</v>
+        <v>5.82769632339478</v>
       </c>
       <c r="H419" t="n">
         <v>1609287</v>
@@ -12636,7 +12636,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G423" t="n">
-        <v>5.823646068573</v>
+        <v>5.82364559173584</v>
       </c>
       <c r="H423" t="n">
         <v>2422377</v>
@@ -12665,7 +12665,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G424" t="n">
-        <v>5.95461940765381</v>
+        <v>5.95461988449097</v>
       </c>
       <c r="H424" t="n">
         <v>963967</v>
@@ -12723,7 +12723,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97757434844971</v>
+        <v>5.97757482528687</v>
       </c>
       <c r="H426" t="n">
         <v>685213</v>
@@ -12752,7 +12752,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G427" t="n">
-        <v>6.19631576538086</v>
+        <v>6.1963152885437</v>
       </c>
       <c r="H427" t="n">
         <v>1981669</v>
@@ -12781,7 +12781,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G428" t="n">
-        <v>6.16931009292603</v>
+        <v>6.16931056976318</v>
       </c>
       <c r="H428" t="n">
         <v>729053</v>
@@ -12810,7 +12810,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G429" t="n">
-        <v>6.1112494468689</v>
+        <v>6.11124897003174</v>
       </c>
       <c r="H429" t="n">
         <v>462036</v>
@@ -12926,7 +12926,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G433" t="n">
-        <v>6.03698587417603</v>
+        <v>6.03698635101318</v>
       </c>
       <c r="H433" t="n">
         <v>771857</v>
@@ -12955,7 +12955,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G434" t="n">
-        <v>6.07479238510132</v>
+        <v>6.07479286193848</v>
       </c>
       <c r="H434" t="n">
         <v>513724</v>
@@ -13013,7 +13013,7 @@
         <v>8.88599967956543</v>
       </c>
       <c r="G436" t="n">
-        <v>5.99917793273926</v>
+        <v>5.99917840957642</v>
       </c>
       <c r="H436" t="n">
         <v>954787</v>
@@ -13071,7 +13071,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G438" t="n">
-        <v>6.0639910697937</v>
+        <v>6.06399059295654</v>
       </c>
       <c r="H438" t="n">
         <v>1115280</v>
@@ -13129,7 +13129,7 @@
         <v>8.95400047302246</v>
       </c>
       <c r="G440" t="n">
-        <v>6.04508781433105</v>
+        <v>6.0450873374939</v>
       </c>
       <c r="H440" t="n">
         <v>556517</v>
@@ -13158,7 +13158,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H441" t="n">
         <v>1296803</v>
@@ -13187,7 +13187,7 @@
         <v>9.07400035858154</v>
       </c>
       <c r="G442" t="n">
-        <v>6.12610292434692</v>
+        <v>6.12610244750977</v>
       </c>
       <c r="H442" t="n">
         <v>812225</v>
@@ -13361,7 +13361,7 @@
         <v>8.86200046539307</v>
       </c>
       <c r="G448" t="n">
-        <v>5.98297595977783</v>
+        <v>5.98297548294067</v>
       </c>
       <c r="H448" t="n">
         <v>1062778</v>
@@ -13506,7 +13506,7 @@
         <v>8.88599967956543</v>
       </c>
       <c r="G453" t="n">
-        <v>5.99917793273926</v>
+        <v>5.99917840957642</v>
       </c>
       <c r="H453" t="n">
         <v>1027395</v>
@@ -13535,7 +13535,7 @@
         <v>8.52600002288818</v>
       </c>
       <c r="G454" t="n">
-        <v>5.75613307952881</v>
+        <v>5.75613260269165</v>
       </c>
       <c r="H454" t="n">
         <v>1565076</v>
@@ -13564,7 +13564,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G455" t="n">
-        <v>5.94246768951416</v>
+        <v>5.94246816635132</v>
       </c>
       <c r="H455" t="n">
         <v>1173522</v>
@@ -13738,7 +13738,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G461" t="n">
-        <v>5.75748252868652</v>
+        <v>5.75748300552368</v>
       </c>
       <c r="H461" t="n">
         <v>1645113</v>
@@ -13825,7 +13825,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>5.29434585571289</v>
+        <v>5.29434537887573</v>
       </c>
       <c r="H464" t="n">
         <v>1025453</v>
@@ -14028,7 +14028,7 @@
         <v>7.24599981307983</v>
       </c>
       <c r="G471" t="n">
-        <v>4.89197015762329</v>
+        <v>4.89196968078613</v>
       </c>
       <c r="H471" t="n">
         <v>13000528</v>
@@ -14057,7 +14057,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G472" t="n">
-        <v>4.82715797424316</v>
+        <v>4.82715749740601</v>
       </c>
       <c r="H472" t="n">
         <v>9194544</v>
@@ -14115,7 +14115,7 @@
         <v>6.9980001449585</v>
       </c>
       <c r="G474" t="n">
-        <v>4.72453880310059</v>
+        <v>4.72453832626343</v>
       </c>
       <c r="H474" t="n">
         <v>3578164</v>
@@ -14289,7 +14289,7 @@
         <v>7.16200017929077</v>
       </c>
       <c r="G480" t="n">
-        <v>4.83525991439819</v>
+        <v>4.83525943756104</v>
       </c>
       <c r="H480" t="n">
         <v>1773638</v>
@@ -14347,7 +14347,7 @@
         <v>7.25</v>
       </c>
       <c r="G482" t="n">
-        <v>4.89467096328735</v>
+        <v>4.8946704864502</v>
       </c>
       <c r="H482" t="n">
         <v>2096743</v>
@@ -14550,7 +14550,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G489" t="n">
-        <v>4.86091423034668</v>
+        <v>4.86091470718384</v>
       </c>
       <c r="H489" t="n">
         <v>997609</v>
@@ -14608,7 +14608,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G491" t="n">
-        <v>5.0431981086731</v>
+        <v>5.04319858551025</v>
       </c>
       <c r="H491" t="n">
         <v>2706817</v>
@@ -14666,7 +14666,7 @@
         <v>7.61600017547607</v>
       </c>
       <c r="G493" t="n">
-        <v>5.14176750183105</v>
+        <v>5.1417670249939</v>
       </c>
       <c r="H493" t="n">
         <v>2819991</v>
@@ -15072,7 +15072,7 @@
         <v>8.00800037384033</v>
       </c>
       <c r="G507" t="n">
-        <v>5.40641736984253</v>
+        <v>5.40641689300537</v>
       </c>
       <c r="H507" t="n">
         <v>1345581</v>
@@ -15101,7 +15101,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G508" t="n">
-        <v>5.38076162338257</v>
+        <v>5.38076210021973</v>
       </c>
       <c r="H508" t="n">
         <v>821721</v>
@@ -15217,7 +15217,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G512" t="n">
-        <v>5.46852874755859</v>
+        <v>5.46852922439575</v>
       </c>
       <c r="H512" t="n">
         <v>1228095</v>
@@ -15275,7 +15275,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G514" t="n">
-        <v>5.52928972244263</v>
+        <v>5.52928924560547</v>
       </c>
       <c r="H514" t="n">
         <v>1172090</v>
@@ -15449,7 +15449,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G520" t="n">
-        <v>6.37724924087524</v>
+        <v>6.3772497177124</v>
       </c>
       <c r="H520" t="n">
         <v>2482896</v>
@@ -15565,7 +15565,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G524" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H524" t="n">
         <v>1721895</v>
@@ -15623,7 +15623,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G526" t="n">
-        <v>6.14500617980957</v>
+        <v>6.14500570297241</v>
       </c>
       <c r="H526" t="n">
         <v>994506</v>
@@ -15652,7 +15652,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G527" t="n">
-        <v>6.28543329238892</v>
+        <v>6.28543281555176</v>
       </c>
       <c r="H527" t="n">
         <v>1251679</v>
@@ -15710,7 +15710,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G529" t="n">
-        <v>6.42450857162476</v>
+        <v>6.4245080947876</v>
       </c>
       <c r="H529" t="n">
         <v>2063351</v>
@@ -15826,7 +15826,7 @@
         <v>9.91199970245361</v>
       </c>
       <c r="G533" t="n">
-        <v>6.69185829162598</v>
+        <v>6.69185876846313</v>
       </c>
       <c r="H533" t="n">
         <v>2342231</v>
@@ -15942,7 +15942,7 @@
         <v>9.86600017547607</v>
       </c>
       <c r="G537" t="n">
-        <v>6.66080331802368</v>
+        <v>6.66080284118652</v>
       </c>
       <c r="H537" t="n">
         <v>956747</v>
@@ -15971,7 +15971,7 @@
         <v>9.91399955749512</v>
       </c>
       <c r="G538" t="n">
-        <v>6.69320869445801</v>
+        <v>6.69320821762085</v>
       </c>
       <c r="H538" t="n">
         <v>1117605</v>
@@ -16000,7 +16000,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G539" t="n">
-        <v>6.62974643707275</v>
+        <v>6.62974691390991</v>
       </c>
       <c r="H539" t="n">
         <v>1373635</v>
@@ -16029,7 +16029,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G540" t="n">
-        <v>7.14284324645996</v>
+        <v>7.14284372329712</v>
       </c>
       <c r="H540" t="n">
         <v>6833320</v>
@@ -16058,7 +16058,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>7.29137182235718</v>
+        <v>7.29137134552002</v>
       </c>
       <c r="H541" t="n">
         <v>3410381</v>
@@ -16087,7 +16087,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G542" t="n">
-        <v>7.33525514602661</v>
+        <v>7.33525466918945</v>
       </c>
       <c r="H542" t="n">
         <v>2008354</v>
@@ -16116,7 +16116,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.43989992141724</v>
+        <v>7.43989944458008</v>
       </c>
       <c r="H543" t="n">
         <v>1957564</v>
@@ -16232,7 +16232,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G547" t="n">
-        <v>7.11246252059937</v>
+        <v>7.11246299743652</v>
       </c>
       <c r="H547" t="n">
         <v>2425730</v>
@@ -16348,7 +16348,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G551" t="n">
-        <v>7.8314733505249</v>
+        <v>7.83147287368774</v>
       </c>
       <c r="H551" t="n">
         <v>2679665</v>
@@ -16377,7 +16377,7 @@
         <v>11.625</v>
       </c>
       <c r="G552" t="n">
-        <v>7.8483510017395</v>
+        <v>7.84835195541382</v>
       </c>
       <c r="H552" t="n">
         <v>1462288</v>
@@ -16435,7 +16435,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G554" t="n">
-        <v>7.68294525146484</v>
+        <v>7.682945728302</v>
       </c>
       <c r="H554" t="n">
         <v>2337716</v>
@@ -16580,7 +16580,7 @@
         <v>11.9549999237061</v>
       </c>
       <c r="G559" t="n">
-        <v>8.07114315032959</v>
+        <v>8.07114219665527</v>
       </c>
       <c r="H559" t="n">
         <v>1480713</v>
@@ -16638,7 +16638,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G561" t="n">
-        <v>8.36819934844971</v>
+        <v>8.36820030212402</v>
       </c>
       <c r="H561" t="n">
         <v>2896424</v>
@@ -16667,7 +16667,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G562" t="n">
-        <v>8.26355361938477</v>
+        <v>8.26355457305908</v>
       </c>
       <c r="H562" t="n">
         <v>2570522</v>
@@ -16870,7 +16870,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G569" t="n">
-        <v>9.32350444793701</v>
+        <v>9.3235034942627</v>
       </c>
       <c r="H569" t="n">
         <v>1639116</v>
@@ -17015,7 +17015,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G574" t="n">
-        <v>9.31675243377686</v>
+        <v>9.31675338745117</v>
       </c>
       <c r="H574" t="n">
         <v>1902319</v>
@@ -17073,7 +17073,7 @@
         <v>13.9949998855591</v>
       </c>
       <c r="G576" t="n">
-        <v>9.44840240478516</v>
+        <v>9.44840145111084</v>
       </c>
       <c r="H576" t="n">
         <v>2197272</v>
@@ -17102,7 +17102,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G577" t="n">
-        <v>9.45852947235107</v>
+        <v>9.45852851867676</v>
       </c>
       <c r="H577" t="n">
         <v>1182892</v>
@@ -17131,7 +17131,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>9.47540664672852</v>
+        <v>9.47540760040283</v>
       </c>
       <c r="H578" t="n">
         <v>1873488</v>
@@ -17160,7 +17160,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G579" t="n">
-        <v>9.84335041046143</v>
+        <v>9.84335136413574</v>
       </c>
       <c r="H579" t="n">
         <v>2092638</v>
@@ -17189,7 +17189,7 @@
         <v>13.5649995803833</v>
       </c>
       <c r="G580" t="n">
-        <v>9.15809726715088</v>
+        <v>9.1580982208252</v>
       </c>
       <c r="H580" t="n">
         <v>4615582</v>
@@ -17276,7 +17276,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G583" t="n">
-        <v>8.5471076965332</v>
+        <v>8.54710674285889</v>
       </c>
       <c r="H583" t="n">
         <v>2183078</v>
@@ -17363,7 +17363,7 @@
         <v>12.5550003051758</v>
       </c>
       <c r="G586" t="n">
-        <v>8.47621917724609</v>
+        <v>8.47622013092041</v>
       </c>
       <c r="H586" t="n">
         <v>1149074</v>
@@ -17421,7 +17421,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G588" t="n">
-        <v>8.34456920623779</v>
+        <v>8.34457015991211</v>
       </c>
       <c r="H588" t="n">
         <v>1138478</v>
@@ -17537,7 +17537,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G592" t="n">
-        <v>7.95277309417725</v>
+        <v>7.9527735710144</v>
       </c>
       <c r="H592" t="n">
         <v>1799211</v>
@@ -17595,7 +17595,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G594" t="n">
-        <v>8.37893772125244</v>
+        <v>8.37893676757812</v>
       </c>
       <c r="H594" t="n">
         <v>1370145</v>
@@ -17624,7 +17624,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G595" t="n">
-        <v>8.11430358886719</v>
+        <v>8.1143045425415</v>
       </c>
       <c r="H595" t="n">
         <v>1343574</v>
@@ -17682,7 +17682,7 @@
         <v>11.5</v>
       </c>
       <c r="G597" t="n">
-        <v>7.90465831756592</v>
+        <v>7.90465784072876</v>
       </c>
       <c r="H597" t="n">
         <v>2070634</v>
@@ -17711,7 +17711,7 @@
         <v>11.5050001144409</v>
       </c>
       <c r="G598" t="n">
-        <v>7.90809488296509</v>
+        <v>7.90809535980225</v>
       </c>
       <c r="H598" t="n">
         <v>1111394</v>
@@ -17740,7 +17740,7 @@
         <v>11.5450000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>7.93558979034424</v>
+        <v>7.93558931350708</v>
       </c>
       <c r="H599" t="n">
         <v>1144101</v>
@@ -17769,7 +17769,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>8.00776290893555</v>
+        <v>8.00776195526123</v>
       </c>
       <c r="H600" t="n">
         <v>1299934</v>
@@ -17856,7 +17856,7 @@
         <v>11.375</v>
       </c>
       <c r="G603" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H603" t="n">
         <v>4357376</v>
@@ -17943,7 +17943,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G606" t="n">
-        <v>7.9596471786499</v>
+        <v>7.95964765548706</v>
       </c>
       <c r="H606" t="n">
         <v>1233297</v>
@@ -18001,7 +18001,7 @@
         <v>11.375</v>
       </c>
       <c r="G608" t="n">
-        <v>7.81873846054077</v>
+        <v>7.81873798370361</v>
       </c>
       <c r="H608" t="n">
         <v>943692</v>
@@ -18059,7 +18059,7 @@
         <v>11.2449998855591</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7293815612793</v>
+        <v>7.72938108444214</v>
       </c>
       <c r="H610" t="n">
         <v>1482029</v>
@@ -18146,7 +18146,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95621061325073</v>
+        <v>7.95621013641357</v>
       </c>
       <c r="H613" t="n">
         <v>953411</v>
@@ -18233,7 +18233,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G616" t="n">
-        <v>7.62627744674683</v>
+        <v>7.62627696990967</v>
       </c>
       <c r="H616" t="n">
         <v>1263861</v>
@@ -18262,7 +18262,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G617" t="n">
-        <v>7.54379415512085</v>
+        <v>7.54379367828369</v>
       </c>
       <c r="H617" t="n">
         <v>1883401</v>
@@ -18349,7 +18349,7 @@
         <v>11.2349996566772</v>
       </c>
       <c r="G620" t="n">
-        <v>7.72250747680664</v>
+        <v>7.72250699996948</v>
       </c>
       <c r="H620" t="n">
         <v>1949076</v>
@@ -18407,7 +18407,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G622" t="n">
-        <v>7.89434814453125</v>
+        <v>7.89434766769409</v>
       </c>
       <c r="H622" t="n">
         <v>2466372</v>
@@ -18436,7 +18436,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H623" t="n">
         <v>1875863</v>
@@ -18465,7 +18465,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G624" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H624" t="n">
         <v>2114723</v>
@@ -18494,7 +18494,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G625" t="n">
-        <v>7.99745225906372</v>
+        <v>7.99745178222656</v>
       </c>
       <c r="H625" t="n">
         <v>1003281</v>
@@ -18552,7 +18552,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H627" t="n">
         <v>2034035</v>
@@ -18639,7 +18639,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34445905685425</v>
+        <v>7.34445858001709</v>
       </c>
       <c r="H630" t="n">
         <v>961522</v>
@@ -18668,7 +18668,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>7.33758497238159</v>
+        <v>7.33758544921875</v>
       </c>
       <c r="H631" t="n">
         <v>1340364</v>
@@ -18726,7 +18726,7 @@
         <v>10.7749996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>7.40632057189941</v>
+        <v>7.40632104873657</v>
       </c>
       <c r="H633" t="n">
         <v>1188311</v>
@@ -18755,7 +18755,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G634" t="n">
-        <v>7.28259658813477</v>
+        <v>7.28259611129761</v>
       </c>
       <c r="H634" t="n">
         <v>922139</v>
@@ -18842,7 +18842,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G637" t="n">
-        <v>7.1966757774353</v>
+        <v>7.19667625427246</v>
       </c>
       <c r="H637" t="n">
         <v>1104944</v>
@@ -18871,7 +18871,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G638" t="n">
-        <v>7.3100905418396</v>
+        <v>7.31009101867676</v>
       </c>
       <c r="H638" t="n">
         <v>1477565</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>7.07982492446899</v>
+        <v>7.07982444763184</v>
       </c>
       <c r="H642" t="n">
         <v>1299347</v>
@@ -19016,7 +19016,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>7.17949151992798</v>
+        <v>7.17949199676514</v>
       </c>
       <c r="H643" t="n">
         <v>1807666</v>
@@ -19103,7 +19103,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G646" t="n">
-        <v>7.68470335006714</v>
+        <v>7.68470287322998</v>
       </c>
       <c r="H646" t="n">
         <v>1668673</v>
@@ -19132,7 +19132,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>7.8668532371521</v>
+        <v>7.86685371398926</v>
       </c>
       <c r="H647" t="n">
         <v>1764822</v>
@@ -19161,7 +19161,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>7.91496896743774</v>
+        <v>7.9149694442749</v>
       </c>
       <c r="H648" t="n">
         <v>1235632</v>
@@ -19190,7 +19190,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G649" t="n">
-        <v>7.90122175216675</v>
+        <v>7.90122127532959</v>
       </c>
       <c r="H649" t="n">
         <v>1397538</v>
@@ -19219,7 +19219,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G650" t="n">
-        <v>7.74656581878662</v>
+        <v>7.74656534194946</v>
       </c>
       <c r="H650" t="n">
         <v>1895690</v>
@@ -19277,7 +19277,7 @@
         <v>11.5950002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>7.96995830535889</v>
+        <v>7.96995782852173</v>
       </c>
       <c r="H652" t="n">
         <v>1855485</v>
@@ -19364,7 +19364,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G655" t="n">
-        <v>6.91485834121704</v>
+        <v>6.91485786437988</v>
       </c>
       <c r="H655" t="n">
         <v>21113678</v>
@@ -19422,7 +19422,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G657" t="n">
-        <v>6.35946989059448</v>
+        <v>6.35946941375732</v>
       </c>
       <c r="H657" t="n">
         <v>4678338</v>
@@ -19451,7 +19451,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G658" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H658" t="n">
         <v>2619573</v>
@@ -19538,7 +19538,7 @@
         <v>9.11800003051758</v>
       </c>
       <c r="G661" t="n">
-        <v>6.26736259460449</v>
+        <v>6.26736307144165</v>
       </c>
       <c r="H661" t="n">
         <v>2610988</v>
@@ -19567,7 +19567,7 @@
         <v>8.6560001373291</v>
       </c>
       <c r="G662" t="n">
-        <v>5.94980239868164</v>
+        <v>5.94980192184448</v>
       </c>
       <c r="H662" t="n">
         <v>4162401</v>
@@ -19596,7 +19596,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>5.77108812332153</v>
+        <v>5.77108764648438</v>
       </c>
       <c r="H663" t="n">
         <v>4859349</v>
@@ -19712,7 +19712,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>5.95255136489868</v>
+        <v>5.95255088806152</v>
       </c>
       <c r="H667" t="n">
         <v>1004735</v>
@@ -19741,7 +19741,7 @@
         <v>8.64200019836426</v>
       </c>
       <c r="G668" t="n">
-        <v>5.94017887115479</v>
+        <v>5.94017934799194</v>
       </c>
       <c r="H668" t="n">
         <v>997482</v>
@@ -19828,7 +19828,7 @@
         <v>8.94200038909912</v>
       </c>
       <c r="G671" t="n">
-        <v>6.14638757705688</v>
+        <v>6.14638805389404</v>
       </c>
       <c r="H671" t="n">
         <v>2096737</v>
@@ -19944,7 +19944,7 @@
         <v>9.05200004577637</v>
       </c>
       <c r="G675" t="n">
-        <v>6.22199726104736</v>
+        <v>6.22199678421021</v>
       </c>
       <c r="H675" t="n">
         <v>1440910</v>
@@ -20031,7 +20031,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G678" t="n">
-        <v>6.36634349822998</v>
+        <v>6.36634302139282</v>
       </c>
       <c r="H678" t="n">
         <v>1366723</v>
@@ -20060,7 +20060,7 @@
         <v>9.2819995880127</v>
       </c>
       <c r="G679" t="n">
-        <v>6.38008975982666</v>
+        <v>6.38009023666382</v>
       </c>
       <c r="H679" t="n">
         <v>980480</v>
@@ -20176,7 +20176,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G683" t="n">
-        <v>6.15188598632812</v>
+        <v>6.15188646316528</v>
       </c>
       <c r="H683" t="n">
         <v>2106694</v>
@@ -20292,7 +20292,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G687" t="n">
-        <v>5.95392560958862</v>
+        <v>5.95392608642578</v>
       </c>
       <c r="H687" t="n">
         <v>1295054</v>
@@ -20466,7 +20466,7 @@
         <v>9.13799953460693</v>
       </c>
       <c r="G693" t="n">
-        <v>6.28110980987549</v>
+        <v>6.28111028671265</v>
       </c>
       <c r="H693" t="n">
         <v>2462515</v>
@@ -20495,7 +20495,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>6.3031063079834</v>
+        <v>6.30310583114624</v>
       </c>
       <c r="H694" t="n">
         <v>1410849</v>
@@ -20524,7 +20524,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G695" t="n">
-        <v>6.4983172416687</v>
+        <v>6.49831676483154</v>
       </c>
       <c r="H695" t="n">
         <v>2437479</v>
@@ -20611,7 +20611,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G698" t="n">
-        <v>6.27286243438721</v>
+        <v>6.27286195755005</v>
       </c>
       <c r="H698" t="n">
         <v>3218967</v>
@@ -20640,7 +20640,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G699" t="n">
-        <v>6.24536752700806</v>
+        <v>6.24536800384521</v>
       </c>
       <c r="H699" t="n">
         <v>1981493</v>
@@ -20669,7 +20669,7 @@
         <v>9.32800006866455</v>
       </c>
       <c r="G700" t="n">
-        <v>6.41170930862427</v>
+        <v>6.41170883178711</v>
       </c>
       <c r="H700" t="n">
         <v>2629183</v>
@@ -20756,7 +20756,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>6.17938041687012</v>
+        <v>6.17938089370728</v>
       </c>
       <c r="H703" t="n">
         <v>3178801</v>
@@ -20785,7 +20785,7 @@
         <v>8.75</v>
       </c>
       <c r="G704" t="n">
-        <v>6.01441383361816</v>
+        <v>6.01441431045532</v>
       </c>
       <c r="H704" t="n">
         <v>3618036</v>
@@ -20901,7 +20901,7 @@
         <v>9.03400039672852</v>
       </c>
       <c r="G708" t="n">
-        <v>6.20962476730347</v>
+        <v>6.20962524414062</v>
       </c>
       <c r="H708" t="n">
         <v>1498085</v>
@@ -20930,7 +20930,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G709" t="n">
-        <v>6.27698659896851</v>
+        <v>6.27698612213135</v>
       </c>
       <c r="H709" t="n">
         <v>2955864</v>
@@ -20959,7 +20959,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G710" t="n">
-        <v>6.19450330734253</v>
+        <v>6.19450283050537</v>
       </c>
       <c r="H710" t="n">
         <v>2554492</v>
@@ -21162,7 +21162,7 @@
         <v>9.64200019836426</v>
       </c>
       <c r="G717" t="n">
-        <v>6.62754011154175</v>
+        <v>6.62754058837891</v>
       </c>
       <c r="H717" t="n">
         <v>2640643</v>
@@ -21220,7 +21220,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G719" t="n">
-        <v>6.62204122543335</v>
+        <v>6.62204170227051</v>
       </c>
       <c r="H719" t="n">
         <v>1962181</v>
@@ -21278,7 +21278,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G721" t="n">
-        <v>6.8976731300354</v>
+        <v>6.89767360687256</v>
       </c>
       <c r="H721" t="n">
         <v>3961916</v>
@@ -21336,7 +21336,7 @@
         <v>9.83600044250488</v>
       </c>
       <c r="G723" t="n">
-        <v>6.76088905334473</v>
+        <v>6.76088857650757</v>
       </c>
       <c r="H723" t="n">
         <v>3582670</v>
@@ -21365,7 +21365,7 @@
         <v>9.55399990081787</v>
       </c>
       <c r="G724" t="n">
-        <v>6.56705284118652</v>
+        <v>6.56705236434937</v>
       </c>
       <c r="H724" t="n">
         <v>2210569</v>
@@ -21423,7 +21423,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G726" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H726" t="n">
         <v>1858552</v>
@@ -21539,7 +21539,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G730" t="n">
-        <v>7.0110878944397</v>
+        <v>7.01108837127686</v>
       </c>
       <c r="H730" t="n">
         <v>8286642</v>
@@ -21626,7 +21626,7 @@
         <v>9.86400032043457</v>
       </c>
       <c r="G733" t="n">
-        <v>6.78013467788696</v>
+        <v>6.78013515472412</v>
       </c>
       <c r="H733" t="n">
         <v>4138184</v>
@@ -21713,7 +21713,7 @@
         <v>9.59799957275391</v>
       </c>
       <c r="G736" t="n">
-        <v>6.59729671478271</v>
+        <v>6.59729623794556</v>
       </c>
       <c r="H736" t="n">
         <v>2990029</v>
@@ -21742,7 +21742,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G737" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H737" t="n">
         <v>1630942</v>
@@ -21858,7 +21858,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G741" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H741" t="n">
         <v>1657610</v>
@@ -21974,7 +21974,7 @@
         <v>9.5019998550415</v>
       </c>
       <c r="G745" t="n">
-        <v>6.53131008148193</v>
+        <v>6.53130960464478</v>
       </c>
       <c r="H745" t="n">
         <v>2906567</v>
@@ -22061,7 +22061,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G748" t="n">
-        <v>6.64678716659546</v>
+        <v>6.6467866897583</v>
       </c>
       <c r="H748" t="n">
         <v>1472605</v>
@@ -22119,7 +22119,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G750" t="n">
-        <v>6.82000160217285</v>
+        <v>6.82000207901001</v>
       </c>
       <c r="H750" t="n">
         <v>2428586</v>
@@ -22206,7 +22206,7 @@
         <v>9.69600009918213</v>
       </c>
       <c r="G753" t="n">
-        <v>6.6646580696106</v>
+        <v>6.66465854644775</v>
       </c>
       <c r="H753" t="n">
         <v>1373245</v>
@@ -22235,7 +22235,7 @@
         <v>9.82600021362305</v>
       </c>
       <c r="G754" t="n">
-        <v>6.75401496887207</v>
+        <v>6.75401544570923</v>
       </c>
       <c r="H754" t="n">
         <v>1786995</v>
@@ -22293,7 +22293,7 @@
         <v>9.95400047302246</v>
       </c>
       <c r="G756" t="n">
-        <v>6.84199810028076</v>
+        <v>6.8419976234436</v>
       </c>
       <c r="H756" t="n">
         <v>2943745</v>
@@ -22322,7 +22322,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G757" t="n">
-        <v>6.54093313217163</v>
+        <v>6.54093265533447</v>
       </c>
       <c r="H757" t="n">
         <v>3277617</v>
@@ -22438,7 +22438,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G761" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H761" t="n">
         <v>2579512</v>
@@ -22467,7 +22467,7 @@
         <v>9.21599960327148</v>
       </c>
       <c r="G762" t="n">
-        <v>6.33472394943237</v>
+        <v>6.33472442626953</v>
       </c>
       <c r="H762" t="n">
         <v>1442117</v>
@@ -22554,7 +22554,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G765" t="n">
-        <v>6.37046670913696</v>
+        <v>6.37046718597412</v>
       </c>
       <c r="H765" t="n">
         <v>2725833</v>
@@ -22902,7 +22902,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G777" t="n">
-        <v>7.25166511535645</v>
+        <v>7.25166463851929</v>
       </c>
       <c r="H777" t="n">
         <v>3966282</v>
@@ -22989,7 +22989,7 @@
         <v>10.8649997711182</v>
       </c>
       <c r="G780" t="n">
-        <v>7.46818399429321</v>
+        <v>7.46818351745605</v>
       </c>
       <c r="H780" t="n">
         <v>2399106</v>
@@ -23192,7 +23192,7 @@
         <v>11.5649995803833</v>
       </c>
       <c r="G787" t="n">
-        <v>7.94933652877808</v>
+        <v>7.94933605194092</v>
       </c>
       <c r="H787" t="n">
         <v>3020927</v>
@@ -23250,7 +23250,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G789" t="n">
-        <v>7.8290491104126</v>
+        <v>7.82904863357544</v>
       </c>
       <c r="H789" t="n">
         <v>2034103</v>
@@ -23279,7 +23279,7 @@
         <v>11.6049995422363</v>
       </c>
       <c r="G790" t="n">
-        <v>7.97683143615723</v>
+        <v>7.97683095932007</v>
       </c>
       <c r="H790" t="n">
         <v>2487608</v>
@@ -23395,7 +23395,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G794" t="n">
-        <v>10.2210664749146</v>
+        <v>10.2210674285889</v>
       </c>
       <c r="H794" t="n">
         <v>4399432</v>
@@ -23656,7 +23656,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G803" t="n">
-        <v>10.4341497421265</v>
+        <v>10.4341487884521</v>
       </c>
       <c r="H803" t="n">
         <v>1560972</v>
@@ -23830,7 +23830,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G809" t="n">
-        <v>10.8500022888184</v>
+        <v>10.8500032424927</v>
       </c>
       <c r="H809" t="n">
         <v>3171229</v>
@@ -23859,7 +23859,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G810" t="n">
-        <v>11.1249465942383</v>
+        <v>11.1249475479126</v>
       </c>
       <c r="H810" t="n">
         <v>2951875</v>
@@ -23888,7 +23888,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G811" t="n">
-        <v>10.6953468322754</v>
+        <v>10.6953458786011</v>
       </c>
       <c r="H811" t="n">
         <v>2115144</v>
@@ -23946,7 +23946,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G813" t="n">
-        <v>10.2485618591309</v>
+        <v>10.2485609054565</v>
       </c>
       <c r="H813" t="n">
         <v>1560898</v>
@@ -24033,7 +24033,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G816" t="n">
-        <v>11.1352577209473</v>
+        <v>11.1352586746216</v>
       </c>
       <c r="H816" t="n">
         <v>3500840</v>
@@ -24120,7 +24120,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G819" t="n">
-        <v>11.5029964447021</v>
+        <v>11.5029973983765</v>
       </c>
       <c r="H819" t="n">
         <v>2998052</v>
@@ -24207,7 +24207,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3208456039429</v>
+        <v>11.3208446502686</v>
       </c>
       <c r="H822" t="n">
         <v>1495955</v>
@@ -24236,7 +24236,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G823" t="n">
-        <v>11.4376955032349</v>
+        <v>11.4376964569092</v>
       </c>
       <c r="H823" t="n">
         <v>1503927</v>
@@ -24294,7 +24294,7 @@
         <v>16.5</v>
       </c>
       <c r="G825" t="n">
-        <v>11.3414659500122</v>
+        <v>11.3414669036865</v>
       </c>
       <c r="H825" t="n">
         <v>1813430</v>
@@ -24352,7 +24352,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>10.3585386276245</v>
+        <v>10.3585395812988</v>
       </c>
       <c r="H827" t="n">
         <v>2267336</v>
@@ -24381,7 +24381,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G828" t="n">
-        <v>10.3069877624512</v>
+        <v>10.3069868087769</v>
       </c>
       <c r="H828" t="n">
         <v>1710958</v>
@@ -24526,7 +24526,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G833" t="n">
-        <v>8.84634399414062</v>
+        <v>8.84634304046631</v>
       </c>
       <c r="H833" t="n">
         <v>2682628</v>
@@ -24584,7 +24584,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>9.12472438812256</v>
+        <v>9.12472534179688</v>
       </c>
       <c r="H835" t="n">
         <v>2895890</v>
@@ -24613,7 +24613,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G836" t="n">
-        <v>9.16940402984619</v>
+        <v>9.16940307617188</v>
       </c>
       <c r="H836" t="n">
         <v>1823500</v>
@@ -35958,6 +35958,35 @@
         <v>463212</v>
       </c>
       <c r="I1227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1228" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>14.3800001144409</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>3624040</v>
+      </c>
+      <c r="I1228" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IVG.MI.xlsx
+++ b/data/IVG.MI.xlsx
@@ -35984,9 +35984,38 @@
         <v>14.3699998855591</v>
       </c>
       <c r="H1228" t="n">
-        <v>3624040</v>
+        <v>3671845</v>
       </c>
       <c r="I1228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1229" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>14.3850002288818</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>14.3649997711182</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>4268352</v>
+      </c>
+      <c r="I1229" t="s">
         <v>9</v>
       </c>
     </row>
